--- a/raw/BUS.xlsx
+++ b/raw/BUS.xlsx
@@ -8,9 +8,8 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="05" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="15.10" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="16" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="17" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Лист1" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -22,9 +21,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="133">
-  <si>
-    <t xml:space="preserve">  05.10. 2026 ж. </t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="97">
+  <si>
+    <t xml:space="preserve">  17.10. 2026 ж. </t>
   </si>
   <si>
     <t xml:space="preserve"> ЦДН 1</t>
@@ -51,376 +50,268 @@
     <t xml:space="preserve">списаниеге</t>
   </si>
   <si>
+    <t xml:space="preserve">20-233AG12   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2714/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-349AS12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-262AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35,2-Н2984/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-149AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-H359312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-Н614760  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-H2675/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н3136/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2713/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-194AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35,2-Н3025/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-175AG12  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-Н0592/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1-H267812 37DEA12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-341AS12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-198AG12   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35,2-Н2972/12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-181AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-Н3397/12  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-216AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35,2-Н2952/12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-Н2649/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-Н3408/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н3564/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2291/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-219AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-H269412 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ППД</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-Н2652/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-827AI12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-857AI12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н3204/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-Н2641/12   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-250AG12   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-Н2695/12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-968AC12 н </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2715/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н3569/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-587AI12  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н1544/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-228AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-352AS12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бурение</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 20-177AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-847AI12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-206AG 12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-H3574/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">резерв</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЦПП</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н3153/12  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н3135/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н3196/12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-H2631/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-H614805 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2710/12 д/н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2716/12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-213AG12  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-H2664/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2708/12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н3218/12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">окс</t>
+  </si>
+  <si>
     <t xml:space="preserve">20-180AG12 </t>
   </si>
   <si>
-    <t xml:space="preserve">35-215AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-206AG 12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-250AG12   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35,2-Н2984/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-181AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-H359312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-Н0592/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-175AG12  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н2706/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н1544/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-H2631/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35,2-Н3025/12 </t>
+    <t xml:space="preserve">35-214AG12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2939/12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">УТТ КРС</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н3180/12 н </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЦАП</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2705/12 н</t>
   </si>
   <si>
     <t xml:space="preserve">20-173AG12 </t>
   </si>
   <si>
-    <t xml:space="preserve">20-Н3397/12  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1-H2673 12        35-29ABI 12  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н2708/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-H2675/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35,2-Н2972/12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-149AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-Н614760  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н2710/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35,2-Н2952/12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 20-177AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-Н2652/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-827AI12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-214AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-968AC12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-Н2649/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ППД</t>
+    <t xml:space="preserve">35.1-H2673/12        35-29ABI12  н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-H2672/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-337AS12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-215AG12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-217AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> отд кадр</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2706/12 н </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-218AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ремонт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-178AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н1543/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-209AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ТБ класс ПРЦЭО</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РСУ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-192AG12 </t>
   </si>
   <si>
     <t xml:space="preserve">20-Н2689/12   </t>
   </si>
   <si>
-    <t xml:space="preserve">35-Н3136/12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-857AI12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н2705/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-198AG12   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-178AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-262AG12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н3564/12 н  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н2715/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-337AS12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-194AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н2716/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-352AS12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Бурение</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-Н2641/12   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-209AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н2939/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-H3574/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">резерв</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЦПП</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н3153/12  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н3218 12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н3196/12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-233AG12   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-H614805 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-228AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-219AG12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-213AG12  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-Н2695/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-847AI12 д</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н3204/12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">окс</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-H2664/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-341AS12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н3569/12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">УТТ КРС</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-847AI12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-Н3408/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЦАП</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-216AG12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-218AG12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-587AI12  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1-H267812 37DEA12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-H2672/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-217AG12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-349AS12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н3135/12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н3180/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ремонт</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> отд кадр</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н2713/12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н2714/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-192AG12 </t>
-  </si>
-  <si>
     <t xml:space="preserve">20-Н614761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н2291/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н1543/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ТБ класс ПРЦЭО</t>
-  </si>
-  <si>
-    <t xml:space="preserve">РСУ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-H269412 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  15.10. 2026 ж. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-349AS12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-262AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н3136/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н2713/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1-H267812 37DEA12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-341AS12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-216AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н3564/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-219AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-827AI12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н3204/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-Н2695/12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-209AG12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н3569/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-847AI12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н3135/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н2710/12 д/н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н2716/12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н2708/12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н3218 12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-214AG12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н2939/12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н3180/12 н </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н2705/12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1-H2673 12        35-29ABI 12  н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-337AS12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-215AG12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-217AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н2706/12 н </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-218AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  16.10. 2026 ж. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-968AC12 н </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н3218/12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1-H2673/12        35-29ABI12  н</t>
   </si>
 </sst>
 </file>
@@ -436,7 +327,7 @@
     <numFmt numFmtId="169" formatCode="[$-409]m/d/yyyy"/>
     <numFmt numFmtId="170" formatCode="@"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="27">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -540,9 +431,23 @@
       <charset val="204"/>
     </font>
     <font>
+      <sz val="16"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="16"/>
+      <color rgb="FF008000"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
@@ -557,6 +462,13 @@
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FF339966"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF008000"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
@@ -578,7 +490,8 @@
       <charset val="204"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
@@ -602,44 +515,8 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF993300"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="16"/>
-      <color rgb="FF008000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FF008000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -668,12 +545,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF969696"/>
         <bgColor rgb="FF808080"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF99CC"/>
-        <bgColor rgb="FFFF8080"/>
       </patternFill>
     </fill>
     <fill>
@@ -2001,7 +1872,7 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="47">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2046,19 +1917,111 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="3" borderId="2" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="2" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="2" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="3" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="5" borderId="2" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="167" fontId="5" fillId="3" borderId="2" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2066,75 +2029,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="4" borderId="2" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="21" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="24" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2142,7 +2037,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="21" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="24" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2150,112 +2045,20 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="2" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="5" borderId="2" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="25" fillId="3" borderId="2" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="25" fillId="0" borderId="2" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="2" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="2" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="27" fillId="0" borderId="2" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="25" fillId="3" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="25" fillId="5" borderId="2" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -3474,163 +3277,7 @@
     <cellStyle name="Финансовый 2 2" xfId="1225"/>
     <cellStyle name="Финансовый 2 3" xfId="1226"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="204"/>
-        <family val="0"/>
-        <color rgb="FF800080"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="204"/>
-        <family val="0"/>
-        <color rgb="FF800080"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="204"/>
-        <family val="0"/>
-        <color rgb="FF800080"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="204"/>
-        <family val="0"/>
-        <color rgb="FF800080"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="204"/>
-        <family val="0"/>
-        <color rgb="FF800080"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="204"/>
-        <family val="0"/>
-        <color rgb="FF800080"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="204"/>
-        <family val="0"/>
-        <color rgb="FF800080"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="204"/>
-        <family val="0"/>
-        <color rgb="FF800080"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="204"/>
-        <family val="0"/>
-        <color rgb="FF800080"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="204"/>
-        <family val="0"/>
-        <color rgb="FF800080"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="204"/>
-        <family val="0"/>
-        <color rgb="FF800080"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="204"/>
-        <family val="0"/>
-        <color rgb="FF800080"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF99CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -3724,183 +3371,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>298440</xdr:colOff>
+      <xdr:colOff>299520</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>152640</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="0" name="AutoShape 3"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1017360" y="6648480"/>
-          <a:ext cx="298440" cy="655560"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
-        <a:fontRef idx="minor"/>
-      </xdr:style>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>93960</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>30600</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>392400</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>14760</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AutoShape 3"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1111320" y="6679080"/>
-          <a:ext cx="298440" cy="654840"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
-        <a:fontRef idx="minor"/>
-      </xdr:style>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>298440</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>152640</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="AutoShape 3"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1017360" y="6648480"/>
-          <a:ext cx="298440" cy="655560"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
-        <a:fontRef idx="minor"/>
-      </xdr:style>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>93960</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>30600</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>392400</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>14760</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="AutoShape 3"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1111320" y="6679080"/>
-          <a:ext cx="298440" cy="654840"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
-        <a:fontRef idx="minor"/>
-      </xdr:style>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>299520</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>152640</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="AutoShape 3"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3940,7 +3417,7 @@
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="AutoShape 3"/>
+        <xdr:cNvPr id="1" name="AutoShape 3"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4082,15 +3559,8 @@
   <dimension ref="A1:P45"/>
   <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="13.2" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="12.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="14.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="15.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="17.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="15.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="16.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="13.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="14.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="2" style="2" width="25.43"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="10" min="10" style="2" width="9.1"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="11" style="2" width="9.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="24.1"/>
@@ -4148,10 +3618,10 @@
       <c r="A3" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="12" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="11" t="s">
@@ -4160,10 +3630,10 @@
       <c r="E3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="13" t="s">
         <v>15</v>
       </c>
       <c r="H3" s="11" t="s">
@@ -4178,10 +3648,10 @@
       <c r="B4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="11" t="s">
         <v>20</v>
       </c>
       <c r="E4" s="11" t="s">
@@ -4190,16 +3660,17 @@
       <c r="F4" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="P4" s="11"/>
+      <c r="P4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="B5" s="13"/>
+      <c r="C5" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="11" t="s">
@@ -4208,24 +3679,25 @@
       <c r="E5" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="P5" s="11"/>
+      <c r="P5" s="15"/>
     </row>
     <row r="6" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="16"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="13" t="s">
+      <c r="B6" s="19"/>
+      <c r="C6" s="11" t="s">
         <v>30</v>
       </c>
+      <c r="D6" s="13"/>
       <c r="E6" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="18" t="s">
         <v>32</v>
       </c>
       <c r="H6" s="11" t="s">
@@ -4233,17 +3705,17 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="9"/>
+      <c r="B7" s="20"/>
       <c r="C7" s="11" t="s">
         <v>35</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="13" t="s">
         <v>37</v>
       </c>
       <c r="G7" s="9" t="s">
@@ -4254,276 +3726,279 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="21" t="s">
         <v>40</v>
       </c>
+      <c r="B8" s="13"/>
       <c r="C8" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="21" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="17" t="s">
         <v>46</v>
       </c>
+      <c r="B9" s="13"/>
       <c r="C9" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="21"/>
+      <c r="F9" s="22"/>
       <c r="G9" s="11" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C10" s="11" t="s">
+      <c r="A10" s="11" t="s">
         <v>50</v>
+      </c>
+      <c r="B10" s="13"/>
+      <c r="C10" s="12" t="s">
+        <v>51</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="F10" s="23" t="s">
         <v>53</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="24"/>
+      <c r="B11" s="13"/>
       <c r="C11" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" s="15" t="s">
         <v>55</v>
       </c>
+      <c r="E11" s="11" t="s">
+        <v>56</v>
+      </c>
       <c r="F11" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I11" s="23" t="s">
         <v>57</v>
+      </c>
+      <c r="I11" s="25" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
-        <v>58</v>
+      <c r="A12" s="26" t="s">
+        <v>59</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" s="15" t="s">
         <v>60</v>
       </c>
+      <c r="E12" s="11" t="s">
+        <v>61</v>
+      </c>
       <c r="F12" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="I12" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="K12" s="25"/>
-      <c r="P12" s="11"/>
+      <c r="I12" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="K12" s="28"/>
+      <c r="P12" s="15"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" s="12" t="s">
+      <c r="A13" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="C13" s="30" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="27" t="s">
+      <c r="E13" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="I13" s="25" t="s">
+      <c r="F13" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="P13" s="11"/>
+      <c r="I13" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="P13" s="15"/>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C14" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" s="17" t="s">
+      <c r="C14" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="F14" s="12"/>
+      <c r="E14" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="33"/>
       <c r="G14" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I14" s="25" t="s">
         <v>71</v>
+      </c>
+      <c r="I14" s="34" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C15" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E15" s="17" t="s">
+      <c r="C15" s="21" t="s">
         <v>73</v>
       </c>
+      <c r="E15" s="21" t="s">
+        <v>74</v>
+      </c>
       <c r="F15" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G15" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="I15" s="25" t="s">
+      <c r="G15" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="P15" s="11"/>
+      <c r="I15" s="13"/>
+      <c r="P15" s="15"/>
     </row>
     <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="E16" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="F16" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="G16" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="G16" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="P16" s="11"/>
+      <c r="P16" s="15"/>
     </row>
     <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E17" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="C17" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="G17" s="29"/>
+      <c r="G17" s="35"/>
     </row>
     <row r="18" customFormat="false" ht="19.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
-      <c r="E18" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="I18" s="30" t="s">
-        <v>87</v>
+      <c r="E18" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="I19" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="E19" s="17" t="s">
+    </row>
+    <row r="20" s="15" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="I20" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="I19" s="31" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="20" s="11" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="32" t="s">
-        <v>92</v>
-      </c>
-      <c r="I20" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="J20" s="15"/>
-      <c r="M20" s="2"/>
+      <c r="J20" s="38"/>
     </row>
     <row r="21" customFormat="false" ht="19.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
-      <c r="B21" s="11"/>
-      <c r="I21" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="J21" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="P21" s="11"/>
+      <c r="B21" s="15"/>
+      <c r="I21" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="J21" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="P21" s="15"/>
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="I22" s="31"/>
-      <c r="J22" s="35"/>
-      <c r="P22" s="11"/>
+      <c r="A22" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="I22" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="J22" s="41"/>
+      <c r="P22" s="15"/>
     </row>
     <row r="23" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B23" s="15"/>
-      <c r="G23" s="36"/>
+      <c r="A23" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="38"/>
+      <c r="G23" s="42"/>
+      <c r="I23" s="37" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
-      <c r="B24" s="37"/>
+      <c r="B24" s="43"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="37"/>
+      <c r="B25" s="43"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="37"/>
-      <c r="G26" s="11"/>
+      <c r="B26" s="43"/>
+      <c r="G26" s="15"/>
     </row>
     <row r="27" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="37"/>
-      <c r="G27" s="11"/>
-      <c r="M27" s="11"/>
+      <c r="B27" s="43"/>
+      <c r="G27" s="15"/>
     </row>
     <row r="28" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="37"/>
-      <c r="C28" s="38"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="44"/>
       <c r="D28" s="1"/>
-      <c r="G28" s="12"/>
+      <c r="G28" s="33"/>
     </row>
     <row r="29" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="39"/>
+      <c r="B29" s="45"/>
       <c r="D29" s="1"/>
-      <c r="G29" s="11"/>
-      <c r="P29" s="11"/>
+      <c r="G29" s="15"/>
+      <c r="P29" s="15"/>
     </row>
     <row r="30" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="40"/>
-      <c r="C30" s="15"/>
-      <c r="O30" s="11"/>
-      <c r="P30" s="11"/>
+      <c r="B30" s="46"/>
+      <c r="C30" s="38"/>
+      <c r="O30" s="15"/>
+      <c r="P30" s="15"/>
     </row>
     <row r="31" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="39"/>
-      <c r="C31" s="15"/>
-      <c r="K31" s="11"/>
+      <c r="B31" s="45"/>
+      <c r="C31" s="38"/>
+      <c r="K31" s="15"/>
     </row>
     <row r="32" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="15"/>
-      <c r="D32" s="15"/>
+      <c r="B32" s="38"/>
+      <c r="D32" s="38"/>
+    </row>
+    <row r="34" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M34" s="15"/>
     </row>
     <row r="45" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M45" s="11"/>
+      <c r="M45" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4531,9 +4006,9 @@
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="G16:G17"/>
   </mergeCells>
-  <conditionalFormatting sqref="C5">
+  <conditionalFormatting sqref="C6">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>AND(COUNTIF($C$5:$C$5,C5)&gt;1,NOT(ISBLANK(C5)))</formula>
+      <formula>AND(COUNTIF($C$6:$C$6,C6)&gt;1,NOT(ISBLANK(C6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K29">
@@ -4563,7 +4038,7 @@
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -4575,985 +4050,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="true"/>
-  </sheetPr>
-  <dimension ref="A1:P45"/>
-  <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="13.2" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="12.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="14.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="15.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="17.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="15.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="16.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="13.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="14.55"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="10" min="10" style="2" width="9.1"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="11" style="2" width="9.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="24.1"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="9.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="16.77"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="16" style="2" width="9.1"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="4" customFormat="true" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="6"/>
-    </row>
-    <row r="2" customFormat="false" ht="23.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" s="5"/>
-    </row>
-    <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" s="14"/>
-    </row>
-    <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="P4" s="11"/>
-    </row>
-    <row r="5" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="P5" s="11"/>
-    </row>
-    <row r="6" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="19" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="F9" s="21"/>
-      <c r="G9" s="11" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C10" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C11" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I11" s="23" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="I12" s="41" t="s">
-        <v>20</v>
-      </c>
-      <c r="K12" s="25"/>
-      <c r="P12" s="11"/>
-    </row>
-    <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="F13" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="I13" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="P13" s="11"/>
-    </row>
-    <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C14" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="F14" s="12"/>
-      <c r="G14" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I14" s="43" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C15" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G15" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="I15" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="P15" s="11"/>
-    </row>
-    <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="45" t="s">
-        <v>123</v>
-      </c>
-      <c r="P16" s="11"/>
-    </row>
-    <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="G17" s="45"/>
-    </row>
-    <row r="18" customFormat="false" ht="19.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
-      <c r="E18" s="42" t="s">
-        <v>125</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="G19" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="I19" s="30" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" s="11" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="I20" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="J20" s="15"/>
-    </row>
-    <row r="21" customFormat="false" ht="19.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2"/>
-      <c r="B21" s="11"/>
-      <c r="I21" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="J21" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="P21" s="11"/>
-    </row>
-    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="I22" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="J22" s="35"/>
-      <c r="P22" s="11"/>
-    </row>
-    <row r="23" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="15"/>
-      <c r="G23" s="36"/>
-      <c r="I23" s="31" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2"/>
-      <c r="B24" s="37"/>
-      <c r="I24" s="31"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="37"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="37"/>
-      <c r="G26" s="11"/>
-    </row>
-    <row r="27" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="37"/>
-      <c r="G27" s="11"/>
-    </row>
-    <row r="28" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="37"/>
-      <c r="C28" s="38"/>
-      <c r="D28" s="1"/>
-      <c r="G28" s="12"/>
-    </row>
-    <row r="29" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="39"/>
-      <c r="D29" s="1"/>
-      <c r="G29" s="11"/>
-      <c r="P29" s="11"/>
-    </row>
-    <row r="30" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="40"/>
-      <c r="C30" s="15"/>
-      <c r="O30" s="11"/>
-      <c r="P30" s="11"/>
-    </row>
-    <row r="31" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="39"/>
-      <c r="C31" s="15"/>
-      <c r="K31" s="11"/>
-    </row>
-    <row r="32" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="15"/>
-      <c r="D32" s="15"/>
-    </row>
-    <row r="34" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M34" s="11"/>
-    </row>
-    <row r="45" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M45" s="11"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="G16:G17"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C6">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
-      <formula>AND(COUNTIF($C$6:$C$6,C6)&gt;1,NOT(ISBLANK(C6)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K29">
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
-      <formula>AND(COUNTIF($K$29:$K$29,K29)&gt;1,NOT(ISBLANK(K29)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D37">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
-      <formula>AND(COUNTIF($D$37:$D$37,D37)&gt;1,NOT(ISBLANK(D37)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K34">
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
-      <formula>AND(COUNTIF($K$34:$K$34,K34)&gt;1,NOT(ISBLANK(K34)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D33">
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
-      <formula>AND(COUNTIF($D$33:$D$33,D33)&gt;1,NOT(ISBLANK(D33)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D40">
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
-      <formula>AND(COUNTIF($D$40:$D$40,D40)&gt;1,NOT(ISBLANK(D40)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="0" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P45"/>
-  <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="13.2" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="2" style="2" width="25.43"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="10" min="10" style="2" width="9.1"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="11" style="2" width="9.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="24.1"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="9.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="16.77"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="16" style="2" width="9.1"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="4" customFormat="true" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="6"/>
-    </row>
-    <row r="2" customFormat="false" ht="23.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" s="5"/>
-    </row>
-    <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="46" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" s="46" t="s">
-        <v>90</v>
-      </c>
-      <c r="C3" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="D3" s="46" t="s">
-        <v>100</v>
-      </c>
-      <c r="E3" s="46" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="48" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" s="14"/>
-    </row>
-    <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="46" t="s">
-        <v>101</v>
-      </c>
-      <c r="C4" s="46" t="s">
-        <v>102</v>
-      </c>
-      <c r="D4" s="46" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="46" t="s">
-        <v>16</v>
-      </c>
-      <c r="P4" s="11"/>
-    </row>
-    <row r="5" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="46" t="s">
-        <v>104</v>
-      </c>
-      <c r="D5" s="46" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="51" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="P5" s="11"/>
-    </row>
-    <row r="6" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="49"/>
-      <c r="B6" s="52"/>
-      <c r="C6" s="46" t="s">
-        <v>105</v>
-      </c>
-      <c r="D6" s="48"/>
-      <c r="E6" s="50" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="51" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" s="46" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="47" t="s">
-        <v>106</v>
-      </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="46" t="s">
-        <v>93</v>
-      </c>
-      <c r="E7" s="46" t="s">
-        <v>107</v>
-      </c>
-      <c r="F7" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" s="46" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="54" t="s">
-        <v>108</v>
-      </c>
-      <c r="B8" s="48"/>
-      <c r="C8" s="46" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="46" t="s">
-        <v>109</v>
-      </c>
-      <c r="F8" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="54" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="50" t="s">
-        <v>130</v>
-      </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="46" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="46" t="s">
-        <v>112</v>
-      </c>
-      <c r="F9" s="21"/>
-      <c r="G9" s="46" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="55"/>
-      <c r="B10" s="48"/>
-      <c r="C10" s="47" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="46" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" s="46" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="55"/>
-      <c r="B11" s="48"/>
-      <c r="C11" s="46" t="s">
-        <v>113</v>
-      </c>
-      <c r="E11" s="46" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="46" t="s">
-        <v>56</v>
-      </c>
-      <c r="I11" s="23" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" s="46" t="s">
-        <v>114</v>
-      </c>
-      <c r="F12" s="50" t="s">
-        <v>61</v>
-      </c>
-      <c r="I12" s="56" t="s">
-        <v>20</v>
-      </c>
-      <c r="K12" s="25"/>
-      <c r="P12" s="11"/>
-    </row>
-    <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="57" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" s="58" t="s">
-        <v>115</v>
-      </c>
-      <c r="E13" s="54" t="s">
-        <v>116</v>
-      </c>
-      <c r="F13" s="59" t="s">
-        <v>66</v>
-      </c>
-      <c r="I13" s="60" t="s">
-        <v>71</v>
-      </c>
-      <c r="P13" s="11"/>
-    </row>
-    <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C14" s="54" t="s">
-        <v>117</v>
-      </c>
-      <c r="E14" s="54" t="s">
-        <v>131</v>
-      </c>
-      <c r="F14" s="12"/>
-      <c r="G14" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I14" s="61" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C15" s="54" t="s">
-        <v>119</v>
-      </c>
-      <c r="E15" s="54" t="s">
-        <v>120</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G15" s="58" t="s">
-        <v>121</v>
-      </c>
-      <c r="I15" s="48"/>
-      <c r="P15" s="11"/>
-    </row>
-    <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="E16" s="54" t="s">
-        <v>122</v>
-      </c>
-      <c r="F16" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="62" t="s">
-        <v>132</v>
-      </c>
-      <c r="P16" s="11"/>
-    </row>
-    <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="47" t="s">
-        <v>82</v>
-      </c>
-      <c r="E17" s="54" t="s">
-        <v>124</v>
-      </c>
-      <c r="G17" s="62"/>
-    </row>
-    <row r="18" customFormat="false" ht="19.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
-      <c r="E18" s="58" t="s">
-        <v>125</v>
-      </c>
-      <c r="G18" s="46" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E19" s="54" t="s">
-        <v>127</v>
-      </c>
-      <c r="G19" s="47" t="s">
-        <v>128</v>
-      </c>
-      <c r="I19" s="30" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" s="11" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="47" t="s">
-        <v>44</v>
-      </c>
-      <c r="I20" s="63" t="s">
-        <v>19</v>
-      </c>
-      <c r="J20" s="15"/>
-    </row>
-    <row r="21" customFormat="false" ht="19.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2"/>
-      <c r="B21" s="11"/>
-      <c r="I21" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="J21" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="P21" s="11"/>
-    </row>
-    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="I22" s="63" t="s">
-        <v>54</v>
-      </c>
-      <c r="J22" s="35"/>
-      <c r="P22" s="11"/>
-    </row>
-    <row r="23" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="46" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="15"/>
-      <c r="G23" s="36"/>
-      <c r="I23" s="63" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2"/>
-      <c r="B24" s="37"/>
-      <c r="I24" s="63" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="37"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="37"/>
-      <c r="G26" s="11"/>
-    </row>
-    <row r="27" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="37"/>
-      <c r="G27" s="11"/>
-    </row>
-    <row r="28" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="37"/>
-      <c r="C28" s="38"/>
-      <c r="D28" s="1"/>
-      <c r="G28" s="12"/>
-    </row>
-    <row r="29" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="39"/>
-      <c r="D29" s="1"/>
-      <c r="G29" s="11"/>
-      <c r="P29" s="11"/>
-    </row>
-    <row r="30" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="40"/>
-      <c r="C30" s="15"/>
-      <c r="O30" s="11"/>
-      <c r="P30" s="11"/>
-    </row>
-    <row r="31" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="39"/>
-      <c r="C31" s="15"/>
-      <c r="K31" s="11"/>
-    </row>
-    <row r="32" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="15"/>
-      <c r="D32" s="15"/>
-    </row>
-    <row r="34" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M34" s="11"/>
-    </row>
-    <row r="45" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M45" s="11"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="G16:G17"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C6">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
-      <formula>AND(COUNTIF($C$6:$C$6,C6)&gt;1,NOT(ISBLANK(C6)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K29">
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
-      <formula>AND(COUNTIF($K$29:$K$29,K29)&gt;1,NOT(ISBLANK(K29)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D37">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
-      <formula>AND(COUNTIF($D$37:$D$37,D37)&gt;1,NOT(ISBLANK(D37)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K34">
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
-      <formula>AND(COUNTIF($K$34:$K$34,K34)&gt;1,NOT(ISBLANK(K34)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D33">
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
-      <formula>AND(COUNTIF($D$33:$D$33,D33)&gt;1,NOT(ISBLANK(D33)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D40">
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
-      <formula>AND(COUNTIF($D$40:$D$40,D40)&gt;1,NOT(ISBLANK(D40)))</formula>
-    </cfRule>
-  </conditionalFormatting>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5561,6 +4062,5 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/raw/BUS.xlsx
+++ b/raw/BUS.xlsx
@@ -9,8 +9,11 @@
   </bookViews>
   <sheets>
     <sheet name="17" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Лист1" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="18" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="false" name="_xlfn_AGGREGATE" vbProcedure="false"/>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -20,8 +23,206 @@
 </workbook>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">оқу</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>41</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>15</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>85</xdr:colOff>
+                <xdr:row>8</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">оқу</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>84</xdr:colOff>
+                <xdr:row>12</xdr:row>
+                <xdr:rowOff>3</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>16</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">оқу</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>21</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>6</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>48</xdr:colOff>
+                <xdr:row>11</xdr:row>
+                <xdr:rowOff>17</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">оқу</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>21</xdr:colOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>11</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>48</xdr:colOff>
+                <xdr:row>14</xdr:row>
+                <xdr:rowOff>4</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="115">
   <si>
     <t xml:space="preserve">  17.10. 2026 ж. </t>
   </si>
@@ -50,268 +251,322 @@
     <t xml:space="preserve">списаниеге</t>
   </si>
   <si>
+    <t xml:space="preserve">20-181AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2714/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-349AS12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-262AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35,2-Н2984/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-198AG12   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-H359312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-Н0592/12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-175AG12  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н3136/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2713/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 20-177AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35,2-Н3025/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-173AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-Н614760  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1-H267812 37DEA12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-341AS12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-250AG12   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35,2-Н2972/12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-H2631/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-Н3397/12  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-216AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35,2-Н2952/12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-178AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-H2672/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н3564/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2291/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-219AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-587AI12  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ППД</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-Н2652/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н1544/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-857AI12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н3204/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-Н2649/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-194AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-Н2689/12   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-827AI12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2715/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н3569/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-Н2641/12   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-968AC12 н </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-228AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-352AS12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бурение</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-180AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-847AI12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-206AG 12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-H3574/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">резерв</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЦПП</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н3153/12  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н3135/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н3196/12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-H2664/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-H614805 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2710/12 д/н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2716/12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-213AG12  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-Н2695/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2708/12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н3218/12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">окс</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-Н3408/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-214AG12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2939/12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">УТТ КРС</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н3180/12 н </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЦАП</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2705/12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-149AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1-H2673/12        35-29ABI12  н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-H2675/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-337AS12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-215AG12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-217AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> отд кадр</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2706/12 н </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-218AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ремонт</t>
+  </si>
+  <si>
     <t xml:space="preserve">20-233AG12   </t>
   </si>
   <si>
-    <t xml:space="preserve">35-Н2714/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-349AS12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-262AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35,2-Н2984/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-149AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-H359312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-Н614760  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-H2675/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н3136/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н2713/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-194AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35,2-Н3025/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-175AG12  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-Н0592/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1-H267812 37DEA12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-341AS12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-198AG12   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35,2-Н2972/12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-181AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-Н3397/12  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-216AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35,2-Н2952/12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-Н2649/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-Н3408/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н3564/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н2291/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-219AG12 </t>
+    <t xml:space="preserve">35-Н1543/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-209AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ТБ класс ПРЦЭО</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РСУ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-192AG12 </t>
   </si>
   <si>
     <t xml:space="preserve">20-H269412 </t>
   </si>
   <si>
-    <t xml:space="preserve">ППД</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-Н2652/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-827AI12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-857AI12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н3204/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-Н2641/12   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-250AG12   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-Н2695/12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-968AC12 н </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н2715/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н3569/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-587AI12  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н1544/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-228AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-352AS12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Бурение</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 20-177AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-847AI12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-206AG 12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-H3574/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">резерв</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЦПП</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н3153/12  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н3135/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н3196/12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-H2631/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-H614805 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н2710/12 д/н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н2716/12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-213AG12  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-H2664/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н2708/12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н3218/12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">окс</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-180AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-214AG12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н2939/12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">УТТ КРС</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н3180/12 н </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ЦАП</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н2705/12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-173AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1-H2673/12        35-29ABI12  н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-H2672/12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-337AS12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-215AG12 н</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-217AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> отд кадр</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н2706/12 н </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-218AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ремонт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-178AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-Н1543/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35-209AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ТБ класс ПРЦЭО</t>
-  </si>
-  <si>
-    <t xml:space="preserve">РСУ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-192AG12 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20-Н2689/12   </t>
-  </si>
-  <si>
     <t xml:space="preserve">20-Н614761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  18.10. 2026 ж. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тогайбаев Бакитжан Танатарович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Жүргізуші</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K1506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н3204/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЦПКРС</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.10-19.10.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Урбисинов Есиркеп Сайлаубекович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">К2141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-352AI/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Арал Талғат Бегалыұлы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K0678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1-H2678/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">МӨЦ-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Латыпов Ревкат</t>
+  </si>
+  <si>
+    <t xml:space="preserve">К3070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-H1544/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">МӨЦ-3</t>
   </si>
 </sst>
 </file>
@@ -327,7 +582,7 @@
     <numFmt numFmtId="169" formatCode="[$-409]m/d/yyyy"/>
     <numFmt numFmtId="170" formatCode="@"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -384,7 +639,7 @@
     <font>
       <b val="true"/>
       <i val="true"/>
-      <sz val="20"/>
+      <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -400,23 +655,6 @@
     </font>
     <font>
       <b val="true"/>
-      <i val="true"/>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b val="true"/>
       <sz val="12"/>
       <color rgb="FF008000"/>
       <name val="Arial"/>
@@ -425,20 +663,20 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
+      <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
+      <sz val="12"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -446,29 +684,44 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="16"/>
-      <color rgb="FF008000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="12"/>
+      <color rgb="FF339966"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF339966"/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color rgb="FF008000"/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
@@ -484,13 +737,14 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF339966"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
     </font>
     <font>
-      <sz val="16"/>
+      <b val="true"/>
+      <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -498,8 +752,9 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="204"/>
     </font>
     <font>
@@ -510,13 +765,22 @@
       <charset val="204"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="9"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -537,14 +801,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC0C0C0"/>
-        <bgColor rgb="FFCCCCFF"/>
+        <fgColor rgb="FF969696"/>
+        <bgColor rgb="FF808080"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF969696"/>
-        <bgColor rgb="FF808080"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0C0C0"/>
+        <bgColor rgb="FFCCCCFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -560,12 +830,26 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
@@ -577,8 +861,22 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
       <right style="thin"/>
-      <top style="thin"/>
+      <top/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
@@ -1872,92 +2170,300 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="77">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="1222" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="3" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="3" borderId="3" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="4" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="18" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="18" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="3" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="3" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="1222" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="15" fillId="3" borderId="2" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="3" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="2" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="2" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="3" borderId="1" xfId="1217" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1965,100 +2471,12 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="2" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="15" fillId="3" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="15" fillId="5" borderId="2" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="2" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="3" borderId="1" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="24" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="24" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -3277,7 +3695,85 @@
     <cellStyle name="Финансовый 2 2" xfId="1225"/>
     <cellStyle name="Финансовый 2 3" xfId="1226"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="204"/>
+        <family val="0"/>
+        <color rgb="FF800080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="204"/>
+        <family val="0"/>
+        <color rgb="FF800080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="204"/>
+        <family val="0"/>
+        <color rgb="FF800080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="204"/>
+        <family val="0"/>
+        <color rgb="FF800080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="204"/>
+        <family val="0"/>
+        <color rgb="FF800080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="204"/>
+        <family val="0"/>
+        <color rgb="FF800080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
@@ -3366,14 +3862,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>299520</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>152640</xdr:rowOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>60840</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3382,8 +3878,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1792440" y="6648480"/>
-          <a:ext cx="299520" cy="655560"/>
+          <a:off x="1792440" y="5764680"/>
+          <a:ext cx="299520" cy="563760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3406,14 +3902,14 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>94680</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>30600</xdr:rowOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>394200</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>14760</xdr:rowOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>75960</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3422,8 +3918,173 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1887120" y="6679080"/>
-          <a:ext cx="299520" cy="654840"/>
+          <a:off x="1887120" y="5764680"/>
+          <a:ext cx="299520" cy="578880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>298080</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>152280</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1080000" y="4922640"/>
+          <a:ext cx="298080" cy="655200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>94320</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>30600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>392040</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>23040</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1174320" y="4953240"/>
+          <a:ext cx="297720" cy="662760"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>298080</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>60840</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1080000" y="4922640"/>
+          <a:ext cx="298080" cy="563760"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>94320</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>22680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>392040</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>98640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1174320" y="4945320"/>
+          <a:ext cx="297720" cy="578880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3554,74 +4215,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:P45"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="13.2" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="2" style="2" width="25.43"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="10" min="10" style="2" width="9.1"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="11" style="2" width="9.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="24.1"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="9.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="16.77"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="16" style="2" width="9.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="1" style="1" width="25.43"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="10" min="10" style="1" width="9.1"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="11" style="1" width="9.1"/>
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="true" ht="26.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="6"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="23.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="5"/>
+      <c r="J2" s="9"/>
     </row>
     <row r="3" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="11" t="s">
@@ -3633,13 +4288,14 @@
       <c r="F3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="13" t="s">
         <v>16</v>
       </c>
       <c r="I3" s="14"/>
+      <c r="J3" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
@@ -3660,345 +4316,397 @@
       <c r="F4" s="11" t="s">
         <v>22</v>
       </c>
+      <c r="G4" s="12"/>
       <c r="H4" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="P4" s="15"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="13"/>
+      <c r="B5" s="12"/>
       <c r="C5" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="G5" s="12"/>
+      <c r="H5" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="P5" s="15"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16"/>
-      <c r="B6" s="19"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="6"/>
       <c r="C6" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="17" t="s">
+      <c r="D6" s="12"/>
+      <c r="E6" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="G6" s="12"/>
+      <c r="H6" s="10" t="s">
         <v>33</v>
       </c>
+      <c r="I6" s="12"/>
+      <c r="J6" s="9"/>
     </row>
     <row r="7" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="20"/>
+      <c r="B7" s="7"/>
       <c r="C7" s="11" t="s">
         <v>35</v>
       </c>
+      <c r="D7" s="12"/>
       <c r="E7" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="7" t="s">
         <v>38</v>
       </c>
       <c r="H7" s="11" t="s">
         <v>39</v>
       </c>
+      <c r="I7" s="12"/>
+      <c r="J7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="13"/>
+      <c r="B8" s="12"/>
       <c r="C8" s="11" t="s">
         <v>41</v>
       </c>
+      <c r="D8" s="12"/>
       <c r="E8" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="10" t="s">
         <v>43</v>
       </c>
       <c r="G8" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="H8" s="21" t="s">
+      <c r="H8" s="11" t="s">
         <v>45</v>
       </c>
+      <c r="I8" s="12"/>
+      <c r="J8" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="13"/>
+      <c r="B9" s="12"/>
       <c r="C9" s="11" t="s">
         <v>47</v>
       </c>
+      <c r="D9" s="12"/>
       <c r="E9" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="22"/>
-      <c r="G9" s="11" t="s">
+      <c r="F9" s="11"/>
+      <c r="G9" s="10" t="s">
         <v>49</v>
       </c>
+      <c r="H9" s="18"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="9"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="12" t="s">
+      <c r="B10" s="12"/>
+      <c r="C10" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="9"/>
+      <c r="D10" s="7"/>
       <c r="E10" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="23" t="s">
+      <c r="F10" s="19" t="s">
         <v>53</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>54</v>
       </c>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24"/>
-      <c r="B11" s="13"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="12"/>
       <c r="C11" s="11" t="s">
         <v>55</v>
       </c>
+      <c r="D11" s="12"/>
       <c r="E11" s="11" t="s">
         <v>56</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="I11" s="25" t="s">
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="20" t="s">
         <v>58</v>
       </c>
+      <c r="J11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="21" t="s">
         <v>59</v>
       </c>
+      <c r="B12" s="12"/>
       <c r="C12" s="11" t="s">
         <v>60</v>
       </c>
+      <c r="D12" s="12"/>
       <c r="E12" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="I12" s="27" t="s">
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="K12" s="28"/>
-      <c r="P12" s="15"/>
+      <c r="J12" s="9"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="B13" s="12"/>
+      <c r="C13" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="D13" s="12"/>
+      <c r="E13" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="31" t="s">
+      <c r="F13" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="I13" s="32" t="s">
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="P13" s="15"/>
+      <c r="J13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C14" s="21" t="s">
+      <c r="A14" s="25"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="D14" s="12"/>
+      <c r="E14" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="F14" s="33"/>
-      <c r="G14" s="9" t="s">
+      <c r="F14" s="10"/>
+      <c r="G14" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="I14" s="34" t="s">
+      <c r="H14" s="12"/>
+      <c r="I14" s="11" t="s">
         <v>72</v>
       </c>
+      <c r="J14" s="9"/>
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C15" s="21" t="s">
+      <c r="A15" s="25"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="D15" s="12"/>
+      <c r="E15" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="G15" s="30" t="s">
+      <c r="G15" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="I15" s="13"/>
-      <c r="P15" s="15"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="E16" s="21" t="s">
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="13" t="s">
         <v>78</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="G16" s="35" t="s">
+      <c r="G16" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="P16" s="15"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="9"/>
     </row>
     <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="E17" s="21" t="s">
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="G17" s="35"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="19.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2"/>
-      <c r="E18" s="30" t="s">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="23" t="s">
         <v>83</v>
       </c>
+      <c r="F18" s="12"/>
       <c r="G18" s="11" t="s">
         <v>84</v>
       </c>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="9"/>
     </row>
     <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E19" s="21" t="s">
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="G19" s="12" t="s">
+      <c r="F19" s="12"/>
+      <c r="G19" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="I19" s="36" t="s">
+      <c r="H19" s="12"/>
+      <c r="I19" s="27" t="s">
         <v>88</v>
       </c>
+      <c r="J19" s="9"/>
     </row>
-    <row r="20" s="15" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
+    <row r="20" s="30" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="I20" s="37" t="s">
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="J20" s="38"/>
+      <c r="J20" s="29"/>
     </row>
     <row r="21" customFormat="false" ht="19.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2"/>
-      <c r="B21" s="15"/>
-      <c r="I21" s="37" t="s">
+      <c r="A21" s="12"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="J21" s="39" t="s">
+      <c r="J21" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="P21" s="15"/>
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="40" t="s">
+      <c r="A22" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="I22" s="37" t="s">
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="J22" s="41"/>
-      <c r="P22" s="15"/>
+      <c r="J22" s="33"/>
     </row>
     <row r="23" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="B23" s="38"/>
-      <c r="G23" s="42"/>
-      <c r="I23" s="37" t="s">
+      <c r="B23" s="35"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="28" t="s">
         <v>96</v>
       </c>
+      <c r="J23" s="37"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2"/>
-      <c r="B24" s="43"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="43"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="43"/>
-      <c r="G26" s="15"/>
-    </row>
-    <row r="27" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="43"/>
-      <c r="G27" s="15"/>
-    </row>
-    <row r="28" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="43"/>
-      <c r="C28" s="44"/>
-      <c r="D28" s="1"/>
-      <c r="G28" s="33"/>
-    </row>
-    <row r="29" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="45"/>
-      <c r="D29" s="1"/>
-      <c r="G29" s="15"/>
-      <c r="P29" s="15"/>
-    </row>
-    <row r="30" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="46"/>
-      <c r="C30" s="38"/>
-      <c r="O30" s="15"/>
-      <c r="P30" s="15"/>
-    </row>
-    <row r="31" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="45"/>
-      <c r="C31" s="38"/>
-      <c r="K31" s="15"/>
-    </row>
-    <row r="32" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="38"/>
-      <c r="D32" s="38"/>
-    </row>
-    <row r="34" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M34" s="15"/>
-    </row>
-    <row r="45" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M45" s="15"/>
+      <c r="A24" s="38"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4011,34 +4719,9 @@
       <formula>AND(COUNTIF($C$6:$C$6,C6)&gt;1,NOT(ISBLANK(C6)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K29">
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>AND(COUNTIF($K$29:$K$29,K29)&gt;1,NOT(ISBLANK(K29)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D37">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>AND(COUNTIF($D$37:$D$37,D37)&gt;1,NOT(ISBLANK(D37)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K34">
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>AND(COUNTIF($K$34:$K$34,K34)&gt;1,NOT(ISBLANK(K34)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D33">
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
-      <formula>AND(COUNTIF($D$33:$D$33,D33)&gt;1,NOT(ISBLANK(D33)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D40">
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
-      <formula>AND(COUNTIF($D$40:$D$40,D40)&gt;1,NOT(ISBLANK(D40)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -4050,17 +4733,641 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15.32"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="43"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="18"/>
+      <c r="H4" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="18"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="18"/>
+      <c r="C5" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="18"/>
+      <c r="H5" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="18"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="44"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="18"/>
+      <c r="E6" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="18"/>
+      <c r="H6" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="18"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="47"/>
+      <c r="C7" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="18"/>
+      <c r="E7" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="18"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="18"/>
+      <c r="C8" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="18"/>
+      <c r="E8" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="18"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="18"/>
+      <c r="E9" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="41"/>
+      <c r="G9" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="49"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="47"/>
+      <c r="E10" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="51"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="18"/>
+      <c r="E11" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="52" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="51"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="18"/>
+      <c r="E12" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="45" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="53" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="18"/>
+      <c r="C13" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="18"/>
+      <c r="E13" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" s="55" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="53" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="56" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="18"/>
+      <c r="C14" s="57" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="18"/>
+      <c r="E14" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="40"/>
+      <c r="G14" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="18"/>
+      <c r="I14" s="53" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="58"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="42" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="18"/>
+      <c r="E15" s="42" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" s="57" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="18"/>
+      <c r="C16" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" s="18"/>
+      <c r="E16" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="59" t="s">
+        <v>80</v>
+      </c>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" s="18"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="57" t="s">
+        <v>83</v>
+      </c>
+      <c r="F18" s="18"/>
+      <c r="G18" s="41" t="s">
+        <v>84</v>
+      </c>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="60" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="42" t="s">
+        <v>86</v>
+      </c>
+      <c r="F19" s="18"/>
+      <c r="G19" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="H19" s="18"/>
+      <c r="I19" s="61" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="41" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="62" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="62" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="63" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="62" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="64"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="62" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="67" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" s="68" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" s="69" t="s">
+        <v>100</v>
+      </c>
+      <c r="D26" s="70" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="71" t="s">
+        <v>101</v>
+      </c>
+      <c r="F26" s="72" t="s">
+        <v>102</v>
+      </c>
+      <c r="G26" s="73" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="67" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" s="68" t="s">
+        <v>99</v>
+      </c>
+      <c r="C27" s="69" t="s">
+        <v>105</v>
+      </c>
+      <c r="D27" s="70" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" s="74" t="s">
+        <v>106</v>
+      </c>
+      <c r="F27" s="72" t="s">
+        <v>102</v>
+      </c>
+      <c r="G27" s="73" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="75" t="s">
+        <v>107</v>
+      </c>
+      <c r="B28" s="68" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28" s="69" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="70" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="74" t="s">
+        <v>109</v>
+      </c>
+      <c r="F28" s="72" t="s">
+        <v>110</v>
+      </c>
+      <c r="G28" s="73" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="67" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" s="68" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="71" t="s">
+        <v>112</v>
+      </c>
+      <c r="D29" s="70" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" s="76" t="s">
+        <v>113</v>
+      </c>
+      <c r="F29" s="72" t="s">
+        <v>114</v>
+      </c>
+      <c r="G29" s="73" t="s">
+        <v>103</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G16:G17"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C6">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>AND(COUNTIF($C$6:$C$6,C6)&gt;1,NOT(ISBLANK(C6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E29">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>AND(COUNTIF($E$29:$E$29,E29)&gt;1,NOT(ISBLANK(E29)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E27:E28">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>AND(COUNTIF($E$27:$E$28,E27)&gt;1,NOT(ISBLANK(E27)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C26">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+      <formula>AND(COUNTIF($C$26:$C$26,C26)&gt;1,NOT(ISBLANK(C26)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C26">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>AND(COUNTIF($C$26:$C$26,C26)&gt;1,NOT(ISBLANK(C26)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C27">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>AND(COUNTIF($C$27:$C$27,C27)&gt;1,NOT(ISBLANK(C27)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C27">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>AND(COUNTIF($C$27:$C$27,C27)&gt;1,NOT(ISBLANK(C27)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C28">
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>AND(COUNTIF($C$28:$C$28,C28)&gt;1,NOT(ISBLANK(C28)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C28">
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>AND(COUNTIF($C$28:$C$28,C28)&gt;1,NOT(ISBLANK(C28)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C29">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+      <formula>AND(COUNTIF($C$29:$C$29,C29)&gt;1,NOT(ISBLANK(C29)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C29">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>AND(COUNTIF($C$29:$C$29,C29)&gt;1,NOT(ISBLANK(C29)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/raw/BUS.xlsx
+++ b/raw/BUS.xlsx
@@ -10,6 +10,7 @@
   <sheets>
     <sheet name="17" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="18" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="19" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" name="_xlfn_AGGREGATE" vbProcedure="false"/>
@@ -76,7 +77,7 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
-    <comment ref="C13" authorId="0">
+    <comment ref="C11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -107,14 +108,14 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>3</xdr:col>
-                <xdr:colOff>84</xdr:colOff>
-                <xdr:row>12</xdr:row>
+                <xdr:colOff>76</xdr:colOff>
+                <xdr:row>10</xdr:row>
                 <xdr:rowOff>3</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>5</xdr:col>
-                <xdr:colOff>12</xdr:colOff>
-                <xdr:row>16</xdr:row>
+                <xdr:colOff>4</xdr:colOff>
+                <xdr:row>14</xdr:row>
                 <xdr:rowOff>14</xdr:rowOff>
               </xdr:to>
             </anchor>
@@ -154,13 +155,13 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>6</xdr:col>
-                <xdr:colOff>21</xdr:colOff>
+                <xdr:colOff>13</xdr:colOff>
                 <xdr:row>7</xdr:row>
                 <xdr:rowOff>6</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>7</xdr:col>
-                <xdr:colOff>48</xdr:colOff>
+                <xdr:colOff>40</xdr:colOff>
                 <xdr:row>11</xdr:row>
                 <xdr:rowOff>17</xdr:rowOff>
               </xdr:to>
@@ -201,13 +202,13 @@
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>6</xdr:col>
-                <xdr:colOff>21</xdr:colOff>
+                <xdr:colOff>13</xdr:colOff>
                 <xdr:row>9</xdr:row>
                 <xdr:rowOff>11</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>7</xdr:col>
-                <xdr:colOff>48</xdr:colOff>
+                <xdr:colOff>40</xdr:colOff>
                 <xdr:row>14</xdr:row>
                 <xdr:rowOff>4</xdr:rowOff>
               </xdr:to>
@@ -221,8 +222,206 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">оқу</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>56</xdr:colOff>
+                <xdr:row>8</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">оқу</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>58</xdr:colOff>
+                <xdr:row>14</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">оқу</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>29</xdr:colOff>
+                <xdr:row>11</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">оқу</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>8</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>29</xdr:colOff>
+                <xdr:row>13</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="118">
   <si>
     <t xml:space="preserve">  17.10. 2026 ж. </t>
   </si>
@@ -518,6 +717,9 @@
     <t xml:space="preserve">  18.10. 2026 ж. </t>
   </si>
   <si>
+    <t xml:space="preserve">35-214AG12 д/н</t>
+  </si>
+  <si>
     <t xml:space="preserve">Тогайбаев Бакитжан Танатарович</t>
   </si>
   <si>
@@ -567,6 +769,12 @@
   </si>
   <si>
     <t xml:space="preserve">МӨЦ-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  19.10. 2026 ж. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">САБАҚ</t>
   </si>
 </sst>
 </file>
@@ -582,7 +790,7 @@
     <numFmt numFmtId="169" formatCode="[$-409]m/d/yyyy"/>
     <numFmt numFmtId="170" formatCode="@"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -779,6 +987,14 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF993300"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -2170,7 +2386,7 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="82">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2367,46 +2583,46 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="3" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="3" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="3" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="3" borderId="3" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2476,6 +2692,26 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="170" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="18" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3695,7 +3931,150 @@
     <cellStyle name="Финансовый 2 2" xfId="1225"/>
     <cellStyle name="Финансовый 2 3" xfId="1226"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="23">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="204"/>
+        <family val="0"/>
+        <color rgb="FF800080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="204"/>
+        <family val="0"/>
+        <color rgb="FF800080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="204"/>
+        <family val="0"/>
+        <color rgb="FF800080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="204"/>
+        <family val="0"/>
+        <color rgb="FF800080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="204"/>
+        <family val="0"/>
+        <color rgb="FF800080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="204"/>
+        <family val="0"/>
+        <color rgb="FF800080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="204"/>
+        <family val="0"/>
+        <color rgb="FF800080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="204"/>
+        <family val="0"/>
+        <color rgb="FF800080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="204"/>
+        <family val="0"/>
+        <color rgb="FF800080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="204"/>
+        <family val="0"/>
+        <color rgb="FF800080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="204"/>
+        <family val="0"/>
+        <color rgb="FF800080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
@@ -4106,6 +4485,171 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>298080</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>152280</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1080000" y="4922640"/>
+          <a:ext cx="298080" cy="655200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>94320</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>30600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>392040</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>23040</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1174320" y="4953240"/>
+          <a:ext cx="297720" cy="662760"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>298080</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>60840</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1080000" y="4922640"/>
+          <a:ext cx="298080" cy="563760"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>94320</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>22680</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>392040</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>98640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1174320" y="4945320"/>
+          <a:ext cx="297720" cy="578880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
   <a:themeElements>
@@ -4740,7 +5284,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16.43"/>
@@ -4870,7 +5414,7 @@
       <c r="A6" s="44"/>
       <c r="B6" s="46"/>
       <c r="C6" s="41" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D6" s="18"/>
       <c r="E6" s="45" t="s">
@@ -4891,7 +5435,7 @@
       </c>
       <c r="B7" s="47"/>
       <c r="C7" s="41" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D7" s="18"/>
       <c r="E7" s="41" t="s">
@@ -4909,12 +5453,12 @@
       <c r="I7" s="18"/>
     </row>
     <row r="8" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="42" t="s">
-        <v>46</v>
+      <c r="A8" s="41" t="s">
+        <v>30</v>
       </c>
       <c r="B8" s="18"/>
-      <c r="C8" s="41" t="s">
-        <v>41</v>
+      <c r="C8" s="40" t="s">
+        <v>51</v>
       </c>
       <c r="D8" s="18"/>
       <c r="E8" s="48" t="s">
@@ -4932,12 +5476,12 @@
       <c r="I8" s="18"/>
     </row>
     <row r="9" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="45" t="s">
-        <v>50</v>
+      <c r="A9" s="42" t="s">
+        <v>46</v>
       </c>
       <c r="B9" s="18"/>
       <c r="C9" s="41" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="41" t="s">
@@ -4951,16 +5495,18 @@
       <c r="I9" s="18"/>
     </row>
     <row r="10" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="49"/>
+      <c r="A10" s="45" t="s">
+        <v>50</v>
+      </c>
       <c r="B10" s="18"/>
-      <c r="C10" s="40" t="s">
-        <v>51</v>
+      <c r="C10" s="41" t="s">
+        <v>60</v>
       </c>
       <c r="D10" s="47"/>
       <c r="E10" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="50" t="s">
+      <c r="F10" s="49" t="s">
         <v>53</v>
       </c>
       <c r="G10" s="41" t="s">
@@ -4970,10 +5516,10 @@
       <c r="I10" s="18"/>
     </row>
     <row r="11" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="51"/>
+      <c r="A11" s="50"/>
       <c r="B11" s="18"/>
-      <c r="C11" s="41" t="s">
-        <v>55</v>
+      <c r="C11" s="48" t="s">
+        <v>40</v>
       </c>
       <c r="D11" s="18"/>
       <c r="E11" s="41" t="s">
@@ -4984,15 +5530,15 @@
       </c>
       <c r="G11" s="18"/>
       <c r="H11" s="18"/>
-      <c r="I11" s="52" t="s">
+      <c r="I11" s="51" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51"/>
+      <c r="A12" s="50"/>
       <c r="B12" s="18"/>
-      <c r="C12" s="41" t="s">
-        <v>60</v>
+      <c r="C12" s="52" t="s">
+        <v>65</v>
       </c>
       <c r="D12" s="18"/>
       <c r="E12" s="41" t="s">
@@ -5012,8 +5558,8 @@
         <v>59</v>
       </c>
       <c r="B13" s="18"/>
-      <c r="C13" s="48" t="s">
-        <v>40</v>
+      <c r="C13" s="42" t="s">
+        <v>98</v>
       </c>
       <c r="D13" s="18"/>
       <c r="E13" s="42" t="s">
@@ -5033,8 +5579,8 @@
         <v>64</v>
       </c>
       <c r="B14" s="18"/>
-      <c r="C14" s="57" t="s">
-        <v>65</v>
+      <c r="C14" s="42" t="s">
+        <v>69</v>
       </c>
       <c r="D14" s="18"/>
       <c r="E14" s="42" t="s">
@@ -5050,11 +5596,9 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="58"/>
+      <c r="A15" s="57"/>
       <c r="B15" s="18"/>
-      <c r="C15" s="42" t="s">
-        <v>69</v>
-      </c>
+      <c r="C15" s="58"/>
       <c r="D15" s="18"/>
       <c r="E15" s="42" t="s">
         <v>74</v>
@@ -5062,7 +5606,7 @@
       <c r="F15" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="G15" s="57" t="s">
+      <c r="G15" s="52" t="s">
         <v>76</v>
       </c>
       <c r="H15" s="18"/>
@@ -5073,9 +5617,7 @@
         <v>77</v>
       </c>
       <c r="B16" s="18"/>
-      <c r="C16" s="42" t="s">
-        <v>73</v>
-      </c>
+      <c r="C16" s="58"/>
       <c r="D16" s="18"/>
       <c r="E16" s="42" t="s">
         <v>78</v>
@@ -5109,7 +5651,7 @@
       <c r="B18" s="18"/>
       <c r="C18" s="18"/>
       <c r="D18" s="18"/>
-      <c r="E18" s="57" t="s">
+      <c r="E18" s="52" t="s">
         <v>83</v>
       </c>
       <c r="F18" s="18"/>
@@ -5205,98 +5747,100 @@
       <c r="F24" s="18"/>
       <c r="G24" s="18"/>
       <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
+      <c r="I24" s="41" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="67" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B26" s="68" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C26" s="69" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D26" s="70" t="n">
         <v>2</v>
       </c>
       <c r="E26" s="71" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F26" s="72" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G26" s="73" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="67" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B27" s="68" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C27" s="69" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D27" s="70" t="n">
         <v>2</v>
       </c>
       <c r="E27" s="74" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F27" s="72" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G27" s="73" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="75" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B28" s="68" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C28" s="69" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D28" s="70" t="n">
         <v>2</v>
       </c>
       <c r="E28" s="74" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F28" s="72" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G28" s="73" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="67" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B29" s="68" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C29" s="71" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D29" s="70" t="n">
         <v>2</v>
       </c>
       <c r="E29" s="76" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F29" s="72" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G29" s="73" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -5305,9 +5849,9 @@
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="G16:G17"/>
   </mergeCells>
-  <conditionalFormatting sqref="C6">
+  <conditionalFormatting sqref="A8">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>AND(COUNTIF($C$6:$C$6,C6)&gt;1,NOT(ISBLANK(C6)))</formula>
+      <formula>AND(COUNTIF($A$8:$A$8,A8)&gt;1,NOT(ISBLANK(A8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
@@ -5370,4 +5914,649 @@
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I29"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15.32"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="43"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="18"/>
+      <c r="H4" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="18"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="18"/>
+      <c r="C5" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="18"/>
+      <c r="H5" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="18"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="44"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="18"/>
+      <c r="E6" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="18"/>
+      <c r="H6" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="18"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="47"/>
+      <c r="C7" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="18"/>
+      <c r="E7" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="18"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="18"/>
+      <c r="C8" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="18"/>
+      <c r="E8" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="41" t="s">
+        <v>68</v>
+      </c>
+      <c r="I8" s="18"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="18"/>
+      <c r="E9" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="41"/>
+      <c r="G9" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="47"/>
+      <c r="E10" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="50"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="18"/>
+      <c r="E11" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="51" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="50"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="18"/>
+      <c r="E12" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="45" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="18"/>
+      <c r="I12" s="53" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="18"/>
+      <c r="C13" s="52" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="18"/>
+      <c r="E13" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" s="55" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="77" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="56" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="18"/>
+      <c r="C14" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="18"/>
+      <c r="E14" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="40"/>
+      <c r="G14" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="18"/>
+      <c r="I14" s="53" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="57"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="42" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="18"/>
+      <c r="E15" s="42" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" s="52" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="18"/>
+      <c r="C16" s="58"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="59" t="s">
+        <v>80</v>
+      </c>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" s="18"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="F18" s="18"/>
+      <c r="G18" s="41" t="s">
+        <v>84</v>
+      </c>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="60" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="42" t="s">
+        <v>86</v>
+      </c>
+      <c r="F19" s="18"/>
+      <c r="G19" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="H19" s="18"/>
+      <c r="I19" s="61" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="41" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="62" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="62" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="63" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="62" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="64"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="62" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G25" s="78" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="67" t="s">
+        <v>99</v>
+      </c>
+      <c r="B26" s="68" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" s="69" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" s="70" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="79" t="s">
+        <v>102</v>
+      </c>
+      <c r="F26" s="72" t="s">
+        <v>103</v>
+      </c>
+      <c r="G26" s="73" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="67" t="s">
+        <v>105</v>
+      </c>
+      <c r="B27" s="68" t="s">
+        <v>100</v>
+      </c>
+      <c r="C27" s="69" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" s="70" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" s="80" t="s">
+        <v>107</v>
+      </c>
+      <c r="F27" s="72" t="s">
+        <v>103</v>
+      </c>
+      <c r="G27" s="73" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="75" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" s="68" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" s="69" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" s="70" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="80" t="s">
+        <v>110</v>
+      </c>
+      <c r="F28" s="72" t="s">
+        <v>111</v>
+      </c>
+      <c r="G28" s="73" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="67" t="s">
+        <v>112</v>
+      </c>
+      <c r="B29" s="68" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" s="71" t="s">
+        <v>113</v>
+      </c>
+      <c r="D29" s="70" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" s="81" t="s">
+        <v>114</v>
+      </c>
+      <c r="F29" s="72" t="s">
+        <v>115</v>
+      </c>
+      <c r="G29" s="73" t="s">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G16:G17"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A8">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+      <formula>AND(COUNTIF($A$8:$A$8,A8)&gt;1,NOT(ISBLANK(A8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E29">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+      <formula>AND(COUNTIF($E$29:$E$29,E29)&gt;1,NOT(ISBLANK(E29)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E27:E28">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+      <formula>AND(COUNTIF($E$27:$E$28,E27)&gt;1,NOT(ISBLANK(E27)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C26">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+      <formula>AND(COUNTIF($C$26:$C$26,C26)&gt;1,NOT(ISBLANK(C26)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C26">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+      <formula>AND(COUNTIF($C$26:$C$26,C26)&gt;1,NOT(ISBLANK(C26)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C27">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+      <formula>AND(COUNTIF($C$27:$C$27,C27)&gt;1,NOT(ISBLANK(C27)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C27">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+      <formula>AND(COUNTIF($C$27:$C$27,C27)&gt;1,NOT(ISBLANK(C27)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C28">
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+      <formula>AND(COUNTIF($C$28:$C$28,C28)&gt;1,NOT(ISBLANK(C28)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C28">
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
+      <formula>AND(COUNTIF($C$28:$C$28,C28)&gt;1,NOT(ISBLANK(C28)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C29">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+      <formula>AND(COUNTIF($C$29:$C$29,C29)&gt;1,NOT(ISBLANK(C29)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C29">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
+      <formula>AND(COUNTIF($C$29:$C$29,C29)&gt;1,NOT(ISBLANK(C29)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
 </file>
--- a/raw/BUS.xlsx
+++ b/raw/BUS.xlsx
@@ -11,6 +11,7 @@
     <sheet name="17" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="18" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="19" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="20" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" name="_xlfn_AGGREGATE" vbProcedure="false"/>
@@ -421,7 +422,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="119">
   <si>
     <t xml:space="preserve">  17.10. 2026 ж. </t>
   </si>
@@ -775,6 +776,9 @@
   </si>
   <si>
     <t xml:space="preserve">САБАҚ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  20.10. 2026 ж. </t>
   </si>
 </sst>
 </file>
@@ -790,7 +794,7 @@
     <numFmt numFmtId="169" formatCode="[$-409]m/d/yyyy"/>
     <numFmt numFmtId="170" formatCode="@"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -995,6 +999,15 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b val="true"/>
+      <i val="true"/>
+      <sz val="20"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -2386,7 +2399,7 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="85">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2713,6 +2726,18 @@
     </xf>
     <xf numFmtId="170" fontId="18" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="1" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -3931,7 +3956,20 @@
     <cellStyle name="Финансовый 2 2" xfId="1225"/>
     <cellStyle name="Финансовый 2 3" xfId="1226"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="24">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="204"/>
+        <family val="0"/>
+        <color rgb="FF800080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
@@ -4650,6 +4688,171 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>298080</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>152640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1080000" y="5036760"/>
+          <a:ext cx="298080" cy="655560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>94320</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>30960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>392040</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>22680</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1174320" y="5067720"/>
+          <a:ext cx="297720" cy="662400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>23040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>298080</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>83880</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1080000" y="5059800"/>
+          <a:ext cx="298080" cy="563760"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>94320</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>23040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>392040</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>99000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1174320" y="5059800"/>
+          <a:ext cx="297720" cy="578880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
   <a:themeElements>
@@ -6559,4 +6762,507 @@
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I34"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15.32"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="24.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="82" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+    </row>
+    <row r="2" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="43"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="18"/>
+      <c r="H4" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="18"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="83" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="18"/>
+      <c r="C5" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="18"/>
+      <c r="H5" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="18"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="83"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="18"/>
+      <c r="E6" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="18"/>
+      <c r="H6" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="18"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="47"/>
+      <c r="C7" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="18"/>
+      <c r="E7" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="18"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="18"/>
+      <c r="C8" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="18"/>
+      <c r="E8" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="18"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="18"/>
+      <c r="E9" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="41"/>
+      <c r="G9" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="47"/>
+      <c r="E10" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="50"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="18"/>
+      <c r="E11" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="18"/>
+      <c r="I11" s="51" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="50"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="18"/>
+      <c r="E12" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="45" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="18"/>
+      <c r="I12" s="53" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="18"/>
+      <c r="C13" s="52" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="18"/>
+      <c r="E13" s="42" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" s="55" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="53" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="56" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="18"/>
+      <c r="C14" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="18"/>
+      <c r="E14" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="40"/>
+      <c r="G14" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="18"/>
+      <c r="I14" s="53" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="57"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="42" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="18"/>
+      <c r="E15" s="42" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" s="52" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="18"/>
+      <c r="C16" s="58"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="59" t="s">
+        <v>80</v>
+      </c>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" s="18"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="F18" s="18"/>
+      <c r="G18" s="41" t="s">
+        <v>84</v>
+      </c>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="60" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="42" t="s">
+        <v>86</v>
+      </c>
+      <c r="F19" s="18"/>
+      <c r="G19" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="H19" s="18"/>
+      <c r="I19" s="61" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="41" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="62" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="62" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="63" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="62" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="64"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="62" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="58"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H25" s="84"/>
+    </row>
+    <row r="34" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H34" s="84"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G16:G17"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A8">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
+      <formula>AND(COUNTIF($A$8:$A$8,A8)&gt;1,NOT(ISBLANK(A8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/raw/BUS.xlsx
+++ b/raw/BUS.xlsx
@@ -12,6 +12,7 @@
     <sheet name="18" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="19" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="20" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="20 ауысым" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" name="_xlfn_AGGREGATE" vbProcedure="false"/>
@@ -422,7 +423,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="140">
   <si>
     <t xml:space="preserve">  17.10. 2026 ж. </t>
   </si>
@@ -779,6 +780,69 @@
   </si>
   <si>
     <t xml:space="preserve">  20.10. 2026 ж. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-214AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1-H2673/12        35-29ABI12  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35,2-Н2972/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2706/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35,2-Н2952/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2708/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2939/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-215AG12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2705/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н3218/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2714/12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-968AC12  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н3153/12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-827AI12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2716/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2710/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-857AI12 д/н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-352AS12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-228AG12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н3180/12  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-337AS12 </t>
   </si>
 </sst>
 </file>
@@ -2399,7 +2463,7 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="88">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2738,6 +2802,18 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="0" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -3956,7 +4032,20 @@
     <cellStyle name="Финансовый 2 2" xfId="1225"/>
     <cellStyle name="Финансовый 2 3" xfId="1226"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="25">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="204"/>
+        <family val="0"/>
+        <color rgb="FF800080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
@@ -4853,6 +4942,171 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>298080</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>152640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1080000" y="5036760"/>
+          <a:ext cx="298080" cy="655560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>94320</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>30960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>392040</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>22680</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1174320" y="5067720"/>
+          <a:ext cx="297720" cy="662400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>23040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>298080</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>83880</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1080000" y="5059800"/>
+          <a:ext cx="298080" cy="563760"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>94320</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>23040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>392040</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>99000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1174320" y="5059800"/>
+          <a:ext cx="297720" cy="578880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
   <a:themeElements>
@@ -7265,4 +7519,574 @@
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:L41"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12.21"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="24.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="82" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+    </row>
+    <row r="2" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="43"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="18"/>
+      <c r="H4" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="18"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="83" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="18"/>
+      <c r="C5" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>121</v>
+      </c>
+      <c r="F5" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="18"/>
+      <c r="H5" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="18"/>
+      <c r="L5" s="85"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="83"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" s="18"/>
+      <c r="E6" s="45" t="s">
+        <v>123</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="18"/>
+      <c r="H6" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="18"/>
+      <c r="L6" s="85"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="47"/>
+      <c r="C7" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="18"/>
+      <c r="E7" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="18"/>
+      <c r="L7" s="85"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="18"/>
+      <c r="C8" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="D8" s="18"/>
+      <c r="E8" s="41" t="s">
+        <v>127</v>
+      </c>
+      <c r="F8" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="41" t="s">
+        <v>68</v>
+      </c>
+      <c r="H8" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="18"/>
+      <c r="L8" s="85"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="18"/>
+      <c r="E9" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="41"/>
+      <c r="G9" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="L9" s="85"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="47"/>
+      <c r="E10" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="F10" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="L10" s="85"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11" s="18"/>
+      <c r="C11" s="41" t="s">
+        <v>132</v>
+      </c>
+      <c r="D11" s="18"/>
+      <c r="E11" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="F11" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="18"/>
+      <c r="I11" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="L11" s="85"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="50"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="18"/>
+      <c r="E12" s="86" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12" s="45" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="18"/>
+      <c r="I12" s="53" t="s">
+        <v>63</v>
+      </c>
+      <c r="L12" s="85"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="18"/>
+      <c r="C13" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="D13" s="18"/>
+      <c r="E13" s="87" t="s">
+        <v>136</v>
+      </c>
+      <c r="F13" s="55" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="L13" s="85"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="56" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="18"/>
+      <c r="C14" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="18"/>
+      <c r="E14" s="87" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="40"/>
+      <c r="G14" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="18"/>
+      <c r="L14" s="85"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="57"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="18"/>
+      <c r="E15" s="87" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" s="83" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="L15" s="85"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="18"/>
+      <c r="C16" s="58"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="87" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="83"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="L16" s="85"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="87" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="18"/>
+      <c r="G17" s="52" t="s">
+        <v>137</v>
+      </c>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="L17" s="85"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="42" t="s">
+        <v>84</v>
+      </c>
+      <c r="F18" s="18"/>
+      <c r="G18" s="40" t="s">
+        <v>138</v>
+      </c>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="L18" s="85"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="60" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="87" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" s="18"/>
+      <c r="G19" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="H19" s="18"/>
+      <c r="I19" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="L19" s="85"/>
+    </row>
+    <row r="20" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="41" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="62" t="s">
+        <v>90</v>
+      </c>
+      <c r="L20" s="85"/>
+    </row>
+    <row r="21" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="62" t="s">
+        <v>91</v>
+      </c>
+      <c r="L21" s="85"/>
+    </row>
+    <row r="22" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="63" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="62" t="s">
+        <v>94</v>
+      </c>
+      <c r="L22" s="85"/>
+    </row>
+    <row r="23" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="64"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="L23" s="85"/>
+    </row>
+    <row r="24" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="L24" s="85"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H25" s="84"/>
+      <c r="L25" s="85"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L26" s="85"/>
+    </row>
+    <row r="27" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L27" s="85"/>
+    </row>
+    <row r="28" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L28" s="85"/>
+    </row>
+    <row r="29" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L29" s="85"/>
+    </row>
+    <row r="30" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L30" s="85"/>
+    </row>
+    <row r="31" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L31" s="85"/>
+    </row>
+    <row r="32" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L32" s="85"/>
+    </row>
+    <row r="33" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L33" s="85"/>
+    </row>
+    <row r="34" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H34" s="84"/>
+      <c r="L34" s="85"/>
+    </row>
+    <row r="35" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L35" s="85"/>
+    </row>
+    <row r="36" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L36" s="85"/>
+    </row>
+    <row r="37" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L37" s="85"/>
+    </row>
+    <row r="38" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L38" s="85"/>
+    </row>
+    <row r="39" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L39" s="85"/>
+    </row>
+    <row r="40" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L40" s="85"/>
+    </row>
+    <row r="41" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L41" s="85"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G15:G16"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E18">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+      <formula>AND(COUNTIF($E$18:$E$18,E18)&gt;1,NOT(ISBLANK(E18)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/raw/BUS.xlsx
+++ b/raw/BUS.xlsx
@@ -13,6 +13,7 @@
     <sheet name="19" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="20" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="20 ауысым" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="21" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" name="_xlfn_AGGREGATE" vbProcedure="false"/>
@@ -422,8 +423,159 @@
 </comments>
 </file>
 
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">оқу</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>56</xdr:colOff>
+                <xdr:row>8</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">оқу</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>29</xdr:colOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E7" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">оқу</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>29</xdr:colOff>
+                <xdr:row>10</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="155">
   <si>
     <t xml:space="preserve">  17.10. 2026 ж. </t>
   </si>
@@ -843,6 +995,51 @@
   </si>
   <si>
     <t xml:space="preserve">35-337AS12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  21.10. 2026 ж. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35,2-Н2984/12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35,2-Н3025/12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-217AG12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н3196/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-213AG12  н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-857AI12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-206AG 12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2291/12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н3135/12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1-H267812 37DEA12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н1544/12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-219AG12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н3204/12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-Н2715/12 н</t>
   </si>
 </sst>
 </file>
@@ -2463,7 +2660,7 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2813,6 +3010,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4032,7 +4233,20 @@
     <cellStyle name="Финансовый 2 2" xfId="1225"/>
     <cellStyle name="Финансовый 2 3" xfId="1226"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="26">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="204"/>
+        <family val="0"/>
+        <color rgb="FF800080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
@@ -5107,6 +5321,171 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>298080</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>152640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1080000" y="5036760"/>
+          <a:ext cx="298080" cy="655560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>94320</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>30960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>392040</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>22680</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1174320" y="5067720"/>
+          <a:ext cx="297720" cy="662400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>23040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>298080</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>83880</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1080000" y="5059800"/>
+          <a:ext cx="298080" cy="563760"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>94320</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>23040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>392040</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>99000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1174320" y="5059800"/>
+          <a:ext cx="297720" cy="578880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
   <a:themeElements>
@@ -8089,4 +8468,575 @@
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:L41"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12.21"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="24.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="82" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+    </row>
+    <row r="2" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="45" t="s">
+        <v>141</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="43"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="F4" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="18"/>
+      <c r="H4" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="18"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="83" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="18"/>
+      <c r="C5" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F5" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="18"/>
+      <c r="H5" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="18"/>
+      <c r="L5" s="85"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="83"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" s="18"/>
+      <c r="E6" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="18"/>
+      <c r="H6" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="18"/>
+      <c r="L6" s="85"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="47"/>
+      <c r="C7" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="18"/>
+      <c r="E7" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="18"/>
+      <c r="L7" s="85"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="18"/>
+      <c r="C8" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="D8" s="18"/>
+      <c r="E8" s="41" t="s">
+        <v>127</v>
+      </c>
+      <c r="F8" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="41" t="s">
+        <v>68</v>
+      </c>
+      <c r="H8" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="18"/>
+      <c r="L8" s="85"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="18"/>
+      <c r="E9" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="41"/>
+      <c r="G9" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="L9" s="85"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="47"/>
+      <c r="E10" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="F10" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="L10" s="85"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="18"/>
+      <c r="C11" s="41" t="s">
+        <v>132</v>
+      </c>
+      <c r="D11" s="18"/>
+      <c r="E11" s="41" t="s">
+        <v>133</v>
+      </c>
+      <c r="F11" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="18"/>
+      <c r="I11" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="L11" s="85"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="50"/>
+      <c r="C12" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="18"/>
+      <c r="E12" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12" s="41" t="s">
+        <v>144</v>
+      </c>
+      <c r="G12" s="18"/>
+      <c r="I12" s="53" t="s">
+        <v>63</v>
+      </c>
+      <c r="L12" s="85"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="18"/>
+      <c r="C13" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" s="18"/>
+      <c r="E13" s="42" t="s">
+        <v>136</v>
+      </c>
+      <c r="F13" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="L13" s="85"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="56" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="18"/>
+      <c r="C14" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="D14" s="18"/>
+      <c r="E14" s="42" t="s">
+        <v>147</v>
+      </c>
+      <c r="F14" s="56"/>
+      <c r="G14" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="18"/>
+      <c r="I14" s="53" t="s">
+        <v>94</v>
+      </c>
+      <c r="L14" s="85"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="57"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="42" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" s="18"/>
+      <c r="E15" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="F15" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" s="59" t="s">
+        <v>150</v>
+      </c>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="L15" s="85"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="18"/>
+      <c r="C16" s="42" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16" s="18"/>
+      <c r="E16" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="F16" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="59"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="L16" s="85"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="42" t="s">
+        <v>153</v>
+      </c>
+      <c r="F17" s="57"/>
+      <c r="G17" s="52" t="s">
+        <v>137</v>
+      </c>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="L17" s="85"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="F18" s="57"/>
+      <c r="G18" s="40" t="s">
+        <v>138</v>
+      </c>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="L18" s="85"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="60" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="F19" s="57"/>
+      <c r="G19" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="H19" s="18"/>
+      <c r="I19" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="L19" s="85"/>
+    </row>
+    <row r="20" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="41" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="62" t="s">
+        <v>90</v>
+      </c>
+      <c r="L20" s="85"/>
+    </row>
+    <row r="21" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="L21" s="85"/>
+    </row>
+    <row r="22" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="63" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="L22" s="85"/>
+    </row>
+    <row r="23" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="64"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="58"/>
+      <c r="L23" s="85"/>
+    </row>
+    <row r="24" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="58"/>
+      <c r="L24" s="85"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H25" s="84"/>
+      <c r="L25" s="85"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L26" s="85"/>
+    </row>
+    <row r="27" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L27" s="85"/>
+    </row>
+    <row r="28" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L28" s="85"/>
+    </row>
+    <row r="29" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L29" s="85"/>
+    </row>
+    <row r="30" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L30" s="85"/>
+    </row>
+    <row r="31" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L31" s="85"/>
+    </row>
+    <row r="32" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L32" s="85"/>
+    </row>
+    <row r="33" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L33" s="85"/>
+    </row>
+    <row r="34" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H34" s="84"/>
+      <c r="L34" s="85"/>
+    </row>
+    <row r="35" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L35" s="85"/>
+    </row>
+    <row r="36" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L36" s="85"/>
+    </row>
+    <row r="37" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L37" s="85"/>
+    </row>
+    <row r="38" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L38" s="85"/>
+    </row>
+    <row r="39" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L39" s="85"/>
+    </row>
+    <row r="40" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L40" s="85"/>
+    </row>
+    <row r="41" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L41" s="85"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G15:G16"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A11">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="25">
+      <formula>AND(COUNTIF($A$11:$A$11,A11)&gt;1,NOT(ISBLANK(A11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
 </file>
--- a/raw/BUS.xlsx
+++ b/raw/BUS.xlsx
@@ -14,6 +14,7 @@
     <sheet name="20" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="20 ауысым" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="21" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="22" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" name="_xlfn_AGGREGATE" vbProcedure="false"/>
@@ -574,8 +575,159 @@
 </comments>
 </file>
 
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">оқу</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>56</xdr:colOff>
+                <xdr:row>8</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">оқу</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>29</xdr:colOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E7" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">оқу</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>29</xdr:colOff>
+                <xdr:row>10</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="156">
   <si>
     <t xml:space="preserve">  17.10. 2026 ж. </t>
   </si>
@@ -1040,6 +1192,9 @@
   </si>
   <si>
     <t xml:space="preserve">35-Н2715/12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  22.10. 2026 ж. </t>
   </si>
 </sst>
 </file>
@@ -4233,7 +4388,20 @@
     <cellStyle name="Финансовый 2 2" xfId="1225"/>
     <cellStyle name="Финансовый 2 3" xfId="1226"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="27">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="204"/>
+        <family val="0"/>
+        <color rgb="FF800080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
@@ -5486,6 +5654,171 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>298080</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>152640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1080000" y="5036760"/>
+          <a:ext cx="298080" cy="655560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>94320</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>30960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>392040</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>22680</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1174320" y="5067720"/>
+          <a:ext cx="297720" cy="662400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>23040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>298080</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>83880</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1080000" y="5059800"/>
+          <a:ext cx="298080" cy="563760"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>94320</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>23040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>392040</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>99000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1174320" y="5059800"/>
+          <a:ext cx="297720" cy="578880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
   <a:themeElements>
@@ -9039,4 +9372,573 @@
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:L41"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12.21"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="24.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="82" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+    </row>
+    <row r="2" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="45" t="s">
+        <v>141</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="43"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="F4" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="18"/>
+      <c r="H4" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="18"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="83" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="18"/>
+      <c r="C5" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F5" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="18"/>
+      <c r="H5" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="18"/>
+      <c r="L5" s="85"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="83"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" s="18"/>
+      <c r="E6" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="18"/>
+      <c r="H6" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="18"/>
+      <c r="L6" s="85"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="47"/>
+      <c r="C7" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="18"/>
+      <c r="E7" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="18"/>
+      <c r="L7" s="85"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="18"/>
+      <c r="C8" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="D8" s="18"/>
+      <c r="E8" s="41" t="s">
+        <v>127</v>
+      </c>
+      <c r="F8" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="G8" s="41" t="s">
+        <v>68</v>
+      </c>
+      <c r="H8" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="18"/>
+      <c r="L8" s="85"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="18"/>
+      <c r="E9" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="41"/>
+      <c r="G9" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="L9" s="85"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="47"/>
+      <c r="E10" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="F10" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="L10" s="85"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="18"/>
+      <c r="C11" s="41" t="s">
+        <v>132</v>
+      </c>
+      <c r="D11" s="18"/>
+      <c r="E11" s="41" t="s">
+        <v>133</v>
+      </c>
+      <c r="F11" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="18"/>
+      <c r="I11" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="L11" s="85"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="50"/>
+      <c r="C12" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="18"/>
+      <c r="E12" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12" s="41" t="s">
+        <v>144</v>
+      </c>
+      <c r="G12" s="18"/>
+      <c r="I12" s="53" t="s">
+        <v>63</v>
+      </c>
+      <c r="L12" s="85"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="18"/>
+      <c r="C13" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" s="18"/>
+      <c r="E13" s="42" t="s">
+        <v>136</v>
+      </c>
+      <c r="F13" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="L13" s="85"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="56" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="18"/>
+      <c r="C14" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="D14" s="18"/>
+      <c r="E14" s="42" t="s">
+        <v>147</v>
+      </c>
+      <c r="F14" s="56"/>
+      <c r="G14" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="18"/>
+      <c r="L14" s="85"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="57"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="42" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" s="18"/>
+      <c r="E15" s="42" t="s">
+        <v>149</v>
+      </c>
+      <c r="F15" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" s="59" t="s">
+        <v>150</v>
+      </c>
+      <c r="H15" s="18"/>
+      <c r="L15" s="85"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="18"/>
+      <c r="C16" s="42" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16" s="18"/>
+      <c r="E16" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="F16" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="59"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="L16" s="85"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="42" t="s">
+        <v>153</v>
+      </c>
+      <c r="F17" s="57"/>
+      <c r="G17" s="52" t="s">
+        <v>137</v>
+      </c>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="L17" s="85"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="F18" s="57"/>
+      <c r="G18" s="40" t="s">
+        <v>138</v>
+      </c>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="L18" s="85"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="60" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="F19" s="57"/>
+      <c r="G19" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="H19" s="18"/>
+      <c r="I19" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="L19" s="85"/>
+    </row>
+    <row r="20" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="41" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="62" t="s">
+        <v>90</v>
+      </c>
+      <c r="L20" s="85"/>
+    </row>
+    <row r="21" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="L21" s="85"/>
+    </row>
+    <row r="22" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="63" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="L22" s="85"/>
+    </row>
+    <row r="23" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="64"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="77" t="s">
+        <v>43</v>
+      </c>
+      <c r="L23" s="85"/>
+    </row>
+    <row r="24" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="58"/>
+      <c r="L24" s="85"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H25" s="84"/>
+      <c r="L25" s="85"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L26" s="85"/>
+    </row>
+    <row r="27" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L27" s="85"/>
+    </row>
+    <row r="28" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L28" s="85"/>
+    </row>
+    <row r="29" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L29" s="85"/>
+    </row>
+    <row r="30" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L30" s="85"/>
+    </row>
+    <row r="31" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L31" s="85"/>
+    </row>
+    <row r="32" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L32" s="85"/>
+    </row>
+    <row r="33" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L33" s="85"/>
+    </row>
+    <row r="34" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H34" s="84"/>
+      <c r="L34" s="85"/>
+    </row>
+    <row r="35" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L35" s="85"/>
+    </row>
+    <row r="36" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L36" s="85"/>
+    </row>
+    <row r="37" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L37" s="85"/>
+    </row>
+    <row r="38" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L38" s="85"/>
+    </row>
+    <row r="39" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L39" s="85"/>
+    </row>
+    <row r="40" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L40" s="85"/>
+    </row>
+    <row r="41" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L41" s="85"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G15:G16"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A11">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="26">
+      <formula>AND(COUNTIF($A$11:$A$11,A11)&gt;1,NOT(ISBLANK(A11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
 </file>
--- a/raw/BUS.xlsx
+++ b/raw/BUS.xlsx
@@ -15,6 +15,7 @@
     <sheet name="20 ауысым" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="21" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="22" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="23" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" name="_xlfn_AGGREGATE" vbProcedure="false"/>
@@ -726,8 +727,159 @@
 </comments>
 </file>
 
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="E5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">оқу</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>29</xdr:colOff>
+                <xdr:row>8</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">оқу</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>29</xdr:colOff>
+                <xdr:row>11</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">оқу</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>8</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>29</xdr:colOff>
+                <xdr:row>13</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="160">
   <si>
     <t xml:space="preserve">  17.10. 2026 ж. </t>
   </si>
@@ -1195,6 +1347,18 @@
   </si>
   <si>
     <t xml:space="preserve">  22.10. 2026 ж. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  23.10. 2026 ж. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-149AG12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-341AS12 н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-Н0592/12 </t>
   </si>
 </sst>
 </file>
@@ -4388,7 +4552,20 @@
     <cellStyle name="Финансовый 2 2" xfId="1225"/>
     <cellStyle name="Финансовый 2 3" xfId="1226"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="28">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="204"/>
+        <family val="0"/>
+        <color rgb="FF800080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
@@ -5819,6 +5996,171 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>298080</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>152640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1080000" y="5036760"/>
+          <a:ext cx="298080" cy="655560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>94320</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>30960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>392040</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>22680</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1174320" y="5067720"/>
+          <a:ext cx="297720" cy="662400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>23040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>298080</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>83880</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1080000" y="5059800"/>
+          <a:ext cx="298080" cy="563760"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>94320</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>23040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>392040</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>99000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1174320" y="5059800"/>
+          <a:ext cx="297720" cy="578880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
   <a:themeElements>
@@ -9941,4 +10283,572 @@
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:L41"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12.21"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="24.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="82" t="s">
+        <v>156</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+    </row>
+    <row r="2" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="45" t="s">
+        <v>141</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="88" t="s">
+        <v>157</v>
+      </c>
+      <c r="I3" s="43"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="F4" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="18"/>
+      <c r="H4" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="18"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="83" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="18"/>
+      <c r="C5" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F5" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="18"/>
+      <c r="H5" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="18"/>
+      <c r="L5" s="85"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="83"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" s="18"/>
+      <c r="E6" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="18"/>
+      <c r="H6" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="18"/>
+      <c r="L6" s="85"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="47"/>
+      <c r="C7" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="18"/>
+      <c r="E7" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="18"/>
+      <c r="L7" s="85"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="18"/>
+      <c r="C8" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="D8" s="18"/>
+      <c r="E8" s="41" t="s">
+        <v>127</v>
+      </c>
+      <c r="F8" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="G8" s="41" t="s">
+        <v>68</v>
+      </c>
+      <c r="H8" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="18"/>
+      <c r="L8" s="85"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="18"/>
+      <c r="E9" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="41"/>
+      <c r="G9" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="L9" s="85"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="41" t="s">
+        <v>132</v>
+      </c>
+      <c r="D10" s="47"/>
+      <c r="E10" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="F10" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="L10" s="85"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="18"/>
+      <c r="C11" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="18"/>
+      <c r="E11" s="41" t="s">
+        <v>133</v>
+      </c>
+      <c r="F11" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="18"/>
+      <c r="I11" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="L11" s="85"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="50"/>
+      <c r="C12" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="D12" s="18"/>
+      <c r="E12" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="41" t="s">
+        <v>144</v>
+      </c>
+      <c r="G12" s="18"/>
+      <c r="I12" s="53" t="s">
+        <v>63</v>
+      </c>
+      <c r="L12" s="85"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="18"/>
+      <c r="C13" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="D13" s="18"/>
+      <c r="E13" s="42" t="s">
+        <v>136</v>
+      </c>
+      <c r="F13" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="L13" s="85"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="56" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="18"/>
+      <c r="C14" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="D14" s="18"/>
+      <c r="E14" s="42" t="s">
+        <v>147</v>
+      </c>
+      <c r="F14" s="56"/>
+      <c r="G14" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="18"/>
+      <c r="L14" s="85"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="57"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="42" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" s="18"/>
+      <c r="E15" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="F15" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" s="59" t="s">
+        <v>150</v>
+      </c>
+      <c r="H15" s="18"/>
+      <c r="L15" s="85"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="18"/>
+      <c r="C16" s="42" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16" s="18"/>
+      <c r="E16" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="F16" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="G16" s="59"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="L16" s="85"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="42" t="s">
+        <v>153</v>
+      </c>
+      <c r="F17" s="57"/>
+      <c r="G17" s="52" t="s">
+        <v>137</v>
+      </c>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="L17" s="85"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="F18" s="57"/>
+      <c r="G18" s="40" t="s">
+        <v>138</v>
+      </c>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="L18" s="85"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="60" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="F19" s="57"/>
+      <c r="G19" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="H19" s="18"/>
+      <c r="I19" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="L19" s="85"/>
+    </row>
+    <row r="20" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="41" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="62" t="s">
+        <v>90</v>
+      </c>
+      <c r="L20" s="85"/>
+    </row>
+    <row r="21" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="L21" s="85"/>
+    </row>
+    <row r="22" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="63" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="L22" s="85"/>
+    </row>
+    <row r="23" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="64"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="62" t="s">
+        <v>43</v>
+      </c>
+      <c r="L23" s="85"/>
+    </row>
+    <row r="24" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="58"/>
+      <c r="L24" s="85"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H25" s="84"/>
+      <c r="L25" s="85"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L26" s="85"/>
+    </row>
+    <row r="27" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L27" s="85"/>
+    </row>
+    <row r="28" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L28" s="85"/>
+    </row>
+    <row r="29" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L29" s="85"/>
+    </row>
+    <row r="30" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L30" s="85"/>
+    </row>
+    <row r="31" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L31" s="85"/>
+    </row>
+    <row r="32" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L32" s="85"/>
+    </row>
+    <row r="33" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L33" s="85"/>
+    </row>
+    <row r="34" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H34" s="84"/>
+      <c r="L34" s="85"/>
+    </row>
+    <row r="35" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L35" s="85"/>
+    </row>
+    <row r="36" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L36" s="85"/>
+    </row>
+    <row r="37" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L37" s="85"/>
+    </row>
+    <row r="38" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L38" s="85"/>
+    </row>
+    <row r="39" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L39" s="85"/>
+    </row>
+    <row r="40" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L40" s="85"/>
+    </row>
+    <row r="41" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L41" s="85"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G15:G16"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A11">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="27">
+      <formula>AND(COUNTIF($A$11:$A$11,A11)&gt;1,NOT(ISBLANK(A11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
 </file>
--- a/raw/BUS.xlsx
+++ b/raw/BUS.xlsx
@@ -10843,7 +10843,7 @@
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/raw/BUS.xlsx
+++ b/raw/BUS.xlsx
@@ -16,6 +16,7 @@
     <sheet name="21" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="22" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="23" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="24" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" name="_xlfn_AGGREGATE" vbProcedure="false"/>
@@ -878,8 +879,159 @@
 </comments>
 </file>
 
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="E5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">оқу</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>3</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>29</xdr:colOff>
+                <xdr:row>8</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">оқу</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>6</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>29</xdr:colOff>
+                <xdr:row>11</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">оқу</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>8</xdr:row>
+                <xdr:rowOff>10</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>29</xdr:colOff>
+                <xdr:row>13</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="161">
   <si>
     <t xml:space="preserve">  17.10. 2026 ж. </t>
   </si>
@@ -1359,6 +1511,9 @@
   </si>
   <si>
     <t xml:space="preserve">20-Н0592/12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  24.10. 2026 ж. </t>
   </si>
 </sst>
 </file>
@@ -4552,7 +4707,20 @@
     <cellStyle name="Финансовый 2 2" xfId="1225"/>
     <cellStyle name="Финансовый 2 3" xfId="1226"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="29">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="204"/>
+        <family val="0"/>
+        <color rgb="FF800080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
@@ -6161,6 +6329,171 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>298080</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>152640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1080000" y="5036760"/>
+          <a:ext cx="298080" cy="655560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>94320</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>30960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>392040</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>22680</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1174320" y="5067720"/>
+          <a:ext cx="297720" cy="662400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>23040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>298080</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>83880</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1080000" y="5059800"/>
+          <a:ext cx="298080" cy="563760"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>94320</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>23040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>392040</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>99000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1174320" y="5059800"/>
+          <a:ext cx="297720" cy="578880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
   <a:themeElements>
@@ -10609,6 +10942,9 @@
         <v>71</v>
       </c>
       <c r="H14" s="18"/>
+      <c r="I14" s="77" t="s">
+        <v>90</v>
+      </c>
       <c r="L14" s="85"/>
     </row>
     <row r="15" customFormat="false" ht="13.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10715,7 +11051,7 @@
       <c r="G20" s="41"/>
       <c r="H20" s="41"/>
       <c r="I20" s="62" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="L20" s="85"/>
     </row>
@@ -10729,7 +11065,7 @@
       <c r="G21" s="18"/>
       <c r="H21" s="18"/>
       <c r="I21" s="62" t="s">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="L21" s="85"/>
     </row>
@@ -10745,7 +11081,7 @@
       <c r="G22" s="18"/>
       <c r="H22" s="18"/>
       <c r="I22" s="62" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L22" s="85"/>
     </row>
@@ -10760,9 +11096,6 @@
       <c r="F23" s="18"/>
       <c r="G23" s="65"/>
       <c r="H23" s="18"/>
-      <c r="I23" s="62" t="s">
-        <v>43</v>
-      </c>
       <c r="L23" s="85"/>
     </row>
     <row r="24" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10843,7 +11176,574 @@
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:L41"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12.21"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="24.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="82" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+    </row>
+    <row r="2" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="45" t="s">
+        <v>141</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="88" t="s">
+        <v>157</v>
+      </c>
+      <c r="I3" s="43"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="F4" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="18"/>
+      <c r="H4" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="18"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="83" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="18"/>
+      <c r="C5" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F5" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="18"/>
+      <c r="H5" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="18"/>
+      <c r="L5" s="85"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="83"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" s="18"/>
+      <c r="E6" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="18"/>
+      <c r="H6" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="18"/>
+      <c r="L6" s="85"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="47"/>
+      <c r="C7" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="18"/>
+      <c r="E7" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="18"/>
+      <c r="L7" s="85"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="18"/>
+      <c r="C8" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="D8" s="18"/>
+      <c r="E8" s="41" t="s">
+        <v>127</v>
+      </c>
+      <c r="F8" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="18"/>
+      <c r="L8" s="85"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="18"/>
+      <c r="E9" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="41"/>
+      <c r="G9" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="L9" s="85"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="41" t="s">
+        <v>132</v>
+      </c>
+      <c r="D10" s="47"/>
+      <c r="E10" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="F10" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="L10" s="85"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="18"/>
+      <c r="C11" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="18"/>
+      <c r="E11" s="41" t="s">
+        <v>133</v>
+      </c>
+      <c r="F11" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="18"/>
+      <c r="I11" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="L11" s="85"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="50"/>
+      <c r="C12" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="D12" s="18"/>
+      <c r="E12" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="41" t="s">
+        <v>144</v>
+      </c>
+      <c r="G12" s="18"/>
+      <c r="I12" s="53" t="s">
+        <v>63</v>
+      </c>
+      <c r="L12" s="85"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="18"/>
+      <c r="C13" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="D13" s="18"/>
+      <c r="E13" s="42" t="s">
+        <v>136</v>
+      </c>
+      <c r="F13" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="L13" s="85"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="56" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="18"/>
+      <c r="C14" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="D14" s="18"/>
+      <c r="E14" s="42" t="s">
+        <v>147</v>
+      </c>
+      <c r="F14" s="56"/>
+      <c r="G14" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="18"/>
+      <c r="I14" s="53" t="s">
+        <v>90</v>
+      </c>
+      <c r="L14" s="85"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="57"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="42" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" s="18"/>
+      <c r="E15" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="F15" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" s="59" t="s">
+        <v>150</v>
+      </c>
+      <c r="H15" s="18"/>
+      <c r="I15" s="77" t="s">
+        <v>68</v>
+      </c>
+      <c r="L15" s="85"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="18"/>
+      <c r="C16" s="42" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16" s="18"/>
+      <c r="E16" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="F16" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="G16" s="59"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="77" t="s">
+        <v>94</v>
+      </c>
+      <c r="L16" s="85"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="42" t="s">
+        <v>153</v>
+      </c>
+      <c r="F17" s="57"/>
+      <c r="G17" s="52" t="s">
+        <v>137</v>
+      </c>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="L17" s="85"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="F18" s="57"/>
+      <c r="G18" s="40" t="s">
+        <v>138</v>
+      </c>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="L18" s="85"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="60" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="F19" s="57"/>
+      <c r="G19" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="H19" s="18"/>
+      <c r="I19" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="L19" s="85"/>
+    </row>
+    <row r="20" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="41" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="L20" s="85"/>
+    </row>
+    <row r="21" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="L21" s="85"/>
+    </row>
+    <row r="22" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="63" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="L22" s="85"/>
+    </row>
+    <row r="23" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="64"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="18"/>
+      <c r="L23" s="85"/>
+    </row>
+    <row r="24" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="58"/>
+      <c r="L24" s="85"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H25" s="84"/>
+      <c r="L25" s="85"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L26" s="85"/>
+    </row>
+    <row r="27" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L27" s="85"/>
+    </row>
+    <row r="28" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L28" s="85"/>
+    </row>
+    <row r="29" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L29" s="85"/>
+    </row>
+    <row r="30" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L30" s="85"/>
+    </row>
+    <row r="31" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L31" s="85"/>
+    </row>
+    <row r="32" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L32" s="85"/>
+    </row>
+    <row r="33" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L33" s="85"/>
+    </row>
+    <row r="34" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H34" s="84"/>
+      <c r="L34" s="85"/>
+    </row>
+    <row r="35" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L35" s="85"/>
+    </row>
+    <row r="36" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L36" s="85"/>
+    </row>
+    <row r="37" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L37" s="85"/>
+    </row>
+    <row r="38" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L38" s="85"/>
+    </row>
+    <row r="39" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L39" s="85"/>
+    </row>
+    <row r="40" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L40" s="85"/>
+    </row>
+    <row r="41" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L41" s="85"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G15:G16"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A11">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="28">
+      <formula>AND(COUNTIF($A$11:$A$11,A11)&gt;1,NOT(ISBLANK(A11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/raw/BUS.xlsx
+++ b/raw/BUS.xlsx
@@ -17,6 +17,7 @@
     <sheet name="22" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="23" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="24" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="25" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" name="_xlfn_AGGREGATE" vbProcedure="false"/>
@@ -44,8 +45,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
 </t>
@@ -55,8 +56,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">оқу</t>
         </r>
@@ -91,8 +92,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
 </t>
@@ -102,8 +103,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">оқу</t>
         </r>
@@ -138,8 +139,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
 </t>
@@ -149,8 +150,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">оқу</t>
         </r>
@@ -185,8 +186,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
 </t>
@@ -196,8 +197,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">оқу</t>
         </r>
@@ -242,8 +243,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
 </t>
@@ -253,8 +254,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">оқу</t>
         </r>
@@ -289,8 +290,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
 </t>
@@ -300,8 +301,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">оқу</t>
         </r>
@@ -336,8 +337,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
 </t>
@@ -347,8 +348,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">оқу</t>
         </r>
@@ -383,8 +384,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
 </t>
@@ -394,8 +395,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">оқу</t>
         </r>
@@ -440,8 +441,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
 </t>
@@ -451,8 +452,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">оқу</t>
         </r>
@@ -487,8 +488,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
 </t>
@@ -498,8 +499,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">оқу</t>
         </r>
@@ -534,8 +535,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
 </t>
@@ -545,8 +546,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">оқу</t>
         </r>
@@ -591,8 +592,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
 </t>
@@ -602,8 +603,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">оқу</t>
         </r>
@@ -638,8 +639,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
 </t>
@@ -649,8 +650,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">оқу</t>
         </r>
@@ -685,8 +686,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
 </t>
@@ -696,8 +697,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">оқу</t>
         </r>
@@ -742,8 +743,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
 </t>
@@ -753,8 +754,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">оқу</t>
         </r>
@@ -789,8 +790,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
 </t>
@@ -800,8 +801,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">оқу</t>
         </r>
@@ -836,8 +837,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
 </t>
@@ -847,8 +848,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">оқу</t>
         </r>
@@ -893,8 +894,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
 </t>
@@ -904,8 +905,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">оқу</t>
         </r>
@@ -940,8 +941,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
 </t>
@@ -951,8 +952,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">оқу</t>
         </r>
@@ -987,8 +988,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">Бекмагамбетов Уалихан Мухтарович:
 </t>
@@ -998,8 +999,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">оқу</t>
         </r>
@@ -1031,7 +1032,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="162">
   <si>
     <t xml:space="preserve">  17.10. 2026 ж. </t>
   </si>
@@ -1514,6 +1515,9 @@
   </si>
   <si>
     <t xml:space="preserve">  24.10. 2026 ж. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  25.10. 2026 ж. </t>
   </si>
 </sst>
 </file>
@@ -1716,15 +1720,15 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b val="true"/>
@@ -4707,7 +4711,20 @@
     <cellStyle name="Финансовый 2 2" xfId="1225"/>
     <cellStyle name="Финансовый 2 3" xfId="1226"/>
   </cellStyles>
-  <dxfs count="29">
+  <dxfs count="30">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="204"/>
+        <family val="0"/>
+        <color rgb="FF800080"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF99CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
@@ -5153,6 +5170,171 @@
         <a:xfrm>
           <a:off x="1887120" y="5764680"/>
           <a:ext cx="299520" cy="578880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>298080</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>152640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1080000" y="5036760"/>
+          <a:ext cx="298080" cy="655560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>94320</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>30960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>392040</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>22680</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1174320" y="5067720"/>
+          <a:ext cx="297720" cy="662400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>23040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>298080</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>83880</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1080000" y="5059800"/>
+          <a:ext cx="298080" cy="563760"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>94320</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>23040</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>392040</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>99000</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1174320" y="5059800"/>
+          <a:ext cx="297720" cy="578880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7118,6 +7300,574 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:L41"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="13.2" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12.21"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="24.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="82" t="s">
+        <v>161</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+    </row>
+    <row r="2" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="45" t="s">
+        <v>141</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="88" t="s">
+        <v>157</v>
+      </c>
+      <c r="I3" s="43"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="F4" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="18"/>
+      <c r="H4" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="18"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="83" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="18"/>
+      <c r="C5" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="F5" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="18"/>
+      <c r="H5" s="40" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="18"/>
+      <c r="L5" s="85"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="83"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" s="18"/>
+      <c r="E6" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="18"/>
+      <c r="H6" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="18"/>
+      <c r="L6" s="85"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="47"/>
+      <c r="C7" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="18"/>
+      <c r="E7" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="F7" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="18"/>
+      <c r="L7" s="85"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="18"/>
+      <c r="C8" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="D8" s="18"/>
+      <c r="E8" s="41" t="s">
+        <v>127</v>
+      </c>
+      <c r="F8" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="18"/>
+      <c r="L8" s="85"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="18"/>
+      <c r="C9" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="18"/>
+      <c r="E9" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="41"/>
+      <c r="G9" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="41" t="s">
+        <v>68</v>
+      </c>
+      <c r="I9" s="18"/>
+      <c r="L9" s="85"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="41" t="s">
+        <v>132</v>
+      </c>
+      <c r="D10" s="47"/>
+      <c r="E10" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="F10" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="L10" s="85"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="18"/>
+      <c r="C11" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="18"/>
+      <c r="E11" s="41" t="s">
+        <v>133</v>
+      </c>
+      <c r="F11" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="18"/>
+      <c r="I11" s="51" t="s">
+        <v>58</v>
+      </c>
+      <c r="L11" s="85"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="50"/>
+      <c r="C12" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="D12" s="18"/>
+      <c r="E12" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="41" t="s">
+        <v>144</v>
+      </c>
+      <c r="G12" s="18"/>
+      <c r="I12" s="53" t="s">
+        <v>63</v>
+      </c>
+      <c r="L12" s="85"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="18"/>
+      <c r="C13" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="D13" s="18"/>
+      <c r="E13" s="42" t="s">
+        <v>136</v>
+      </c>
+      <c r="F13" s="88" t="s">
+        <v>145</v>
+      </c>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="L13" s="85"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="56" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="18"/>
+      <c r="C14" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="D14" s="18"/>
+      <c r="E14" s="42" t="s">
+        <v>147</v>
+      </c>
+      <c r="F14" s="56"/>
+      <c r="G14" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="18"/>
+      <c r="I14" s="53" t="s">
+        <v>90</v>
+      </c>
+      <c r="L14" s="85"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="57"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="42" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" s="18"/>
+      <c r="E15" s="42" t="s">
+        <v>158</v>
+      </c>
+      <c r="F15" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" s="59" t="s">
+        <v>150</v>
+      </c>
+      <c r="H15" s="18"/>
+      <c r="I15" s="53" t="s">
+        <v>94</v>
+      </c>
+      <c r="L15" s="85"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="18"/>
+      <c r="C16" s="42" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16" s="18"/>
+      <c r="E16" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="F16" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="G16" s="59"/>
+      <c r="H16" s="18"/>
+      <c r="L16" s="85"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="42" t="s">
+        <v>153</v>
+      </c>
+      <c r="F17" s="57"/>
+      <c r="G17" s="52" t="s">
+        <v>137</v>
+      </c>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="L17" s="85"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="F18" s="57"/>
+      <c r="G18" s="40" t="s">
+        <v>138</v>
+      </c>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="L18" s="85"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="60" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="F19" s="57"/>
+      <c r="G19" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="H19" s="18"/>
+      <c r="I19" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="L19" s="85"/>
+    </row>
+    <row r="20" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="41" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="L20" s="85"/>
+    </row>
+    <row r="21" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="58"/>
+      <c r="L21" s="85"/>
+    </row>
+    <row r="22" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="63" t="s">
+        <v>93</v>
+      </c>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="58"/>
+      <c r="L22" s="85"/>
+    </row>
+    <row r="23" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="64"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="58"/>
+      <c r="L23" s="85"/>
+    </row>
+    <row r="24" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18"/>
+      <c r="B24" s="66"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="58"/>
+      <c r="L24" s="85"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H25" s="84"/>
+      <c r="L25" s="85"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L26" s="85"/>
+    </row>
+    <row r="27" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L27" s="85"/>
+    </row>
+    <row r="28" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L28" s="85"/>
+    </row>
+    <row r="29" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L29" s="85"/>
+    </row>
+    <row r="30" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L30" s="85"/>
+    </row>
+    <row r="31" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L31" s="85"/>
+    </row>
+    <row r="32" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L32" s="85"/>
+    </row>
+    <row r="33" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L33" s="85"/>
+    </row>
+    <row r="34" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H34" s="84"/>
+      <c r="L34" s="85"/>
+    </row>
+    <row r="35" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L35" s="85"/>
+    </row>
+    <row r="36" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L36" s="85"/>
+    </row>
+    <row r="37" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L37" s="85"/>
+    </row>
+    <row r="38" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L38" s="85"/>
+    </row>
+    <row r="39" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L39" s="85"/>
+    </row>
+    <row r="40" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L40" s="85"/>
+    </row>
+    <row r="41" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L41" s="85"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="G15:G16"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A11">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="29">
+      <formula>AND(COUNTIF($A$11:$A$11,A11)&gt;1,NOT(ISBLANK(A11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">

--- a/raw/BUS.xlsx
+++ b/raw/BUS.xlsx
@@ -11,6 +11,7 @@
     <sheet name="ацн" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="bas" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="25" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="26" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -419,8 +420,241 @@
 </comments>
 </file>
 
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">20
+ kbm-13
+tms -  8
+dtt - 6/1</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>25</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>30</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A29" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">35--8/9</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>27</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>32</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A30" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">35-   15/6
+</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>28</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>33</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A31" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">35.1- 1/1
+</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>29</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>34</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A32" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve"> 35.2-  2/2
+</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>30</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>35</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="H16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">с вод
+</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>14</xdr:row>
+                <xdr:rowOff>17</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>10</xdr:col>
+                <xdr:colOff>43</xdr:colOff>
+                <xdr:row>17</xdr:row>
+                <xdr:rowOff>22</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="177">
   <si>
     <t xml:space="preserve">35.1-2673</t>
   </si>
@@ -935,10 +1169,22 @@
     <t xml:space="preserve">-</t>
   </si>
   <si>
+    <t xml:space="preserve"> сводка выхода  26  октября 2026 года </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-3569 d/n</t>
+  </si>
+  <si>
     <t xml:space="preserve">tms 7/8</t>
   </si>
   <si>
     <t xml:space="preserve">kbm 17/6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1-1/1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2-2/2</t>
   </si>
 </sst>
 </file>
@@ -955,7 +1201,7 @@
     <numFmt numFmtId="170" formatCode="[$-409]m/d/yyyy"/>
     <numFmt numFmtId="171" formatCode="[$-409]d\-mmm"/>
   </numFmts>
-  <fonts count="50">
+  <fonts count="52">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1315,6 +1561,22 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFF00FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF993300"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -2679,7 +2941,7 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="93">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3037,6 +3299,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="171" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4304,6 +4578,51 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>23400</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>48240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>321840</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>151200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1" name="AutoShape 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="883800" y="5872320"/>
+          <a:ext cx="298440" cy="2055240"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
   <a:themeElements>
@@ -5775,20 +6094,477 @@
       <c r="D28" s="88"/>
     </row>
     <row r="29" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="89" t="s">
-        <v>171</v>
-      </c>
+      <c r="A29" s="89"/>
     </row>
     <row r="30" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="80" t="s">
-        <v>172</v>
-      </c>
+      <c r="A30" s="80"/>
     </row>
     <row r="31" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="89"/>
     </row>
     <row r="32" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="80"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:R32"/>
+  <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="12.55" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="60" width="12.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="60" width="12.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="60" width="14.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="60" width="12.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="60" width="17.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="60" width="15.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="60" width="13.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="60" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="60" width="14.55"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="10" min="10" style="60" width="9.1"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="11" style="60" width="9.1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="62" customFormat="true" ht="26.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="61" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="L1" s="63" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="23.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="64" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="64" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" s="64" t="s">
+        <v>151</v>
+      </c>
+      <c r="D2" s="64" t="s">
+        <v>152</v>
+      </c>
+      <c r="E2" s="64" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2" s="64" t="s">
+        <v>153</v>
+      </c>
+      <c r="G2" s="64" t="s">
+        <v>58</v>
+      </c>
+      <c r="H2" s="65" t="s">
+        <v>142</v>
+      </c>
+      <c r="I2" s="66"/>
+      <c r="L2" s="63" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="67" t="s">
+        <v>154</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="I3" s="68"/>
+    </row>
+    <row r="4" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="69" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="70" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="E4" s="67" t="s">
+        <v>155</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="H4" s="69" t="s">
+        <v>139</v>
+      </c>
+      <c r="I4" s="68"/>
+    </row>
+    <row r="5" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="70" t="s">
+        <v>156</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G5" s="65" t="s">
+        <v>71</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="I5" s="71"/>
+    </row>
+    <row r="6" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="70" t="s">
+        <v>157</v>
+      </c>
+      <c r="F6" s="69" t="s">
+        <v>120</v>
+      </c>
+      <c r="G6" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="I6" s="71"/>
+    </row>
+    <row r="7" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="70" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="H7" s="69" t="s">
+        <v>131</v>
+      </c>
+      <c r="I7" s="68"/>
+    </row>
+    <row r="8" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="72" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="H8" s="69" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="90" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="70" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="74"/>
+      <c r="H9" s="75" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="73" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="70" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="76" t="s">
+        <v>158</v>
+      </c>
+      <c r="G10" s="65"/>
+    </row>
+    <row r="11" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="72" t="s">
+        <v>159</v>
+      </c>
+      <c r="E11" s="91" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="69" t="s">
+        <v>116</v>
+      </c>
+      <c r="H11" s="77"/>
+    </row>
+    <row r="12" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="75" t="s">
+        <v>172</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="77"/>
+      <c r="H12" s="69"/>
+    </row>
+    <row r="13" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="65" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="75" t="s">
+        <v>41</v>
+      </c>
+      <c r="H13" s="69"/>
+    </row>
+    <row r="14" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="75" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="75" t="s">
+        <v>160</v>
+      </c>
+      <c r="E14" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="78" t="s">
+        <v>161</v>
+      </c>
+      <c r="I14" s="79" t="s">
+        <v>162</v>
+      </c>
+      <c r="L14" s="60" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="64" t="s">
+        <v>164</v>
+      </c>
+      <c r="C15" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="75" t="s">
+        <v>165</v>
+      </c>
+      <c r="E15" s="75" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="80" t="s">
+        <v>52</v>
+      </c>
+      <c r="I15" s="81" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" s="67" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="67" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H16" s="92" t="s">
+        <v>5</v>
+      </c>
+      <c r="I16" s="81" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E17" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="69" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17" s="80" t="s">
+        <v>167</v>
+      </c>
+      <c r="I17" s="81" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E18" s="67" t="s">
+        <v>36</v>
+      </c>
+      <c r="H18" s="80"/>
+      <c r="I18" s="92" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H19" s="80"/>
+    </row>
+    <row r="20" s="82" customFormat="true" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H20" s="80"/>
+      <c r="J20" s="83"/>
+      <c r="K20" s="60"/>
+      <c r="L20" s="60"/>
+      <c r="M20" s="60"/>
+      <c r="N20" s="60"/>
+    </row>
+    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="82"/>
+      <c r="G21" s="84"/>
+      <c r="H21" s="80"/>
+      <c r="I21" s="81"/>
+      <c r="J21" s="85" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="86"/>
+      <c r="G22" s="86"/>
+      <c r="H22" s="80"/>
+      <c r="I22" s="81"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="81"/>
+      <c r="R23" s="87"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="81"/>
+      <c r="L24" s="60" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I25" s="81"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="3"/>
+      <c r="I26" s="81"/>
+    </row>
+    <row r="28" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D28" s="88"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="89" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="89" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="89" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="80" t="s">
+        <v>176</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/raw/BUS.xlsx
+++ b/raw/BUS.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -12,6 +12,7 @@
     <sheet name="bas" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="25" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="26" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="27" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -653,8 +654,204 @@
 </comments>
 </file>
 
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">20
+ kbm-13
+tms -  8
+dtt - 6/1</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>25</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>30</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A29" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">35--8/9</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>27</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>32</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A30" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">35-   15/6
+</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>28</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>33</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A31" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">35.1- 1/1
+</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>29</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>34</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A32" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve"> 35.2-  2/2
+</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>30</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>35</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="181">
   <si>
     <t xml:space="preserve">35.1-2673</t>
   </si>
@@ -1185,6 +1382,18 @@
   </si>
   <si>
     <t xml:space="preserve">35.2-2/2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> сводка выхода  27  октября 2026 года </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2-2984 d/n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tms 6/8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kbm 19/6</t>
   </si>
 </sst>
 </file>
@@ -1201,7 +1410,7 @@
     <numFmt numFmtId="170" formatCode="[$-409]m/d/yyyy"/>
     <numFmt numFmtId="171" formatCode="[$-409]d\-mmm"/>
   </numFmts>
-  <fonts count="52">
+  <fonts count="53">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1577,6 +1786,14 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFCC99"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -2941,7 +3158,7 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="95">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3311,6 +3528,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="52" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="52" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4550,7 +4775,7 @@
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="0" name="AutoShape 3"/>
+        <xdr:cNvPr id="1" name="AutoShape 3" descr="C:\Users\A_Tumayeva\Desktop\9hq.webp"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -4595,13 +4820,58 @@
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="1" name="AutoShape 3"/>
+        <xdr:cNvPr id="2" name="AutoShape 3" descr="C:\Users\A_Tumayeva\Desktop\9hq.webp"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
           <a:off x="883800" y="5872320"/>
           <a:ext cx="298440" cy="2055240"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>23400</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>48240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>321840</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>32040</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="AutoShape 3" descr="C:\Users\A_Tumayeva\Desktop\9hq.webp"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="883800" y="5872320"/>
+          <a:ext cx="298440" cy="2095200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4631,37 +4901,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -4735,7 +5005,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N50"/>
-  <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="14.4" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="14.87"/>
@@ -5134,8 +5404,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
-  <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="15.05" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW40"/>
+  <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="15.05" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="22" width="15.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="23" width="14.43"/>
@@ -5148,7 +5418,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="11" style="24" width="9.1"/>
   </cols>
   <sheetData>
-    <row r="1" s="27" customFormat="true" ht="19.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="19.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
         <v>44</v>
       </c>
@@ -5156,12 +5426,260 @@
       <c r="C1" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
       <c r="I1" s="28"/>
+      <c r="J1" s="27"/>
       <c r="K1" s="29" t="s">
         <v>46</v>
       </c>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="27"/>
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="27"/>
+      <c r="Y1" s="27"/>
+      <c r="Z1" s="27"/>
+      <c r="AA1" s="27"/>
+      <c r="AB1" s="27"/>
+      <c r="AC1" s="27"/>
+      <c r="AD1" s="27"/>
+      <c r="AE1" s="27"/>
+      <c r="AF1" s="27"/>
+      <c r="AG1" s="27"/>
+      <c r="AH1" s="27"/>
+      <c r="AI1" s="27"/>
+      <c r="AJ1" s="27"/>
+      <c r="AK1" s="27"/>
+      <c r="AL1" s="27"/>
+      <c r="AM1" s="27"/>
+      <c r="AN1" s="27"/>
+      <c r="AO1" s="27"/>
+      <c r="AP1" s="27"/>
+      <c r="AQ1" s="27"/>
+      <c r="AR1" s="27"/>
+      <c r="AS1" s="27"/>
+      <c r="AT1" s="27"/>
+      <c r="AU1" s="27"/>
+      <c r="AV1" s="27"/>
+      <c r="AW1" s="27"/>
+      <c r="AX1" s="27"/>
+      <c r="AY1" s="27"/>
+      <c r="AZ1" s="27"/>
+      <c r="BA1" s="27"/>
+      <c r="BB1" s="27"/>
+      <c r="BC1" s="27"/>
+      <c r="BD1" s="27"/>
+      <c r="BE1" s="27"/>
+      <c r="BF1" s="27"/>
+      <c r="BG1" s="27"/>
+      <c r="BH1" s="27"/>
+      <c r="BI1" s="27"/>
+      <c r="BJ1" s="27"/>
+      <c r="BK1" s="27"/>
+      <c r="BL1" s="27"/>
+      <c r="BM1" s="27"/>
+      <c r="BN1" s="27"/>
+      <c r="BO1" s="27"/>
+      <c r="BP1" s="27"/>
+      <c r="BQ1" s="27"/>
+      <c r="BR1" s="27"/>
+      <c r="BS1" s="27"/>
+      <c r="BT1" s="27"/>
+      <c r="BU1" s="27"/>
+      <c r="BV1" s="27"/>
+      <c r="BW1" s="27"/>
+      <c r="BX1" s="27"/>
+      <c r="BY1" s="27"/>
+      <c r="BZ1" s="27"/>
+      <c r="CA1" s="27"/>
+      <c r="CB1" s="27"/>
+      <c r="CC1" s="27"/>
+      <c r="CD1" s="27"/>
+      <c r="CE1" s="27"/>
+      <c r="CF1" s="27"/>
+      <c r="CG1" s="27"/>
+      <c r="CH1" s="27"/>
+      <c r="CI1" s="27"/>
+      <c r="CJ1" s="27"/>
+      <c r="CK1" s="27"/>
+      <c r="CL1" s="27"/>
+      <c r="CM1" s="27"/>
+      <c r="CN1" s="27"/>
+      <c r="CO1" s="27"/>
+      <c r="CP1" s="27"/>
+      <c r="CQ1" s="27"/>
+      <c r="CR1" s="27"/>
+      <c r="CS1" s="27"/>
+      <c r="CT1" s="27"/>
+      <c r="CU1" s="27"/>
+      <c r="CV1" s="27"/>
+      <c r="CW1" s="27"/>
+      <c r="CX1" s="27"/>
+      <c r="CY1" s="27"/>
+      <c r="CZ1" s="27"/>
+      <c r="DA1" s="27"/>
+      <c r="DB1" s="27"/>
+      <c r="DC1" s="27"/>
+      <c r="DD1" s="27"/>
+      <c r="DE1" s="27"/>
+      <c r="DF1" s="27"/>
+      <c r="DG1" s="27"/>
+      <c r="DH1" s="27"/>
+      <c r="DI1" s="27"/>
+      <c r="DJ1" s="27"/>
+      <c r="DK1" s="27"/>
+      <c r="DL1" s="27"/>
+      <c r="DM1" s="27"/>
+      <c r="DN1" s="27"/>
+      <c r="DO1" s="27"/>
+      <c r="DP1" s="27"/>
+      <c r="DQ1" s="27"/>
+      <c r="DR1" s="27"/>
+      <c r="DS1" s="27"/>
+      <c r="DT1" s="27"/>
+      <c r="DU1" s="27"/>
+      <c r="DV1" s="27"/>
+      <c r="DW1" s="27"/>
+      <c r="DX1" s="27"/>
+      <c r="DY1" s="27"/>
+      <c r="DZ1" s="27"/>
+      <c r="EA1" s="27"/>
+      <c r="EB1" s="27"/>
+      <c r="EC1" s="27"/>
+      <c r="ED1" s="27"/>
+      <c r="EE1" s="27"/>
+      <c r="EF1" s="27"/>
+      <c r="EG1" s="27"/>
+      <c r="EH1" s="27"/>
+      <c r="EI1" s="27"/>
+      <c r="EJ1" s="27"/>
+      <c r="EK1" s="27"/>
+      <c r="EL1" s="27"/>
+      <c r="EM1" s="27"/>
+      <c r="EN1" s="27"/>
+      <c r="EO1" s="27"/>
+      <c r="EP1" s="27"/>
+      <c r="EQ1" s="27"/>
+      <c r="ER1" s="27"/>
+      <c r="ES1" s="27"/>
+      <c r="ET1" s="27"/>
+      <c r="EU1" s="27"/>
+      <c r="EV1" s="27"/>
+      <c r="EW1" s="27"/>
+      <c r="EX1" s="27"/>
+      <c r="EY1" s="27"/>
+      <c r="EZ1" s="27"/>
+      <c r="FA1" s="27"/>
+      <c r="FB1" s="27"/>
+      <c r="FC1" s="27"/>
+      <c r="FD1" s="27"/>
+      <c r="FE1" s="27"/>
+      <c r="FF1" s="27"/>
+      <c r="FG1" s="27"/>
+      <c r="FH1" s="27"/>
+      <c r="FI1" s="27"/>
+      <c r="FJ1" s="27"/>
+      <c r="FK1" s="27"/>
+      <c r="FL1" s="27"/>
+      <c r="FM1" s="27"/>
+      <c r="FN1" s="27"/>
+      <c r="FO1" s="27"/>
+      <c r="FP1" s="27"/>
+      <c r="FQ1" s="27"/>
+      <c r="FR1" s="27"/>
+      <c r="FS1" s="27"/>
+      <c r="FT1" s="27"/>
+      <c r="FU1" s="27"/>
+      <c r="FV1" s="27"/>
+      <c r="FW1" s="27"/>
+      <c r="FX1" s="27"/>
+      <c r="FY1" s="27"/>
+      <c r="FZ1" s="27"/>
+      <c r="GA1" s="27"/>
+      <c r="GB1" s="27"/>
+      <c r="GC1" s="27"/>
+      <c r="GD1" s="27"/>
+      <c r="GE1" s="27"/>
+      <c r="GF1" s="27"/>
+      <c r="GG1" s="27"/>
+      <c r="GH1" s="27"/>
+      <c r="GI1" s="27"/>
+      <c r="GJ1" s="27"/>
+      <c r="GK1" s="27"/>
+      <c r="GL1" s="27"/>
+      <c r="GM1" s="27"/>
+      <c r="GN1" s="27"/>
+      <c r="GO1" s="27"/>
+      <c r="GP1" s="27"/>
+      <c r="GQ1" s="27"/>
+      <c r="GR1" s="27"/>
+      <c r="GS1" s="27"/>
+      <c r="GT1" s="27"/>
+      <c r="GU1" s="27"/>
+      <c r="GV1" s="27"/>
+      <c r="GW1" s="27"/>
+      <c r="GX1" s="27"/>
+      <c r="GY1" s="27"/>
+      <c r="GZ1" s="27"/>
+      <c r="HA1" s="27"/>
+      <c r="HB1" s="27"/>
+      <c r="HC1" s="27"/>
+      <c r="HD1" s="27"/>
+      <c r="HE1" s="27"/>
+      <c r="HF1" s="27"/>
+      <c r="HG1" s="27"/>
+      <c r="HH1" s="27"/>
+      <c r="HI1" s="27"/>
+      <c r="HJ1" s="27"/>
+      <c r="HK1" s="27"/>
+      <c r="HL1" s="27"/>
+      <c r="HM1" s="27"/>
+      <c r="HN1" s="27"/>
+      <c r="HO1" s="27"/>
+      <c r="HP1" s="27"/>
+      <c r="HQ1" s="27"/>
+      <c r="HR1" s="27"/>
+      <c r="HS1" s="27"/>
+      <c r="HT1" s="27"/>
+      <c r="HU1" s="27"/>
+      <c r="HV1" s="27"/>
+      <c r="HW1" s="27"/>
+      <c r="HX1" s="27"/>
+      <c r="HY1" s="27"/>
+      <c r="HZ1" s="27"/>
+      <c r="IA1" s="27"/>
+      <c r="IB1" s="27"/>
+      <c r="IC1" s="27"/>
+      <c r="ID1" s="27"/>
+      <c r="IE1" s="27"/>
+      <c r="IF1" s="27"/>
+      <c r="IG1" s="27"/>
+      <c r="IH1" s="27"/>
+      <c r="II1" s="27"/>
+      <c r="IJ1" s="27"/>
+      <c r="IK1" s="27"/>
+      <c r="IL1" s="27"/>
+      <c r="IM1" s="27"/>
+      <c r="IN1" s="27"/>
+      <c r="IO1" s="27"/>
+      <c r="IP1" s="27"/>
+      <c r="IQ1" s="27"/>
+      <c r="IR1" s="27"/>
+      <c r="IS1" s="27"/>
+      <c r="IT1" s="27"/>
+      <c r="IU1" s="27"/>
+      <c r="IV1" s="27"/>
+      <c r="IW1" s="27"/>
     </row>
     <row r="2" customFormat="false" ht="19.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="30" t="s">
@@ -5674,8 +6192,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R32"/>
-  <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="12.55" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW32"/>
+  <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="12.55" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="60" width="12.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="60" width="12.99"/>
@@ -5690,7 +6208,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="11" style="60" width="9.1"/>
   </cols>
   <sheetData>
-    <row r="1" s="62" customFormat="true" ht="26.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="26.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="61" t="s">
         <v>148</v>
       </c>
@@ -5702,9 +6220,256 @@
       <c r="G1" s="61"/>
       <c r="H1" s="61"/>
       <c r="I1" s="61"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
       <c r="L1" s="63" t="s">
         <v>46</v>
       </c>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
+      <c r="S1" s="62"/>
+      <c r="T1" s="62"/>
+      <c r="U1" s="62"/>
+      <c r="V1" s="62"/>
+      <c r="W1" s="62"/>
+      <c r="X1" s="62"/>
+      <c r="Y1" s="62"/>
+      <c r="Z1" s="62"/>
+      <c r="AA1" s="62"/>
+      <c r="AB1" s="62"/>
+      <c r="AC1" s="62"/>
+      <c r="AD1" s="62"/>
+      <c r="AE1" s="62"/>
+      <c r="AF1" s="62"/>
+      <c r="AG1" s="62"/>
+      <c r="AH1" s="62"/>
+      <c r="AI1" s="62"/>
+      <c r="AJ1" s="62"/>
+      <c r="AK1" s="62"/>
+      <c r="AL1" s="62"/>
+      <c r="AM1" s="62"/>
+      <c r="AN1" s="62"/>
+      <c r="AO1" s="62"/>
+      <c r="AP1" s="62"/>
+      <c r="AQ1" s="62"/>
+      <c r="AR1" s="62"/>
+      <c r="AS1" s="62"/>
+      <c r="AT1" s="62"/>
+      <c r="AU1" s="62"/>
+      <c r="AV1" s="62"/>
+      <c r="AW1" s="62"/>
+      <c r="AX1" s="62"/>
+      <c r="AY1" s="62"/>
+      <c r="AZ1" s="62"/>
+      <c r="BA1" s="62"/>
+      <c r="BB1" s="62"/>
+      <c r="BC1" s="62"/>
+      <c r="BD1" s="62"/>
+      <c r="BE1" s="62"/>
+      <c r="BF1" s="62"/>
+      <c r="BG1" s="62"/>
+      <c r="BH1" s="62"/>
+      <c r="BI1" s="62"/>
+      <c r="BJ1" s="62"/>
+      <c r="BK1" s="62"/>
+      <c r="BL1" s="62"/>
+      <c r="BM1" s="62"/>
+      <c r="BN1" s="62"/>
+      <c r="BO1" s="62"/>
+      <c r="BP1" s="62"/>
+      <c r="BQ1" s="62"/>
+      <c r="BR1" s="62"/>
+      <c r="BS1" s="62"/>
+      <c r="BT1" s="62"/>
+      <c r="BU1" s="62"/>
+      <c r="BV1" s="62"/>
+      <c r="BW1" s="62"/>
+      <c r="BX1" s="62"/>
+      <c r="BY1" s="62"/>
+      <c r="BZ1" s="62"/>
+      <c r="CA1" s="62"/>
+      <c r="CB1" s="62"/>
+      <c r="CC1" s="62"/>
+      <c r="CD1" s="62"/>
+      <c r="CE1" s="62"/>
+      <c r="CF1" s="62"/>
+      <c r="CG1" s="62"/>
+      <c r="CH1" s="62"/>
+      <c r="CI1" s="62"/>
+      <c r="CJ1" s="62"/>
+      <c r="CK1" s="62"/>
+      <c r="CL1" s="62"/>
+      <c r="CM1" s="62"/>
+      <c r="CN1" s="62"/>
+      <c r="CO1" s="62"/>
+      <c r="CP1" s="62"/>
+      <c r="CQ1" s="62"/>
+      <c r="CR1" s="62"/>
+      <c r="CS1" s="62"/>
+      <c r="CT1" s="62"/>
+      <c r="CU1" s="62"/>
+      <c r="CV1" s="62"/>
+      <c r="CW1" s="62"/>
+      <c r="CX1" s="62"/>
+      <c r="CY1" s="62"/>
+      <c r="CZ1" s="62"/>
+      <c r="DA1" s="62"/>
+      <c r="DB1" s="62"/>
+      <c r="DC1" s="62"/>
+      <c r="DD1" s="62"/>
+      <c r="DE1" s="62"/>
+      <c r="DF1" s="62"/>
+      <c r="DG1" s="62"/>
+      <c r="DH1" s="62"/>
+      <c r="DI1" s="62"/>
+      <c r="DJ1" s="62"/>
+      <c r="DK1" s="62"/>
+      <c r="DL1" s="62"/>
+      <c r="DM1" s="62"/>
+      <c r="DN1" s="62"/>
+      <c r="DO1" s="62"/>
+      <c r="DP1" s="62"/>
+      <c r="DQ1" s="62"/>
+      <c r="DR1" s="62"/>
+      <c r="DS1" s="62"/>
+      <c r="DT1" s="62"/>
+      <c r="DU1" s="62"/>
+      <c r="DV1" s="62"/>
+      <c r="DW1" s="62"/>
+      <c r="DX1" s="62"/>
+      <c r="DY1" s="62"/>
+      <c r="DZ1" s="62"/>
+      <c r="EA1" s="62"/>
+      <c r="EB1" s="62"/>
+      <c r="EC1" s="62"/>
+      <c r="ED1" s="62"/>
+      <c r="EE1" s="62"/>
+      <c r="EF1" s="62"/>
+      <c r="EG1" s="62"/>
+      <c r="EH1" s="62"/>
+      <c r="EI1" s="62"/>
+      <c r="EJ1" s="62"/>
+      <c r="EK1" s="62"/>
+      <c r="EL1" s="62"/>
+      <c r="EM1" s="62"/>
+      <c r="EN1" s="62"/>
+      <c r="EO1" s="62"/>
+      <c r="EP1" s="62"/>
+      <c r="EQ1" s="62"/>
+      <c r="ER1" s="62"/>
+      <c r="ES1" s="62"/>
+      <c r="ET1" s="62"/>
+      <c r="EU1" s="62"/>
+      <c r="EV1" s="62"/>
+      <c r="EW1" s="62"/>
+      <c r="EX1" s="62"/>
+      <c r="EY1" s="62"/>
+      <c r="EZ1" s="62"/>
+      <c r="FA1" s="62"/>
+      <c r="FB1" s="62"/>
+      <c r="FC1" s="62"/>
+      <c r="FD1" s="62"/>
+      <c r="FE1" s="62"/>
+      <c r="FF1" s="62"/>
+      <c r="FG1" s="62"/>
+      <c r="FH1" s="62"/>
+      <c r="FI1" s="62"/>
+      <c r="FJ1" s="62"/>
+      <c r="FK1" s="62"/>
+      <c r="FL1" s="62"/>
+      <c r="FM1" s="62"/>
+      <c r="FN1" s="62"/>
+      <c r="FO1" s="62"/>
+      <c r="FP1" s="62"/>
+      <c r="FQ1" s="62"/>
+      <c r="FR1" s="62"/>
+      <c r="FS1" s="62"/>
+      <c r="FT1" s="62"/>
+      <c r="FU1" s="62"/>
+      <c r="FV1" s="62"/>
+      <c r="FW1" s="62"/>
+      <c r="FX1" s="62"/>
+      <c r="FY1" s="62"/>
+      <c r="FZ1" s="62"/>
+      <c r="GA1" s="62"/>
+      <c r="GB1" s="62"/>
+      <c r="GC1" s="62"/>
+      <c r="GD1" s="62"/>
+      <c r="GE1" s="62"/>
+      <c r="GF1" s="62"/>
+      <c r="GG1" s="62"/>
+      <c r="GH1" s="62"/>
+      <c r="GI1" s="62"/>
+      <c r="GJ1" s="62"/>
+      <c r="GK1" s="62"/>
+      <c r="GL1" s="62"/>
+      <c r="GM1" s="62"/>
+      <c r="GN1" s="62"/>
+      <c r="GO1" s="62"/>
+      <c r="GP1" s="62"/>
+      <c r="GQ1" s="62"/>
+      <c r="GR1" s="62"/>
+      <c r="GS1" s="62"/>
+      <c r="GT1" s="62"/>
+      <c r="GU1" s="62"/>
+      <c r="GV1" s="62"/>
+      <c r="GW1" s="62"/>
+      <c r="GX1" s="62"/>
+      <c r="GY1" s="62"/>
+      <c r="GZ1" s="62"/>
+      <c r="HA1" s="62"/>
+      <c r="HB1" s="62"/>
+      <c r="HC1" s="62"/>
+      <c r="HD1" s="62"/>
+      <c r="HE1" s="62"/>
+      <c r="HF1" s="62"/>
+      <c r="HG1" s="62"/>
+      <c r="HH1" s="62"/>
+      <c r="HI1" s="62"/>
+      <c r="HJ1" s="62"/>
+      <c r="HK1" s="62"/>
+      <c r="HL1" s="62"/>
+      <c r="HM1" s="62"/>
+      <c r="HN1" s="62"/>
+      <c r="HO1" s="62"/>
+      <c r="HP1" s="62"/>
+      <c r="HQ1" s="62"/>
+      <c r="HR1" s="62"/>
+      <c r="HS1" s="62"/>
+      <c r="HT1" s="62"/>
+      <c r="HU1" s="62"/>
+      <c r="HV1" s="62"/>
+      <c r="HW1" s="62"/>
+      <c r="HX1" s="62"/>
+      <c r="HY1" s="62"/>
+      <c r="HZ1" s="62"/>
+      <c r="IA1" s="62"/>
+      <c r="IB1" s="62"/>
+      <c r="IC1" s="62"/>
+      <c r="ID1" s="62"/>
+      <c r="IE1" s="62"/>
+      <c r="IF1" s="62"/>
+      <c r="IG1" s="62"/>
+      <c r="IH1" s="62"/>
+      <c r="II1" s="62"/>
+      <c r="IJ1" s="62"/>
+      <c r="IK1" s="62"/>
+      <c r="IL1" s="62"/>
+      <c r="IM1" s="62"/>
+      <c r="IN1" s="62"/>
+      <c r="IO1" s="62"/>
+      <c r="IP1" s="62"/>
+      <c r="IQ1" s="62"/>
+      <c r="IR1" s="62"/>
+      <c r="IS1" s="62"/>
+      <c r="IT1" s="62"/>
+      <c r="IU1" s="62"/>
+      <c r="IV1" s="62"/>
+      <c r="IW1" s="62"/>
     </row>
     <row r="2" customFormat="false" ht="23.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="64" t="s">
@@ -6050,13 +6815,260 @@
       </c>
       <c r="H19" s="80"/>
     </row>
-    <row r="20" s="82" customFormat="true" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="82"/>
+      <c r="B20" s="82"/>
+      <c r="C20" s="82"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="82"/>
+      <c r="F20" s="82"/>
+      <c r="G20" s="82"/>
       <c r="H20" s="80"/>
+      <c r="I20" s="82"/>
       <c r="J20" s="83"/>
-      <c r="K20" s="60"/>
-      <c r="L20" s="60"/>
-      <c r="M20" s="60"/>
-      <c r="N20" s="60"/>
+      <c r="O20" s="82"/>
+      <c r="P20" s="82"/>
+      <c r="Q20" s="82"/>
+      <c r="R20" s="82"/>
+      <c r="S20" s="82"/>
+      <c r="T20" s="82"/>
+      <c r="U20" s="82"/>
+      <c r="V20" s="82"/>
+      <c r="W20" s="82"/>
+      <c r="X20" s="82"/>
+      <c r="Y20" s="82"/>
+      <c r="Z20" s="82"/>
+      <c r="AA20" s="82"/>
+      <c r="AB20" s="82"/>
+      <c r="AC20" s="82"/>
+      <c r="AD20" s="82"/>
+      <c r="AE20" s="82"/>
+      <c r="AF20" s="82"/>
+      <c r="AG20" s="82"/>
+      <c r="AH20" s="82"/>
+      <c r="AI20" s="82"/>
+      <c r="AJ20" s="82"/>
+      <c r="AK20" s="82"/>
+      <c r="AL20" s="82"/>
+      <c r="AM20" s="82"/>
+      <c r="AN20" s="82"/>
+      <c r="AO20" s="82"/>
+      <c r="AP20" s="82"/>
+      <c r="AQ20" s="82"/>
+      <c r="AR20" s="82"/>
+      <c r="AS20" s="82"/>
+      <c r="AT20" s="82"/>
+      <c r="AU20" s="82"/>
+      <c r="AV20" s="82"/>
+      <c r="AW20" s="82"/>
+      <c r="AX20" s="82"/>
+      <c r="AY20" s="82"/>
+      <c r="AZ20" s="82"/>
+      <c r="BA20" s="82"/>
+      <c r="BB20" s="82"/>
+      <c r="BC20" s="82"/>
+      <c r="BD20" s="82"/>
+      <c r="BE20" s="82"/>
+      <c r="BF20" s="82"/>
+      <c r="BG20" s="82"/>
+      <c r="BH20" s="82"/>
+      <c r="BI20" s="82"/>
+      <c r="BJ20" s="82"/>
+      <c r="BK20" s="82"/>
+      <c r="BL20" s="82"/>
+      <c r="BM20" s="82"/>
+      <c r="BN20" s="82"/>
+      <c r="BO20" s="82"/>
+      <c r="BP20" s="82"/>
+      <c r="BQ20" s="82"/>
+      <c r="BR20" s="82"/>
+      <c r="BS20" s="82"/>
+      <c r="BT20" s="82"/>
+      <c r="BU20" s="82"/>
+      <c r="BV20" s="82"/>
+      <c r="BW20" s="82"/>
+      <c r="BX20" s="82"/>
+      <c r="BY20" s="82"/>
+      <c r="BZ20" s="82"/>
+      <c r="CA20" s="82"/>
+      <c r="CB20" s="82"/>
+      <c r="CC20" s="82"/>
+      <c r="CD20" s="82"/>
+      <c r="CE20" s="82"/>
+      <c r="CF20" s="82"/>
+      <c r="CG20" s="82"/>
+      <c r="CH20" s="82"/>
+      <c r="CI20" s="82"/>
+      <c r="CJ20" s="82"/>
+      <c r="CK20" s="82"/>
+      <c r="CL20" s="82"/>
+      <c r="CM20" s="82"/>
+      <c r="CN20" s="82"/>
+      <c r="CO20" s="82"/>
+      <c r="CP20" s="82"/>
+      <c r="CQ20" s="82"/>
+      <c r="CR20" s="82"/>
+      <c r="CS20" s="82"/>
+      <c r="CT20" s="82"/>
+      <c r="CU20" s="82"/>
+      <c r="CV20" s="82"/>
+      <c r="CW20" s="82"/>
+      <c r="CX20" s="82"/>
+      <c r="CY20" s="82"/>
+      <c r="CZ20" s="82"/>
+      <c r="DA20" s="82"/>
+      <c r="DB20" s="82"/>
+      <c r="DC20" s="82"/>
+      <c r="DD20" s="82"/>
+      <c r="DE20" s="82"/>
+      <c r="DF20" s="82"/>
+      <c r="DG20" s="82"/>
+      <c r="DH20" s="82"/>
+      <c r="DI20" s="82"/>
+      <c r="DJ20" s="82"/>
+      <c r="DK20" s="82"/>
+      <c r="DL20" s="82"/>
+      <c r="DM20" s="82"/>
+      <c r="DN20" s="82"/>
+      <c r="DO20" s="82"/>
+      <c r="DP20" s="82"/>
+      <c r="DQ20" s="82"/>
+      <c r="DR20" s="82"/>
+      <c r="DS20" s="82"/>
+      <c r="DT20" s="82"/>
+      <c r="DU20" s="82"/>
+      <c r="DV20" s="82"/>
+      <c r="DW20" s="82"/>
+      <c r="DX20" s="82"/>
+      <c r="DY20" s="82"/>
+      <c r="DZ20" s="82"/>
+      <c r="EA20" s="82"/>
+      <c r="EB20" s="82"/>
+      <c r="EC20" s="82"/>
+      <c r="ED20" s="82"/>
+      <c r="EE20" s="82"/>
+      <c r="EF20" s="82"/>
+      <c r="EG20" s="82"/>
+      <c r="EH20" s="82"/>
+      <c r="EI20" s="82"/>
+      <c r="EJ20" s="82"/>
+      <c r="EK20" s="82"/>
+      <c r="EL20" s="82"/>
+      <c r="EM20" s="82"/>
+      <c r="EN20" s="82"/>
+      <c r="EO20" s="82"/>
+      <c r="EP20" s="82"/>
+      <c r="EQ20" s="82"/>
+      <c r="ER20" s="82"/>
+      <c r="ES20" s="82"/>
+      <c r="ET20" s="82"/>
+      <c r="EU20" s="82"/>
+      <c r="EV20" s="82"/>
+      <c r="EW20" s="82"/>
+      <c r="EX20" s="82"/>
+      <c r="EY20" s="82"/>
+      <c r="EZ20" s="82"/>
+      <c r="FA20" s="82"/>
+      <c r="FB20" s="82"/>
+      <c r="FC20" s="82"/>
+      <c r="FD20" s="82"/>
+      <c r="FE20" s="82"/>
+      <c r="FF20" s="82"/>
+      <c r="FG20" s="82"/>
+      <c r="FH20" s="82"/>
+      <c r="FI20" s="82"/>
+      <c r="FJ20" s="82"/>
+      <c r="FK20" s="82"/>
+      <c r="FL20" s="82"/>
+      <c r="FM20" s="82"/>
+      <c r="FN20" s="82"/>
+      <c r="FO20" s="82"/>
+      <c r="FP20" s="82"/>
+      <c r="FQ20" s="82"/>
+      <c r="FR20" s="82"/>
+      <c r="FS20" s="82"/>
+      <c r="FT20" s="82"/>
+      <c r="FU20" s="82"/>
+      <c r="FV20" s="82"/>
+      <c r="FW20" s="82"/>
+      <c r="FX20" s="82"/>
+      <c r="FY20" s="82"/>
+      <c r="FZ20" s="82"/>
+      <c r="GA20" s="82"/>
+      <c r="GB20" s="82"/>
+      <c r="GC20" s="82"/>
+      <c r="GD20" s="82"/>
+      <c r="GE20" s="82"/>
+      <c r="GF20" s="82"/>
+      <c r="GG20" s="82"/>
+      <c r="GH20" s="82"/>
+      <c r="GI20" s="82"/>
+      <c r="GJ20" s="82"/>
+      <c r="GK20" s="82"/>
+      <c r="GL20" s="82"/>
+      <c r="GM20" s="82"/>
+      <c r="GN20" s="82"/>
+      <c r="GO20" s="82"/>
+      <c r="GP20" s="82"/>
+      <c r="GQ20" s="82"/>
+      <c r="GR20" s="82"/>
+      <c r="GS20" s="82"/>
+      <c r="GT20" s="82"/>
+      <c r="GU20" s="82"/>
+      <c r="GV20" s="82"/>
+      <c r="GW20" s="82"/>
+      <c r="GX20" s="82"/>
+      <c r="GY20" s="82"/>
+      <c r="GZ20" s="82"/>
+      <c r="HA20" s="82"/>
+      <c r="HB20" s="82"/>
+      <c r="HC20" s="82"/>
+      <c r="HD20" s="82"/>
+      <c r="HE20" s="82"/>
+      <c r="HF20" s="82"/>
+      <c r="HG20" s="82"/>
+      <c r="HH20" s="82"/>
+      <c r="HI20" s="82"/>
+      <c r="HJ20" s="82"/>
+      <c r="HK20" s="82"/>
+      <c r="HL20" s="82"/>
+      <c r="HM20" s="82"/>
+      <c r="HN20" s="82"/>
+      <c r="HO20" s="82"/>
+      <c r="HP20" s="82"/>
+      <c r="HQ20" s="82"/>
+      <c r="HR20" s="82"/>
+      <c r="HS20" s="82"/>
+      <c r="HT20" s="82"/>
+      <c r="HU20" s="82"/>
+      <c r="HV20" s="82"/>
+      <c r="HW20" s="82"/>
+      <c r="HX20" s="82"/>
+      <c r="HY20" s="82"/>
+      <c r="HZ20" s="82"/>
+      <c r="IA20" s="82"/>
+      <c r="IB20" s="82"/>
+      <c r="IC20" s="82"/>
+      <c r="ID20" s="82"/>
+      <c r="IE20" s="82"/>
+      <c r="IF20" s="82"/>
+      <c r="IG20" s="82"/>
+      <c r="IH20" s="82"/>
+      <c r="II20" s="82"/>
+      <c r="IJ20" s="82"/>
+      <c r="IK20" s="82"/>
+      <c r="IL20" s="82"/>
+      <c r="IM20" s="82"/>
+      <c r="IN20" s="82"/>
+      <c r="IO20" s="82"/>
+      <c r="IP20" s="82"/>
+      <c r="IQ20" s="82"/>
+      <c r="IR20" s="82"/>
+      <c r="IS20" s="82"/>
+      <c r="IT20" s="82"/>
+      <c r="IU20" s="82"/>
+      <c r="IV20" s="82"/>
+      <c r="IW20" s="82"/>
     </row>
     <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="82"/>
@@ -6126,8 +7138,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R32"/>
-  <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="12.55" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:IW32"/>
+  <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="12.55" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="60" width="12.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="60" width="12.99"/>
@@ -6142,7 +7154,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="11" style="60" width="9.1"/>
   </cols>
   <sheetData>
-    <row r="1" s="62" customFormat="true" ht="26.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="26.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="61" t="s">
         <v>171</v>
       </c>
@@ -6154,9 +7166,256 @@
       <c r="G1" s="61"/>
       <c r="H1" s="61"/>
       <c r="I1" s="61"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
       <c r="L1" s="63" t="s">
         <v>46</v>
       </c>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
+      <c r="S1" s="62"/>
+      <c r="T1" s="62"/>
+      <c r="U1" s="62"/>
+      <c r="V1" s="62"/>
+      <c r="W1" s="62"/>
+      <c r="X1" s="62"/>
+      <c r="Y1" s="62"/>
+      <c r="Z1" s="62"/>
+      <c r="AA1" s="62"/>
+      <c r="AB1" s="62"/>
+      <c r="AC1" s="62"/>
+      <c r="AD1" s="62"/>
+      <c r="AE1" s="62"/>
+      <c r="AF1" s="62"/>
+      <c r="AG1" s="62"/>
+      <c r="AH1" s="62"/>
+      <c r="AI1" s="62"/>
+      <c r="AJ1" s="62"/>
+      <c r="AK1" s="62"/>
+      <c r="AL1" s="62"/>
+      <c r="AM1" s="62"/>
+      <c r="AN1" s="62"/>
+      <c r="AO1" s="62"/>
+      <c r="AP1" s="62"/>
+      <c r="AQ1" s="62"/>
+      <c r="AR1" s="62"/>
+      <c r="AS1" s="62"/>
+      <c r="AT1" s="62"/>
+      <c r="AU1" s="62"/>
+      <c r="AV1" s="62"/>
+      <c r="AW1" s="62"/>
+      <c r="AX1" s="62"/>
+      <c r="AY1" s="62"/>
+      <c r="AZ1" s="62"/>
+      <c r="BA1" s="62"/>
+      <c r="BB1" s="62"/>
+      <c r="BC1" s="62"/>
+      <c r="BD1" s="62"/>
+      <c r="BE1" s="62"/>
+      <c r="BF1" s="62"/>
+      <c r="BG1" s="62"/>
+      <c r="BH1" s="62"/>
+      <c r="BI1" s="62"/>
+      <c r="BJ1" s="62"/>
+      <c r="BK1" s="62"/>
+      <c r="BL1" s="62"/>
+      <c r="BM1" s="62"/>
+      <c r="BN1" s="62"/>
+      <c r="BO1" s="62"/>
+      <c r="BP1" s="62"/>
+      <c r="BQ1" s="62"/>
+      <c r="BR1" s="62"/>
+      <c r="BS1" s="62"/>
+      <c r="BT1" s="62"/>
+      <c r="BU1" s="62"/>
+      <c r="BV1" s="62"/>
+      <c r="BW1" s="62"/>
+      <c r="BX1" s="62"/>
+      <c r="BY1" s="62"/>
+      <c r="BZ1" s="62"/>
+      <c r="CA1" s="62"/>
+      <c r="CB1" s="62"/>
+      <c r="CC1" s="62"/>
+      <c r="CD1" s="62"/>
+      <c r="CE1" s="62"/>
+      <c r="CF1" s="62"/>
+      <c r="CG1" s="62"/>
+      <c r="CH1" s="62"/>
+      <c r="CI1" s="62"/>
+      <c r="CJ1" s="62"/>
+      <c r="CK1" s="62"/>
+      <c r="CL1" s="62"/>
+      <c r="CM1" s="62"/>
+      <c r="CN1" s="62"/>
+      <c r="CO1" s="62"/>
+      <c r="CP1" s="62"/>
+      <c r="CQ1" s="62"/>
+      <c r="CR1" s="62"/>
+      <c r="CS1" s="62"/>
+      <c r="CT1" s="62"/>
+      <c r="CU1" s="62"/>
+      <c r="CV1" s="62"/>
+      <c r="CW1" s="62"/>
+      <c r="CX1" s="62"/>
+      <c r="CY1" s="62"/>
+      <c r="CZ1" s="62"/>
+      <c r="DA1" s="62"/>
+      <c r="DB1" s="62"/>
+      <c r="DC1" s="62"/>
+      <c r="DD1" s="62"/>
+      <c r="DE1" s="62"/>
+      <c r="DF1" s="62"/>
+      <c r="DG1" s="62"/>
+      <c r="DH1" s="62"/>
+      <c r="DI1" s="62"/>
+      <c r="DJ1" s="62"/>
+      <c r="DK1" s="62"/>
+      <c r="DL1" s="62"/>
+      <c r="DM1" s="62"/>
+      <c r="DN1" s="62"/>
+      <c r="DO1" s="62"/>
+      <c r="DP1" s="62"/>
+      <c r="DQ1" s="62"/>
+      <c r="DR1" s="62"/>
+      <c r="DS1" s="62"/>
+      <c r="DT1" s="62"/>
+      <c r="DU1" s="62"/>
+      <c r="DV1" s="62"/>
+      <c r="DW1" s="62"/>
+      <c r="DX1" s="62"/>
+      <c r="DY1" s="62"/>
+      <c r="DZ1" s="62"/>
+      <c r="EA1" s="62"/>
+      <c r="EB1" s="62"/>
+      <c r="EC1" s="62"/>
+      <c r="ED1" s="62"/>
+      <c r="EE1" s="62"/>
+      <c r="EF1" s="62"/>
+      <c r="EG1" s="62"/>
+      <c r="EH1" s="62"/>
+      <c r="EI1" s="62"/>
+      <c r="EJ1" s="62"/>
+      <c r="EK1" s="62"/>
+      <c r="EL1" s="62"/>
+      <c r="EM1" s="62"/>
+      <c r="EN1" s="62"/>
+      <c r="EO1" s="62"/>
+      <c r="EP1" s="62"/>
+      <c r="EQ1" s="62"/>
+      <c r="ER1" s="62"/>
+      <c r="ES1" s="62"/>
+      <c r="ET1" s="62"/>
+      <c r="EU1" s="62"/>
+      <c r="EV1" s="62"/>
+      <c r="EW1" s="62"/>
+      <c r="EX1" s="62"/>
+      <c r="EY1" s="62"/>
+      <c r="EZ1" s="62"/>
+      <c r="FA1" s="62"/>
+      <c r="FB1" s="62"/>
+      <c r="FC1" s="62"/>
+      <c r="FD1" s="62"/>
+      <c r="FE1" s="62"/>
+      <c r="FF1" s="62"/>
+      <c r="FG1" s="62"/>
+      <c r="FH1" s="62"/>
+      <c r="FI1" s="62"/>
+      <c r="FJ1" s="62"/>
+      <c r="FK1" s="62"/>
+      <c r="FL1" s="62"/>
+      <c r="FM1" s="62"/>
+      <c r="FN1" s="62"/>
+      <c r="FO1" s="62"/>
+      <c r="FP1" s="62"/>
+      <c r="FQ1" s="62"/>
+      <c r="FR1" s="62"/>
+      <c r="FS1" s="62"/>
+      <c r="FT1" s="62"/>
+      <c r="FU1" s="62"/>
+      <c r="FV1" s="62"/>
+      <c r="FW1" s="62"/>
+      <c r="FX1" s="62"/>
+      <c r="FY1" s="62"/>
+      <c r="FZ1" s="62"/>
+      <c r="GA1" s="62"/>
+      <c r="GB1" s="62"/>
+      <c r="GC1" s="62"/>
+      <c r="GD1" s="62"/>
+      <c r="GE1" s="62"/>
+      <c r="GF1" s="62"/>
+      <c r="GG1" s="62"/>
+      <c r="GH1" s="62"/>
+      <c r="GI1" s="62"/>
+      <c r="GJ1" s="62"/>
+      <c r="GK1" s="62"/>
+      <c r="GL1" s="62"/>
+      <c r="GM1" s="62"/>
+      <c r="GN1" s="62"/>
+      <c r="GO1" s="62"/>
+      <c r="GP1" s="62"/>
+      <c r="GQ1" s="62"/>
+      <c r="GR1" s="62"/>
+      <c r="GS1" s="62"/>
+      <c r="GT1" s="62"/>
+      <c r="GU1" s="62"/>
+      <c r="GV1" s="62"/>
+      <c r="GW1" s="62"/>
+      <c r="GX1" s="62"/>
+      <c r="GY1" s="62"/>
+      <c r="GZ1" s="62"/>
+      <c r="HA1" s="62"/>
+      <c r="HB1" s="62"/>
+      <c r="HC1" s="62"/>
+      <c r="HD1" s="62"/>
+      <c r="HE1" s="62"/>
+      <c r="HF1" s="62"/>
+      <c r="HG1" s="62"/>
+      <c r="HH1" s="62"/>
+      <c r="HI1" s="62"/>
+      <c r="HJ1" s="62"/>
+      <c r="HK1" s="62"/>
+      <c r="HL1" s="62"/>
+      <c r="HM1" s="62"/>
+      <c r="HN1" s="62"/>
+      <c r="HO1" s="62"/>
+      <c r="HP1" s="62"/>
+      <c r="HQ1" s="62"/>
+      <c r="HR1" s="62"/>
+      <c r="HS1" s="62"/>
+      <c r="HT1" s="62"/>
+      <c r="HU1" s="62"/>
+      <c r="HV1" s="62"/>
+      <c r="HW1" s="62"/>
+      <c r="HX1" s="62"/>
+      <c r="HY1" s="62"/>
+      <c r="HZ1" s="62"/>
+      <c r="IA1" s="62"/>
+      <c r="IB1" s="62"/>
+      <c r="IC1" s="62"/>
+      <c r="ID1" s="62"/>
+      <c r="IE1" s="62"/>
+      <c r="IF1" s="62"/>
+      <c r="IG1" s="62"/>
+      <c r="IH1" s="62"/>
+      <c r="II1" s="62"/>
+      <c r="IJ1" s="62"/>
+      <c r="IK1" s="62"/>
+      <c r="IL1" s="62"/>
+      <c r="IM1" s="62"/>
+      <c r="IN1" s="62"/>
+      <c r="IO1" s="62"/>
+      <c r="IP1" s="62"/>
+      <c r="IQ1" s="62"/>
+      <c r="IR1" s="62"/>
+      <c r="IS1" s="62"/>
+      <c r="IT1" s="62"/>
+      <c r="IU1" s="62"/>
+      <c r="IV1" s="62"/>
+      <c r="IW1" s="62"/>
     </row>
     <row r="2" customFormat="false" ht="23.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="64" t="s">
@@ -6503,13 +7762,260 @@
     <row r="19" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H19" s="80"/>
     </row>
-    <row r="20" s="82" customFormat="true" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="82"/>
+      <c r="B20" s="82"/>
+      <c r="C20" s="82"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="82"/>
+      <c r="F20" s="82"/>
+      <c r="G20" s="82"/>
       <c r="H20" s="80"/>
+      <c r="I20" s="82"/>
       <c r="J20" s="83"/>
-      <c r="K20" s="60"/>
-      <c r="L20" s="60"/>
-      <c r="M20" s="60"/>
-      <c r="N20" s="60"/>
+      <c r="O20" s="82"/>
+      <c r="P20" s="82"/>
+      <c r="Q20" s="82"/>
+      <c r="R20" s="82"/>
+      <c r="S20" s="82"/>
+      <c r="T20" s="82"/>
+      <c r="U20" s="82"/>
+      <c r="V20" s="82"/>
+      <c r="W20" s="82"/>
+      <c r="X20" s="82"/>
+      <c r="Y20" s="82"/>
+      <c r="Z20" s="82"/>
+      <c r="AA20" s="82"/>
+      <c r="AB20" s="82"/>
+      <c r="AC20" s="82"/>
+      <c r="AD20" s="82"/>
+      <c r="AE20" s="82"/>
+      <c r="AF20" s="82"/>
+      <c r="AG20" s="82"/>
+      <c r="AH20" s="82"/>
+      <c r="AI20" s="82"/>
+      <c r="AJ20" s="82"/>
+      <c r="AK20" s="82"/>
+      <c r="AL20" s="82"/>
+      <c r="AM20" s="82"/>
+      <c r="AN20" s="82"/>
+      <c r="AO20" s="82"/>
+      <c r="AP20" s="82"/>
+      <c r="AQ20" s="82"/>
+      <c r="AR20" s="82"/>
+      <c r="AS20" s="82"/>
+      <c r="AT20" s="82"/>
+      <c r="AU20" s="82"/>
+      <c r="AV20" s="82"/>
+      <c r="AW20" s="82"/>
+      <c r="AX20" s="82"/>
+      <c r="AY20" s="82"/>
+      <c r="AZ20" s="82"/>
+      <c r="BA20" s="82"/>
+      <c r="BB20" s="82"/>
+      <c r="BC20" s="82"/>
+      <c r="BD20" s="82"/>
+      <c r="BE20" s="82"/>
+      <c r="BF20" s="82"/>
+      <c r="BG20" s="82"/>
+      <c r="BH20" s="82"/>
+      <c r="BI20" s="82"/>
+      <c r="BJ20" s="82"/>
+      <c r="BK20" s="82"/>
+      <c r="BL20" s="82"/>
+      <c r="BM20" s="82"/>
+      <c r="BN20" s="82"/>
+      <c r="BO20" s="82"/>
+      <c r="BP20" s="82"/>
+      <c r="BQ20" s="82"/>
+      <c r="BR20" s="82"/>
+      <c r="BS20" s="82"/>
+      <c r="BT20" s="82"/>
+      <c r="BU20" s="82"/>
+      <c r="BV20" s="82"/>
+      <c r="BW20" s="82"/>
+      <c r="BX20" s="82"/>
+      <c r="BY20" s="82"/>
+      <c r="BZ20" s="82"/>
+      <c r="CA20" s="82"/>
+      <c r="CB20" s="82"/>
+      <c r="CC20" s="82"/>
+      <c r="CD20" s="82"/>
+      <c r="CE20" s="82"/>
+      <c r="CF20" s="82"/>
+      <c r="CG20" s="82"/>
+      <c r="CH20" s="82"/>
+      <c r="CI20" s="82"/>
+      <c r="CJ20" s="82"/>
+      <c r="CK20" s="82"/>
+      <c r="CL20" s="82"/>
+      <c r="CM20" s="82"/>
+      <c r="CN20" s="82"/>
+      <c r="CO20" s="82"/>
+      <c r="CP20" s="82"/>
+      <c r="CQ20" s="82"/>
+      <c r="CR20" s="82"/>
+      <c r="CS20" s="82"/>
+      <c r="CT20" s="82"/>
+      <c r="CU20" s="82"/>
+      <c r="CV20" s="82"/>
+      <c r="CW20" s="82"/>
+      <c r="CX20" s="82"/>
+      <c r="CY20" s="82"/>
+      <c r="CZ20" s="82"/>
+      <c r="DA20" s="82"/>
+      <c r="DB20" s="82"/>
+      <c r="DC20" s="82"/>
+      <c r="DD20" s="82"/>
+      <c r="DE20" s="82"/>
+      <c r="DF20" s="82"/>
+      <c r="DG20" s="82"/>
+      <c r="DH20" s="82"/>
+      <c r="DI20" s="82"/>
+      <c r="DJ20" s="82"/>
+      <c r="DK20" s="82"/>
+      <c r="DL20" s="82"/>
+      <c r="DM20" s="82"/>
+      <c r="DN20" s="82"/>
+      <c r="DO20" s="82"/>
+      <c r="DP20" s="82"/>
+      <c r="DQ20" s="82"/>
+      <c r="DR20" s="82"/>
+      <c r="DS20" s="82"/>
+      <c r="DT20" s="82"/>
+      <c r="DU20" s="82"/>
+      <c r="DV20" s="82"/>
+      <c r="DW20" s="82"/>
+      <c r="DX20" s="82"/>
+      <c r="DY20" s="82"/>
+      <c r="DZ20" s="82"/>
+      <c r="EA20" s="82"/>
+      <c r="EB20" s="82"/>
+      <c r="EC20" s="82"/>
+      <c r="ED20" s="82"/>
+      <c r="EE20" s="82"/>
+      <c r="EF20" s="82"/>
+      <c r="EG20" s="82"/>
+      <c r="EH20" s="82"/>
+      <c r="EI20" s="82"/>
+      <c r="EJ20" s="82"/>
+      <c r="EK20" s="82"/>
+      <c r="EL20" s="82"/>
+      <c r="EM20" s="82"/>
+      <c r="EN20" s="82"/>
+      <c r="EO20" s="82"/>
+      <c r="EP20" s="82"/>
+      <c r="EQ20" s="82"/>
+      <c r="ER20" s="82"/>
+      <c r="ES20" s="82"/>
+      <c r="ET20" s="82"/>
+      <c r="EU20" s="82"/>
+      <c r="EV20" s="82"/>
+      <c r="EW20" s="82"/>
+      <c r="EX20" s="82"/>
+      <c r="EY20" s="82"/>
+      <c r="EZ20" s="82"/>
+      <c r="FA20" s="82"/>
+      <c r="FB20" s="82"/>
+      <c r="FC20" s="82"/>
+      <c r="FD20" s="82"/>
+      <c r="FE20" s="82"/>
+      <c r="FF20" s="82"/>
+      <c r="FG20" s="82"/>
+      <c r="FH20" s="82"/>
+      <c r="FI20" s="82"/>
+      <c r="FJ20" s="82"/>
+      <c r="FK20" s="82"/>
+      <c r="FL20" s="82"/>
+      <c r="FM20" s="82"/>
+      <c r="FN20" s="82"/>
+      <c r="FO20" s="82"/>
+      <c r="FP20" s="82"/>
+      <c r="FQ20" s="82"/>
+      <c r="FR20" s="82"/>
+      <c r="FS20" s="82"/>
+      <c r="FT20" s="82"/>
+      <c r="FU20" s="82"/>
+      <c r="FV20" s="82"/>
+      <c r="FW20" s="82"/>
+      <c r="FX20" s="82"/>
+      <c r="FY20" s="82"/>
+      <c r="FZ20" s="82"/>
+      <c r="GA20" s="82"/>
+      <c r="GB20" s="82"/>
+      <c r="GC20" s="82"/>
+      <c r="GD20" s="82"/>
+      <c r="GE20" s="82"/>
+      <c r="GF20" s="82"/>
+      <c r="GG20" s="82"/>
+      <c r="GH20" s="82"/>
+      <c r="GI20" s="82"/>
+      <c r="GJ20" s="82"/>
+      <c r="GK20" s="82"/>
+      <c r="GL20" s="82"/>
+      <c r="GM20" s="82"/>
+      <c r="GN20" s="82"/>
+      <c r="GO20" s="82"/>
+      <c r="GP20" s="82"/>
+      <c r="GQ20" s="82"/>
+      <c r="GR20" s="82"/>
+      <c r="GS20" s="82"/>
+      <c r="GT20" s="82"/>
+      <c r="GU20" s="82"/>
+      <c r="GV20" s="82"/>
+      <c r="GW20" s="82"/>
+      <c r="GX20" s="82"/>
+      <c r="GY20" s="82"/>
+      <c r="GZ20" s="82"/>
+      <c r="HA20" s="82"/>
+      <c r="HB20" s="82"/>
+      <c r="HC20" s="82"/>
+      <c r="HD20" s="82"/>
+      <c r="HE20" s="82"/>
+      <c r="HF20" s="82"/>
+      <c r="HG20" s="82"/>
+      <c r="HH20" s="82"/>
+      <c r="HI20" s="82"/>
+      <c r="HJ20" s="82"/>
+      <c r="HK20" s="82"/>
+      <c r="HL20" s="82"/>
+      <c r="HM20" s="82"/>
+      <c r="HN20" s="82"/>
+      <c r="HO20" s="82"/>
+      <c r="HP20" s="82"/>
+      <c r="HQ20" s="82"/>
+      <c r="HR20" s="82"/>
+      <c r="HS20" s="82"/>
+      <c r="HT20" s="82"/>
+      <c r="HU20" s="82"/>
+      <c r="HV20" s="82"/>
+      <c r="HW20" s="82"/>
+      <c r="HX20" s="82"/>
+      <c r="HY20" s="82"/>
+      <c r="HZ20" s="82"/>
+      <c r="IA20" s="82"/>
+      <c r="IB20" s="82"/>
+      <c r="IC20" s="82"/>
+      <c r="ID20" s="82"/>
+      <c r="IE20" s="82"/>
+      <c r="IF20" s="82"/>
+      <c r="IG20" s="82"/>
+      <c r="IH20" s="82"/>
+      <c r="II20" s="82"/>
+      <c r="IJ20" s="82"/>
+      <c r="IK20" s="82"/>
+      <c r="IL20" s="82"/>
+      <c r="IM20" s="82"/>
+      <c r="IN20" s="82"/>
+      <c r="IO20" s="82"/>
+      <c r="IP20" s="82"/>
+      <c r="IQ20" s="82"/>
+      <c r="IR20" s="82"/>
+      <c r="IS20" s="82"/>
+      <c r="IT20" s="82"/>
+      <c r="IU20" s="82"/>
+      <c r="IV20" s="82"/>
+      <c r="IW20" s="82"/>
     </row>
     <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="82"/>
@@ -6554,6 +8060,957 @@
     <row r="30" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="89" t="s">
         <v>174</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="89" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="80" t="s">
+        <v>176</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:IW32"/>
+  <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="12.55" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="60" width="12.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="60" width="12.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="60" width="14.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="60" width="12.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="60" width="17.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="60" width="15.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="60" width="13.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="60" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="60" width="14.55"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="10" min="10" style="60" width="9.1"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="11" style="60" width="9.1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="26.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="61" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
+      <c r="S1" s="62"/>
+      <c r="T1" s="62"/>
+      <c r="U1" s="62"/>
+      <c r="V1" s="62"/>
+      <c r="W1" s="62"/>
+      <c r="X1" s="62"/>
+      <c r="Y1" s="62"/>
+      <c r="Z1" s="62"/>
+      <c r="AA1" s="62"/>
+      <c r="AB1" s="62"/>
+      <c r="AC1" s="62"/>
+      <c r="AD1" s="62"/>
+      <c r="AE1" s="62"/>
+      <c r="AF1" s="62"/>
+      <c r="AG1" s="62"/>
+      <c r="AH1" s="62"/>
+      <c r="AI1" s="62"/>
+      <c r="AJ1" s="62"/>
+      <c r="AK1" s="62"/>
+      <c r="AL1" s="62"/>
+      <c r="AM1" s="62"/>
+      <c r="AN1" s="62"/>
+      <c r="AO1" s="62"/>
+      <c r="AP1" s="62"/>
+      <c r="AQ1" s="62"/>
+      <c r="AR1" s="62"/>
+      <c r="AS1" s="62"/>
+      <c r="AT1" s="62"/>
+      <c r="AU1" s="62"/>
+      <c r="AV1" s="62"/>
+      <c r="AW1" s="62"/>
+      <c r="AX1" s="62"/>
+      <c r="AY1" s="62"/>
+      <c r="AZ1" s="62"/>
+      <c r="BA1" s="62"/>
+      <c r="BB1" s="62"/>
+      <c r="BC1" s="62"/>
+      <c r="BD1" s="62"/>
+      <c r="BE1" s="62"/>
+      <c r="BF1" s="62"/>
+      <c r="BG1" s="62"/>
+      <c r="BH1" s="62"/>
+      <c r="BI1" s="62"/>
+      <c r="BJ1" s="62"/>
+      <c r="BK1" s="62"/>
+      <c r="BL1" s="62"/>
+      <c r="BM1" s="62"/>
+      <c r="BN1" s="62"/>
+      <c r="BO1" s="62"/>
+      <c r="BP1" s="62"/>
+      <c r="BQ1" s="62"/>
+      <c r="BR1" s="62"/>
+      <c r="BS1" s="62"/>
+      <c r="BT1" s="62"/>
+      <c r="BU1" s="62"/>
+      <c r="BV1" s="62"/>
+      <c r="BW1" s="62"/>
+      <c r="BX1" s="62"/>
+      <c r="BY1" s="62"/>
+      <c r="BZ1" s="62"/>
+      <c r="CA1" s="62"/>
+      <c r="CB1" s="62"/>
+      <c r="CC1" s="62"/>
+      <c r="CD1" s="62"/>
+      <c r="CE1" s="62"/>
+      <c r="CF1" s="62"/>
+      <c r="CG1" s="62"/>
+      <c r="CH1" s="62"/>
+      <c r="CI1" s="62"/>
+      <c r="CJ1" s="62"/>
+      <c r="CK1" s="62"/>
+      <c r="CL1" s="62"/>
+      <c r="CM1" s="62"/>
+      <c r="CN1" s="62"/>
+      <c r="CO1" s="62"/>
+      <c r="CP1" s="62"/>
+      <c r="CQ1" s="62"/>
+      <c r="CR1" s="62"/>
+      <c r="CS1" s="62"/>
+      <c r="CT1" s="62"/>
+      <c r="CU1" s="62"/>
+      <c r="CV1" s="62"/>
+      <c r="CW1" s="62"/>
+      <c r="CX1" s="62"/>
+      <c r="CY1" s="62"/>
+      <c r="CZ1" s="62"/>
+      <c r="DA1" s="62"/>
+      <c r="DB1" s="62"/>
+      <c r="DC1" s="62"/>
+      <c r="DD1" s="62"/>
+      <c r="DE1" s="62"/>
+      <c r="DF1" s="62"/>
+      <c r="DG1" s="62"/>
+      <c r="DH1" s="62"/>
+      <c r="DI1" s="62"/>
+      <c r="DJ1" s="62"/>
+      <c r="DK1" s="62"/>
+      <c r="DL1" s="62"/>
+      <c r="DM1" s="62"/>
+      <c r="DN1" s="62"/>
+      <c r="DO1" s="62"/>
+      <c r="DP1" s="62"/>
+      <c r="DQ1" s="62"/>
+      <c r="DR1" s="62"/>
+      <c r="DS1" s="62"/>
+      <c r="DT1" s="62"/>
+      <c r="DU1" s="62"/>
+      <c r="DV1" s="62"/>
+      <c r="DW1" s="62"/>
+      <c r="DX1" s="62"/>
+      <c r="DY1" s="62"/>
+      <c r="DZ1" s="62"/>
+      <c r="EA1" s="62"/>
+      <c r="EB1" s="62"/>
+      <c r="EC1" s="62"/>
+      <c r="ED1" s="62"/>
+      <c r="EE1" s="62"/>
+      <c r="EF1" s="62"/>
+      <c r="EG1" s="62"/>
+      <c r="EH1" s="62"/>
+      <c r="EI1" s="62"/>
+      <c r="EJ1" s="62"/>
+      <c r="EK1" s="62"/>
+      <c r="EL1" s="62"/>
+      <c r="EM1" s="62"/>
+      <c r="EN1" s="62"/>
+      <c r="EO1" s="62"/>
+      <c r="EP1" s="62"/>
+      <c r="EQ1" s="62"/>
+      <c r="ER1" s="62"/>
+      <c r="ES1" s="62"/>
+      <c r="ET1" s="62"/>
+      <c r="EU1" s="62"/>
+      <c r="EV1" s="62"/>
+      <c r="EW1" s="62"/>
+      <c r="EX1" s="62"/>
+      <c r="EY1" s="62"/>
+      <c r="EZ1" s="62"/>
+      <c r="FA1" s="62"/>
+      <c r="FB1" s="62"/>
+      <c r="FC1" s="62"/>
+      <c r="FD1" s="62"/>
+      <c r="FE1" s="62"/>
+      <c r="FF1" s="62"/>
+      <c r="FG1" s="62"/>
+      <c r="FH1" s="62"/>
+      <c r="FI1" s="62"/>
+      <c r="FJ1" s="62"/>
+      <c r="FK1" s="62"/>
+      <c r="FL1" s="62"/>
+      <c r="FM1" s="62"/>
+      <c r="FN1" s="62"/>
+      <c r="FO1" s="62"/>
+      <c r="FP1" s="62"/>
+      <c r="FQ1" s="62"/>
+      <c r="FR1" s="62"/>
+      <c r="FS1" s="62"/>
+      <c r="FT1" s="62"/>
+      <c r="FU1" s="62"/>
+      <c r="FV1" s="62"/>
+      <c r="FW1" s="62"/>
+      <c r="FX1" s="62"/>
+      <c r="FY1" s="62"/>
+      <c r="FZ1" s="62"/>
+      <c r="GA1" s="62"/>
+      <c r="GB1" s="62"/>
+      <c r="GC1" s="62"/>
+      <c r="GD1" s="62"/>
+      <c r="GE1" s="62"/>
+      <c r="GF1" s="62"/>
+      <c r="GG1" s="62"/>
+      <c r="GH1" s="62"/>
+      <c r="GI1" s="62"/>
+      <c r="GJ1" s="62"/>
+      <c r="GK1" s="62"/>
+      <c r="GL1" s="62"/>
+      <c r="GM1" s="62"/>
+      <c r="GN1" s="62"/>
+      <c r="GO1" s="62"/>
+      <c r="GP1" s="62"/>
+      <c r="GQ1" s="62"/>
+      <c r="GR1" s="62"/>
+      <c r="GS1" s="62"/>
+      <c r="GT1" s="62"/>
+      <c r="GU1" s="62"/>
+      <c r="GV1" s="62"/>
+      <c r="GW1" s="62"/>
+      <c r="GX1" s="62"/>
+      <c r="GY1" s="62"/>
+      <c r="GZ1" s="62"/>
+      <c r="HA1" s="62"/>
+      <c r="HB1" s="62"/>
+      <c r="HC1" s="62"/>
+      <c r="HD1" s="62"/>
+      <c r="HE1" s="62"/>
+      <c r="HF1" s="62"/>
+      <c r="HG1" s="62"/>
+      <c r="HH1" s="62"/>
+      <c r="HI1" s="62"/>
+      <c r="HJ1" s="62"/>
+      <c r="HK1" s="62"/>
+      <c r="HL1" s="62"/>
+      <c r="HM1" s="62"/>
+      <c r="HN1" s="62"/>
+      <c r="HO1" s="62"/>
+      <c r="HP1" s="62"/>
+      <c r="HQ1" s="62"/>
+      <c r="HR1" s="62"/>
+      <c r="HS1" s="62"/>
+      <c r="HT1" s="62"/>
+      <c r="HU1" s="62"/>
+      <c r="HV1" s="62"/>
+      <c r="HW1" s="62"/>
+      <c r="HX1" s="62"/>
+      <c r="HY1" s="62"/>
+      <c r="HZ1" s="62"/>
+      <c r="IA1" s="62"/>
+      <c r="IB1" s="62"/>
+      <c r="IC1" s="62"/>
+      <c r="ID1" s="62"/>
+      <c r="IE1" s="62"/>
+      <c r="IF1" s="62"/>
+      <c r="IG1" s="62"/>
+      <c r="IH1" s="62"/>
+      <c r="II1" s="62"/>
+      <c r="IJ1" s="62"/>
+      <c r="IK1" s="62"/>
+      <c r="IL1" s="62"/>
+      <c r="IM1" s="62"/>
+      <c r="IN1" s="62"/>
+      <c r="IO1" s="62"/>
+      <c r="IP1" s="62"/>
+      <c r="IQ1" s="62"/>
+      <c r="IR1" s="62"/>
+      <c r="IS1" s="62"/>
+      <c r="IT1" s="62"/>
+      <c r="IU1" s="62"/>
+      <c r="IV1" s="62"/>
+      <c r="IW1" s="62"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="64" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="72" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="64" t="s">
+        <v>151</v>
+      </c>
+      <c r="D2" s="64" t="s">
+        <v>152</v>
+      </c>
+      <c r="E2" s="64" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2" s="64" t="s">
+        <v>153</v>
+      </c>
+      <c r="G2" s="64" t="s">
+        <v>58</v>
+      </c>
+      <c r="H2" s="65" t="s">
+        <v>142</v>
+      </c>
+      <c r="I2" s="66"/>
+      <c r="L2" s="63" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="67" t="s">
+        <v>154</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="I3" s="68"/>
+    </row>
+    <row r="4" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="69" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="E4" s="67" t="s">
+        <v>178</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="H4" s="69" t="s">
+        <v>139</v>
+      </c>
+      <c r="I4" s="68"/>
+    </row>
+    <row r="5" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="70" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="70" t="s">
+        <v>156</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G5" s="65" t="s">
+        <v>71</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="I5" s="71"/>
+    </row>
+    <row r="6" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="69" t="s">
+        <v>120</v>
+      </c>
+      <c r="G6" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="I6" s="71"/>
+    </row>
+    <row r="7" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="93" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="70" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="H7" s="69" t="s">
+        <v>131</v>
+      </c>
+      <c r="I7" s="68"/>
+    </row>
+    <row r="8" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="70" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="70" t="s">
+        <v>167</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="H8" s="69" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="75" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="64" t="s">
+        <v>164</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="70" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="74"/>
+      <c r="H9" s="75" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="73" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="75" t="s">
+        <v>172</v>
+      </c>
+      <c r="F10" s="76" t="s">
+        <v>158</v>
+      </c>
+      <c r="G10" s="65"/>
+    </row>
+    <row r="11" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C11" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="72" t="s">
+        <v>159</v>
+      </c>
+      <c r="E11" s="94" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="69" t="s">
+        <v>116</v>
+      </c>
+      <c r="H11" s="77"/>
+    </row>
+    <row r="12" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C12" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="77"/>
+      <c r="H12" s="69"/>
+    </row>
+    <row r="13" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="65" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="75" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="75" t="s">
+        <v>41</v>
+      </c>
+      <c r="H13" s="69"/>
+    </row>
+    <row r="14" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="70" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="67" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" s="78" t="s">
+        <v>161</v>
+      </c>
+      <c r="I14" s="79" t="s">
+        <v>162</v>
+      </c>
+      <c r="L14" s="60" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C15" s="75" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="75" t="s">
+        <v>160</v>
+      </c>
+      <c r="E15" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="80" t="s">
+        <v>52</v>
+      </c>
+      <c r="I15" s="81" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C16" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="75" t="s">
+        <v>165</v>
+      </c>
+      <c r="E16" s="67" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H16" s="92" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="81" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C17" s="67" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="69" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17" s="92" t="s">
+        <v>40</v>
+      </c>
+      <c r="I17" s="81" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H18" s="80"/>
+      <c r="I18" s="81" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H19" s="80"/>
+    </row>
+    <row r="20" customFormat="false" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="82"/>
+      <c r="B20" s="82"/>
+      <c r="C20" s="82"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="82"/>
+      <c r="F20" s="82"/>
+      <c r="G20" s="82"/>
+      <c r="H20" s="80"/>
+      <c r="I20" s="82"/>
+      <c r="J20" s="83"/>
+      <c r="O20" s="82"/>
+      <c r="P20" s="82"/>
+      <c r="Q20" s="82"/>
+      <c r="R20" s="82"/>
+      <c r="S20" s="82"/>
+      <c r="T20" s="82"/>
+      <c r="U20" s="82"/>
+      <c r="V20" s="82"/>
+      <c r="W20" s="82"/>
+      <c r="X20" s="82"/>
+      <c r="Y20" s="82"/>
+      <c r="Z20" s="82"/>
+      <c r="AA20" s="82"/>
+      <c r="AB20" s="82"/>
+      <c r="AC20" s="82"/>
+      <c r="AD20" s="82"/>
+      <c r="AE20" s="82"/>
+      <c r="AF20" s="82"/>
+      <c r="AG20" s="82"/>
+      <c r="AH20" s="82"/>
+      <c r="AI20" s="82"/>
+      <c r="AJ20" s="82"/>
+      <c r="AK20" s="82"/>
+      <c r="AL20" s="82"/>
+      <c r="AM20" s="82"/>
+      <c r="AN20" s="82"/>
+      <c r="AO20" s="82"/>
+      <c r="AP20" s="82"/>
+      <c r="AQ20" s="82"/>
+      <c r="AR20" s="82"/>
+      <c r="AS20" s="82"/>
+      <c r="AT20" s="82"/>
+      <c r="AU20" s="82"/>
+      <c r="AV20" s="82"/>
+      <c r="AW20" s="82"/>
+      <c r="AX20" s="82"/>
+      <c r="AY20" s="82"/>
+      <c r="AZ20" s="82"/>
+      <c r="BA20" s="82"/>
+      <c r="BB20" s="82"/>
+      <c r="BC20" s="82"/>
+      <c r="BD20" s="82"/>
+      <c r="BE20" s="82"/>
+      <c r="BF20" s="82"/>
+      <c r="BG20" s="82"/>
+      <c r="BH20" s="82"/>
+      <c r="BI20" s="82"/>
+      <c r="BJ20" s="82"/>
+      <c r="BK20" s="82"/>
+      <c r="BL20" s="82"/>
+      <c r="BM20" s="82"/>
+      <c r="BN20" s="82"/>
+      <c r="BO20" s="82"/>
+      <c r="BP20" s="82"/>
+      <c r="BQ20" s="82"/>
+      <c r="BR20" s="82"/>
+      <c r="BS20" s="82"/>
+      <c r="BT20" s="82"/>
+      <c r="BU20" s="82"/>
+      <c r="BV20" s="82"/>
+      <c r="BW20" s="82"/>
+      <c r="BX20" s="82"/>
+      <c r="BY20" s="82"/>
+      <c r="BZ20" s="82"/>
+      <c r="CA20" s="82"/>
+      <c r="CB20" s="82"/>
+      <c r="CC20" s="82"/>
+      <c r="CD20" s="82"/>
+      <c r="CE20" s="82"/>
+      <c r="CF20" s="82"/>
+      <c r="CG20" s="82"/>
+      <c r="CH20" s="82"/>
+      <c r="CI20" s="82"/>
+      <c r="CJ20" s="82"/>
+      <c r="CK20" s="82"/>
+      <c r="CL20" s="82"/>
+      <c r="CM20" s="82"/>
+      <c r="CN20" s="82"/>
+      <c r="CO20" s="82"/>
+      <c r="CP20" s="82"/>
+      <c r="CQ20" s="82"/>
+      <c r="CR20" s="82"/>
+      <c r="CS20" s="82"/>
+      <c r="CT20" s="82"/>
+      <c r="CU20" s="82"/>
+      <c r="CV20" s="82"/>
+      <c r="CW20" s="82"/>
+      <c r="CX20" s="82"/>
+      <c r="CY20" s="82"/>
+      <c r="CZ20" s="82"/>
+      <c r="DA20" s="82"/>
+      <c r="DB20" s="82"/>
+      <c r="DC20" s="82"/>
+      <c r="DD20" s="82"/>
+      <c r="DE20" s="82"/>
+      <c r="DF20" s="82"/>
+      <c r="DG20" s="82"/>
+      <c r="DH20" s="82"/>
+      <c r="DI20" s="82"/>
+      <c r="DJ20" s="82"/>
+      <c r="DK20" s="82"/>
+      <c r="DL20" s="82"/>
+      <c r="DM20" s="82"/>
+      <c r="DN20" s="82"/>
+      <c r="DO20" s="82"/>
+      <c r="DP20" s="82"/>
+      <c r="DQ20" s="82"/>
+      <c r="DR20" s="82"/>
+      <c r="DS20" s="82"/>
+      <c r="DT20" s="82"/>
+      <c r="DU20" s="82"/>
+      <c r="DV20" s="82"/>
+      <c r="DW20" s="82"/>
+      <c r="DX20" s="82"/>
+      <c r="DY20" s="82"/>
+      <c r="DZ20" s="82"/>
+      <c r="EA20" s="82"/>
+      <c r="EB20" s="82"/>
+      <c r="EC20" s="82"/>
+      <c r="ED20" s="82"/>
+      <c r="EE20" s="82"/>
+      <c r="EF20" s="82"/>
+      <c r="EG20" s="82"/>
+      <c r="EH20" s="82"/>
+      <c r="EI20" s="82"/>
+      <c r="EJ20" s="82"/>
+      <c r="EK20" s="82"/>
+      <c r="EL20" s="82"/>
+      <c r="EM20" s="82"/>
+      <c r="EN20" s="82"/>
+      <c r="EO20" s="82"/>
+      <c r="EP20" s="82"/>
+      <c r="EQ20" s="82"/>
+      <c r="ER20" s="82"/>
+      <c r="ES20" s="82"/>
+      <c r="ET20" s="82"/>
+      <c r="EU20" s="82"/>
+      <c r="EV20" s="82"/>
+      <c r="EW20" s="82"/>
+      <c r="EX20" s="82"/>
+      <c r="EY20" s="82"/>
+      <c r="EZ20" s="82"/>
+      <c r="FA20" s="82"/>
+      <c r="FB20" s="82"/>
+      <c r="FC20" s="82"/>
+      <c r="FD20" s="82"/>
+      <c r="FE20" s="82"/>
+      <c r="FF20" s="82"/>
+      <c r="FG20" s="82"/>
+      <c r="FH20" s="82"/>
+      <c r="FI20" s="82"/>
+      <c r="FJ20" s="82"/>
+      <c r="FK20" s="82"/>
+      <c r="FL20" s="82"/>
+      <c r="FM20" s="82"/>
+      <c r="FN20" s="82"/>
+      <c r="FO20" s="82"/>
+      <c r="FP20" s="82"/>
+      <c r="FQ20" s="82"/>
+      <c r="FR20" s="82"/>
+      <c r="FS20" s="82"/>
+      <c r="FT20" s="82"/>
+      <c r="FU20" s="82"/>
+      <c r="FV20" s="82"/>
+      <c r="FW20" s="82"/>
+      <c r="FX20" s="82"/>
+      <c r="FY20" s="82"/>
+      <c r="FZ20" s="82"/>
+      <c r="GA20" s="82"/>
+      <c r="GB20" s="82"/>
+      <c r="GC20" s="82"/>
+      <c r="GD20" s="82"/>
+      <c r="GE20" s="82"/>
+      <c r="GF20" s="82"/>
+      <c r="GG20" s="82"/>
+      <c r="GH20" s="82"/>
+      <c r="GI20" s="82"/>
+      <c r="GJ20" s="82"/>
+      <c r="GK20" s="82"/>
+      <c r="GL20" s="82"/>
+      <c r="GM20" s="82"/>
+      <c r="GN20" s="82"/>
+      <c r="GO20" s="82"/>
+      <c r="GP20" s="82"/>
+      <c r="GQ20" s="82"/>
+      <c r="GR20" s="82"/>
+      <c r="GS20" s="82"/>
+      <c r="GT20" s="82"/>
+      <c r="GU20" s="82"/>
+      <c r="GV20" s="82"/>
+      <c r="GW20" s="82"/>
+      <c r="GX20" s="82"/>
+      <c r="GY20" s="82"/>
+      <c r="GZ20" s="82"/>
+      <c r="HA20" s="82"/>
+      <c r="HB20" s="82"/>
+      <c r="HC20" s="82"/>
+      <c r="HD20" s="82"/>
+      <c r="HE20" s="82"/>
+      <c r="HF20" s="82"/>
+      <c r="HG20" s="82"/>
+      <c r="HH20" s="82"/>
+      <c r="HI20" s="82"/>
+      <c r="HJ20" s="82"/>
+      <c r="HK20" s="82"/>
+      <c r="HL20" s="82"/>
+      <c r="HM20" s="82"/>
+      <c r="HN20" s="82"/>
+      <c r="HO20" s="82"/>
+      <c r="HP20" s="82"/>
+      <c r="HQ20" s="82"/>
+      <c r="HR20" s="82"/>
+      <c r="HS20" s="82"/>
+      <c r="HT20" s="82"/>
+      <c r="HU20" s="82"/>
+      <c r="HV20" s="82"/>
+      <c r="HW20" s="82"/>
+      <c r="HX20" s="82"/>
+      <c r="HY20" s="82"/>
+      <c r="HZ20" s="82"/>
+      <c r="IA20" s="82"/>
+      <c r="IB20" s="82"/>
+      <c r="IC20" s="82"/>
+      <c r="ID20" s="82"/>
+      <c r="IE20" s="82"/>
+      <c r="IF20" s="82"/>
+      <c r="IG20" s="82"/>
+      <c r="IH20" s="82"/>
+      <c r="II20" s="82"/>
+      <c r="IJ20" s="82"/>
+      <c r="IK20" s="82"/>
+      <c r="IL20" s="82"/>
+      <c r="IM20" s="82"/>
+      <c r="IN20" s="82"/>
+      <c r="IO20" s="82"/>
+      <c r="IP20" s="82"/>
+      <c r="IQ20" s="82"/>
+      <c r="IR20" s="82"/>
+      <c r="IS20" s="82"/>
+      <c r="IT20" s="82"/>
+      <c r="IU20" s="82"/>
+      <c r="IV20" s="82"/>
+      <c r="IW20" s="82"/>
+    </row>
+    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="82"/>
+      <c r="G21" s="84"/>
+      <c r="H21" s="80"/>
+      <c r="I21" s="81"/>
+      <c r="J21" s="85" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="86"/>
+      <c r="G22" s="86"/>
+      <c r="H22" s="80"/>
+      <c r="I22" s="81"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="81"/>
+      <c r="R23" s="87"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="81"/>
+      <c r="L24" s="60" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I25" s="81"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="3"/>
+      <c r="I26" s="81"/>
+    </row>
+    <row r="28" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D28" s="88"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="89" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="89" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/raw/BUS.xlsx
+++ b/raw/BUS.xlsx
@@ -13,6 +13,7 @@
     <sheet name="25" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="26" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="27" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Лист1" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -850,8 +851,204 @@
 </comments>
 </file>
 
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">20
+ kbm-13
+tms -  8
+dtt - 6/1</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>25</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>30</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A29" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">35--8/9</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>27</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>32</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A30" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">35-   15/6
+</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>28</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>33</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A31" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">35.1- 1/1
+</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>29</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>34</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A32" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve"> 35.2-  2/2
+</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>30</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>35</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="182">
   <si>
     <t xml:space="preserve">35.1-2673</t>
   </si>
@@ -1394,6 +1591,9 @@
   </si>
   <si>
     <t xml:space="preserve">kbm 19/6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-0592</t>
   </si>
 </sst>
 </file>
@@ -4893,6 +5093,51 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>23400</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>48240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>321840</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>71640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="AutoShape 3" descr="C:\Users\A_Tumayeva\Desktop\9hq.webp"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="883800" y="5872320"/>
+          <a:ext cx="298440" cy="2134800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
   <a:themeElements>
@@ -9037,4 +9282,955 @@
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:IW32"/>
+  <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="12.55" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="60" width="12.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="60" width="12.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="60" width="14.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="60" width="12.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="60" width="17.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="60" width="15.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="60" width="13.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="60" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="60" width="14.55"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="10" min="10" style="60" width="9.1"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="11" style="60" width="9.1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="26.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="61" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
+      <c r="S1" s="62"/>
+      <c r="T1" s="62"/>
+      <c r="U1" s="62"/>
+      <c r="V1" s="62"/>
+      <c r="W1" s="62"/>
+      <c r="X1" s="62"/>
+      <c r="Y1" s="62"/>
+      <c r="Z1" s="62"/>
+      <c r="AA1" s="62"/>
+      <c r="AB1" s="62"/>
+      <c r="AC1" s="62"/>
+      <c r="AD1" s="62"/>
+      <c r="AE1" s="62"/>
+      <c r="AF1" s="62"/>
+      <c r="AG1" s="62"/>
+      <c r="AH1" s="62"/>
+      <c r="AI1" s="62"/>
+      <c r="AJ1" s="62"/>
+      <c r="AK1" s="62"/>
+      <c r="AL1" s="62"/>
+      <c r="AM1" s="62"/>
+      <c r="AN1" s="62"/>
+      <c r="AO1" s="62"/>
+      <c r="AP1" s="62"/>
+      <c r="AQ1" s="62"/>
+      <c r="AR1" s="62"/>
+      <c r="AS1" s="62"/>
+      <c r="AT1" s="62"/>
+      <c r="AU1" s="62"/>
+      <c r="AV1" s="62"/>
+      <c r="AW1" s="62"/>
+      <c r="AX1" s="62"/>
+      <c r="AY1" s="62"/>
+      <c r="AZ1" s="62"/>
+      <c r="BA1" s="62"/>
+      <c r="BB1" s="62"/>
+      <c r="BC1" s="62"/>
+      <c r="BD1" s="62"/>
+      <c r="BE1" s="62"/>
+      <c r="BF1" s="62"/>
+      <c r="BG1" s="62"/>
+      <c r="BH1" s="62"/>
+      <c r="BI1" s="62"/>
+      <c r="BJ1" s="62"/>
+      <c r="BK1" s="62"/>
+      <c r="BL1" s="62"/>
+      <c r="BM1" s="62"/>
+      <c r="BN1" s="62"/>
+      <c r="BO1" s="62"/>
+      <c r="BP1" s="62"/>
+      <c r="BQ1" s="62"/>
+      <c r="BR1" s="62"/>
+      <c r="BS1" s="62"/>
+      <c r="BT1" s="62"/>
+      <c r="BU1" s="62"/>
+      <c r="BV1" s="62"/>
+      <c r="BW1" s="62"/>
+      <c r="BX1" s="62"/>
+      <c r="BY1" s="62"/>
+      <c r="BZ1" s="62"/>
+      <c r="CA1" s="62"/>
+      <c r="CB1" s="62"/>
+      <c r="CC1" s="62"/>
+      <c r="CD1" s="62"/>
+      <c r="CE1" s="62"/>
+      <c r="CF1" s="62"/>
+      <c r="CG1" s="62"/>
+      <c r="CH1" s="62"/>
+      <c r="CI1" s="62"/>
+      <c r="CJ1" s="62"/>
+      <c r="CK1" s="62"/>
+      <c r="CL1" s="62"/>
+      <c r="CM1" s="62"/>
+      <c r="CN1" s="62"/>
+      <c r="CO1" s="62"/>
+      <c r="CP1" s="62"/>
+      <c r="CQ1" s="62"/>
+      <c r="CR1" s="62"/>
+      <c r="CS1" s="62"/>
+      <c r="CT1" s="62"/>
+      <c r="CU1" s="62"/>
+      <c r="CV1" s="62"/>
+      <c r="CW1" s="62"/>
+      <c r="CX1" s="62"/>
+      <c r="CY1" s="62"/>
+      <c r="CZ1" s="62"/>
+      <c r="DA1" s="62"/>
+      <c r="DB1" s="62"/>
+      <c r="DC1" s="62"/>
+      <c r="DD1" s="62"/>
+      <c r="DE1" s="62"/>
+      <c r="DF1" s="62"/>
+      <c r="DG1" s="62"/>
+      <c r="DH1" s="62"/>
+      <c r="DI1" s="62"/>
+      <c r="DJ1" s="62"/>
+      <c r="DK1" s="62"/>
+      <c r="DL1" s="62"/>
+      <c r="DM1" s="62"/>
+      <c r="DN1" s="62"/>
+      <c r="DO1" s="62"/>
+      <c r="DP1" s="62"/>
+      <c r="DQ1" s="62"/>
+      <c r="DR1" s="62"/>
+      <c r="DS1" s="62"/>
+      <c r="DT1" s="62"/>
+      <c r="DU1" s="62"/>
+      <c r="DV1" s="62"/>
+      <c r="DW1" s="62"/>
+      <c r="DX1" s="62"/>
+      <c r="DY1" s="62"/>
+      <c r="DZ1" s="62"/>
+      <c r="EA1" s="62"/>
+      <c r="EB1" s="62"/>
+      <c r="EC1" s="62"/>
+      <c r="ED1" s="62"/>
+      <c r="EE1" s="62"/>
+      <c r="EF1" s="62"/>
+      <c r="EG1" s="62"/>
+      <c r="EH1" s="62"/>
+      <c r="EI1" s="62"/>
+      <c r="EJ1" s="62"/>
+      <c r="EK1" s="62"/>
+      <c r="EL1" s="62"/>
+      <c r="EM1" s="62"/>
+      <c r="EN1" s="62"/>
+      <c r="EO1" s="62"/>
+      <c r="EP1" s="62"/>
+      <c r="EQ1" s="62"/>
+      <c r="ER1" s="62"/>
+      <c r="ES1" s="62"/>
+      <c r="ET1" s="62"/>
+      <c r="EU1" s="62"/>
+      <c r="EV1" s="62"/>
+      <c r="EW1" s="62"/>
+      <c r="EX1" s="62"/>
+      <c r="EY1" s="62"/>
+      <c r="EZ1" s="62"/>
+      <c r="FA1" s="62"/>
+      <c r="FB1" s="62"/>
+      <c r="FC1" s="62"/>
+      <c r="FD1" s="62"/>
+      <c r="FE1" s="62"/>
+      <c r="FF1" s="62"/>
+      <c r="FG1" s="62"/>
+      <c r="FH1" s="62"/>
+      <c r="FI1" s="62"/>
+      <c r="FJ1" s="62"/>
+      <c r="FK1" s="62"/>
+      <c r="FL1" s="62"/>
+      <c r="FM1" s="62"/>
+      <c r="FN1" s="62"/>
+      <c r="FO1" s="62"/>
+      <c r="FP1" s="62"/>
+      <c r="FQ1" s="62"/>
+      <c r="FR1" s="62"/>
+      <c r="FS1" s="62"/>
+      <c r="FT1" s="62"/>
+      <c r="FU1" s="62"/>
+      <c r="FV1" s="62"/>
+      <c r="FW1" s="62"/>
+      <c r="FX1" s="62"/>
+      <c r="FY1" s="62"/>
+      <c r="FZ1" s="62"/>
+      <c r="GA1" s="62"/>
+      <c r="GB1" s="62"/>
+      <c r="GC1" s="62"/>
+      <c r="GD1" s="62"/>
+      <c r="GE1" s="62"/>
+      <c r="GF1" s="62"/>
+      <c r="GG1" s="62"/>
+      <c r="GH1" s="62"/>
+      <c r="GI1" s="62"/>
+      <c r="GJ1" s="62"/>
+      <c r="GK1" s="62"/>
+      <c r="GL1" s="62"/>
+      <c r="GM1" s="62"/>
+      <c r="GN1" s="62"/>
+      <c r="GO1" s="62"/>
+      <c r="GP1" s="62"/>
+      <c r="GQ1" s="62"/>
+      <c r="GR1" s="62"/>
+      <c r="GS1" s="62"/>
+      <c r="GT1" s="62"/>
+      <c r="GU1" s="62"/>
+      <c r="GV1" s="62"/>
+      <c r="GW1" s="62"/>
+      <c r="GX1" s="62"/>
+      <c r="GY1" s="62"/>
+      <c r="GZ1" s="62"/>
+      <c r="HA1" s="62"/>
+      <c r="HB1" s="62"/>
+      <c r="HC1" s="62"/>
+      <c r="HD1" s="62"/>
+      <c r="HE1" s="62"/>
+      <c r="HF1" s="62"/>
+      <c r="HG1" s="62"/>
+      <c r="HH1" s="62"/>
+      <c r="HI1" s="62"/>
+      <c r="HJ1" s="62"/>
+      <c r="HK1" s="62"/>
+      <c r="HL1" s="62"/>
+      <c r="HM1" s="62"/>
+      <c r="HN1" s="62"/>
+      <c r="HO1" s="62"/>
+      <c r="HP1" s="62"/>
+      <c r="HQ1" s="62"/>
+      <c r="HR1" s="62"/>
+      <c r="HS1" s="62"/>
+      <c r="HT1" s="62"/>
+      <c r="HU1" s="62"/>
+      <c r="HV1" s="62"/>
+      <c r="HW1" s="62"/>
+      <c r="HX1" s="62"/>
+      <c r="HY1" s="62"/>
+      <c r="HZ1" s="62"/>
+      <c r="IA1" s="62"/>
+      <c r="IB1" s="62"/>
+      <c r="IC1" s="62"/>
+      <c r="ID1" s="62"/>
+      <c r="IE1" s="62"/>
+      <c r="IF1" s="62"/>
+      <c r="IG1" s="62"/>
+      <c r="IH1" s="62"/>
+      <c r="II1" s="62"/>
+      <c r="IJ1" s="62"/>
+      <c r="IK1" s="62"/>
+      <c r="IL1" s="62"/>
+      <c r="IM1" s="62"/>
+      <c r="IN1" s="62"/>
+      <c r="IO1" s="62"/>
+      <c r="IP1" s="62"/>
+      <c r="IQ1" s="62"/>
+      <c r="IR1" s="62"/>
+      <c r="IS1" s="62"/>
+      <c r="IT1" s="62"/>
+      <c r="IU1" s="62"/>
+      <c r="IV1" s="62"/>
+      <c r="IW1" s="62"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="64" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="72" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="64" t="s">
+        <v>151</v>
+      </c>
+      <c r="D2" s="64" t="s">
+        <v>152</v>
+      </c>
+      <c r="E2" s="64" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2" s="64" t="s">
+        <v>153</v>
+      </c>
+      <c r="G2" s="64" t="s">
+        <v>58</v>
+      </c>
+      <c r="H2" s="65" t="s">
+        <v>142</v>
+      </c>
+      <c r="I2" s="66"/>
+      <c r="L2" s="63" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" s="67" t="s">
+        <v>154</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="I3" s="68"/>
+    </row>
+    <row r="4" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="69" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" s="67" t="s">
+        <v>178</v>
+      </c>
+      <c r="F4" s="69" t="s">
+        <v>139</v>
+      </c>
+      <c r="H4" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4" s="68"/>
+    </row>
+    <row r="5" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="70" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="70" t="s">
+        <v>156</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" s="65" t="s">
+        <v>71</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="I5" s="71"/>
+    </row>
+    <row r="6" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="G6" s="69" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="I6" s="71"/>
+    </row>
+    <row r="7" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="93" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="70" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="H7" s="69" t="s">
+        <v>147</v>
+      </c>
+      <c r="I7" s="68"/>
+    </row>
+    <row r="8" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="70" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="70" t="s">
+        <v>167</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="H8" s="69" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="75" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="64" t="s">
+        <v>164</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="70" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="74"/>
+      <c r="H9" s="75" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="73" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="75" t="s">
+        <v>172</v>
+      </c>
+      <c r="F10" s="76" t="s">
+        <v>158</v>
+      </c>
+      <c r="G10" s="65"/>
+    </row>
+    <row r="11" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C11" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="72" t="s">
+        <v>159</v>
+      </c>
+      <c r="E11" s="94" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="69" t="s">
+        <v>116</v>
+      </c>
+      <c r="H11" s="77"/>
+    </row>
+    <row r="12" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C12" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="77"/>
+      <c r="H12" s="69"/>
+    </row>
+    <row r="13" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="65" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="75" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="75" t="s">
+        <v>41</v>
+      </c>
+      <c r="H13" s="69"/>
+    </row>
+    <row r="14" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="70" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="67" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" s="78" t="s">
+        <v>161</v>
+      </c>
+      <c r="I14" s="79" t="s">
+        <v>162</v>
+      </c>
+      <c r="L14" s="60" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C15" s="75" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="75" t="s">
+        <v>160</v>
+      </c>
+      <c r="E15" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="80" t="s">
+        <v>52</v>
+      </c>
+      <c r="I15" s="92" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C16" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="75" t="s">
+        <v>165</v>
+      </c>
+      <c r="E16" s="67" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H16" s="80" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16" s="92" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C17" s="67" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" s="80" t="s">
+        <v>40</v>
+      </c>
+      <c r="I17" s="81" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H18" s="80"/>
+      <c r="I18" s="81" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H19" s="80"/>
+    </row>
+    <row r="20" customFormat="false" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="82"/>
+      <c r="B20" s="82"/>
+      <c r="C20" s="82"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="82"/>
+      <c r="F20" s="82"/>
+      <c r="G20" s="82"/>
+      <c r="H20" s="80"/>
+      <c r="I20" s="82"/>
+      <c r="J20" s="83"/>
+      <c r="O20" s="82"/>
+      <c r="P20" s="82"/>
+      <c r="Q20" s="82"/>
+      <c r="R20" s="82"/>
+      <c r="S20" s="82"/>
+      <c r="T20" s="82"/>
+      <c r="U20" s="82"/>
+      <c r="V20" s="82"/>
+      <c r="W20" s="82"/>
+      <c r="X20" s="82"/>
+      <c r="Y20" s="82"/>
+      <c r="Z20" s="82"/>
+      <c r="AA20" s="82"/>
+      <c r="AB20" s="82"/>
+      <c r="AC20" s="82"/>
+      <c r="AD20" s="82"/>
+      <c r="AE20" s="82"/>
+      <c r="AF20" s="82"/>
+      <c r="AG20" s="82"/>
+      <c r="AH20" s="82"/>
+      <c r="AI20" s="82"/>
+      <c r="AJ20" s="82"/>
+      <c r="AK20" s="82"/>
+      <c r="AL20" s="82"/>
+      <c r="AM20" s="82"/>
+      <c r="AN20" s="82"/>
+      <c r="AO20" s="82"/>
+      <c r="AP20" s="82"/>
+      <c r="AQ20" s="82"/>
+      <c r="AR20" s="82"/>
+      <c r="AS20" s="82"/>
+      <c r="AT20" s="82"/>
+      <c r="AU20" s="82"/>
+      <c r="AV20" s="82"/>
+      <c r="AW20" s="82"/>
+      <c r="AX20" s="82"/>
+      <c r="AY20" s="82"/>
+      <c r="AZ20" s="82"/>
+      <c r="BA20" s="82"/>
+      <c r="BB20" s="82"/>
+      <c r="BC20" s="82"/>
+      <c r="BD20" s="82"/>
+      <c r="BE20" s="82"/>
+      <c r="BF20" s="82"/>
+      <c r="BG20" s="82"/>
+      <c r="BH20" s="82"/>
+      <c r="BI20" s="82"/>
+      <c r="BJ20" s="82"/>
+      <c r="BK20" s="82"/>
+      <c r="BL20" s="82"/>
+      <c r="BM20" s="82"/>
+      <c r="BN20" s="82"/>
+      <c r="BO20" s="82"/>
+      <c r="BP20" s="82"/>
+      <c r="BQ20" s="82"/>
+      <c r="BR20" s="82"/>
+      <c r="BS20" s="82"/>
+      <c r="BT20" s="82"/>
+      <c r="BU20" s="82"/>
+      <c r="BV20" s="82"/>
+      <c r="BW20" s="82"/>
+      <c r="BX20" s="82"/>
+      <c r="BY20" s="82"/>
+      <c r="BZ20" s="82"/>
+      <c r="CA20" s="82"/>
+      <c r="CB20" s="82"/>
+      <c r="CC20" s="82"/>
+      <c r="CD20" s="82"/>
+      <c r="CE20" s="82"/>
+      <c r="CF20" s="82"/>
+      <c r="CG20" s="82"/>
+      <c r="CH20" s="82"/>
+      <c r="CI20" s="82"/>
+      <c r="CJ20" s="82"/>
+      <c r="CK20" s="82"/>
+      <c r="CL20" s="82"/>
+      <c r="CM20" s="82"/>
+      <c r="CN20" s="82"/>
+      <c r="CO20" s="82"/>
+      <c r="CP20" s="82"/>
+      <c r="CQ20" s="82"/>
+      <c r="CR20" s="82"/>
+      <c r="CS20" s="82"/>
+      <c r="CT20" s="82"/>
+      <c r="CU20" s="82"/>
+      <c r="CV20" s="82"/>
+      <c r="CW20" s="82"/>
+      <c r="CX20" s="82"/>
+      <c r="CY20" s="82"/>
+      <c r="CZ20" s="82"/>
+      <c r="DA20" s="82"/>
+      <c r="DB20" s="82"/>
+      <c r="DC20" s="82"/>
+      <c r="DD20" s="82"/>
+      <c r="DE20" s="82"/>
+      <c r="DF20" s="82"/>
+      <c r="DG20" s="82"/>
+      <c r="DH20" s="82"/>
+      <c r="DI20" s="82"/>
+      <c r="DJ20" s="82"/>
+      <c r="DK20" s="82"/>
+      <c r="DL20" s="82"/>
+      <c r="DM20" s="82"/>
+      <c r="DN20" s="82"/>
+      <c r="DO20" s="82"/>
+      <c r="DP20" s="82"/>
+      <c r="DQ20" s="82"/>
+      <c r="DR20" s="82"/>
+      <c r="DS20" s="82"/>
+      <c r="DT20" s="82"/>
+      <c r="DU20" s="82"/>
+      <c r="DV20" s="82"/>
+      <c r="DW20" s="82"/>
+      <c r="DX20" s="82"/>
+      <c r="DY20" s="82"/>
+      <c r="DZ20" s="82"/>
+      <c r="EA20" s="82"/>
+      <c r="EB20" s="82"/>
+      <c r="EC20" s="82"/>
+      <c r="ED20" s="82"/>
+      <c r="EE20" s="82"/>
+      <c r="EF20" s="82"/>
+      <c r="EG20" s="82"/>
+      <c r="EH20" s="82"/>
+      <c r="EI20" s="82"/>
+      <c r="EJ20" s="82"/>
+      <c r="EK20" s="82"/>
+      <c r="EL20" s="82"/>
+      <c r="EM20" s="82"/>
+      <c r="EN20" s="82"/>
+      <c r="EO20" s="82"/>
+      <c r="EP20" s="82"/>
+      <c r="EQ20" s="82"/>
+      <c r="ER20" s="82"/>
+      <c r="ES20" s="82"/>
+      <c r="ET20" s="82"/>
+      <c r="EU20" s="82"/>
+      <c r="EV20" s="82"/>
+      <c r="EW20" s="82"/>
+      <c r="EX20" s="82"/>
+      <c r="EY20" s="82"/>
+      <c r="EZ20" s="82"/>
+      <c r="FA20" s="82"/>
+      <c r="FB20" s="82"/>
+      <c r="FC20" s="82"/>
+      <c r="FD20" s="82"/>
+      <c r="FE20" s="82"/>
+      <c r="FF20" s="82"/>
+      <c r="FG20" s="82"/>
+      <c r="FH20" s="82"/>
+      <c r="FI20" s="82"/>
+      <c r="FJ20" s="82"/>
+      <c r="FK20" s="82"/>
+      <c r="FL20" s="82"/>
+      <c r="FM20" s="82"/>
+      <c r="FN20" s="82"/>
+      <c r="FO20" s="82"/>
+      <c r="FP20" s="82"/>
+      <c r="FQ20" s="82"/>
+      <c r="FR20" s="82"/>
+      <c r="FS20" s="82"/>
+      <c r="FT20" s="82"/>
+      <c r="FU20" s="82"/>
+      <c r="FV20" s="82"/>
+      <c r="FW20" s="82"/>
+      <c r="FX20" s="82"/>
+      <c r="FY20" s="82"/>
+      <c r="FZ20" s="82"/>
+      <c r="GA20" s="82"/>
+      <c r="GB20" s="82"/>
+      <c r="GC20" s="82"/>
+      <c r="GD20" s="82"/>
+      <c r="GE20" s="82"/>
+      <c r="GF20" s="82"/>
+      <c r="GG20" s="82"/>
+      <c r="GH20" s="82"/>
+      <c r="GI20" s="82"/>
+      <c r="GJ20" s="82"/>
+      <c r="GK20" s="82"/>
+      <c r="GL20" s="82"/>
+      <c r="GM20" s="82"/>
+      <c r="GN20" s="82"/>
+      <c r="GO20" s="82"/>
+      <c r="GP20" s="82"/>
+      <c r="GQ20" s="82"/>
+      <c r="GR20" s="82"/>
+      <c r="GS20" s="82"/>
+      <c r="GT20" s="82"/>
+      <c r="GU20" s="82"/>
+      <c r="GV20" s="82"/>
+      <c r="GW20" s="82"/>
+      <c r="GX20" s="82"/>
+      <c r="GY20" s="82"/>
+      <c r="GZ20" s="82"/>
+      <c r="HA20" s="82"/>
+      <c r="HB20" s="82"/>
+      <c r="HC20" s="82"/>
+      <c r="HD20" s="82"/>
+      <c r="HE20" s="82"/>
+      <c r="HF20" s="82"/>
+      <c r="HG20" s="82"/>
+      <c r="HH20" s="82"/>
+      <c r="HI20" s="82"/>
+      <c r="HJ20" s="82"/>
+      <c r="HK20" s="82"/>
+      <c r="HL20" s="82"/>
+      <c r="HM20" s="82"/>
+      <c r="HN20" s="82"/>
+      <c r="HO20" s="82"/>
+      <c r="HP20" s="82"/>
+      <c r="HQ20" s="82"/>
+      <c r="HR20" s="82"/>
+      <c r="HS20" s="82"/>
+      <c r="HT20" s="82"/>
+      <c r="HU20" s="82"/>
+      <c r="HV20" s="82"/>
+      <c r="HW20" s="82"/>
+      <c r="HX20" s="82"/>
+      <c r="HY20" s="82"/>
+      <c r="HZ20" s="82"/>
+      <c r="IA20" s="82"/>
+      <c r="IB20" s="82"/>
+      <c r="IC20" s="82"/>
+      <c r="ID20" s="82"/>
+      <c r="IE20" s="82"/>
+      <c r="IF20" s="82"/>
+      <c r="IG20" s="82"/>
+      <c r="IH20" s="82"/>
+      <c r="II20" s="82"/>
+      <c r="IJ20" s="82"/>
+      <c r="IK20" s="82"/>
+      <c r="IL20" s="82"/>
+      <c r="IM20" s="82"/>
+      <c r="IN20" s="82"/>
+      <c r="IO20" s="82"/>
+      <c r="IP20" s="82"/>
+      <c r="IQ20" s="82"/>
+      <c r="IR20" s="82"/>
+      <c r="IS20" s="82"/>
+      <c r="IT20" s="82"/>
+      <c r="IU20" s="82"/>
+      <c r="IV20" s="82"/>
+      <c r="IW20" s="82"/>
+    </row>
+    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="82"/>
+      <c r="G21" s="84"/>
+      <c r="H21" s="80"/>
+      <c r="I21" s="81"/>
+      <c r="J21" s="85" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="86"/>
+      <c r="G22" s="86"/>
+      <c r="H22" s="80"/>
+      <c r="I22" s="81"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="81"/>
+      <c r="R23" s="87"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="81"/>
+      <c r="L24" s="60" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I25" s="81"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="3"/>
+      <c r="I26" s="81"/>
+    </row>
+    <row r="28" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D28" s="88"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="89" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="89" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="89" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="80" t="s">
+        <v>176</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
 </file>
--- a/raw/BUS.xlsx
+++ b/raw/BUS.xlsx
@@ -13,7 +13,7 @@
     <sheet name="25" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="26" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="27" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Лист1" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="28" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -1043,12 +1043,49 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">после обеда
+цдн-3
+</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>23</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>44</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>22</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="183">
   <si>
     <t xml:space="preserve">35.1-2673</t>
   </si>
@@ -1591,6 +1628,9 @@
   </si>
   <si>
     <t xml:space="preserve">kbm 19/6</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> сводка выхода  28  октября 2026 года </t>
   </si>
   <si>
     <t xml:space="preserve">20-0592</t>
@@ -1610,7 +1650,7 @@
     <numFmt numFmtId="170" formatCode="[$-409]m/d/yyyy"/>
     <numFmt numFmtId="171" formatCode="[$-409]d\-mmm"/>
   </numFmts>
-  <fonts count="53">
+  <fonts count="54">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1994,6 +2034,14 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFCC00"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -3358,7 +3406,7 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="97">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3736,6 +3784,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="52" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="53" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="53" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9307,7 +9363,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="61" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B1" s="61"/>
       <c r="C1" s="61"/>
@@ -9572,8 +9628,8 @@
       <c r="A2" s="64" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="72" t="s">
-        <v>63</v>
+      <c r="B2" s="64" t="s">
+        <v>150</v>
       </c>
       <c r="C2" s="64" t="s">
         <v>151</v>
@@ -9603,7 +9659,7 @@
         <v>91</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>14</v>
@@ -9621,7 +9677,7 @@
         <v>57</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I3" s="68"/>
     </row>
@@ -9636,7 +9692,7 @@
         <v>113</v>
       </c>
       <c r="E4" s="67" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="F4" s="69" t="s">
         <v>139</v>
@@ -9650,9 +9706,6 @@
       <c r="A5" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="65" t="s">
-        <v>48</v>
-      </c>
       <c r="C5" s="70" t="s">
         <v>24</v>
       </c>
@@ -9677,14 +9730,11 @@
       <c r="A6" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>47</v>
-      </c>
       <c r="C6" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="13" t="s">
-        <v>20</v>
+      <c r="E6" s="70" t="s">
+        <v>157</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>94</v>
@@ -9698,17 +9748,14 @@
       <c r="I6" s="71"/>
     </row>
     <row r="7" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="93" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>34</v>
+      <c r="A7" s="13" t="s">
+        <v>8</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="70" t="s">
-        <v>23</v>
+      <c r="E7" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>104</v>
@@ -9722,14 +9769,14 @@
       <c r="I7" s="68"/>
     </row>
     <row r="8" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
-        <v>16</v>
+      <c r="A8" s="95" t="s">
+        <v>27</v>
       </c>
       <c r="C8" s="70" t="s">
         <v>6</v>
       </c>
       <c r="E8" s="70" t="s">
-        <v>167</v>
+        <v>23</v>
       </c>
       <c r="F8" s="13" t="s">
         <v>141</v>
@@ -9745,14 +9792,14 @@
       <c r="A9" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="64" t="s">
-        <v>164</v>
+      <c r="B9" s="72" t="s">
+        <v>63</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>25</v>
       </c>
       <c r="E9" s="70" t="s">
-        <v>15</v>
+        <v>167</v>
       </c>
       <c r="G9" s="74"/>
       <c r="H9" s="75" t="s">
@@ -9764,13 +9811,13 @@
         <v>30</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="75" t="s">
-        <v>172</v>
+      <c r="E10" s="70" t="s">
+        <v>15</v>
       </c>
       <c r="F10" s="76" t="s">
         <v>158</v>
@@ -9784,8 +9831,8 @@
       <c r="D11" s="72" t="s">
         <v>159</v>
       </c>
-      <c r="E11" s="94" t="s">
-        <v>27</v>
+      <c r="E11" s="75" t="s">
+        <v>172</v>
       </c>
       <c r="F11" s="69" t="s">
         <v>116</v>
@@ -9799,8 +9846,8 @@
       <c r="D12" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="E12" s="67" t="s">
-        <v>3</v>
+      <c r="E12" s="96" t="s">
+        <v>27</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>42</v>
@@ -9812,14 +9859,17 @@
       <c r="A13" s="65" t="s">
         <v>67</v>
       </c>
+      <c r="B13" s="65" t="s">
+        <v>48</v>
+      </c>
       <c r="C13" s="13" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="E13" s="75" t="s">
-        <v>21</v>
+      <c r="E13" s="67" t="s">
+        <v>3</v>
       </c>
       <c r="F13" s="75" t="s">
         <v>41</v>
@@ -9830,14 +9880,17 @@
       <c r="A14" s="13" t="s">
         <v>70</v>
       </c>
+      <c r="B14" s="13" t="s">
+        <v>47</v>
+      </c>
       <c r="C14" s="13" t="s">
         <v>28</v>
       </c>
       <c r="D14" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="67" t="s">
-        <v>35</v>
+      <c r="E14" s="75" t="s">
+        <v>21</v>
       </c>
       <c r="H14" s="78" t="s">
         <v>161</v>
@@ -9856,55 +9909,61 @@
       <c r="D15" s="75" t="s">
         <v>160</v>
       </c>
-      <c r="E15" s="75" t="s">
-        <v>33</v>
-      </c>
-      <c r="H15" s="80" t="s">
-        <v>52</v>
-      </c>
-      <c r="I15" s="92" t="s">
+      <c r="E15" s="67" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" s="92" t="s">
+        <v>127</v>
+      </c>
+      <c r="I15" s="81" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="64" t="s">
+        <v>164</v>
+      </c>
       <c r="C16" s="67" t="s">
         <v>22</v>
       </c>
       <c r="D16" s="75" t="s">
         <v>165</v>
       </c>
-      <c r="E16" s="67" t="s">
-        <v>36</v>
+      <c r="E16" s="75" t="s">
+        <v>33</v>
       </c>
       <c r="F16" s="65" t="s">
         <v>166</v>
       </c>
       <c r="H16" s="80" t="s">
-        <v>8</v>
-      </c>
-      <c r="I16" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16" s="81" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="13" t="s">
+        <v>120</v>
+      </c>
       <c r="C17" s="67" t="s">
         <v>26</v>
       </c>
+      <c r="E17" s="67" t="s">
+        <v>36</v>
+      </c>
       <c r="F17" s="69" t="s">
         <v>62</v>
       </c>
       <c r="H17" s="80" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="I17" s="81" t="s">
-        <v>127</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H18" s="80"/>
-      <c r="I18" s="81" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="19" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="H19" s="80"/>

--- a/raw/BUS.xlsx
+++ b/raw/BUS.xlsx
@@ -14,6 +14,7 @@
     <sheet name="26" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="27" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="28" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="29" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -1084,8 +1085,241 @@
 </comments>
 </file>
 
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">20
+ kbm-13
+tms -  8
+dtt - 6/1</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>25</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>30</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A29" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">35--8/9</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>27</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>32</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A30" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">35-   15/6
+</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>28</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>33</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A31" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">35.1- 1/1
+</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>29</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>34</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A32" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve"> 35.2-  2/2
+</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>30</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>35</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="H17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="0"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">с вод
+</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>15</xdr:row>
+                <xdr:rowOff>17</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>10</xdr:col>
+                <xdr:colOff>43</xdr:colOff>
+                <xdr:row>18</xdr:row>
+                <xdr:rowOff>22</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="186">
   <si>
     <t xml:space="preserve">35.1-2673</t>
   </si>
@@ -1634,6 +1868,15 @@
   </si>
   <si>
     <t xml:space="preserve">20-0592</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> сводка выхода  29  октября 2026 года </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-228 d/n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-2291 d/n</t>
   </si>
 </sst>
 </file>
@@ -5194,6 +5437,51 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>23400</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>48240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>321840</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>111600</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 3" descr="C:\Users\A_Tumayeva\Desktop\9hq.webp"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="883800" y="5872320"/>
+          <a:ext cx="298440" cy="2174760"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
   <a:themeElements>
@@ -10292,4 +10580,951 @@
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:IW32"/>
+  <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="12.55" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="60" width="12.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="60" width="12.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="60" width="14.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="60" width="12.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="60" width="17.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="60" width="15.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="60" width="13.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="60" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="60" width="14.55"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="10" min="10" style="60" width="9.1"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="11" style="60" width="9.1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="26.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="61" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
+      <c r="S1" s="62"/>
+      <c r="T1" s="62"/>
+      <c r="U1" s="62"/>
+      <c r="V1" s="62"/>
+      <c r="W1" s="62"/>
+      <c r="X1" s="62"/>
+      <c r="Y1" s="62"/>
+      <c r="Z1" s="62"/>
+      <c r="AA1" s="62"/>
+      <c r="AB1" s="62"/>
+      <c r="AC1" s="62"/>
+      <c r="AD1" s="62"/>
+      <c r="AE1" s="62"/>
+      <c r="AF1" s="62"/>
+      <c r="AG1" s="62"/>
+      <c r="AH1" s="62"/>
+      <c r="AI1" s="62"/>
+      <c r="AJ1" s="62"/>
+      <c r="AK1" s="62"/>
+      <c r="AL1" s="62"/>
+      <c r="AM1" s="62"/>
+      <c r="AN1" s="62"/>
+      <c r="AO1" s="62"/>
+      <c r="AP1" s="62"/>
+      <c r="AQ1" s="62"/>
+      <c r="AR1" s="62"/>
+      <c r="AS1" s="62"/>
+      <c r="AT1" s="62"/>
+      <c r="AU1" s="62"/>
+      <c r="AV1" s="62"/>
+      <c r="AW1" s="62"/>
+      <c r="AX1" s="62"/>
+      <c r="AY1" s="62"/>
+      <c r="AZ1" s="62"/>
+      <c r="BA1" s="62"/>
+      <c r="BB1" s="62"/>
+      <c r="BC1" s="62"/>
+      <c r="BD1" s="62"/>
+      <c r="BE1" s="62"/>
+      <c r="BF1" s="62"/>
+      <c r="BG1" s="62"/>
+      <c r="BH1" s="62"/>
+      <c r="BI1" s="62"/>
+      <c r="BJ1" s="62"/>
+      <c r="BK1" s="62"/>
+      <c r="BL1" s="62"/>
+      <c r="BM1" s="62"/>
+      <c r="BN1" s="62"/>
+      <c r="BO1" s="62"/>
+      <c r="BP1" s="62"/>
+      <c r="BQ1" s="62"/>
+      <c r="BR1" s="62"/>
+      <c r="BS1" s="62"/>
+      <c r="BT1" s="62"/>
+      <c r="BU1" s="62"/>
+      <c r="BV1" s="62"/>
+      <c r="BW1" s="62"/>
+      <c r="BX1" s="62"/>
+      <c r="BY1" s="62"/>
+      <c r="BZ1" s="62"/>
+      <c r="CA1" s="62"/>
+      <c r="CB1" s="62"/>
+      <c r="CC1" s="62"/>
+      <c r="CD1" s="62"/>
+      <c r="CE1" s="62"/>
+      <c r="CF1" s="62"/>
+      <c r="CG1" s="62"/>
+      <c r="CH1" s="62"/>
+      <c r="CI1" s="62"/>
+      <c r="CJ1" s="62"/>
+      <c r="CK1" s="62"/>
+      <c r="CL1" s="62"/>
+      <c r="CM1" s="62"/>
+      <c r="CN1" s="62"/>
+      <c r="CO1" s="62"/>
+      <c r="CP1" s="62"/>
+      <c r="CQ1" s="62"/>
+      <c r="CR1" s="62"/>
+      <c r="CS1" s="62"/>
+      <c r="CT1" s="62"/>
+      <c r="CU1" s="62"/>
+      <c r="CV1" s="62"/>
+      <c r="CW1" s="62"/>
+      <c r="CX1" s="62"/>
+      <c r="CY1" s="62"/>
+      <c r="CZ1" s="62"/>
+      <c r="DA1" s="62"/>
+      <c r="DB1" s="62"/>
+      <c r="DC1" s="62"/>
+      <c r="DD1" s="62"/>
+      <c r="DE1" s="62"/>
+      <c r="DF1" s="62"/>
+      <c r="DG1" s="62"/>
+      <c r="DH1" s="62"/>
+      <c r="DI1" s="62"/>
+      <c r="DJ1" s="62"/>
+      <c r="DK1" s="62"/>
+      <c r="DL1" s="62"/>
+      <c r="DM1" s="62"/>
+      <c r="DN1" s="62"/>
+      <c r="DO1" s="62"/>
+      <c r="DP1" s="62"/>
+      <c r="DQ1" s="62"/>
+      <c r="DR1" s="62"/>
+      <c r="DS1" s="62"/>
+      <c r="DT1" s="62"/>
+      <c r="DU1" s="62"/>
+      <c r="DV1" s="62"/>
+      <c r="DW1" s="62"/>
+      <c r="DX1" s="62"/>
+      <c r="DY1" s="62"/>
+      <c r="DZ1" s="62"/>
+      <c r="EA1" s="62"/>
+      <c r="EB1" s="62"/>
+      <c r="EC1" s="62"/>
+      <c r="ED1" s="62"/>
+      <c r="EE1" s="62"/>
+      <c r="EF1" s="62"/>
+      <c r="EG1" s="62"/>
+      <c r="EH1" s="62"/>
+      <c r="EI1" s="62"/>
+      <c r="EJ1" s="62"/>
+      <c r="EK1" s="62"/>
+      <c r="EL1" s="62"/>
+      <c r="EM1" s="62"/>
+      <c r="EN1" s="62"/>
+      <c r="EO1" s="62"/>
+      <c r="EP1" s="62"/>
+      <c r="EQ1" s="62"/>
+      <c r="ER1" s="62"/>
+      <c r="ES1" s="62"/>
+      <c r="ET1" s="62"/>
+      <c r="EU1" s="62"/>
+      <c r="EV1" s="62"/>
+      <c r="EW1" s="62"/>
+      <c r="EX1" s="62"/>
+      <c r="EY1" s="62"/>
+      <c r="EZ1" s="62"/>
+      <c r="FA1" s="62"/>
+      <c r="FB1" s="62"/>
+      <c r="FC1" s="62"/>
+      <c r="FD1" s="62"/>
+      <c r="FE1" s="62"/>
+      <c r="FF1" s="62"/>
+      <c r="FG1" s="62"/>
+      <c r="FH1" s="62"/>
+      <c r="FI1" s="62"/>
+      <c r="FJ1" s="62"/>
+      <c r="FK1" s="62"/>
+      <c r="FL1" s="62"/>
+      <c r="FM1" s="62"/>
+      <c r="FN1" s="62"/>
+      <c r="FO1" s="62"/>
+      <c r="FP1" s="62"/>
+      <c r="FQ1" s="62"/>
+      <c r="FR1" s="62"/>
+      <c r="FS1" s="62"/>
+      <c r="FT1" s="62"/>
+      <c r="FU1" s="62"/>
+      <c r="FV1" s="62"/>
+      <c r="FW1" s="62"/>
+      <c r="FX1" s="62"/>
+      <c r="FY1" s="62"/>
+      <c r="FZ1" s="62"/>
+      <c r="GA1" s="62"/>
+      <c r="GB1" s="62"/>
+      <c r="GC1" s="62"/>
+      <c r="GD1" s="62"/>
+      <c r="GE1" s="62"/>
+      <c r="GF1" s="62"/>
+      <c r="GG1" s="62"/>
+      <c r="GH1" s="62"/>
+      <c r="GI1" s="62"/>
+      <c r="GJ1" s="62"/>
+      <c r="GK1" s="62"/>
+      <c r="GL1" s="62"/>
+      <c r="GM1" s="62"/>
+      <c r="GN1" s="62"/>
+      <c r="GO1" s="62"/>
+      <c r="GP1" s="62"/>
+      <c r="GQ1" s="62"/>
+      <c r="GR1" s="62"/>
+      <c r="GS1" s="62"/>
+      <c r="GT1" s="62"/>
+      <c r="GU1" s="62"/>
+      <c r="GV1" s="62"/>
+      <c r="GW1" s="62"/>
+      <c r="GX1" s="62"/>
+      <c r="GY1" s="62"/>
+      <c r="GZ1" s="62"/>
+      <c r="HA1" s="62"/>
+      <c r="HB1" s="62"/>
+      <c r="HC1" s="62"/>
+      <c r="HD1" s="62"/>
+      <c r="HE1" s="62"/>
+      <c r="HF1" s="62"/>
+      <c r="HG1" s="62"/>
+      <c r="HH1" s="62"/>
+      <c r="HI1" s="62"/>
+      <c r="HJ1" s="62"/>
+      <c r="HK1" s="62"/>
+      <c r="HL1" s="62"/>
+      <c r="HM1" s="62"/>
+      <c r="HN1" s="62"/>
+      <c r="HO1" s="62"/>
+      <c r="HP1" s="62"/>
+      <c r="HQ1" s="62"/>
+      <c r="HR1" s="62"/>
+      <c r="HS1" s="62"/>
+      <c r="HT1" s="62"/>
+      <c r="HU1" s="62"/>
+      <c r="HV1" s="62"/>
+      <c r="HW1" s="62"/>
+      <c r="HX1" s="62"/>
+      <c r="HY1" s="62"/>
+      <c r="HZ1" s="62"/>
+      <c r="IA1" s="62"/>
+      <c r="IB1" s="62"/>
+      <c r="IC1" s="62"/>
+      <c r="ID1" s="62"/>
+      <c r="IE1" s="62"/>
+      <c r="IF1" s="62"/>
+      <c r="IG1" s="62"/>
+      <c r="IH1" s="62"/>
+      <c r="II1" s="62"/>
+      <c r="IJ1" s="62"/>
+      <c r="IK1" s="62"/>
+      <c r="IL1" s="62"/>
+      <c r="IM1" s="62"/>
+      <c r="IN1" s="62"/>
+      <c r="IO1" s="62"/>
+      <c r="IP1" s="62"/>
+      <c r="IQ1" s="62"/>
+      <c r="IR1" s="62"/>
+      <c r="IS1" s="62"/>
+      <c r="IT1" s="62"/>
+      <c r="IU1" s="62"/>
+      <c r="IV1" s="62"/>
+      <c r="IW1" s="62"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="64" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="72" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="64" t="s">
+        <v>151</v>
+      </c>
+      <c r="D2" s="64" t="s">
+        <v>152</v>
+      </c>
+      <c r="E2" s="64" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2" s="64" t="s">
+        <v>153</v>
+      </c>
+      <c r="G2" s="64" t="s">
+        <v>58</v>
+      </c>
+      <c r="H2" s="65" t="s">
+        <v>142</v>
+      </c>
+      <c r="I2" s="66"/>
+      <c r="L2" s="63" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" s="67" t="s">
+        <v>154</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="I3" s="68"/>
+    </row>
+    <row r="4" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="69" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" s="67" t="s">
+        <v>155</v>
+      </c>
+      <c r="F4" s="69" t="s">
+        <v>139</v>
+      </c>
+      <c r="H4" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4" s="68"/>
+    </row>
+    <row r="5" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="70" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="70" t="s">
+        <v>156</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" s="65" t="s">
+        <v>71</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="I5" s="71"/>
+    </row>
+    <row r="6" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="65" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="70" t="s">
+        <v>157</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="G6" s="69" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="I6" s="71"/>
+    </row>
+    <row r="7" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="H7" s="69" t="s">
+        <v>147</v>
+      </c>
+      <c r="I7" s="68"/>
+    </row>
+    <row r="8" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="70" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="70" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="H8" s="69" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="75" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="70" t="s">
+        <v>167</v>
+      </c>
+      <c r="G9" s="74"/>
+      <c r="H9" s="75" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="75" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="70" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="76" t="s">
+        <v>158</v>
+      </c>
+      <c r="G10" s="65"/>
+    </row>
+    <row r="11" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C11" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="72" t="s">
+        <v>159</v>
+      </c>
+      <c r="E11" s="75" t="s">
+        <v>172</v>
+      </c>
+      <c r="F11" s="69" t="s">
+        <v>116</v>
+      </c>
+      <c r="H11" s="77"/>
+    </row>
+    <row r="12" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C12" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="77"/>
+      <c r="H12" s="69"/>
+    </row>
+    <row r="13" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="65" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="64" t="s">
+        <v>164</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="75" t="s">
+        <v>41</v>
+      </c>
+      <c r="H13" s="69"/>
+    </row>
+    <row r="14" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="75" t="s">
+        <v>184</v>
+      </c>
+      <c r="E14" s="75" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="78" t="s">
+        <v>161</v>
+      </c>
+      <c r="I14" s="79" t="s">
+        <v>162</v>
+      </c>
+      <c r="L14" s="60" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C15" s="75" t="s">
+        <v>185</v>
+      </c>
+      <c r="D15" s="75" t="s">
+        <v>165</v>
+      </c>
+      <c r="E15" s="67" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" s="80" t="s">
+        <v>127</v>
+      </c>
+      <c r="I15" s="81" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C16" s="67" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="65" t="s">
+        <v>166</v>
+      </c>
+      <c r="H16" s="80" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16" s="81" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C17" s="67" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="67" t="s">
+        <v>36</v>
+      </c>
+      <c r="F17" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" s="92" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" s="81" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H18" s="92" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H19" s="80"/>
+    </row>
+    <row r="20" customFormat="false" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="82"/>
+      <c r="B20" s="82"/>
+      <c r="C20" s="82"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="82"/>
+      <c r="F20" s="82"/>
+      <c r="G20" s="82"/>
+      <c r="H20" s="80"/>
+      <c r="I20" s="82"/>
+      <c r="J20" s="83"/>
+      <c r="O20" s="82"/>
+      <c r="P20" s="82"/>
+      <c r="Q20" s="82"/>
+      <c r="R20" s="82"/>
+      <c r="S20" s="82"/>
+      <c r="T20" s="82"/>
+      <c r="U20" s="82"/>
+      <c r="V20" s="82"/>
+      <c r="W20" s="82"/>
+      <c r="X20" s="82"/>
+      <c r="Y20" s="82"/>
+      <c r="Z20" s="82"/>
+      <c r="AA20" s="82"/>
+      <c r="AB20" s="82"/>
+      <c r="AC20" s="82"/>
+      <c r="AD20" s="82"/>
+      <c r="AE20" s="82"/>
+      <c r="AF20" s="82"/>
+      <c r="AG20" s="82"/>
+      <c r="AH20" s="82"/>
+      <c r="AI20" s="82"/>
+      <c r="AJ20" s="82"/>
+      <c r="AK20" s="82"/>
+      <c r="AL20" s="82"/>
+      <c r="AM20" s="82"/>
+      <c r="AN20" s="82"/>
+      <c r="AO20" s="82"/>
+      <c r="AP20" s="82"/>
+      <c r="AQ20" s="82"/>
+      <c r="AR20" s="82"/>
+      <c r="AS20" s="82"/>
+      <c r="AT20" s="82"/>
+      <c r="AU20" s="82"/>
+      <c r="AV20" s="82"/>
+      <c r="AW20" s="82"/>
+      <c r="AX20" s="82"/>
+      <c r="AY20" s="82"/>
+      <c r="AZ20" s="82"/>
+      <c r="BA20" s="82"/>
+      <c r="BB20" s="82"/>
+      <c r="BC20" s="82"/>
+      <c r="BD20" s="82"/>
+      <c r="BE20" s="82"/>
+      <c r="BF20" s="82"/>
+      <c r="BG20" s="82"/>
+      <c r="BH20" s="82"/>
+      <c r="BI20" s="82"/>
+      <c r="BJ20" s="82"/>
+      <c r="BK20" s="82"/>
+      <c r="BL20" s="82"/>
+      <c r="BM20" s="82"/>
+      <c r="BN20" s="82"/>
+      <c r="BO20" s="82"/>
+      <c r="BP20" s="82"/>
+      <c r="BQ20" s="82"/>
+      <c r="BR20" s="82"/>
+      <c r="BS20" s="82"/>
+      <c r="BT20" s="82"/>
+      <c r="BU20" s="82"/>
+      <c r="BV20" s="82"/>
+      <c r="BW20" s="82"/>
+      <c r="BX20" s="82"/>
+      <c r="BY20" s="82"/>
+      <c r="BZ20" s="82"/>
+      <c r="CA20" s="82"/>
+      <c r="CB20" s="82"/>
+      <c r="CC20" s="82"/>
+      <c r="CD20" s="82"/>
+      <c r="CE20" s="82"/>
+      <c r="CF20" s="82"/>
+      <c r="CG20" s="82"/>
+      <c r="CH20" s="82"/>
+      <c r="CI20" s="82"/>
+      <c r="CJ20" s="82"/>
+      <c r="CK20" s="82"/>
+      <c r="CL20" s="82"/>
+      <c r="CM20" s="82"/>
+      <c r="CN20" s="82"/>
+      <c r="CO20" s="82"/>
+      <c r="CP20" s="82"/>
+      <c r="CQ20" s="82"/>
+      <c r="CR20" s="82"/>
+      <c r="CS20" s="82"/>
+      <c r="CT20" s="82"/>
+      <c r="CU20" s="82"/>
+      <c r="CV20" s="82"/>
+      <c r="CW20" s="82"/>
+      <c r="CX20" s="82"/>
+      <c r="CY20" s="82"/>
+      <c r="CZ20" s="82"/>
+      <c r="DA20" s="82"/>
+      <c r="DB20" s="82"/>
+      <c r="DC20" s="82"/>
+      <c r="DD20" s="82"/>
+      <c r="DE20" s="82"/>
+      <c r="DF20" s="82"/>
+      <c r="DG20" s="82"/>
+      <c r="DH20" s="82"/>
+      <c r="DI20" s="82"/>
+      <c r="DJ20" s="82"/>
+      <c r="DK20" s="82"/>
+      <c r="DL20" s="82"/>
+      <c r="DM20" s="82"/>
+      <c r="DN20" s="82"/>
+      <c r="DO20" s="82"/>
+      <c r="DP20" s="82"/>
+      <c r="DQ20" s="82"/>
+      <c r="DR20" s="82"/>
+      <c r="DS20" s="82"/>
+      <c r="DT20" s="82"/>
+      <c r="DU20" s="82"/>
+      <c r="DV20" s="82"/>
+      <c r="DW20" s="82"/>
+      <c r="DX20" s="82"/>
+      <c r="DY20" s="82"/>
+      <c r="DZ20" s="82"/>
+      <c r="EA20" s="82"/>
+      <c r="EB20" s="82"/>
+      <c r="EC20" s="82"/>
+      <c r="ED20" s="82"/>
+      <c r="EE20" s="82"/>
+      <c r="EF20" s="82"/>
+      <c r="EG20" s="82"/>
+      <c r="EH20" s="82"/>
+      <c r="EI20" s="82"/>
+      <c r="EJ20" s="82"/>
+      <c r="EK20" s="82"/>
+      <c r="EL20" s="82"/>
+      <c r="EM20" s="82"/>
+      <c r="EN20" s="82"/>
+      <c r="EO20" s="82"/>
+      <c r="EP20" s="82"/>
+      <c r="EQ20" s="82"/>
+      <c r="ER20" s="82"/>
+      <c r="ES20" s="82"/>
+      <c r="ET20" s="82"/>
+      <c r="EU20" s="82"/>
+      <c r="EV20" s="82"/>
+      <c r="EW20" s="82"/>
+      <c r="EX20" s="82"/>
+      <c r="EY20" s="82"/>
+      <c r="EZ20" s="82"/>
+      <c r="FA20" s="82"/>
+      <c r="FB20" s="82"/>
+      <c r="FC20" s="82"/>
+      <c r="FD20" s="82"/>
+      <c r="FE20" s="82"/>
+      <c r="FF20" s="82"/>
+      <c r="FG20" s="82"/>
+      <c r="FH20" s="82"/>
+      <c r="FI20" s="82"/>
+      <c r="FJ20" s="82"/>
+      <c r="FK20" s="82"/>
+      <c r="FL20" s="82"/>
+      <c r="FM20" s="82"/>
+      <c r="FN20" s="82"/>
+      <c r="FO20" s="82"/>
+      <c r="FP20" s="82"/>
+      <c r="FQ20" s="82"/>
+      <c r="FR20" s="82"/>
+      <c r="FS20" s="82"/>
+      <c r="FT20" s="82"/>
+      <c r="FU20" s="82"/>
+      <c r="FV20" s="82"/>
+      <c r="FW20" s="82"/>
+      <c r="FX20" s="82"/>
+      <c r="FY20" s="82"/>
+      <c r="FZ20" s="82"/>
+      <c r="GA20" s="82"/>
+      <c r="GB20" s="82"/>
+      <c r="GC20" s="82"/>
+      <c r="GD20" s="82"/>
+      <c r="GE20" s="82"/>
+      <c r="GF20" s="82"/>
+      <c r="GG20" s="82"/>
+      <c r="GH20" s="82"/>
+      <c r="GI20" s="82"/>
+      <c r="GJ20" s="82"/>
+      <c r="GK20" s="82"/>
+      <c r="GL20" s="82"/>
+      <c r="GM20" s="82"/>
+      <c r="GN20" s="82"/>
+      <c r="GO20" s="82"/>
+      <c r="GP20" s="82"/>
+      <c r="GQ20" s="82"/>
+      <c r="GR20" s="82"/>
+      <c r="GS20" s="82"/>
+      <c r="GT20" s="82"/>
+      <c r="GU20" s="82"/>
+      <c r="GV20" s="82"/>
+      <c r="GW20" s="82"/>
+      <c r="GX20" s="82"/>
+      <c r="GY20" s="82"/>
+      <c r="GZ20" s="82"/>
+      <c r="HA20" s="82"/>
+      <c r="HB20" s="82"/>
+      <c r="HC20" s="82"/>
+      <c r="HD20" s="82"/>
+      <c r="HE20" s="82"/>
+      <c r="HF20" s="82"/>
+      <c r="HG20" s="82"/>
+      <c r="HH20" s="82"/>
+      <c r="HI20" s="82"/>
+      <c r="HJ20" s="82"/>
+      <c r="HK20" s="82"/>
+      <c r="HL20" s="82"/>
+      <c r="HM20" s="82"/>
+      <c r="HN20" s="82"/>
+      <c r="HO20" s="82"/>
+      <c r="HP20" s="82"/>
+      <c r="HQ20" s="82"/>
+      <c r="HR20" s="82"/>
+      <c r="HS20" s="82"/>
+      <c r="HT20" s="82"/>
+      <c r="HU20" s="82"/>
+      <c r="HV20" s="82"/>
+      <c r="HW20" s="82"/>
+      <c r="HX20" s="82"/>
+      <c r="HY20" s="82"/>
+      <c r="HZ20" s="82"/>
+      <c r="IA20" s="82"/>
+      <c r="IB20" s="82"/>
+      <c r="IC20" s="82"/>
+      <c r="ID20" s="82"/>
+      <c r="IE20" s="82"/>
+      <c r="IF20" s="82"/>
+      <c r="IG20" s="82"/>
+      <c r="IH20" s="82"/>
+      <c r="II20" s="82"/>
+      <c r="IJ20" s="82"/>
+      <c r="IK20" s="82"/>
+      <c r="IL20" s="82"/>
+      <c r="IM20" s="82"/>
+      <c r="IN20" s="82"/>
+      <c r="IO20" s="82"/>
+      <c r="IP20" s="82"/>
+      <c r="IQ20" s="82"/>
+      <c r="IR20" s="82"/>
+      <c r="IS20" s="82"/>
+      <c r="IT20" s="82"/>
+      <c r="IU20" s="82"/>
+      <c r="IV20" s="82"/>
+      <c r="IW20" s="82"/>
+    </row>
+    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="82"/>
+      <c r="G21" s="84"/>
+      <c r="H21" s="80"/>
+      <c r="I21" s="81"/>
+      <c r="J21" s="85" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="86"/>
+      <c r="G22" s="86"/>
+      <c r="H22" s="80"/>
+      <c r="I22" s="81"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="81"/>
+      <c r="R23" s="87"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="81"/>
+      <c r="L24" s="60" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I25" s="81"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="3"/>
+      <c r="I26" s="81"/>
+    </row>
+    <row r="28" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D28" s="88"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="89" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="89" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="89" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="80" t="s">
+        <v>176</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
 </file>
--- a/raw/BUS.xlsx
+++ b/raw/BUS.xlsx
@@ -15,6 +15,7 @@
     <sheet name="27" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="28" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="29" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="30" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -133,52 +134,6 @@
                 <xdr:colOff>41</xdr:colOff>
                 <xdr:row>38</xdr:row>
                 <xdr:rowOff>17</xdr:rowOff>
-              </xdr:to>
-            </anchor>
-          </commentPr>
-        </mc:Choice>
-        <mc:Fallback/>
-      </mc:AlternateContent>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="H8" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">do 6 
-</t>
-        </r>
-      </text>
-      <mc:AlternateContent>
-        <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
-            <anchor moveWithCells="false" sizeWithCells="false">
-              <xdr:from>
-                <xdr:col>8</xdr:col>
-                <xdr:colOff>12</xdr:colOff>
-                <xdr:row>6</xdr:row>
-                <xdr:rowOff>11</xdr:rowOff>
-              </xdr:from>
-              <xdr:to>
-                <xdr:col>9</xdr:col>
-                <xdr:colOff>15</xdr:colOff>
-                <xdr:row>9</xdr:row>
-                <xdr:rowOff>13</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1318,8 +1273,204 @@
 </comments>
 </file>
 
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">20
+ kbm-13
+tms -  8
+dtt - 6/1</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>25</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>30</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A29" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">35--8/9</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>27</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>32</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A30" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">35-   15/6
+</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>28</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>33</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A31" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">35.1- 1/1
+</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>29</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>34</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A32" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve"> 35.2-  2/2
+</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>30</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>35</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="188">
   <si>
     <t xml:space="preserve">35.1-2673</t>
   </si>
@@ -1648,7 +1799,7 @@
     <t xml:space="preserve">Бекбергенов</t>
   </si>
   <si>
-    <t xml:space="preserve">КЫЗЫЛГУЛОВ  ДЖАНБЫР</t>
+    <t xml:space="preserve">Аккенжеев Ержан</t>
   </si>
   <si>
     <t xml:space="preserve">20-192</t>
@@ -1720,9 +1871,6 @@
     <t xml:space="preserve">Жеткизгенов</t>
   </si>
   <si>
-    <t xml:space="preserve">Аккенжеев Ержан</t>
-  </si>
-  <si>
     <t xml:space="preserve">35-0592</t>
   </si>
   <si>
@@ -1873,10 +2021,19 @@
     <t xml:space="preserve"> сводка выхода  29  октября 2026 года </t>
   </si>
   <si>
+    <t xml:space="preserve">35-2291 d/n</t>
+  </si>
+  <si>
     <t xml:space="preserve">35-228 d/n</t>
   </si>
   <si>
-    <t xml:space="preserve">35-2291 d/n</t>
+    <t xml:space="preserve"> сводка выхода  30  октября 2026 года </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.2-3025 d/n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-2714 </t>
   </si>
 </sst>
 </file>
@@ -1893,7 +2050,7 @@
     <numFmt numFmtId="170" formatCode="[$-409]m/d/yyyy"/>
     <numFmt numFmtId="171" formatCode="[$-409]d\-mmm"/>
   </numFmts>
-  <fonts count="54">
+  <fonts count="55">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2130,6 +2287,13 @@
       <color rgb="FF33CCCC"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF0066CC"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b val="true"/>
@@ -3649,7 +3813,7 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="98">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3850,6 +4014,10 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="170" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="170" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3866,7 +4034,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3874,11 +4042,11 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3886,7 +4054,7 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3894,23 +4062,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="0" borderId="1" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="1" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="41" fillId="0" borderId="1" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="1" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="41" fillId="0" borderId="1" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="1" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3922,7 +4090,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="43" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3934,11 +4102,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="43" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3946,7 +4114,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="43" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="44" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3954,11 +4122,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="41" fillId="0" borderId="1" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="1" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3966,7 +4134,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3974,7 +4142,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3982,27 +4150,27 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="46" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="47" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="46" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="47" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="47" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="48" fillId="0" borderId="1" xfId="1207" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="49" fillId="0" borderId="1" xfId="1207" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4010,23 +4178,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="50" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="51" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="50" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="51" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="52" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="52" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="52" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4035,6 +4195,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="53" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="54" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="54" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5482,6 +5650,51 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>23400</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>48240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>321840</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>151560</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="AutoShape 3" descr="C:\Users\A_Tumayeva\Desktop\9hq.webp"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="883800" y="5872320"/>
+          <a:ext cx="298440" cy="2214720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
   <a:themeElements>
@@ -6560,6 +6773,9 @@
       <c r="H17" s="40" t="s">
         <v>106</v>
       </c>
+      <c r="I17" s="50" t="n">
+        <v>46322</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="19.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="30" t="s">
@@ -6571,7 +6787,7 @@
       <c r="C18" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="G18" s="50"/>
+      <c r="G18" s="51"/>
       <c r="H18" s="40" t="s">
         <v>109</v>
       </c>
@@ -6586,8 +6802,8 @@
       <c r="C19" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="G19" s="50"/>
-      <c r="H19" s="51" t="s">
+      <c r="G19" s="51"/>
+      <c r="H19" s="52" t="s">
         <v>112</v>
       </c>
       <c r="I19" s="30"/>
@@ -6621,7 +6837,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="52" t="s">
+      <c r="A22" s="53" t="s">
         <v>120</v>
       </c>
       <c r="B22" s="31" t="s">
@@ -6635,7 +6851,7 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="52" t="s">
+      <c r="A23" s="53" t="s">
         <v>124</v>
       </c>
       <c r="B23" s="31" t="s">
@@ -6655,7 +6871,7 @@
       <c r="B24" s="31" t="s">
         <v>128</v>
       </c>
-      <c r="C24" s="53" t="s">
+      <c r="C24" s="54" t="s">
         <v>129</v>
       </c>
       <c r="H24" s="40" t="s">
@@ -6672,27 +6888,24 @@
       <c r="C25" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="H25" s="40" t="s">
-        <v>133</v>
-      </c>
     </row>
     <row r="26" customFormat="false" ht="20.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="B26" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="B26" s="31" t="s">
+      <c r="C26" s="31" t="s">
         <v>135</v>
-      </c>
-      <c r="C26" s="31" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="20.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="39" t="s">
+        <v>136</v>
+      </c>
+      <c r="B27" s="31" t="s">
         <v>137</v>
-      </c>
-      <c r="B27" s="31" t="s">
-        <v>138</v>
       </c>
       <c r="C27" s="31" t="s">
         <v>122</v>
@@ -6700,55 +6913,55 @@
     </row>
     <row r="28" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="39" t="s">
+        <v>138</v>
+      </c>
+      <c r="B28" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="C28" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="B28" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="C28" s="31" t="s">
+      <c r="E28" s="55"/>
+    </row>
+    <row r="29" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="56" t="s">
         <v>140</v>
       </c>
-      <c r="E28" s="54"/>
-    </row>
-    <row r="29" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="55" t="s">
+      <c r="B29" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="B29" s="31" t="s">
+      <c r="C29" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="C29" s="31" t="s">
+    </row>
+    <row r="30" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="57"/>
+    </row>
+    <row r="31" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="57" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="56"/>
-    </row>
-    <row r="31" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="56" t="s">
+    <row r="32" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="58" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="57" t="s">
+      <c r="B32" s="24"/>
+    </row>
+    <row r="33" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="57" t="s">
         <v>145</v>
       </c>
-      <c r="B32" s="24"/>
-    </row>
-    <row r="33" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="56" t="s">
+      <c r="B33" s="24"/>
+    </row>
+    <row r="34" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="57" t="s">
         <v>146</v>
       </c>
-      <c r="B33" s="24"/>
-    </row>
-    <row r="34" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="56" t="s">
-        <v>147</v>
-      </c>
       <c r="B34" s="24"/>
     </row>
     <row r="35" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="58"/>
+      <c r="A35" s="59"/>
       <c r="B35" s="24"/>
     </row>
     <row r="36" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6756,13 +6969,13 @@
       <c r="B36" s="24"/>
     </row>
     <row r="38" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="59"/>
+      <c r="A38" s="60"/>
     </row>
     <row r="39" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="59"/>
+      <c r="A39" s="60"/>
     </row>
     <row r="40" customFormat="false" ht="15.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="57"/>
+      <c r="A40" s="58"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -6772,7 +6985,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -6784,309 +6996,309 @@
   <dimension ref="A1:IW32"/>
   <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="12.55" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="60" width="12.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="60" width="12.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="60" width="14.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="60" width="12.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="60" width="17.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="60" width="15.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="60" width="13.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="60" width="13.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="60" width="14.55"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="10" min="10" style="60" width="9.1"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="11" style="60" width="9.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="61" width="12.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="61" width="12.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="61" width="14.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="61" width="12.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="61" width="17.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="61" width="15.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="61" width="13.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="61" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="61" width="14.55"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="10" min="10" style="61" width="9.1"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="11" style="61" width="9.1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="26.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="62" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="64" t="s">
+        <v>46</v>
+      </c>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="63"/>
+      <c r="T1" s="63"/>
+      <c r="U1" s="63"/>
+      <c r="V1" s="63"/>
+      <c r="W1" s="63"/>
+      <c r="X1" s="63"/>
+      <c r="Y1" s="63"/>
+      <c r="Z1" s="63"/>
+      <c r="AA1" s="63"/>
+      <c r="AB1" s="63"/>
+      <c r="AC1" s="63"/>
+      <c r="AD1" s="63"/>
+      <c r="AE1" s="63"/>
+      <c r="AF1" s="63"/>
+      <c r="AG1" s="63"/>
+      <c r="AH1" s="63"/>
+      <c r="AI1" s="63"/>
+      <c r="AJ1" s="63"/>
+      <c r="AK1" s="63"/>
+      <c r="AL1" s="63"/>
+      <c r="AM1" s="63"/>
+      <c r="AN1" s="63"/>
+      <c r="AO1" s="63"/>
+      <c r="AP1" s="63"/>
+      <c r="AQ1" s="63"/>
+      <c r="AR1" s="63"/>
+      <c r="AS1" s="63"/>
+      <c r="AT1" s="63"/>
+      <c r="AU1" s="63"/>
+      <c r="AV1" s="63"/>
+      <c r="AW1" s="63"/>
+      <c r="AX1" s="63"/>
+      <c r="AY1" s="63"/>
+      <c r="AZ1" s="63"/>
+      <c r="BA1" s="63"/>
+      <c r="BB1" s="63"/>
+      <c r="BC1" s="63"/>
+      <c r="BD1" s="63"/>
+      <c r="BE1" s="63"/>
+      <c r="BF1" s="63"/>
+      <c r="BG1" s="63"/>
+      <c r="BH1" s="63"/>
+      <c r="BI1" s="63"/>
+      <c r="BJ1" s="63"/>
+      <c r="BK1" s="63"/>
+      <c r="BL1" s="63"/>
+      <c r="BM1" s="63"/>
+      <c r="BN1" s="63"/>
+      <c r="BO1" s="63"/>
+      <c r="BP1" s="63"/>
+      <c r="BQ1" s="63"/>
+      <c r="BR1" s="63"/>
+      <c r="BS1" s="63"/>
+      <c r="BT1" s="63"/>
+      <c r="BU1" s="63"/>
+      <c r="BV1" s="63"/>
+      <c r="BW1" s="63"/>
+      <c r="BX1" s="63"/>
+      <c r="BY1" s="63"/>
+      <c r="BZ1" s="63"/>
+      <c r="CA1" s="63"/>
+      <c r="CB1" s="63"/>
+      <c r="CC1" s="63"/>
+      <c r="CD1" s="63"/>
+      <c r="CE1" s="63"/>
+      <c r="CF1" s="63"/>
+      <c r="CG1" s="63"/>
+      <c r="CH1" s="63"/>
+      <c r="CI1" s="63"/>
+      <c r="CJ1" s="63"/>
+      <c r="CK1" s="63"/>
+      <c r="CL1" s="63"/>
+      <c r="CM1" s="63"/>
+      <c r="CN1" s="63"/>
+      <c r="CO1" s="63"/>
+      <c r="CP1" s="63"/>
+      <c r="CQ1" s="63"/>
+      <c r="CR1" s="63"/>
+      <c r="CS1" s="63"/>
+      <c r="CT1" s="63"/>
+      <c r="CU1" s="63"/>
+      <c r="CV1" s="63"/>
+      <c r="CW1" s="63"/>
+      <c r="CX1" s="63"/>
+      <c r="CY1" s="63"/>
+      <c r="CZ1" s="63"/>
+      <c r="DA1" s="63"/>
+      <c r="DB1" s="63"/>
+      <c r="DC1" s="63"/>
+      <c r="DD1" s="63"/>
+      <c r="DE1" s="63"/>
+      <c r="DF1" s="63"/>
+      <c r="DG1" s="63"/>
+      <c r="DH1" s="63"/>
+      <c r="DI1" s="63"/>
+      <c r="DJ1" s="63"/>
+      <c r="DK1" s="63"/>
+      <c r="DL1" s="63"/>
+      <c r="DM1" s="63"/>
+      <c r="DN1" s="63"/>
+      <c r="DO1" s="63"/>
+      <c r="DP1" s="63"/>
+      <c r="DQ1" s="63"/>
+      <c r="DR1" s="63"/>
+      <c r="DS1" s="63"/>
+      <c r="DT1" s="63"/>
+      <c r="DU1" s="63"/>
+      <c r="DV1" s="63"/>
+      <c r="DW1" s="63"/>
+      <c r="DX1" s="63"/>
+      <c r="DY1" s="63"/>
+      <c r="DZ1" s="63"/>
+      <c r="EA1" s="63"/>
+      <c r="EB1" s="63"/>
+      <c r="EC1" s="63"/>
+      <c r="ED1" s="63"/>
+      <c r="EE1" s="63"/>
+      <c r="EF1" s="63"/>
+      <c r="EG1" s="63"/>
+      <c r="EH1" s="63"/>
+      <c r="EI1" s="63"/>
+      <c r="EJ1" s="63"/>
+      <c r="EK1" s="63"/>
+      <c r="EL1" s="63"/>
+      <c r="EM1" s="63"/>
+      <c r="EN1" s="63"/>
+      <c r="EO1" s="63"/>
+      <c r="EP1" s="63"/>
+      <c r="EQ1" s="63"/>
+      <c r="ER1" s="63"/>
+      <c r="ES1" s="63"/>
+      <c r="ET1" s="63"/>
+      <c r="EU1" s="63"/>
+      <c r="EV1" s="63"/>
+      <c r="EW1" s="63"/>
+      <c r="EX1" s="63"/>
+      <c r="EY1" s="63"/>
+      <c r="EZ1" s="63"/>
+      <c r="FA1" s="63"/>
+      <c r="FB1" s="63"/>
+      <c r="FC1" s="63"/>
+      <c r="FD1" s="63"/>
+      <c r="FE1" s="63"/>
+      <c r="FF1" s="63"/>
+      <c r="FG1" s="63"/>
+      <c r="FH1" s="63"/>
+      <c r="FI1" s="63"/>
+      <c r="FJ1" s="63"/>
+      <c r="FK1" s="63"/>
+      <c r="FL1" s="63"/>
+      <c r="FM1" s="63"/>
+      <c r="FN1" s="63"/>
+      <c r="FO1" s="63"/>
+      <c r="FP1" s="63"/>
+      <c r="FQ1" s="63"/>
+      <c r="FR1" s="63"/>
+      <c r="FS1" s="63"/>
+      <c r="FT1" s="63"/>
+      <c r="FU1" s="63"/>
+      <c r="FV1" s="63"/>
+      <c r="FW1" s="63"/>
+      <c r="FX1" s="63"/>
+      <c r="FY1" s="63"/>
+      <c r="FZ1" s="63"/>
+      <c r="GA1" s="63"/>
+      <c r="GB1" s="63"/>
+      <c r="GC1" s="63"/>
+      <c r="GD1" s="63"/>
+      <c r="GE1" s="63"/>
+      <c r="GF1" s="63"/>
+      <c r="GG1" s="63"/>
+      <c r="GH1" s="63"/>
+      <c r="GI1" s="63"/>
+      <c r="GJ1" s="63"/>
+      <c r="GK1" s="63"/>
+      <c r="GL1" s="63"/>
+      <c r="GM1" s="63"/>
+      <c r="GN1" s="63"/>
+      <c r="GO1" s="63"/>
+      <c r="GP1" s="63"/>
+      <c r="GQ1" s="63"/>
+      <c r="GR1" s="63"/>
+      <c r="GS1" s="63"/>
+      <c r="GT1" s="63"/>
+      <c r="GU1" s="63"/>
+      <c r="GV1" s="63"/>
+      <c r="GW1" s="63"/>
+      <c r="GX1" s="63"/>
+      <c r="GY1" s="63"/>
+      <c r="GZ1" s="63"/>
+      <c r="HA1" s="63"/>
+      <c r="HB1" s="63"/>
+      <c r="HC1" s="63"/>
+      <c r="HD1" s="63"/>
+      <c r="HE1" s="63"/>
+      <c r="HF1" s="63"/>
+      <c r="HG1" s="63"/>
+      <c r="HH1" s="63"/>
+      <c r="HI1" s="63"/>
+      <c r="HJ1" s="63"/>
+      <c r="HK1" s="63"/>
+      <c r="HL1" s="63"/>
+      <c r="HM1" s="63"/>
+      <c r="HN1" s="63"/>
+      <c r="HO1" s="63"/>
+      <c r="HP1" s="63"/>
+      <c r="HQ1" s="63"/>
+      <c r="HR1" s="63"/>
+      <c r="HS1" s="63"/>
+      <c r="HT1" s="63"/>
+      <c r="HU1" s="63"/>
+      <c r="HV1" s="63"/>
+      <c r="HW1" s="63"/>
+      <c r="HX1" s="63"/>
+      <c r="HY1" s="63"/>
+      <c r="HZ1" s="63"/>
+      <c r="IA1" s="63"/>
+      <c r="IB1" s="63"/>
+      <c r="IC1" s="63"/>
+      <c r="ID1" s="63"/>
+      <c r="IE1" s="63"/>
+      <c r="IF1" s="63"/>
+      <c r="IG1" s="63"/>
+      <c r="IH1" s="63"/>
+      <c r="II1" s="63"/>
+      <c r="IJ1" s="63"/>
+      <c r="IK1" s="63"/>
+      <c r="IL1" s="63"/>
+      <c r="IM1" s="63"/>
+      <c r="IN1" s="63"/>
+      <c r="IO1" s="63"/>
+      <c r="IP1" s="63"/>
+      <c r="IQ1" s="63"/>
+      <c r="IR1" s="63"/>
+      <c r="IS1" s="63"/>
+      <c r="IT1" s="63"/>
+      <c r="IU1" s="63"/>
+      <c r="IV1" s="63"/>
+      <c r="IW1" s="63"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="65" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="63" t="s">
-        <v>46</v>
-      </c>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
-      <c r="T1" s="62"/>
-      <c r="U1" s="62"/>
-      <c r="V1" s="62"/>
-      <c r="W1" s="62"/>
-      <c r="X1" s="62"/>
-      <c r="Y1" s="62"/>
-      <c r="Z1" s="62"/>
-      <c r="AA1" s="62"/>
-      <c r="AB1" s="62"/>
-      <c r="AC1" s="62"/>
-      <c r="AD1" s="62"/>
-      <c r="AE1" s="62"/>
-      <c r="AF1" s="62"/>
-      <c r="AG1" s="62"/>
-      <c r="AH1" s="62"/>
-      <c r="AI1" s="62"/>
-      <c r="AJ1" s="62"/>
-      <c r="AK1" s="62"/>
-      <c r="AL1" s="62"/>
-      <c r="AM1" s="62"/>
-      <c r="AN1" s="62"/>
-      <c r="AO1" s="62"/>
-      <c r="AP1" s="62"/>
-      <c r="AQ1" s="62"/>
-      <c r="AR1" s="62"/>
-      <c r="AS1" s="62"/>
-      <c r="AT1" s="62"/>
-      <c r="AU1" s="62"/>
-      <c r="AV1" s="62"/>
-      <c r="AW1" s="62"/>
-      <c r="AX1" s="62"/>
-      <c r="AY1" s="62"/>
-      <c r="AZ1" s="62"/>
-      <c r="BA1" s="62"/>
-      <c r="BB1" s="62"/>
-      <c r="BC1" s="62"/>
-      <c r="BD1" s="62"/>
-      <c r="BE1" s="62"/>
-      <c r="BF1" s="62"/>
-      <c r="BG1" s="62"/>
-      <c r="BH1" s="62"/>
-      <c r="BI1" s="62"/>
-      <c r="BJ1" s="62"/>
-      <c r="BK1" s="62"/>
-      <c r="BL1" s="62"/>
-      <c r="BM1" s="62"/>
-      <c r="BN1" s="62"/>
-      <c r="BO1" s="62"/>
-      <c r="BP1" s="62"/>
-      <c r="BQ1" s="62"/>
-      <c r="BR1" s="62"/>
-      <c r="BS1" s="62"/>
-      <c r="BT1" s="62"/>
-      <c r="BU1" s="62"/>
-      <c r="BV1" s="62"/>
-      <c r="BW1" s="62"/>
-      <c r="BX1" s="62"/>
-      <c r="BY1" s="62"/>
-      <c r="BZ1" s="62"/>
-      <c r="CA1" s="62"/>
-      <c r="CB1" s="62"/>
-      <c r="CC1" s="62"/>
-      <c r="CD1" s="62"/>
-      <c r="CE1" s="62"/>
-      <c r="CF1" s="62"/>
-      <c r="CG1" s="62"/>
-      <c r="CH1" s="62"/>
-      <c r="CI1" s="62"/>
-      <c r="CJ1" s="62"/>
-      <c r="CK1" s="62"/>
-      <c r="CL1" s="62"/>
-      <c r="CM1" s="62"/>
-      <c r="CN1" s="62"/>
-      <c r="CO1" s="62"/>
-      <c r="CP1" s="62"/>
-      <c r="CQ1" s="62"/>
-      <c r="CR1" s="62"/>
-      <c r="CS1" s="62"/>
-      <c r="CT1" s="62"/>
-      <c r="CU1" s="62"/>
-      <c r="CV1" s="62"/>
-      <c r="CW1" s="62"/>
-      <c r="CX1" s="62"/>
-      <c r="CY1" s="62"/>
-      <c r="CZ1" s="62"/>
-      <c r="DA1" s="62"/>
-      <c r="DB1" s="62"/>
-      <c r="DC1" s="62"/>
-      <c r="DD1" s="62"/>
-      <c r="DE1" s="62"/>
-      <c r="DF1" s="62"/>
-      <c r="DG1" s="62"/>
-      <c r="DH1" s="62"/>
-      <c r="DI1" s="62"/>
-      <c r="DJ1" s="62"/>
-      <c r="DK1" s="62"/>
-      <c r="DL1" s="62"/>
-      <c r="DM1" s="62"/>
-      <c r="DN1" s="62"/>
-      <c r="DO1" s="62"/>
-      <c r="DP1" s="62"/>
-      <c r="DQ1" s="62"/>
-      <c r="DR1" s="62"/>
-      <c r="DS1" s="62"/>
-      <c r="DT1" s="62"/>
-      <c r="DU1" s="62"/>
-      <c r="DV1" s="62"/>
-      <c r="DW1" s="62"/>
-      <c r="DX1" s="62"/>
-      <c r="DY1" s="62"/>
-      <c r="DZ1" s="62"/>
-      <c r="EA1" s="62"/>
-      <c r="EB1" s="62"/>
-      <c r="EC1" s="62"/>
-      <c r="ED1" s="62"/>
-      <c r="EE1" s="62"/>
-      <c r="EF1" s="62"/>
-      <c r="EG1" s="62"/>
-      <c r="EH1" s="62"/>
-      <c r="EI1" s="62"/>
-      <c r="EJ1" s="62"/>
-      <c r="EK1" s="62"/>
-      <c r="EL1" s="62"/>
-      <c r="EM1" s="62"/>
-      <c r="EN1" s="62"/>
-      <c r="EO1" s="62"/>
-      <c r="EP1" s="62"/>
-      <c r="EQ1" s="62"/>
-      <c r="ER1" s="62"/>
-      <c r="ES1" s="62"/>
-      <c r="ET1" s="62"/>
-      <c r="EU1" s="62"/>
-      <c r="EV1" s="62"/>
-      <c r="EW1" s="62"/>
-      <c r="EX1" s="62"/>
-      <c r="EY1" s="62"/>
-      <c r="EZ1" s="62"/>
-      <c r="FA1" s="62"/>
-      <c r="FB1" s="62"/>
-      <c r="FC1" s="62"/>
-      <c r="FD1" s="62"/>
-      <c r="FE1" s="62"/>
-      <c r="FF1" s="62"/>
-      <c r="FG1" s="62"/>
-      <c r="FH1" s="62"/>
-      <c r="FI1" s="62"/>
-      <c r="FJ1" s="62"/>
-      <c r="FK1" s="62"/>
-      <c r="FL1" s="62"/>
-      <c r="FM1" s="62"/>
-      <c r="FN1" s="62"/>
-      <c r="FO1" s="62"/>
-      <c r="FP1" s="62"/>
-      <c r="FQ1" s="62"/>
-      <c r="FR1" s="62"/>
-      <c r="FS1" s="62"/>
-      <c r="FT1" s="62"/>
-      <c r="FU1" s="62"/>
-      <c r="FV1" s="62"/>
-      <c r="FW1" s="62"/>
-      <c r="FX1" s="62"/>
-      <c r="FY1" s="62"/>
-      <c r="FZ1" s="62"/>
-      <c r="GA1" s="62"/>
-      <c r="GB1" s="62"/>
-      <c r="GC1" s="62"/>
-      <c r="GD1" s="62"/>
-      <c r="GE1" s="62"/>
-      <c r="GF1" s="62"/>
-      <c r="GG1" s="62"/>
-      <c r="GH1" s="62"/>
-      <c r="GI1" s="62"/>
-      <c r="GJ1" s="62"/>
-      <c r="GK1" s="62"/>
-      <c r="GL1" s="62"/>
-      <c r="GM1" s="62"/>
-      <c r="GN1" s="62"/>
-      <c r="GO1" s="62"/>
-      <c r="GP1" s="62"/>
-      <c r="GQ1" s="62"/>
-      <c r="GR1" s="62"/>
-      <c r="GS1" s="62"/>
-      <c r="GT1" s="62"/>
-      <c r="GU1" s="62"/>
-      <c r="GV1" s="62"/>
-      <c r="GW1" s="62"/>
-      <c r="GX1" s="62"/>
-      <c r="GY1" s="62"/>
-      <c r="GZ1" s="62"/>
-      <c r="HA1" s="62"/>
-      <c r="HB1" s="62"/>
-      <c r="HC1" s="62"/>
-      <c r="HD1" s="62"/>
-      <c r="HE1" s="62"/>
-      <c r="HF1" s="62"/>
-      <c r="HG1" s="62"/>
-      <c r="HH1" s="62"/>
-      <c r="HI1" s="62"/>
-      <c r="HJ1" s="62"/>
-      <c r="HK1" s="62"/>
-      <c r="HL1" s="62"/>
-      <c r="HM1" s="62"/>
-      <c r="HN1" s="62"/>
-      <c r="HO1" s="62"/>
-      <c r="HP1" s="62"/>
-      <c r="HQ1" s="62"/>
-      <c r="HR1" s="62"/>
-      <c r="HS1" s="62"/>
-      <c r="HT1" s="62"/>
-      <c r="HU1" s="62"/>
-      <c r="HV1" s="62"/>
-      <c r="HW1" s="62"/>
-      <c r="HX1" s="62"/>
-      <c r="HY1" s="62"/>
-      <c r="HZ1" s="62"/>
-      <c r="IA1" s="62"/>
-      <c r="IB1" s="62"/>
-      <c r="IC1" s="62"/>
-      <c r="ID1" s="62"/>
-      <c r="IE1" s="62"/>
-      <c r="IF1" s="62"/>
-      <c r="IG1" s="62"/>
-      <c r="IH1" s="62"/>
-      <c r="II1" s="62"/>
-      <c r="IJ1" s="62"/>
-      <c r="IK1" s="62"/>
-      <c r="IL1" s="62"/>
-      <c r="IM1" s="62"/>
-      <c r="IN1" s="62"/>
-      <c r="IO1" s="62"/>
-      <c r="IP1" s="62"/>
-      <c r="IQ1" s="62"/>
-      <c r="IR1" s="62"/>
-      <c r="IS1" s="62"/>
-      <c r="IT1" s="62"/>
-      <c r="IU1" s="62"/>
-      <c r="IV1" s="62"/>
-      <c r="IW1" s="62"/>
-    </row>
-    <row r="2" customFormat="false" ht="23.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="64" t="s">
+      <c r="B2" s="65" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="64" t="s">
+      <c r="C2" s="65" t="s">
         <v>150</v>
       </c>
-      <c r="C2" s="64" t="s">
+      <c r="D2" s="65" t="s">
         <v>151</v>
       </c>
-      <c r="D2" s="64" t="s">
+      <c r="E2" s="65" t="s">
         <v>152</v>
       </c>
-      <c r="E2" s="64" t="s">
-        <v>153</v>
-      </c>
-      <c r="F2" s="64" t="s">
-        <v>153</v>
-      </c>
-      <c r="G2" s="64" t="s">
+      <c r="F2" s="65" t="s">
+        <v>152</v>
+      </c>
+      <c r="G2" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="H2" s="65" t="s">
-        <v>142</v>
-      </c>
-      <c r="I2" s="66"/>
-      <c r="L2" s="63" t="s">
+      <c r="H2" s="66" t="s">
+        <v>141</v>
+      </c>
+      <c r="I2" s="67"/>
+      <c r="L2" s="64" t="s">
         <v>51</v>
       </c>
     </row>
@@ -7103,8 +7315,8 @@
       <c r="D3" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="E3" s="67" t="s">
-        <v>154</v>
+      <c r="E3" s="68" t="s">
+        <v>153</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>74</v>
@@ -7115,32 +7327,32 @@
       <c r="H3" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="I3" s="68"/>
+      <c r="I3" s="69"/>
     </row>
     <row r="4" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="69" t="s">
+      <c r="A4" s="70" t="s">
         <v>87</v>
       </c>
       <c r="B4" s="13"/>
-      <c r="C4" s="70" t="s">
+      <c r="C4" s="71" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="E4" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="F4" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="E4" s="67" t="s">
-        <v>155</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="H4" s="69" t="s">
-        <v>139</v>
-      </c>
-      <c r="I4" s="68"/>
+      <c r="H4" s="70" t="s">
+        <v>138</v>
+      </c>
+      <c r="I4" s="69"/>
     </row>
     <row r="5" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="70" t="s">
+      <c r="A5" s="71" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="13" t="s">
@@ -7149,19 +7361,19 @@
       <c r="D5" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="E5" s="70" t="s">
-        <v>156</v>
+      <c r="E5" s="71" t="s">
+        <v>155</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="G5" s="65" t="s">
+      <c r="G5" s="66" t="s">
         <v>71</v>
       </c>
       <c r="H5" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="I5" s="71"/>
+      <c r="I5" s="72"/>
     </row>
     <row r="6" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
@@ -7170,25 +7382,25 @@
       <c r="C6" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="70" t="s">
-        <v>157</v>
-      </c>
-      <c r="F6" s="69" t="s">
+      <c r="E6" s="71" t="s">
+        <v>156</v>
+      </c>
+      <c r="F6" s="70" t="s">
         <v>120</v>
       </c>
-      <c r="G6" s="69" t="s">
+      <c r="G6" s="70" t="s">
         <v>62</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="I6" s="71"/>
+      <c r="I6" s="72"/>
     </row>
     <row r="7" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="70" t="s">
+      <c r="C7" s="71" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="13" t="s">
@@ -7198,18 +7410,18 @@
         <v>77</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="H7" s="69" t="s">
+        <v>145</v>
+      </c>
+      <c r="H7" s="70" t="s">
         <v>131</v>
       </c>
-      <c r="I7" s="68"/>
+      <c r="I7" s="69"/>
     </row>
     <row r="8" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="72" t="s">
+      <c r="B8" s="73" t="s">
         <v>63</v>
       </c>
       <c r="C8" s="13" t="s">
@@ -7219,17 +7431,17 @@
         <v>20</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G8" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="H8" s="69" t="s">
+      <c r="H8" s="70" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="73" t="s">
+      <c r="A9" s="74" t="s">
         <v>32</v>
       </c>
       <c r="B9" s="13" t="s">
@@ -7238,46 +7450,46 @@
       <c r="C9" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="70" t="s">
+      <c r="E9" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="74"/>
-      <c r="H9" s="75" t="s">
+      <c r="G9" s="75"/>
+      <c r="H9" s="76" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="73" t="s">
+      <c r="A10" s="74" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="70" t="s">
+      <c r="E10" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="76" t="s">
-        <v>158</v>
-      </c>
-      <c r="G10" s="65"/>
+      <c r="F10" s="77" t="s">
+        <v>157</v>
+      </c>
+      <c r="G10" s="66"/>
     </row>
     <row r="11" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="65" t="s">
+      <c r="B11" s="66" t="s">
         <v>48</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="72" t="s">
-        <v>159</v>
-      </c>
-      <c r="E11" s="70" t="s">
+      <c r="D11" s="73" t="s">
+        <v>158</v>
+      </c>
+      <c r="E11" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="69" t="s">
+      <c r="F11" s="70" t="s">
         <v>116</v>
       </c>
-      <c r="H11" s="77"/>
+      <c r="H11" s="78"/>
     </row>
     <row r="12" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="13" t="s">
@@ -7295,416 +7507,416 @@
       <c r="F12" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="77"/>
-      <c r="H12" s="69"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="70"/>
     </row>
     <row r="13" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="65" t="s">
+      <c r="A13" s="66" t="s">
         <v>67</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="70" t="s">
+      <c r="D13" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="E13" s="75" t="s">
+      <c r="E13" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="75" t="s">
+      <c r="F13" s="76" t="s">
         <v>41</v>
       </c>
-      <c r="H13" s="69"/>
+      <c r="H13" s="70"/>
     </row>
     <row r="14" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="75" t="s">
+      <c r="C14" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="75" t="s">
+      <c r="D14" s="76" t="s">
+        <v>159</v>
+      </c>
+      <c r="E14" s="68" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="79" t="s">
         <v>160</v>
       </c>
-      <c r="E14" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="78" t="s">
+      <c r="I14" s="80" t="s">
         <v>161</v>
       </c>
-      <c r="I14" s="79" t="s">
+      <c r="L14" s="61" t="s">
         <v>162</v>
       </c>
-      <c r="L14" s="60" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="65" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="64" t="s">
+      <c r="C15" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="76" t="s">
         <v>164</v>
       </c>
-      <c r="C15" s="67" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="75" t="s">
-        <v>165</v>
-      </c>
-      <c r="E15" s="75" t="s">
+      <c r="E15" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="H15" s="80" t="s">
+      <c r="H15" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="I15" s="81" t="s">
-        <v>147</v>
+      <c r="I15" s="82" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="67" t="s">
+      <c r="C16" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="75" t="s">
+      <c r="E16" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="F16" s="65" t="s">
+      <c r="F16" s="66" t="s">
+        <v>165</v>
+      </c>
+      <c r="H16" s="81" t="s">
         <v>166</v>
       </c>
-      <c r="H16" s="80" t="s">
+      <c r="I16" s="82" t="s">
         <v>167</v>
       </c>
-      <c r="I16" s="81" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E17" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="70" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17" s="81"/>
+      <c r="I17" s="82" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E18" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="H18" s="81"/>
+      <c r="I18" s="82"/>
+    </row>
+    <row r="19" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E19" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="H19" s="81"/>
+    </row>
+    <row r="20" customFormat="false" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="83"/>
+      <c r="B20" s="83"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="83"/>
+      <c r="J20" s="84"/>
+      <c r="O20" s="83"/>
+      <c r="P20" s="83"/>
+      <c r="Q20" s="83"/>
+      <c r="R20" s="83"/>
+      <c r="S20" s="83"/>
+      <c r="T20" s="83"/>
+      <c r="U20" s="83"/>
+      <c r="V20" s="83"/>
+      <c r="W20" s="83"/>
+      <c r="X20" s="83"/>
+      <c r="Y20" s="83"/>
+      <c r="Z20" s="83"/>
+      <c r="AA20" s="83"/>
+      <c r="AB20" s="83"/>
+      <c r="AC20" s="83"/>
+      <c r="AD20" s="83"/>
+      <c r="AE20" s="83"/>
+      <c r="AF20" s="83"/>
+      <c r="AG20" s="83"/>
+      <c r="AH20" s="83"/>
+      <c r="AI20" s="83"/>
+      <c r="AJ20" s="83"/>
+      <c r="AK20" s="83"/>
+      <c r="AL20" s="83"/>
+      <c r="AM20" s="83"/>
+      <c r="AN20" s="83"/>
+      <c r="AO20" s="83"/>
+      <c r="AP20" s="83"/>
+      <c r="AQ20" s="83"/>
+      <c r="AR20" s="83"/>
+      <c r="AS20" s="83"/>
+      <c r="AT20" s="83"/>
+      <c r="AU20" s="83"/>
+      <c r="AV20" s="83"/>
+      <c r="AW20" s="83"/>
+      <c r="AX20" s="83"/>
+      <c r="AY20" s="83"/>
+      <c r="AZ20" s="83"/>
+      <c r="BA20" s="83"/>
+      <c r="BB20" s="83"/>
+      <c r="BC20" s="83"/>
+      <c r="BD20" s="83"/>
+      <c r="BE20" s="83"/>
+      <c r="BF20" s="83"/>
+      <c r="BG20" s="83"/>
+      <c r="BH20" s="83"/>
+      <c r="BI20" s="83"/>
+      <c r="BJ20" s="83"/>
+      <c r="BK20" s="83"/>
+      <c r="BL20" s="83"/>
+      <c r="BM20" s="83"/>
+      <c r="BN20" s="83"/>
+      <c r="BO20" s="83"/>
+      <c r="BP20" s="83"/>
+      <c r="BQ20" s="83"/>
+      <c r="BR20" s="83"/>
+      <c r="BS20" s="83"/>
+      <c r="BT20" s="83"/>
+      <c r="BU20" s="83"/>
+      <c r="BV20" s="83"/>
+      <c r="BW20" s="83"/>
+      <c r="BX20" s="83"/>
+      <c r="BY20" s="83"/>
+      <c r="BZ20" s="83"/>
+      <c r="CA20" s="83"/>
+      <c r="CB20" s="83"/>
+      <c r="CC20" s="83"/>
+      <c r="CD20" s="83"/>
+      <c r="CE20" s="83"/>
+      <c r="CF20" s="83"/>
+      <c r="CG20" s="83"/>
+      <c r="CH20" s="83"/>
+      <c r="CI20" s="83"/>
+      <c r="CJ20" s="83"/>
+      <c r="CK20" s="83"/>
+      <c r="CL20" s="83"/>
+      <c r="CM20" s="83"/>
+      <c r="CN20" s="83"/>
+      <c r="CO20" s="83"/>
+      <c r="CP20" s="83"/>
+      <c r="CQ20" s="83"/>
+      <c r="CR20" s="83"/>
+      <c r="CS20" s="83"/>
+      <c r="CT20" s="83"/>
+      <c r="CU20" s="83"/>
+      <c r="CV20" s="83"/>
+      <c r="CW20" s="83"/>
+      <c r="CX20" s="83"/>
+      <c r="CY20" s="83"/>
+      <c r="CZ20" s="83"/>
+      <c r="DA20" s="83"/>
+      <c r="DB20" s="83"/>
+      <c r="DC20" s="83"/>
+      <c r="DD20" s="83"/>
+      <c r="DE20" s="83"/>
+      <c r="DF20" s="83"/>
+      <c r="DG20" s="83"/>
+      <c r="DH20" s="83"/>
+      <c r="DI20" s="83"/>
+      <c r="DJ20" s="83"/>
+      <c r="DK20" s="83"/>
+      <c r="DL20" s="83"/>
+      <c r="DM20" s="83"/>
+      <c r="DN20" s="83"/>
+      <c r="DO20" s="83"/>
+      <c r="DP20" s="83"/>
+      <c r="DQ20" s="83"/>
+      <c r="DR20" s="83"/>
+      <c r="DS20" s="83"/>
+      <c r="DT20" s="83"/>
+      <c r="DU20" s="83"/>
+      <c r="DV20" s="83"/>
+      <c r="DW20" s="83"/>
+      <c r="DX20" s="83"/>
+      <c r="DY20" s="83"/>
+      <c r="DZ20" s="83"/>
+      <c r="EA20" s="83"/>
+      <c r="EB20" s="83"/>
+      <c r="EC20" s="83"/>
+      <c r="ED20" s="83"/>
+      <c r="EE20" s="83"/>
+      <c r="EF20" s="83"/>
+      <c r="EG20" s="83"/>
+      <c r="EH20" s="83"/>
+      <c r="EI20" s="83"/>
+      <c r="EJ20" s="83"/>
+      <c r="EK20" s="83"/>
+      <c r="EL20" s="83"/>
+      <c r="EM20" s="83"/>
+      <c r="EN20" s="83"/>
+      <c r="EO20" s="83"/>
+      <c r="EP20" s="83"/>
+      <c r="EQ20" s="83"/>
+      <c r="ER20" s="83"/>
+      <c r="ES20" s="83"/>
+      <c r="ET20" s="83"/>
+      <c r="EU20" s="83"/>
+      <c r="EV20" s="83"/>
+      <c r="EW20" s="83"/>
+      <c r="EX20" s="83"/>
+      <c r="EY20" s="83"/>
+      <c r="EZ20" s="83"/>
+      <c r="FA20" s="83"/>
+      <c r="FB20" s="83"/>
+      <c r="FC20" s="83"/>
+      <c r="FD20" s="83"/>
+      <c r="FE20" s="83"/>
+      <c r="FF20" s="83"/>
+      <c r="FG20" s="83"/>
+      <c r="FH20" s="83"/>
+      <c r="FI20" s="83"/>
+      <c r="FJ20" s="83"/>
+      <c r="FK20" s="83"/>
+      <c r="FL20" s="83"/>
+      <c r="FM20" s="83"/>
+      <c r="FN20" s="83"/>
+      <c r="FO20" s="83"/>
+      <c r="FP20" s="83"/>
+      <c r="FQ20" s="83"/>
+      <c r="FR20" s="83"/>
+      <c r="FS20" s="83"/>
+      <c r="FT20" s="83"/>
+      <c r="FU20" s="83"/>
+      <c r="FV20" s="83"/>
+      <c r="FW20" s="83"/>
+      <c r="FX20" s="83"/>
+      <c r="FY20" s="83"/>
+      <c r="FZ20" s="83"/>
+      <c r="GA20" s="83"/>
+      <c r="GB20" s="83"/>
+      <c r="GC20" s="83"/>
+      <c r="GD20" s="83"/>
+      <c r="GE20" s="83"/>
+      <c r="GF20" s="83"/>
+      <c r="GG20" s="83"/>
+      <c r="GH20" s="83"/>
+      <c r="GI20" s="83"/>
+      <c r="GJ20" s="83"/>
+      <c r="GK20" s="83"/>
+      <c r="GL20" s="83"/>
+      <c r="GM20" s="83"/>
+      <c r="GN20" s="83"/>
+      <c r="GO20" s="83"/>
+      <c r="GP20" s="83"/>
+      <c r="GQ20" s="83"/>
+      <c r="GR20" s="83"/>
+      <c r="GS20" s="83"/>
+      <c r="GT20" s="83"/>
+      <c r="GU20" s="83"/>
+      <c r="GV20" s="83"/>
+      <c r="GW20" s="83"/>
+      <c r="GX20" s="83"/>
+      <c r="GY20" s="83"/>
+      <c r="GZ20" s="83"/>
+      <c r="HA20" s="83"/>
+      <c r="HB20" s="83"/>
+      <c r="HC20" s="83"/>
+      <c r="HD20" s="83"/>
+      <c r="HE20" s="83"/>
+      <c r="HF20" s="83"/>
+      <c r="HG20" s="83"/>
+      <c r="HH20" s="83"/>
+      <c r="HI20" s="83"/>
+      <c r="HJ20" s="83"/>
+      <c r="HK20" s="83"/>
+      <c r="HL20" s="83"/>
+      <c r="HM20" s="83"/>
+      <c r="HN20" s="83"/>
+      <c r="HO20" s="83"/>
+      <c r="HP20" s="83"/>
+      <c r="HQ20" s="83"/>
+      <c r="HR20" s="83"/>
+      <c r="HS20" s="83"/>
+      <c r="HT20" s="83"/>
+      <c r="HU20" s="83"/>
+      <c r="HV20" s="83"/>
+      <c r="HW20" s="83"/>
+      <c r="HX20" s="83"/>
+      <c r="HY20" s="83"/>
+      <c r="HZ20" s="83"/>
+      <c r="IA20" s="83"/>
+      <c r="IB20" s="83"/>
+      <c r="IC20" s="83"/>
+      <c r="ID20" s="83"/>
+      <c r="IE20" s="83"/>
+      <c r="IF20" s="83"/>
+      <c r="IG20" s="83"/>
+      <c r="IH20" s="83"/>
+      <c r="II20" s="83"/>
+      <c r="IJ20" s="83"/>
+      <c r="IK20" s="83"/>
+      <c r="IL20" s="83"/>
+      <c r="IM20" s="83"/>
+      <c r="IN20" s="83"/>
+      <c r="IO20" s="83"/>
+      <c r="IP20" s="83"/>
+      <c r="IQ20" s="83"/>
+      <c r="IR20" s="83"/>
+      <c r="IS20" s="83"/>
+      <c r="IT20" s="83"/>
+      <c r="IU20" s="83"/>
+      <c r="IV20" s="83"/>
+      <c r="IW20" s="83"/>
+    </row>
+    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="83"/>
+      <c r="G21" s="85"/>
+      <c r="H21" s="81"/>
+      <c r="I21" s="82"/>
+      <c r="J21" s="86" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E17" s="75" t="s">
-        <v>33</v>
-      </c>
-      <c r="F17" s="69" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" s="80"/>
-      <c r="I17" s="81" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E18" s="67" t="s">
-        <v>36</v>
-      </c>
-      <c r="H18" s="80"/>
-      <c r="I18" s="81"/>
-    </row>
-    <row r="19" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E19" s="67" t="s">
-        <v>35</v>
-      </c>
-      <c r="H19" s="80"/>
-    </row>
-    <row r="20" customFormat="false" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="82"/>
-      <c r="B20" s="82"/>
-      <c r="C20" s="82"/>
-      <c r="D20" s="82"/>
-      <c r="E20" s="82"/>
-      <c r="F20" s="82"/>
-      <c r="G20" s="82"/>
-      <c r="H20" s="80"/>
-      <c r="I20" s="82"/>
-      <c r="J20" s="83"/>
-      <c r="O20" s="82"/>
-      <c r="P20" s="82"/>
-      <c r="Q20" s="82"/>
-      <c r="R20" s="82"/>
-      <c r="S20" s="82"/>
-      <c r="T20" s="82"/>
-      <c r="U20" s="82"/>
-      <c r="V20" s="82"/>
-      <c r="W20" s="82"/>
-      <c r="X20" s="82"/>
-      <c r="Y20" s="82"/>
-      <c r="Z20" s="82"/>
-      <c r="AA20" s="82"/>
-      <c r="AB20" s="82"/>
-      <c r="AC20" s="82"/>
-      <c r="AD20" s="82"/>
-      <c r="AE20" s="82"/>
-      <c r="AF20" s="82"/>
-      <c r="AG20" s="82"/>
-      <c r="AH20" s="82"/>
-      <c r="AI20" s="82"/>
-      <c r="AJ20" s="82"/>
-      <c r="AK20" s="82"/>
-      <c r="AL20" s="82"/>
-      <c r="AM20" s="82"/>
-      <c r="AN20" s="82"/>
-      <c r="AO20" s="82"/>
-      <c r="AP20" s="82"/>
-      <c r="AQ20" s="82"/>
-      <c r="AR20" s="82"/>
-      <c r="AS20" s="82"/>
-      <c r="AT20" s="82"/>
-      <c r="AU20" s="82"/>
-      <c r="AV20" s="82"/>
-      <c r="AW20" s="82"/>
-      <c r="AX20" s="82"/>
-      <c r="AY20" s="82"/>
-      <c r="AZ20" s="82"/>
-      <c r="BA20" s="82"/>
-      <c r="BB20" s="82"/>
-      <c r="BC20" s="82"/>
-      <c r="BD20" s="82"/>
-      <c r="BE20" s="82"/>
-      <c r="BF20" s="82"/>
-      <c r="BG20" s="82"/>
-      <c r="BH20" s="82"/>
-      <c r="BI20" s="82"/>
-      <c r="BJ20" s="82"/>
-      <c r="BK20" s="82"/>
-      <c r="BL20" s="82"/>
-      <c r="BM20" s="82"/>
-      <c r="BN20" s="82"/>
-      <c r="BO20" s="82"/>
-      <c r="BP20" s="82"/>
-      <c r="BQ20" s="82"/>
-      <c r="BR20" s="82"/>
-      <c r="BS20" s="82"/>
-      <c r="BT20" s="82"/>
-      <c r="BU20" s="82"/>
-      <c r="BV20" s="82"/>
-      <c r="BW20" s="82"/>
-      <c r="BX20" s="82"/>
-      <c r="BY20" s="82"/>
-      <c r="BZ20" s="82"/>
-      <c r="CA20" s="82"/>
-      <c r="CB20" s="82"/>
-      <c r="CC20" s="82"/>
-      <c r="CD20" s="82"/>
-      <c r="CE20" s="82"/>
-      <c r="CF20" s="82"/>
-      <c r="CG20" s="82"/>
-      <c r="CH20" s="82"/>
-      <c r="CI20" s="82"/>
-      <c r="CJ20" s="82"/>
-      <c r="CK20" s="82"/>
-      <c r="CL20" s="82"/>
-      <c r="CM20" s="82"/>
-      <c r="CN20" s="82"/>
-      <c r="CO20" s="82"/>
-      <c r="CP20" s="82"/>
-      <c r="CQ20" s="82"/>
-      <c r="CR20" s="82"/>
-      <c r="CS20" s="82"/>
-      <c r="CT20" s="82"/>
-      <c r="CU20" s="82"/>
-      <c r="CV20" s="82"/>
-      <c r="CW20" s="82"/>
-      <c r="CX20" s="82"/>
-      <c r="CY20" s="82"/>
-      <c r="CZ20" s="82"/>
-      <c r="DA20" s="82"/>
-      <c r="DB20" s="82"/>
-      <c r="DC20" s="82"/>
-      <c r="DD20" s="82"/>
-      <c r="DE20" s="82"/>
-      <c r="DF20" s="82"/>
-      <c r="DG20" s="82"/>
-      <c r="DH20" s="82"/>
-      <c r="DI20" s="82"/>
-      <c r="DJ20" s="82"/>
-      <c r="DK20" s="82"/>
-      <c r="DL20" s="82"/>
-      <c r="DM20" s="82"/>
-      <c r="DN20" s="82"/>
-      <c r="DO20" s="82"/>
-      <c r="DP20" s="82"/>
-      <c r="DQ20" s="82"/>
-      <c r="DR20" s="82"/>
-      <c r="DS20" s="82"/>
-      <c r="DT20" s="82"/>
-      <c r="DU20" s="82"/>
-      <c r="DV20" s="82"/>
-      <c r="DW20" s="82"/>
-      <c r="DX20" s="82"/>
-      <c r="DY20" s="82"/>
-      <c r="DZ20" s="82"/>
-      <c r="EA20" s="82"/>
-      <c r="EB20" s="82"/>
-      <c r="EC20" s="82"/>
-      <c r="ED20" s="82"/>
-      <c r="EE20" s="82"/>
-      <c r="EF20" s="82"/>
-      <c r="EG20" s="82"/>
-      <c r="EH20" s="82"/>
-      <c r="EI20" s="82"/>
-      <c r="EJ20" s="82"/>
-      <c r="EK20" s="82"/>
-      <c r="EL20" s="82"/>
-      <c r="EM20" s="82"/>
-      <c r="EN20" s="82"/>
-      <c r="EO20" s="82"/>
-      <c r="EP20" s="82"/>
-      <c r="EQ20" s="82"/>
-      <c r="ER20" s="82"/>
-      <c r="ES20" s="82"/>
-      <c r="ET20" s="82"/>
-      <c r="EU20" s="82"/>
-      <c r="EV20" s="82"/>
-      <c r="EW20" s="82"/>
-      <c r="EX20" s="82"/>
-      <c r="EY20" s="82"/>
-      <c r="EZ20" s="82"/>
-      <c r="FA20" s="82"/>
-      <c r="FB20" s="82"/>
-      <c r="FC20" s="82"/>
-      <c r="FD20" s="82"/>
-      <c r="FE20" s="82"/>
-      <c r="FF20" s="82"/>
-      <c r="FG20" s="82"/>
-      <c r="FH20" s="82"/>
-      <c r="FI20" s="82"/>
-      <c r="FJ20" s="82"/>
-      <c r="FK20" s="82"/>
-      <c r="FL20" s="82"/>
-      <c r="FM20" s="82"/>
-      <c r="FN20" s="82"/>
-      <c r="FO20" s="82"/>
-      <c r="FP20" s="82"/>
-      <c r="FQ20" s="82"/>
-      <c r="FR20" s="82"/>
-      <c r="FS20" s="82"/>
-      <c r="FT20" s="82"/>
-      <c r="FU20" s="82"/>
-      <c r="FV20" s="82"/>
-      <c r="FW20" s="82"/>
-      <c r="FX20" s="82"/>
-      <c r="FY20" s="82"/>
-      <c r="FZ20" s="82"/>
-      <c r="GA20" s="82"/>
-      <c r="GB20" s="82"/>
-      <c r="GC20" s="82"/>
-      <c r="GD20" s="82"/>
-      <c r="GE20" s="82"/>
-      <c r="GF20" s="82"/>
-      <c r="GG20" s="82"/>
-      <c r="GH20" s="82"/>
-      <c r="GI20" s="82"/>
-      <c r="GJ20" s="82"/>
-      <c r="GK20" s="82"/>
-      <c r="GL20" s="82"/>
-      <c r="GM20" s="82"/>
-      <c r="GN20" s="82"/>
-      <c r="GO20" s="82"/>
-      <c r="GP20" s="82"/>
-      <c r="GQ20" s="82"/>
-      <c r="GR20" s="82"/>
-      <c r="GS20" s="82"/>
-      <c r="GT20" s="82"/>
-      <c r="GU20" s="82"/>
-      <c r="GV20" s="82"/>
-      <c r="GW20" s="82"/>
-      <c r="GX20" s="82"/>
-      <c r="GY20" s="82"/>
-      <c r="GZ20" s="82"/>
-      <c r="HA20" s="82"/>
-      <c r="HB20" s="82"/>
-      <c r="HC20" s="82"/>
-      <c r="HD20" s="82"/>
-      <c r="HE20" s="82"/>
-      <c r="HF20" s="82"/>
-      <c r="HG20" s="82"/>
-      <c r="HH20" s="82"/>
-      <c r="HI20" s="82"/>
-      <c r="HJ20" s="82"/>
-      <c r="HK20" s="82"/>
-      <c r="HL20" s="82"/>
-      <c r="HM20" s="82"/>
-      <c r="HN20" s="82"/>
-      <c r="HO20" s="82"/>
-      <c r="HP20" s="82"/>
-      <c r="HQ20" s="82"/>
-      <c r="HR20" s="82"/>
-      <c r="HS20" s="82"/>
-      <c r="HT20" s="82"/>
-      <c r="HU20" s="82"/>
-      <c r="HV20" s="82"/>
-      <c r="HW20" s="82"/>
-      <c r="HX20" s="82"/>
-      <c r="HY20" s="82"/>
-      <c r="HZ20" s="82"/>
-      <c r="IA20" s="82"/>
-      <c r="IB20" s="82"/>
-      <c r="IC20" s="82"/>
-      <c r="ID20" s="82"/>
-      <c r="IE20" s="82"/>
-      <c r="IF20" s="82"/>
-      <c r="IG20" s="82"/>
-      <c r="IH20" s="82"/>
-      <c r="II20" s="82"/>
-      <c r="IJ20" s="82"/>
-      <c r="IK20" s="82"/>
-      <c r="IL20" s="82"/>
-      <c r="IM20" s="82"/>
-      <c r="IN20" s="82"/>
-      <c r="IO20" s="82"/>
-      <c r="IP20" s="82"/>
-      <c r="IQ20" s="82"/>
-      <c r="IR20" s="82"/>
-      <c r="IS20" s="82"/>
-      <c r="IT20" s="82"/>
-      <c r="IU20" s="82"/>
-      <c r="IV20" s="82"/>
-      <c r="IW20" s="82"/>
-    </row>
-    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="82"/>
-      <c r="G21" s="84"/>
-      <c r="H21" s="80"/>
-      <c r="I21" s="81"/>
-      <c r="J21" s="85" t="s">
+    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="87"/>
+      <c r="G22" s="87"/>
+      <c r="H22" s="81"/>
+      <c r="I22" s="82"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="82"/>
+      <c r="R23" s="88"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="82"/>
+      <c r="L24" s="61" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="86"/>
-      <c r="G22" s="86"/>
-      <c r="H22" s="80"/>
-      <c r="I22" s="81"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I23" s="81"/>
-      <c r="R23" s="87"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I24" s="81"/>
-      <c r="L24" s="60" t="s">
-        <v>170</v>
-      </c>
-    </row>
     <row r="25" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I25" s="81"/>
+      <c r="I25" s="82"/>
     </row>
     <row r="26" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="3"/>
-      <c r="I26" s="81"/>
+      <c r="I26" s="82"/>
     </row>
     <row r="28" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D28" s="88"/>
+      <c r="D28" s="89"/>
     </row>
     <row r="29" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="89"/>
+      <c r="A29" s="90"/>
     </row>
     <row r="30" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="80"/>
+      <c r="A30" s="81"/>
     </row>
     <row r="31" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="89"/>
+      <c r="A31" s="90"/>
     </row>
     <row r="32" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="80"/>
+      <c r="A32" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7730,309 +7942,309 @@
   <dimension ref="A1:IW32"/>
   <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="12.55" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="60" width="12.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="60" width="12.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="60" width="14.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="60" width="12.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="60" width="17.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="60" width="15.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="60" width="13.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="60" width="13.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="60" width="14.55"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="10" min="10" style="60" width="9.1"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="11" style="60" width="9.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="61" width="12.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="61" width="12.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="61" width="14.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="61" width="12.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="61" width="17.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="61" width="15.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="61" width="13.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="61" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="61" width="14.55"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="10" min="10" style="61" width="9.1"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="11" style="61" width="9.1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="26.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="61" t="s">
-        <v>171</v>
-      </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="63" t="s">
+      <c r="A1" s="62" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
-      <c r="T1" s="62"/>
-      <c r="U1" s="62"/>
-      <c r="V1" s="62"/>
-      <c r="W1" s="62"/>
-      <c r="X1" s="62"/>
-      <c r="Y1" s="62"/>
-      <c r="Z1" s="62"/>
-      <c r="AA1" s="62"/>
-      <c r="AB1" s="62"/>
-      <c r="AC1" s="62"/>
-      <c r="AD1" s="62"/>
-      <c r="AE1" s="62"/>
-      <c r="AF1" s="62"/>
-      <c r="AG1" s="62"/>
-      <c r="AH1" s="62"/>
-      <c r="AI1" s="62"/>
-      <c r="AJ1" s="62"/>
-      <c r="AK1" s="62"/>
-      <c r="AL1" s="62"/>
-      <c r="AM1" s="62"/>
-      <c r="AN1" s="62"/>
-      <c r="AO1" s="62"/>
-      <c r="AP1" s="62"/>
-      <c r="AQ1" s="62"/>
-      <c r="AR1" s="62"/>
-      <c r="AS1" s="62"/>
-      <c r="AT1" s="62"/>
-      <c r="AU1" s="62"/>
-      <c r="AV1" s="62"/>
-      <c r="AW1" s="62"/>
-      <c r="AX1" s="62"/>
-      <c r="AY1" s="62"/>
-      <c r="AZ1" s="62"/>
-      <c r="BA1" s="62"/>
-      <c r="BB1" s="62"/>
-      <c r="BC1" s="62"/>
-      <c r="BD1" s="62"/>
-      <c r="BE1" s="62"/>
-      <c r="BF1" s="62"/>
-      <c r="BG1" s="62"/>
-      <c r="BH1" s="62"/>
-      <c r="BI1" s="62"/>
-      <c r="BJ1" s="62"/>
-      <c r="BK1" s="62"/>
-      <c r="BL1" s="62"/>
-      <c r="BM1" s="62"/>
-      <c r="BN1" s="62"/>
-      <c r="BO1" s="62"/>
-      <c r="BP1" s="62"/>
-      <c r="BQ1" s="62"/>
-      <c r="BR1" s="62"/>
-      <c r="BS1" s="62"/>
-      <c r="BT1" s="62"/>
-      <c r="BU1" s="62"/>
-      <c r="BV1" s="62"/>
-      <c r="BW1" s="62"/>
-      <c r="BX1" s="62"/>
-      <c r="BY1" s="62"/>
-      <c r="BZ1" s="62"/>
-      <c r="CA1" s="62"/>
-      <c r="CB1" s="62"/>
-      <c r="CC1" s="62"/>
-      <c r="CD1" s="62"/>
-      <c r="CE1" s="62"/>
-      <c r="CF1" s="62"/>
-      <c r="CG1" s="62"/>
-      <c r="CH1" s="62"/>
-      <c r="CI1" s="62"/>
-      <c r="CJ1" s="62"/>
-      <c r="CK1" s="62"/>
-      <c r="CL1" s="62"/>
-      <c r="CM1" s="62"/>
-      <c r="CN1" s="62"/>
-      <c r="CO1" s="62"/>
-      <c r="CP1" s="62"/>
-      <c r="CQ1" s="62"/>
-      <c r="CR1" s="62"/>
-      <c r="CS1" s="62"/>
-      <c r="CT1" s="62"/>
-      <c r="CU1" s="62"/>
-      <c r="CV1" s="62"/>
-      <c r="CW1" s="62"/>
-      <c r="CX1" s="62"/>
-      <c r="CY1" s="62"/>
-      <c r="CZ1" s="62"/>
-      <c r="DA1" s="62"/>
-      <c r="DB1" s="62"/>
-      <c r="DC1" s="62"/>
-      <c r="DD1" s="62"/>
-      <c r="DE1" s="62"/>
-      <c r="DF1" s="62"/>
-      <c r="DG1" s="62"/>
-      <c r="DH1" s="62"/>
-      <c r="DI1" s="62"/>
-      <c r="DJ1" s="62"/>
-      <c r="DK1" s="62"/>
-      <c r="DL1" s="62"/>
-      <c r="DM1" s="62"/>
-      <c r="DN1" s="62"/>
-      <c r="DO1" s="62"/>
-      <c r="DP1" s="62"/>
-      <c r="DQ1" s="62"/>
-      <c r="DR1" s="62"/>
-      <c r="DS1" s="62"/>
-      <c r="DT1" s="62"/>
-      <c r="DU1" s="62"/>
-      <c r="DV1" s="62"/>
-      <c r="DW1" s="62"/>
-      <c r="DX1" s="62"/>
-      <c r="DY1" s="62"/>
-      <c r="DZ1" s="62"/>
-      <c r="EA1" s="62"/>
-      <c r="EB1" s="62"/>
-      <c r="EC1" s="62"/>
-      <c r="ED1" s="62"/>
-      <c r="EE1" s="62"/>
-      <c r="EF1" s="62"/>
-      <c r="EG1" s="62"/>
-      <c r="EH1" s="62"/>
-      <c r="EI1" s="62"/>
-      <c r="EJ1" s="62"/>
-      <c r="EK1" s="62"/>
-      <c r="EL1" s="62"/>
-      <c r="EM1" s="62"/>
-      <c r="EN1" s="62"/>
-      <c r="EO1" s="62"/>
-      <c r="EP1" s="62"/>
-      <c r="EQ1" s="62"/>
-      <c r="ER1" s="62"/>
-      <c r="ES1" s="62"/>
-      <c r="ET1" s="62"/>
-      <c r="EU1" s="62"/>
-      <c r="EV1" s="62"/>
-      <c r="EW1" s="62"/>
-      <c r="EX1" s="62"/>
-      <c r="EY1" s="62"/>
-      <c r="EZ1" s="62"/>
-      <c r="FA1" s="62"/>
-      <c r="FB1" s="62"/>
-      <c r="FC1" s="62"/>
-      <c r="FD1" s="62"/>
-      <c r="FE1" s="62"/>
-      <c r="FF1" s="62"/>
-      <c r="FG1" s="62"/>
-      <c r="FH1" s="62"/>
-      <c r="FI1" s="62"/>
-      <c r="FJ1" s="62"/>
-      <c r="FK1" s="62"/>
-      <c r="FL1" s="62"/>
-      <c r="FM1" s="62"/>
-      <c r="FN1" s="62"/>
-      <c r="FO1" s="62"/>
-      <c r="FP1" s="62"/>
-      <c r="FQ1" s="62"/>
-      <c r="FR1" s="62"/>
-      <c r="FS1" s="62"/>
-      <c r="FT1" s="62"/>
-      <c r="FU1" s="62"/>
-      <c r="FV1" s="62"/>
-      <c r="FW1" s="62"/>
-      <c r="FX1" s="62"/>
-      <c r="FY1" s="62"/>
-      <c r="FZ1" s="62"/>
-      <c r="GA1" s="62"/>
-      <c r="GB1" s="62"/>
-      <c r="GC1" s="62"/>
-      <c r="GD1" s="62"/>
-      <c r="GE1" s="62"/>
-      <c r="GF1" s="62"/>
-      <c r="GG1" s="62"/>
-      <c r="GH1" s="62"/>
-      <c r="GI1" s="62"/>
-      <c r="GJ1" s="62"/>
-      <c r="GK1" s="62"/>
-      <c r="GL1" s="62"/>
-      <c r="GM1" s="62"/>
-      <c r="GN1" s="62"/>
-      <c r="GO1" s="62"/>
-      <c r="GP1" s="62"/>
-      <c r="GQ1" s="62"/>
-      <c r="GR1" s="62"/>
-      <c r="GS1" s="62"/>
-      <c r="GT1" s="62"/>
-      <c r="GU1" s="62"/>
-      <c r="GV1" s="62"/>
-      <c r="GW1" s="62"/>
-      <c r="GX1" s="62"/>
-      <c r="GY1" s="62"/>
-      <c r="GZ1" s="62"/>
-      <c r="HA1" s="62"/>
-      <c r="HB1" s="62"/>
-      <c r="HC1" s="62"/>
-      <c r="HD1" s="62"/>
-      <c r="HE1" s="62"/>
-      <c r="HF1" s="62"/>
-      <c r="HG1" s="62"/>
-      <c r="HH1" s="62"/>
-      <c r="HI1" s="62"/>
-      <c r="HJ1" s="62"/>
-      <c r="HK1" s="62"/>
-      <c r="HL1" s="62"/>
-      <c r="HM1" s="62"/>
-      <c r="HN1" s="62"/>
-      <c r="HO1" s="62"/>
-      <c r="HP1" s="62"/>
-      <c r="HQ1" s="62"/>
-      <c r="HR1" s="62"/>
-      <c r="HS1" s="62"/>
-      <c r="HT1" s="62"/>
-      <c r="HU1" s="62"/>
-      <c r="HV1" s="62"/>
-      <c r="HW1" s="62"/>
-      <c r="HX1" s="62"/>
-      <c r="HY1" s="62"/>
-      <c r="HZ1" s="62"/>
-      <c r="IA1" s="62"/>
-      <c r="IB1" s="62"/>
-      <c r="IC1" s="62"/>
-      <c r="ID1" s="62"/>
-      <c r="IE1" s="62"/>
-      <c r="IF1" s="62"/>
-      <c r="IG1" s="62"/>
-      <c r="IH1" s="62"/>
-      <c r="II1" s="62"/>
-      <c r="IJ1" s="62"/>
-      <c r="IK1" s="62"/>
-      <c r="IL1" s="62"/>
-      <c r="IM1" s="62"/>
-      <c r="IN1" s="62"/>
-      <c r="IO1" s="62"/>
-      <c r="IP1" s="62"/>
-      <c r="IQ1" s="62"/>
-      <c r="IR1" s="62"/>
-      <c r="IS1" s="62"/>
-      <c r="IT1" s="62"/>
-      <c r="IU1" s="62"/>
-      <c r="IV1" s="62"/>
-      <c r="IW1" s="62"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="63"/>
+      <c r="T1" s="63"/>
+      <c r="U1" s="63"/>
+      <c r="V1" s="63"/>
+      <c r="W1" s="63"/>
+      <c r="X1" s="63"/>
+      <c r="Y1" s="63"/>
+      <c r="Z1" s="63"/>
+      <c r="AA1" s="63"/>
+      <c r="AB1" s="63"/>
+      <c r="AC1" s="63"/>
+      <c r="AD1" s="63"/>
+      <c r="AE1" s="63"/>
+      <c r="AF1" s="63"/>
+      <c r="AG1" s="63"/>
+      <c r="AH1" s="63"/>
+      <c r="AI1" s="63"/>
+      <c r="AJ1" s="63"/>
+      <c r="AK1" s="63"/>
+      <c r="AL1" s="63"/>
+      <c r="AM1" s="63"/>
+      <c r="AN1" s="63"/>
+      <c r="AO1" s="63"/>
+      <c r="AP1" s="63"/>
+      <c r="AQ1" s="63"/>
+      <c r="AR1" s="63"/>
+      <c r="AS1" s="63"/>
+      <c r="AT1" s="63"/>
+      <c r="AU1" s="63"/>
+      <c r="AV1" s="63"/>
+      <c r="AW1" s="63"/>
+      <c r="AX1" s="63"/>
+      <c r="AY1" s="63"/>
+      <c r="AZ1" s="63"/>
+      <c r="BA1" s="63"/>
+      <c r="BB1" s="63"/>
+      <c r="BC1" s="63"/>
+      <c r="BD1" s="63"/>
+      <c r="BE1" s="63"/>
+      <c r="BF1" s="63"/>
+      <c r="BG1" s="63"/>
+      <c r="BH1" s="63"/>
+      <c r="BI1" s="63"/>
+      <c r="BJ1" s="63"/>
+      <c r="BK1" s="63"/>
+      <c r="BL1" s="63"/>
+      <c r="BM1" s="63"/>
+      <c r="BN1" s="63"/>
+      <c r="BO1" s="63"/>
+      <c r="BP1" s="63"/>
+      <c r="BQ1" s="63"/>
+      <c r="BR1" s="63"/>
+      <c r="BS1" s="63"/>
+      <c r="BT1" s="63"/>
+      <c r="BU1" s="63"/>
+      <c r="BV1" s="63"/>
+      <c r="BW1" s="63"/>
+      <c r="BX1" s="63"/>
+      <c r="BY1" s="63"/>
+      <c r="BZ1" s="63"/>
+      <c r="CA1" s="63"/>
+      <c r="CB1" s="63"/>
+      <c r="CC1" s="63"/>
+      <c r="CD1" s="63"/>
+      <c r="CE1" s="63"/>
+      <c r="CF1" s="63"/>
+      <c r="CG1" s="63"/>
+      <c r="CH1" s="63"/>
+      <c r="CI1" s="63"/>
+      <c r="CJ1" s="63"/>
+      <c r="CK1" s="63"/>
+      <c r="CL1" s="63"/>
+      <c r="CM1" s="63"/>
+      <c r="CN1" s="63"/>
+      <c r="CO1" s="63"/>
+      <c r="CP1" s="63"/>
+      <c r="CQ1" s="63"/>
+      <c r="CR1" s="63"/>
+      <c r="CS1" s="63"/>
+      <c r="CT1" s="63"/>
+      <c r="CU1" s="63"/>
+      <c r="CV1" s="63"/>
+      <c r="CW1" s="63"/>
+      <c r="CX1" s="63"/>
+      <c r="CY1" s="63"/>
+      <c r="CZ1" s="63"/>
+      <c r="DA1" s="63"/>
+      <c r="DB1" s="63"/>
+      <c r="DC1" s="63"/>
+      <c r="DD1" s="63"/>
+      <c r="DE1" s="63"/>
+      <c r="DF1" s="63"/>
+      <c r="DG1" s="63"/>
+      <c r="DH1" s="63"/>
+      <c r="DI1" s="63"/>
+      <c r="DJ1" s="63"/>
+      <c r="DK1" s="63"/>
+      <c r="DL1" s="63"/>
+      <c r="DM1" s="63"/>
+      <c r="DN1" s="63"/>
+      <c r="DO1" s="63"/>
+      <c r="DP1" s="63"/>
+      <c r="DQ1" s="63"/>
+      <c r="DR1" s="63"/>
+      <c r="DS1" s="63"/>
+      <c r="DT1" s="63"/>
+      <c r="DU1" s="63"/>
+      <c r="DV1" s="63"/>
+      <c r="DW1" s="63"/>
+      <c r="DX1" s="63"/>
+      <c r="DY1" s="63"/>
+      <c r="DZ1" s="63"/>
+      <c r="EA1" s="63"/>
+      <c r="EB1" s="63"/>
+      <c r="EC1" s="63"/>
+      <c r="ED1" s="63"/>
+      <c r="EE1" s="63"/>
+      <c r="EF1" s="63"/>
+      <c r="EG1" s="63"/>
+      <c r="EH1" s="63"/>
+      <c r="EI1" s="63"/>
+      <c r="EJ1" s="63"/>
+      <c r="EK1" s="63"/>
+      <c r="EL1" s="63"/>
+      <c r="EM1" s="63"/>
+      <c r="EN1" s="63"/>
+      <c r="EO1" s="63"/>
+      <c r="EP1" s="63"/>
+      <c r="EQ1" s="63"/>
+      <c r="ER1" s="63"/>
+      <c r="ES1" s="63"/>
+      <c r="ET1" s="63"/>
+      <c r="EU1" s="63"/>
+      <c r="EV1" s="63"/>
+      <c r="EW1" s="63"/>
+      <c r="EX1" s="63"/>
+      <c r="EY1" s="63"/>
+      <c r="EZ1" s="63"/>
+      <c r="FA1" s="63"/>
+      <c r="FB1" s="63"/>
+      <c r="FC1" s="63"/>
+      <c r="FD1" s="63"/>
+      <c r="FE1" s="63"/>
+      <c r="FF1" s="63"/>
+      <c r="FG1" s="63"/>
+      <c r="FH1" s="63"/>
+      <c r="FI1" s="63"/>
+      <c r="FJ1" s="63"/>
+      <c r="FK1" s="63"/>
+      <c r="FL1" s="63"/>
+      <c r="FM1" s="63"/>
+      <c r="FN1" s="63"/>
+      <c r="FO1" s="63"/>
+      <c r="FP1" s="63"/>
+      <c r="FQ1" s="63"/>
+      <c r="FR1" s="63"/>
+      <c r="FS1" s="63"/>
+      <c r="FT1" s="63"/>
+      <c r="FU1" s="63"/>
+      <c r="FV1" s="63"/>
+      <c r="FW1" s="63"/>
+      <c r="FX1" s="63"/>
+      <c r="FY1" s="63"/>
+      <c r="FZ1" s="63"/>
+      <c r="GA1" s="63"/>
+      <c r="GB1" s="63"/>
+      <c r="GC1" s="63"/>
+      <c r="GD1" s="63"/>
+      <c r="GE1" s="63"/>
+      <c r="GF1" s="63"/>
+      <c r="GG1" s="63"/>
+      <c r="GH1" s="63"/>
+      <c r="GI1" s="63"/>
+      <c r="GJ1" s="63"/>
+      <c r="GK1" s="63"/>
+      <c r="GL1" s="63"/>
+      <c r="GM1" s="63"/>
+      <c r="GN1" s="63"/>
+      <c r="GO1" s="63"/>
+      <c r="GP1" s="63"/>
+      <c r="GQ1" s="63"/>
+      <c r="GR1" s="63"/>
+      <c r="GS1" s="63"/>
+      <c r="GT1" s="63"/>
+      <c r="GU1" s="63"/>
+      <c r="GV1" s="63"/>
+      <c r="GW1" s="63"/>
+      <c r="GX1" s="63"/>
+      <c r="GY1" s="63"/>
+      <c r="GZ1" s="63"/>
+      <c r="HA1" s="63"/>
+      <c r="HB1" s="63"/>
+      <c r="HC1" s="63"/>
+      <c r="HD1" s="63"/>
+      <c r="HE1" s="63"/>
+      <c r="HF1" s="63"/>
+      <c r="HG1" s="63"/>
+      <c r="HH1" s="63"/>
+      <c r="HI1" s="63"/>
+      <c r="HJ1" s="63"/>
+      <c r="HK1" s="63"/>
+      <c r="HL1" s="63"/>
+      <c r="HM1" s="63"/>
+      <c r="HN1" s="63"/>
+      <c r="HO1" s="63"/>
+      <c r="HP1" s="63"/>
+      <c r="HQ1" s="63"/>
+      <c r="HR1" s="63"/>
+      <c r="HS1" s="63"/>
+      <c r="HT1" s="63"/>
+      <c r="HU1" s="63"/>
+      <c r="HV1" s="63"/>
+      <c r="HW1" s="63"/>
+      <c r="HX1" s="63"/>
+      <c r="HY1" s="63"/>
+      <c r="HZ1" s="63"/>
+      <c r="IA1" s="63"/>
+      <c r="IB1" s="63"/>
+      <c r="IC1" s="63"/>
+      <c r="ID1" s="63"/>
+      <c r="IE1" s="63"/>
+      <c r="IF1" s="63"/>
+      <c r="IG1" s="63"/>
+      <c r="IH1" s="63"/>
+      <c r="II1" s="63"/>
+      <c r="IJ1" s="63"/>
+      <c r="IK1" s="63"/>
+      <c r="IL1" s="63"/>
+      <c r="IM1" s="63"/>
+      <c r="IN1" s="63"/>
+      <c r="IO1" s="63"/>
+      <c r="IP1" s="63"/>
+      <c r="IQ1" s="63"/>
+      <c r="IR1" s="63"/>
+      <c r="IS1" s="63"/>
+      <c r="IT1" s="63"/>
+      <c r="IU1" s="63"/>
+      <c r="IV1" s="63"/>
+      <c r="IW1" s="63"/>
     </row>
     <row r="2" customFormat="false" ht="23.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="65" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="65" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="64" t="s">
+      <c r="C2" s="65" t="s">
         <v>150</v>
       </c>
-      <c r="C2" s="64" t="s">
+      <c r="D2" s="65" t="s">
         <v>151</v>
       </c>
-      <c r="D2" s="64" t="s">
+      <c r="E2" s="65" t="s">
         <v>152</v>
       </c>
-      <c r="E2" s="64" t="s">
-        <v>153</v>
-      </c>
-      <c r="F2" s="64" t="s">
-        <v>153</v>
-      </c>
-      <c r="G2" s="64" t="s">
+      <c r="F2" s="65" t="s">
+        <v>152</v>
+      </c>
+      <c r="G2" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="H2" s="65" t="s">
-        <v>142</v>
-      </c>
-      <c r="I2" s="66"/>
-      <c r="L2" s="63" t="s">
+      <c r="H2" s="66" t="s">
+        <v>141</v>
+      </c>
+      <c r="I2" s="67"/>
+      <c r="L2" s="64" t="s">
         <v>51</v>
       </c>
     </row>
@@ -8049,8 +8261,8 @@
       <c r="D3" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="E3" s="67" t="s">
-        <v>154</v>
+      <c r="E3" s="68" t="s">
+        <v>153</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>74</v>
@@ -8061,32 +8273,32 @@
       <c r="H3" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="I3" s="68"/>
+      <c r="I3" s="69"/>
     </row>
     <row r="4" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="69" t="s">
+      <c r="A4" s="70" t="s">
         <v>87</v>
       </c>
       <c r="B4" s="13"/>
-      <c r="C4" s="70" t="s">
+      <c r="C4" s="71" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="E4" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="F4" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="E4" s="67" t="s">
-        <v>155</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="H4" s="69" t="s">
-        <v>139</v>
-      </c>
-      <c r="I4" s="68"/>
+      <c r="H4" s="70" t="s">
+        <v>138</v>
+      </c>
+      <c r="I4" s="69"/>
     </row>
     <row r="5" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="70" t="s">
+      <c r="A5" s="71" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="13" t="s">
@@ -8095,19 +8307,19 @@
       <c r="D5" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="E5" s="70" t="s">
-        <v>156</v>
+      <c r="E5" s="71" t="s">
+        <v>155</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="G5" s="65" t="s">
+      <c r="G5" s="66" t="s">
         <v>71</v>
       </c>
       <c r="H5" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="I5" s="71"/>
+      <c r="I5" s="72"/>
     </row>
     <row r="6" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
@@ -8116,25 +8328,25 @@
       <c r="C6" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="70" t="s">
-        <v>157</v>
-      </c>
-      <c r="F6" s="69" t="s">
+      <c r="E6" s="71" t="s">
+        <v>156</v>
+      </c>
+      <c r="F6" s="70" t="s">
         <v>120</v>
       </c>
-      <c r="G6" s="69" t="s">
+      <c r="G6" s="70" t="s">
         <v>62</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="I6" s="71"/>
+      <c r="I6" s="72"/>
     </row>
     <row r="7" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="70" t="s">
+      <c r="C7" s="71" t="s">
         <v>6</v>
       </c>
       <c r="E7" s="13" t="s">
@@ -8144,18 +8356,18 @@
         <v>77</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="H7" s="69" t="s">
+        <v>145</v>
+      </c>
+      <c r="H7" s="70" t="s">
         <v>131</v>
       </c>
-      <c r="I7" s="68"/>
+      <c r="I7" s="69"/>
     </row>
     <row r="8" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="72" t="s">
+      <c r="B8" s="73" t="s">
         <v>63</v>
       </c>
       <c r="C8" s="13" t="s">
@@ -8165,17 +8377,17 @@
         <v>20</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G8" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="H8" s="69" t="s">
+      <c r="H8" s="70" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="90" t="s">
+      <c r="A9" s="91" t="s">
         <v>32</v>
       </c>
       <c r="B9" s="13" t="s">
@@ -8184,46 +8396,46 @@
       <c r="C9" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="70" t="s">
+      <c r="E9" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="74"/>
-      <c r="H9" s="75" t="s">
+      <c r="G9" s="75"/>
+      <c r="H9" s="76" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="73" t="s">
+      <c r="A10" s="74" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="70" t="s">
+      <c r="E10" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="76" t="s">
-        <v>158</v>
-      </c>
-      <c r="G10" s="65"/>
+      <c r="F10" s="77" t="s">
+        <v>157</v>
+      </c>
+      <c r="G10" s="66"/>
     </row>
     <row r="11" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="65" t="s">
+      <c r="B11" s="66" t="s">
         <v>48</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="72" t="s">
-        <v>159</v>
-      </c>
-      <c r="E11" s="91" t="s">
+      <c r="D11" s="73" t="s">
+        <v>158</v>
+      </c>
+      <c r="E11" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="69" t="s">
+      <c r="F11" s="70" t="s">
         <v>116</v>
       </c>
-      <c r="H11" s="77"/>
+      <c r="H11" s="78"/>
     </row>
     <row r="12" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="13" t="s">
@@ -8235,430 +8447,430 @@
       <c r="D12" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="E12" s="75" t="s">
-        <v>172</v>
+      <c r="E12" s="76" t="s">
+        <v>171</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="77"/>
-      <c r="H12" s="69"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="70"/>
     </row>
     <row r="13" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="65" t="s">
+      <c r="A13" s="66" t="s">
         <v>67</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="70" t="s">
+      <c r="D13" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="E13" s="75" t="s">
+      <c r="E13" s="76" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="75" t="s">
+      <c r="F13" s="76" t="s">
         <v>41</v>
       </c>
-      <c r="H13" s="69"/>
+      <c r="H13" s="70"/>
     </row>
     <row r="14" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="75" t="s">
+      <c r="C14" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="75" t="s">
+      <c r="D14" s="76" t="s">
+        <v>159</v>
+      </c>
+      <c r="E14" s="68" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="79" t="s">
         <v>160</v>
       </c>
-      <c r="E14" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="78" t="s">
+      <c r="I14" s="80" t="s">
         <v>161</v>
       </c>
-      <c r="I14" s="79" t="s">
+      <c r="L14" s="61" t="s">
         <v>162</v>
       </c>
-      <c r="L14" s="60" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="65" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="64" t="s">
+      <c r="C15" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="76" t="s">
         <v>164</v>
       </c>
-      <c r="C15" s="67" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="75" t="s">
-        <v>165</v>
-      </c>
-      <c r="E15" s="75" t="s">
+      <c r="E15" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="H15" s="80" t="s">
+      <c r="H15" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="I15" s="81" t="s">
-        <v>147</v>
+      <c r="I15" s="82" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="67" t="s">
+      <c r="C16" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="67" t="s">
+      <c r="E16" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="65" t="s">
+      <c r="F16" s="66" t="s">
+        <v>165</v>
+      </c>
+      <c r="H16" s="93" t="s">
+        <v>5</v>
+      </c>
+      <c r="I16" s="82" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E17" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="70" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17" s="81" t="s">
         <v>166</v>
       </c>
-      <c r="H16" s="92" t="s">
-        <v>5</v>
-      </c>
-      <c r="I16" s="81" t="s">
+      <c r="I17" s="82" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E18" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="H18" s="81"/>
+      <c r="I18" s="93" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H19" s="81"/>
+    </row>
+    <row r="20" customFormat="false" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="83"/>
+      <c r="B20" s="83"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="83"/>
+      <c r="J20" s="84"/>
+      <c r="O20" s="83"/>
+      <c r="P20" s="83"/>
+      <c r="Q20" s="83"/>
+      <c r="R20" s="83"/>
+      <c r="S20" s="83"/>
+      <c r="T20" s="83"/>
+      <c r="U20" s="83"/>
+      <c r="V20" s="83"/>
+      <c r="W20" s="83"/>
+      <c r="X20" s="83"/>
+      <c r="Y20" s="83"/>
+      <c r="Z20" s="83"/>
+      <c r="AA20" s="83"/>
+      <c r="AB20" s="83"/>
+      <c r="AC20" s="83"/>
+      <c r="AD20" s="83"/>
+      <c r="AE20" s="83"/>
+      <c r="AF20" s="83"/>
+      <c r="AG20" s="83"/>
+      <c r="AH20" s="83"/>
+      <c r="AI20" s="83"/>
+      <c r="AJ20" s="83"/>
+      <c r="AK20" s="83"/>
+      <c r="AL20" s="83"/>
+      <c r="AM20" s="83"/>
+      <c r="AN20" s="83"/>
+      <c r="AO20" s="83"/>
+      <c r="AP20" s="83"/>
+      <c r="AQ20" s="83"/>
+      <c r="AR20" s="83"/>
+      <c r="AS20" s="83"/>
+      <c r="AT20" s="83"/>
+      <c r="AU20" s="83"/>
+      <c r="AV20" s="83"/>
+      <c r="AW20" s="83"/>
+      <c r="AX20" s="83"/>
+      <c r="AY20" s="83"/>
+      <c r="AZ20" s="83"/>
+      <c r="BA20" s="83"/>
+      <c r="BB20" s="83"/>
+      <c r="BC20" s="83"/>
+      <c r="BD20" s="83"/>
+      <c r="BE20" s="83"/>
+      <c r="BF20" s="83"/>
+      <c r="BG20" s="83"/>
+      <c r="BH20" s="83"/>
+      <c r="BI20" s="83"/>
+      <c r="BJ20" s="83"/>
+      <c r="BK20" s="83"/>
+      <c r="BL20" s="83"/>
+      <c r="BM20" s="83"/>
+      <c r="BN20" s="83"/>
+      <c r="BO20" s="83"/>
+      <c r="BP20" s="83"/>
+      <c r="BQ20" s="83"/>
+      <c r="BR20" s="83"/>
+      <c r="BS20" s="83"/>
+      <c r="BT20" s="83"/>
+      <c r="BU20" s="83"/>
+      <c r="BV20" s="83"/>
+      <c r="BW20" s="83"/>
+      <c r="BX20" s="83"/>
+      <c r="BY20" s="83"/>
+      <c r="BZ20" s="83"/>
+      <c r="CA20" s="83"/>
+      <c r="CB20" s="83"/>
+      <c r="CC20" s="83"/>
+      <c r="CD20" s="83"/>
+      <c r="CE20" s="83"/>
+      <c r="CF20" s="83"/>
+      <c r="CG20" s="83"/>
+      <c r="CH20" s="83"/>
+      <c r="CI20" s="83"/>
+      <c r="CJ20" s="83"/>
+      <c r="CK20" s="83"/>
+      <c r="CL20" s="83"/>
+      <c r="CM20" s="83"/>
+      <c r="CN20" s="83"/>
+      <c r="CO20" s="83"/>
+      <c r="CP20" s="83"/>
+      <c r="CQ20" s="83"/>
+      <c r="CR20" s="83"/>
+      <c r="CS20" s="83"/>
+      <c r="CT20" s="83"/>
+      <c r="CU20" s="83"/>
+      <c r="CV20" s="83"/>
+      <c r="CW20" s="83"/>
+      <c r="CX20" s="83"/>
+      <c r="CY20" s="83"/>
+      <c r="CZ20" s="83"/>
+      <c r="DA20" s="83"/>
+      <c r="DB20" s="83"/>
+      <c r="DC20" s="83"/>
+      <c r="DD20" s="83"/>
+      <c r="DE20" s="83"/>
+      <c r="DF20" s="83"/>
+      <c r="DG20" s="83"/>
+      <c r="DH20" s="83"/>
+      <c r="DI20" s="83"/>
+      <c r="DJ20" s="83"/>
+      <c r="DK20" s="83"/>
+      <c r="DL20" s="83"/>
+      <c r="DM20" s="83"/>
+      <c r="DN20" s="83"/>
+      <c r="DO20" s="83"/>
+      <c r="DP20" s="83"/>
+      <c r="DQ20" s="83"/>
+      <c r="DR20" s="83"/>
+      <c r="DS20" s="83"/>
+      <c r="DT20" s="83"/>
+      <c r="DU20" s="83"/>
+      <c r="DV20" s="83"/>
+      <c r="DW20" s="83"/>
+      <c r="DX20" s="83"/>
+      <c r="DY20" s="83"/>
+      <c r="DZ20" s="83"/>
+      <c r="EA20" s="83"/>
+      <c r="EB20" s="83"/>
+      <c r="EC20" s="83"/>
+      <c r="ED20" s="83"/>
+      <c r="EE20" s="83"/>
+      <c r="EF20" s="83"/>
+      <c r="EG20" s="83"/>
+      <c r="EH20" s="83"/>
+      <c r="EI20" s="83"/>
+      <c r="EJ20" s="83"/>
+      <c r="EK20" s="83"/>
+      <c r="EL20" s="83"/>
+      <c r="EM20" s="83"/>
+      <c r="EN20" s="83"/>
+      <c r="EO20" s="83"/>
+      <c r="EP20" s="83"/>
+      <c r="EQ20" s="83"/>
+      <c r="ER20" s="83"/>
+      <c r="ES20" s="83"/>
+      <c r="ET20" s="83"/>
+      <c r="EU20" s="83"/>
+      <c r="EV20" s="83"/>
+      <c r="EW20" s="83"/>
+      <c r="EX20" s="83"/>
+      <c r="EY20" s="83"/>
+      <c r="EZ20" s="83"/>
+      <c r="FA20" s="83"/>
+      <c r="FB20" s="83"/>
+      <c r="FC20" s="83"/>
+      <c r="FD20" s="83"/>
+      <c r="FE20" s="83"/>
+      <c r="FF20" s="83"/>
+      <c r="FG20" s="83"/>
+      <c r="FH20" s="83"/>
+      <c r="FI20" s="83"/>
+      <c r="FJ20" s="83"/>
+      <c r="FK20" s="83"/>
+      <c r="FL20" s="83"/>
+      <c r="FM20" s="83"/>
+      <c r="FN20" s="83"/>
+      <c r="FO20" s="83"/>
+      <c r="FP20" s="83"/>
+      <c r="FQ20" s="83"/>
+      <c r="FR20" s="83"/>
+      <c r="FS20" s="83"/>
+      <c r="FT20" s="83"/>
+      <c r="FU20" s="83"/>
+      <c r="FV20" s="83"/>
+      <c r="FW20" s="83"/>
+      <c r="FX20" s="83"/>
+      <c r="FY20" s="83"/>
+      <c r="FZ20" s="83"/>
+      <c r="GA20" s="83"/>
+      <c r="GB20" s="83"/>
+      <c r="GC20" s="83"/>
+      <c r="GD20" s="83"/>
+      <c r="GE20" s="83"/>
+      <c r="GF20" s="83"/>
+      <c r="GG20" s="83"/>
+      <c r="GH20" s="83"/>
+      <c r="GI20" s="83"/>
+      <c r="GJ20" s="83"/>
+      <c r="GK20" s="83"/>
+      <c r="GL20" s="83"/>
+      <c r="GM20" s="83"/>
+      <c r="GN20" s="83"/>
+      <c r="GO20" s="83"/>
+      <c r="GP20" s="83"/>
+      <c r="GQ20" s="83"/>
+      <c r="GR20" s="83"/>
+      <c r="GS20" s="83"/>
+      <c r="GT20" s="83"/>
+      <c r="GU20" s="83"/>
+      <c r="GV20" s="83"/>
+      <c r="GW20" s="83"/>
+      <c r="GX20" s="83"/>
+      <c r="GY20" s="83"/>
+      <c r="GZ20" s="83"/>
+      <c r="HA20" s="83"/>
+      <c r="HB20" s="83"/>
+      <c r="HC20" s="83"/>
+      <c r="HD20" s="83"/>
+      <c r="HE20" s="83"/>
+      <c r="HF20" s="83"/>
+      <c r="HG20" s="83"/>
+      <c r="HH20" s="83"/>
+      <c r="HI20" s="83"/>
+      <c r="HJ20" s="83"/>
+      <c r="HK20" s="83"/>
+      <c r="HL20" s="83"/>
+      <c r="HM20" s="83"/>
+      <c r="HN20" s="83"/>
+      <c r="HO20" s="83"/>
+      <c r="HP20" s="83"/>
+      <c r="HQ20" s="83"/>
+      <c r="HR20" s="83"/>
+      <c r="HS20" s="83"/>
+      <c r="HT20" s="83"/>
+      <c r="HU20" s="83"/>
+      <c r="HV20" s="83"/>
+      <c r="HW20" s="83"/>
+      <c r="HX20" s="83"/>
+      <c r="HY20" s="83"/>
+      <c r="HZ20" s="83"/>
+      <c r="IA20" s="83"/>
+      <c r="IB20" s="83"/>
+      <c r="IC20" s="83"/>
+      <c r="ID20" s="83"/>
+      <c r="IE20" s="83"/>
+      <c r="IF20" s="83"/>
+      <c r="IG20" s="83"/>
+      <c r="IH20" s="83"/>
+      <c r="II20" s="83"/>
+      <c r="IJ20" s="83"/>
+      <c r="IK20" s="83"/>
+      <c r="IL20" s="83"/>
+      <c r="IM20" s="83"/>
+      <c r="IN20" s="83"/>
+      <c r="IO20" s="83"/>
+      <c r="IP20" s="83"/>
+      <c r="IQ20" s="83"/>
+      <c r="IR20" s="83"/>
+      <c r="IS20" s="83"/>
+      <c r="IT20" s="83"/>
+      <c r="IU20" s="83"/>
+      <c r="IV20" s="83"/>
+      <c r="IW20" s="83"/>
+    </row>
+    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="83"/>
+      <c r="G21" s="85"/>
+      <c r="H21" s="81"/>
+      <c r="I21" s="82"/>
+      <c r="J21" s="86" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E17" s="75" t="s">
-        <v>33</v>
-      </c>
-      <c r="F17" s="69" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" s="80" t="s">
-        <v>167</v>
-      </c>
-      <c r="I17" s="81" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E18" s="67" t="s">
-        <v>36</v>
-      </c>
-      <c r="H18" s="80"/>
-      <c r="I18" s="92" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H19" s="80"/>
-    </row>
-    <row r="20" customFormat="false" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="82"/>
-      <c r="B20" s="82"/>
-      <c r="C20" s="82"/>
-      <c r="D20" s="82"/>
-      <c r="E20" s="82"/>
-      <c r="F20" s="82"/>
-      <c r="G20" s="82"/>
-      <c r="H20" s="80"/>
-      <c r="I20" s="82"/>
-      <c r="J20" s="83"/>
-      <c r="O20" s="82"/>
-      <c r="P20" s="82"/>
-      <c r="Q20" s="82"/>
-      <c r="R20" s="82"/>
-      <c r="S20" s="82"/>
-      <c r="T20" s="82"/>
-      <c r="U20" s="82"/>
-      <c r="V20" s="82"/>
-      <c r="W20" s="82"/>
-      <c r="X20" s="82"/>
-      <c r="Y20" s="82"/>
-      <c r="Z20" s="82"/>
-      <c r="AA20" s="82"/>
-      <c r="AB20" s="82"/>
-      <c r="AC20" s="82"/>
-      <c r="AD20" s="82"/>
-      <c r="AE20" s="82"/>
-      <c r="AF20" s="82"/>
-      <c r="AG20" s="82"/>
-      <c r="AH20" s="82"/>
-      <c r="AI20" s="82"/>
-      <c r="AJ20" s="82"/>
-      <c r="AK20" s="82"/>
-      <c r="AL20" s="82"/>
-      <c r="AM20" s="82"/>
-      <c r="AN20" s="82"/>
-      <c r="AO20" s="82"/>
-      <c r="AP20" s="82"/>
-      <c r="AQ20" s="82"/>
-      <c r="AR20" s="82"/>
-      <c r="AS20" s="82"/>
-      <c r="AT20" s="82"/>
-      <c r="AU20" s="82"/>
-      <c r="AV20" s="82"/>
-      <c r="AW20" s="82"/>
-      <c r="AX20" s="82"/>
-      <c r="AY20" s="82"/>
-      <c r="AZ20" s="82"/>
-      <c r="BA20" s="82"/>
-      <c r="BB20" s="82"/>
-      <c r="BC20" s="82"/>
-      <c r="BD20" s="82"/>
-      <c r="BE20" s="82"/>
-      <c r="BF20" s="82"/>
-      <c r="BG20" s="82"/>
-      <c r="BH20" s="82"/>
-      <c r="BI20" s="82"/>
-      <c r="BJ20" s="82"/>
-      <c r="BK20" s="82"/>
-      <c r="BL20" s="82"/>
-      <c r="BM20" s="82"/>
-      <c r="BN20" s="82"/>
-      <c r="BO20" s="82"/>
-      <c r="BP20" s="82"/>
-      <c r="BQ20" s="82"/>
-      <c r="BR20" s="82"/>
-      <c r="BS20" s="82"/>
-      <c r="BT20" s="82"/>
-      <c r="BU20" s="82"/>
-      <c r="BV20" s="82"/>
-      <c r="BW20" s="82"/>
-      <c r="BX20" s="82"/>
-      <c r="BY20" s="82"/>
-      <c r="BZ20" s="82"/>
-      <c r="CA20" s="82"/>
-      <c r="CB20" s="82"/>
-      <c r="CC20" s="82"/>
-      <c r="CD20" s="82"/>
-      <c r="CE20" s="82"/>
-      <c r="CF20" s="82"/>
-      <c r="CG20" s="82"/>
-      <c r="CH20" s="82"/>
-      <c r="CI20" s="82"/>
-      <c r="CJ20" s="82"/>
-      <c r="CK20" s="82"/>
-      <c r="CL20" s="82"/>
-      <c r="CM20" s="82"/>
-      <c r="CN20" s="82"/>
-      <c r="CO20" s="82"/>
-      <c r="CP20" s="82"/>
-      <c r="CQ20" s="82"/>
-      <c r="CR20" s="82"/>
-      <c r="CS20" s="82"/>
-      <c r="CT20" s="82"/>
-      <c r="CU20" s="82"/>
-      <c r="CV20" s="82"/>
-      <c r="CW20" s="82"/>
-      <c r="CX20" s="82"/>
-      <c r="CY20" s="82"/>
-      <c r="CZ20" s="82"/>
-      <c r="DA20" s="82"/>
-      <c r="DB20" s="82"/>
-      <c r="DC20" s="82"/>
-      <c r="DD20" s="82"/>
-      <c r="DE20" s="82"/>
-      <c r="DF20" s="82"/>
-      <c r="DG20" s="82"/>
-      <c r="DH20" s="82"/>
-      <c r="DI20" s="82"/>
-      <c r="DJ20" s="82"/>
-      <c r="DK20" s="82"/>
-      <c r="DL20" s="82"/>
-      <c r="DM20" s="82"/>
-      <c r="DN20" s="82"/>
-      <c r="DO20" s="82"/>
-      <c r="DP20" s="82"/>
-      <c r="DQ20" s="82"/>
-      <c r="DR20" s="82"/>
-      <c r="DS20" s="82"/>
-      <c r="DT20" s="82"/>
-      <c r="DU20" s="82"/>
-      <c r="DV20" s="82"/>
-      <c r="DW20" s="82"/>
-      <c r="DX20" s="82"/>
-      <c r="DY20" s="82"/>
-      <c r="DZ20" s="82"/>
-      <c r="EA20" s="82"/>
-      <c r="EB20" s="82"/>
-      <c r="EC20" s="82"/>
-      <c r="ED20" s="82"/>
-      <c r="EE20" s="82"/>
-      <c r="EF20" s="82"/>
-      <c r="EG20" s="82"/>
-      <c r="EH20" s="82"/>
-      <c r="EI20" s="82"/>
-      <c r="EJ20" s="82"/>
-      <c r="EK20" s="82"/>
-      <c r="EL20" s="82"/>
-      <c r="EM20" s="82"/>
-      <c r="EN20" s="82"/>
-      <c r="EO20" s="82"/>
-      <c r="EP20" s="82"/>
-      <c r="EQ20" s="82"/>
-      <c r="ER20" s="82"/>
-      <c r="ES20" s="82"/>
-      <c r="ET20" s="82"/>
-      <c r="EU20" s="82"/>
-      <c r="EV20" s="82"/>
-      <c r="EW20" s="82"/>
-      <c r="EX20" s="82"/>
-      <c r="EY20" s="82"/>
-      <c r="EZ20" s="82"/>
-      <c r="FA20" s="82"/>
-      <c r="FB20" s="82"/>
-      <c r="FC20" s="82"/>
-      <c r="FD20" s="82"/>
-      <c r="FE20" s="82"/>
-      <c r="FF20" s="82"/>
-      <c r="FG20" s="82"/>
-      <c r="FH20" s="82"/>
-      <c r="FI20" s="82"/>
-      <c r="FJ20" s="82"/>
-      <c r="FK20" s="82"/>
-      <c r="FL20" s="82"/>
-      <c r="FM20" s="82"/>
-      <c r="FN20" s="82"/>
-      <c r="FO20" s="82"/>
-      <c r="FP20" s="82"/>
-      <c r="FQ20" s="82"/>
-      <c r="FR20" s="82"/>
-      <c r="FS20" s="82"/>
-      <c r="FT20" s="82"/>
-      <c r="FU20" s="82"/>
-      <c r="FV20" s="82"/>
-      <c r="FW20" s="82"/>
-      <c r="FX20" s="82"/>
-      <c r="FY20" s="82"/>
-      <c r="FZ20" s="82"/>
-      <c r="GA20" s="82"/>
-      <c r="GB20" s="82"/>
-      <c r="GC20" s="82"/>
-      <c r="GD20" s="82"/>
-      <c r="GE20" s="82"/>
-      <c r="GF20" s="82"/>
-      <c r="GG20" s="82"/>
-      <c r="GH20" s="82"/>
-      <c r="GI20" s="82"/>
-      <c r="GJ20" s="82"/>
-      <c r="GK20" s="82"/>
-      <c r="GL20" s="82"/>
-      <c r="GM20" s="82"/>
-      <c r="GN20" s="82"/>
-      <c r="GO20" s="82"/>
-      <c r="GP20" s="82"/>
-      <c r="GQ20" s="82"/>
-      <c r="GR20" s="82"/>
-      <c r="GS20" s="82"/>
-      <c r="GT20" s="82"/>
-      <c r="GU20" s="82"/>
-      <c r="GV20" s="82"/>
-      <c r="GW20" s="82"/>
-      <c r="GX20" s="82"/>
-      <c r="GY20" s="82"/>
-      <c r="GZ20" s="82"/>
-      <c r="HA20" s="82"/>
-      <c r="HB20" s="82"/>
-      <c r="HC20" s="82"/>
-      <c r="HD20" s="82"/>
-      <c r="HE20" s="82"/>
-      <c r="HF20" s="82"/>
-      <c r="HG20" s="82"/>
-      <c r="HH20" s="82"/>
-      <c r="HI20" s="82"/>
-      <c r="HJ20" s="82"/>
-      <c r="HK20" s="82"/>
-      <c r="HL20" s="82"/>
-      <c r="HM20" s="82"/>
-      <c r="HN20" s="82"/>
-      <c r="HO20" s="82"/>
-      <c r="HP20" s="82"/>
-      <c r="HQ20" s="82"/>
-      <c r="HR20" s="82"/>
-      <c r="HS20" s="82"/>
-      <c r="HT20" s="82"/>
-      <c r="HU20" s="82"/>
-      <c r="HV20" s="82"/>
-      <c r="HW20" s="82"/>
-      <c r="HX20" s="82"/>
-      <c r="HY20" s="82"/>
-      <c r="HZ20" s="82"/>
-      <c r="IA20" s="82"/>
-      <c r="IB20" s="82"/>
-      <c r="IC20" s="82"/>
-      <c r="ID20" s="82"/>
-      <c r="IE20" s="82"/>
-      <c r="IF20" s="82"/>
-      <c r="IG20" s="82"/>
-      <c r="IH20" s="82"/>
-      <c r="II20" s="82"/>
-      <c r="IJ20" s="82"/>
-      <c r="IK20" s="82"/>
-      <c r="IL20" s="82"/>
-      <c r="IM20" s="82"/>
-      <c r="IN20" s="82"/>
-      <c r="IO20" s="82"/>
-      <c r="IP20" s="82"/>
-      <c r="IQ20" s="82"/>
-      <c r="IR20" s="82"/>
-      <c r="IS20" s="82"/>
-      <c r="IT20" s="82"/>
-      <c r="IU20" s="82"/>
-      <c r="IV20" s="82"/>
-      <c r="IW20" s="82"/>
-    </row>
-    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="82"/>
-      <c r="G21" s="84"/>
-      <c r="H21" s="80"/>
-      <c r="I21" s="81"/>
-      <c r="J21" s="85" t="s">
+    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="87"/>
+      <c r="G22" s="87"/>
+      <c r="H22" s="81"/>
+      <c r="I22" s="82"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="82"/>
+      <c r="R23" s="88"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="82"/>
+      <c r="L24" s="61" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="86"/>
-      <c r="G22" s="86"/>
-      <c r="H22" s="80"/>
-      <c r="I22" s="81"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I23" s="81"/>
-      <c r="R23" s="87"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I24" s="81"/>
-      <c r="L24" s="60" t="s">
-        <v>170</v>
-      </c>
-    </row>
     <row r="25" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I25" s="81"/>
+      <c r="I25" s="82"/>
     </row>
     <row r="26" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="3"/>
-      <c r="I26" s="81"/>
+      <c r="I26" s="82"/>
     </row>
     <row r="28" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D28" s="88"/>
+      <c r="D28" s="89"/>
     </row>
     <row r="29" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="89" t="s">
+      <c r="A29" s="90" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="90" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="89" t="s">
+    <row r="31" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="90" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="89" t="s">
+    <row r="32" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="81" t="s">
         <v>175</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="80" t="s">
-        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -8685,309 +8897,309 @@
   <dimension ref="A1:IW32"/>
   <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="12.55" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="60" width="12.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="60" width="12.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="60" width="14.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="60" width="12.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="60" width="17.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="60" width="15.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="60" width="13.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="60" width="13.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="60" width="14.55"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="10" min="10" style="60" width="9.1"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="11" style="60" width="9.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="61" width="12.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="61" width="12.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="61" width="14.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="61" width="12.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="61" width="17.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="61" width="15.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="61" width="13.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="61" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="61" width="14.55"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="10" min="10" style="61" width="9.1"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="11" style="61" width="9.1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="26.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="61" t="s">
-        <v>177</v>
-      </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="63" t="s">
+      <c r="A1" s="62" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
-      <c r="T1" s="62"/>
-      <c r="U1" s="62"/>
-      <c r="V1" s="62"/>
-      <c r="W1" s="62"/>
-      <c r="X1" s="62"/>
-      <c r="Y1" s="62"/>
-      <c r="Z1" s="62"/>
-      <c r="AA1" s="62"/>
-      <c r="AB1" s="62"/>
-      <c r="AC1" s="62"/>
-      <c r="AD1" s="62"/>
-      <c r="AE1" s="62"/>
-      <c r="AF1" s="62"/>
-      <c r="AG1" s="62"/>
-      <c r="AH1" s="62"/>
-      <c r="AI1" s="62"/>
-      <c r="AJ1" s="62"/>
-      <c r="AK1" s="62"/>
-      <c r="AL1" s="62"/>
-      <c r="AM1" s="62"/>
-      <c r="AN1" s="62"/>
-      <c r="AO1" s="62"/>
-      <c r="AP1" s="62"/>
-      <c r="AQ1" s="62"/>
-      <c r="AR1" s="62"/>
-      <c r="AS1" s="62"/>
-      <c r="AT1" s="62"/>
-      <c r="AU1" s="62"/>
-      <c r="AV1" s="62"/>
-      <c r="AW1" s="62"/>
-      <c r="AX1" s="62"/>
-      <c r="AY1" s="62"/>
-      <c r="AZ1" s="62"/>
-      <c r="BA1" s="62"/>
-      <c r="BB1" s="62"/>
-      <c r="BC1" s="62"/>
-      <c r="BD1" s="62"/>
-      <c r="BE1" s="62"/>
-      <c r="BF1" s="62"/>
-      <c r="BG1" s="62"/>
-      <c r="BH1" s="62"/>
-      <c r="BI1" s="62"/>
-      <c r="BJ1" s="62"/>
-      <c r="BK1" s="62"/>
-      <c r="BL1" s="62"/>
-      <c r="BM1" s="62"/>
-      <c r="BN1" s="62"/>
-      <c r="BO1" s="62"/>
-      <c r="BP1" s="62"/>
-      <c r="BQ1" s="62"/>
-      <c r="BR1" s="62"/>
-      <c r="BS1" s="62"/>
-      <c r="BT1" s="62"/>
-      <c r="BU1" s="62"/>
-      <c r="BV1" s="62"/>
-      <c r="BW1" s="62"/>
-      <c r="BX1" s="62"/>
-      <c r="BY1" s="62"/>
-      <c r="BZ1" s="62"/>
-      <c r="CA1" s="62"/>
-      <c r="CB1" s="62"/>
-      <c r="CC1" s="62"/>
-      <c r="CD1" s="62"/>
-      <c r="CE1" s="62"/>
-      <c r="CF1" s="62"/>
-      <c r="CG1" s="62"/>
-      <c r="CH1" s="62"/>
-      <c r="CI1" s="62"/>
-      <c r="CJ1" s="62"/>
-      <c r="CK1" s="62"/>
-      <c r="CL1" s="62"/>
-      <c r="CM1" s="62"/>
-      <c r="CN1" s="62"/>
-      <c r="CO1" s="62"/>
-      <c r="CP1" s="62"/>
-      <c r="CQ1" s="62"/>
-      <c r="CR1" s="62"/>
-      <c r="CS1" s="62"/>
-      <c r="CT1" s="62"/>
-      <c r="CU1" s="62"/>
-      <c r="CV1" s="62"/>
-      <c r="CW1" s="62"/>
-      <c r="CX1" s="62"/>
-      <c r="CY1" s="62"/>
-      <c r="CZ1" s="62"/>
-      <c r="DA1" s="62"/>
-      <c r="DB1" s="62"/>
-      <c r="DC1" s="62"/>
-      <c r="DD1" s="62"/>
-      <c r="DE1" s="62"/>
-      <c r="DF1" s="62"/>
-      <c r="DG1" s="62"/>
-      <c r="DH1" s="62"/>
-      <c r="DI1" s="62"/>
-      <c r="DJ1" s="62"/>
-      <c r="DK1" s="62"/>
-      <c r="DL1" s="62"/>
-      <c r="DM1" s="62"/>
-      <c r="DN1" s="62"/>
-      <c r="DO1" s="62"/>
-      <c r="DP1" s="62"/>
-      <c r="DQ1" s="62"/>
-      <c r="DR1" s="62"/>
-      <c r="DS1" s="62"/>
-      <c r="DT1" s="62"/>
-      <c r="DU1" s="62"/>
-      <c r="DV1" s="62"/>
-      <c r="DW1" s="62"/>
-      <c r="DX1" s="62"/>
-      <c r="DY1" s="62"/>
-      <c r="DZ1" s="62"/>
-      <c r="EA1" s="62"/>
-      <c r="EB1" s="62"/>
-      <c r="EC1" s="62"/>
-      <c r="ED1" s="62"/>
-      <c r="EE1" s="62"/>
-      <c r="EF1" s="62"/>
-      <c r="EG1" s="62"/>
-      <c r="EH1" s="62"/>
-      <c r="EI1" s="62"/>
-      <c r="EJ1" s="62"/>
-      <c r="EK1" s="62"/>
-      <c r="EL1" s="62"/>
-      <c r="EM1" s="62"/>
-      <c r="EN1" s="62"/>
-      <c r="EO1" s="62"/>
-      <c r="EP1" s="62"/>
-      <c r="EQ1" s="62"/>
-      <c r="ER1" s="62"/>
-      <c r="ES1" s="62"/>
-      <c r="ET1" s="62"/>
-      <c r="EU1" s="62"/>
-      <c r="EV1" s="62"/>
-      <c r="EW1" s="62"/>
-      <c r="EX1" s="62"/>
-      <c r="EY1" s="62"/>
-      <c r="EZ1" s="62"/>
-      <c r="FA1" s="62"/>
-      <c r="FB1" s="62"/>
-      <c r="FC1" s="62"/>
-      <c r="FD1" s="62"/>
-      <c r="FE1" s="62"/>
-      <c r="FF1" s="62"/>
-      <c r="FG1" s="62"/>
-      <c r="FH1" s="62"/>
-      <c r="FI1" s="62"/>
-      <c r="FJ1" s="62"/>
-      <c r="FK1" s="62"/>
-      <c r="FL1" s="62"/>
-      <c r="FM1" s="62"/>
-      <c r="FN1" s="62"/>
-      <c r="FO1" s="62"/>
-      <c r="FP1" s="62"/>
-      <c r="FQ1" s="62"/>
-      <c r="FR1" s="62"/>
-      <c r="FS1" s="62"/>
-      <c r="FT1" s="62"/>
-      <c r="FU1" s="62"/>
-      <c r="FV1" s="62"/>
-      <c r="FW1" s="62"/>
-      <c r="FX1" s="62"/>
-      <c r="FY1" s="62"/>
-      <c r="FZ1" s="62"/>
-      <c r="GA1" s="62"/>
-      <c r="GB1" s="62"/>
-      <c r="GC1" s="62"/>
-      <c r="GD1" s="62"/>
-      <c r="GE1" s="62"/>
-      <c r="GF1" s="62"/>
-      <c r="GG1" s="62"/>
-      <c r="GH1" s="62"/>
-      <c r="GI1" s="62"/>
-      <c r="GJ1" s="62"/>
-      <c r="GK1" s="62"/>
-      <c r="GL1" s="62"/>
-      <c r="GM1" s="62"/>
-      <c r="GN1" s="62"/>
-      <c r="GO1" s="62"/>
-      <c r="GP1" s="62"/>
-      <c r="GQ1" s="62"/>
-      <c r="GR1" s="62"/>
-      <c r="GS1" s="62"/>
-      <c r="GT1" s="62"/>
-      <c r="GU1" s="62"/>
-      <c r="GV1" s="62"/>
-      <c r="GW1" s="62"/>
-      <c r="GX1" s="62"/>
-      <c r="GY1" s="62"/>
-      <c r="GZ1" s="62"/>
-      <c r="HA1" s="62"/>
-      <c r="HB1" s="62"/>
-      <c r="HC1" s="62"/>
-      <c r="HD1" s="62"/>
-      <c r="HE1" s="62"/>
-      <c r="HF1" s="62"/>
-      <c r="HG1" s="62"/>
-      <c r="HH1" s="62"/>
-      <c r="HI1" s="62"/>
-      <c r="HJ1" s="62"/>
-      <c r="HK1" s="62"/>
-      <c r="HL1" s="62"/>
-      <c r="HM1" s="62"/>
-      <c r="HN1" s="62"/>
-      <c r="HO1" s="62"/>
-      <c r="HP1" s="62"/>
-      <c r="HQ1" s="62"/>
-      <c r="HR1" s="62"/>
-      <c r="HS1" s="62"/>
-      <c r="HT1" s="62"/>
-      <c r="HU1" s="62"/>
-      <c r="HV1" s="62"/>
-      <c r="HW1" s="62"/>
-      <c r="HX1" s="62"/>
-      <c r="HY1" s="62"/>
-      <c r="HZ1" s="62"/>
-      <c r="IA1" s="62"/>
-      <c r="IB1" s="62"/>
-      <c r="IC1" s="62"/>
-      <c r="ID1" s="62"/>
-      <c r="IE1" s="62"/>
-      <c r="IF1" s="62"/>
-      <c r="IG1" s="62"/>
-      <c r="IH1" s="62"/>
-      <c r="II1" s="62"/>
-      <c r="IJ1" s="62"/>
-      <c r="IK1" s="62"/>
-      <c r="IL1" s="62"/>
-      <c r="IM1" s="62"/>
-      <c r="IN1" s="62"/>
-      <c r="IO1" s="62"/>
-      <c r="IP1" s="62"/>
-      <c r="IQ1" s="62"/>
-      <c r="IR1" s="62"/>
-      <c r="IS1" s="62"/>
-      <c r="IT1" s="62"/>
-      <c r="IU1" s="62"/>
-      <c r="IV1" s="62"/>
-      <c r="IW1" s="62"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="63"/>
+      <c r="T1" s="63"/>
+      <c r="U1" s="63"/>
+      <c r="V1" s="63"/>
+      <c r="W1" s="63"/>
+      <c r="X1" s="63"/>
+      <c r="Y1" s="63"/>
+      <c r="Z1" s="63"/>
+      <c r="AA1" s="63"/>
+      <c r="AB1" s="63"/>
+      <c r="AC1" s="63"/>
+      <c r="AD1" s="63"/>
+      <c r="AE1" s="63"/>
+      <c r="AF1" s="63"/>
+      <c r="AG1" s="63"/>
+      <c r="AH1" s="63"/>
+      <c r="AI1" s="63"/>
+      <c r="AJ1" s="63"/>
+      <c r="AK1" s="63"/>
+      <c r="AL1" s="63"/>
+      <c r="AM1" s="63"/>
+      <c r="AN1" s="63"/>
+      <c r="AO1" s="63"/>
+      <c r="AP1" s="63"/>
+      <c r="AQ1" s="63"/>
+      <c r="AR1" s="63"/>
+      <c r="AS1" s="63"/>
+      <c r="AT1" s="63"/>
+      <c r="AU1" s="63"/>
+      <c r="AV1" s="63"/>
+      <c r="AW1" s="63"/>
+      <c r="AX1" s="63"/>
+      <c r="AY1" s="63"/>
+      <c r="AZ1" s="63"/>
+      <c r="BA1" s="63"/>
+      <c r="BB1" s="63"/>
+      <c r="BC1" s="63"/>
+      <c r="BD1" s="63"/>
+      <c r="BE1" s="63"/>
+      <c r="BF1" s="63"/>
+      <c r="BG1" s="63"/>
+      <c r="BH1" s="63"/>
+      <c r="BI1" s="63"/>
+      <c r="BJ1" s="63"/>
+      <c r="BK1" s="63"/>
+      <c r="BL1" s="63"/>
+      <c r="BM1" s="63"/>
+      <c r="BN1" s="63"/>
+      <c r="BO1" s="63"/>
+      <c r="BP1" s="63"/>
+      <c r="BQ1" s="63"/>
+      <c r="BR1" s="63"/>
+      <c r="BS1" s="63"/>
+      <c r="BT1" s="63"/>
+      <c r="BU1" s="63"/>
+      <c r="BV1" s="63"/>
+      <c r="BW1" s="63"/>
+      <c r="BX1" s="63"/>
+      <c r="BY1" s="63"/>
+      <c r="BZ1" s="63"/>
+      <c r="CA1" s="63"/>
+      <c r="CB1" s="63"/>
+      <c r="CC1" s="63"/>
+      <c r="CD1" s="63"/>
+      <c r="CE1" s="63"/>
+      <c r="CF1" s="63"/>
+      <c r="CG1" s="63"/>
+      <c r="CH1" s="63"/>
+      <c r="CI1" s="63"/>
+      <c r="CJ1" s="63"/>
+      <c r="CK1" s="63"/>
+      <c r="CL1" s="63"/>
+      <c r="CM1" s="63"/>
+      <c r="CN1" s="63"/>
+      <c r="CO1" s="63"/>
+      <c r="CP1" s="63"/>
+      <c r="CQ1" s="63"/>
+      <c r="CR1" s="63"/>
+      <c r="CS1" s="63"/>
+      <c r="CT1" s="63"/>
+      <c r="CU1" s="63"/>
+      <c r="CV1" s="63"/>
+      <c r="CW1" s="63"/>
+      <c r="CX1" s="63"/>
+      <c r="CY1" s="63"/>
+      <c r="CZ1" s="63"/>
+      <c r="DA1" s="63"/>
+      <c r="DB1" s="63"/>
+      <c r="DC1" s="63"/>
+      <c r="DD1" s="63"/>
+      <c r="DE1" s="63"/>
+      <c r="DF1" s="63"/>
+      <c r="DG1" s="63"/>
+      <c r="DH1" s="63"/>
+      <c r="DI1" s="63"/>
+      <c r="DJ1" s="63"/>
+      <c r="DK1" s="63"/>
+      <c r="DL1" s="63"/>
+      <c r="DM1" s="63"/>
+      <c r="DN1" s="63"/>
+      <c r="DO1" s="63"/>
+      <c r="DP1" s="63"/>
+      <c r="DQ1" s="63"/>
+      <c r="DR1" s="63"/>
+      <c r="DS1" s="63"/>
+      <c r="DT1" s="63"/>
+      <c r="DU1" s="63"/>
+      <c r="DV1" s="63"/>
+      <c r="DW1" s="63"/>
+      <c r="DX1" s="63"/>
+      <c r="DY1" s="63"/>
+      <c r="DZ1" s="63"/>
+      <c r="EA1" s="63"/>
+      <c r="EB1" s="63"/>
+      <c r="EC1" s="63"/>
+      <c r="ED1" s="63"/>
+      <c r="EE1" s="63"/>
+      <c r="EF1" s="63"/>
+      <c r="EG1" s="63"/>
+      <c r="EH1" s="63"/>
+      <c r="EI1" s="63"/>
+      <c r="EJ1" s="63"/>
+      <c r="EK1" s="63"/>
+      <c r="EL1" s="63"/>
+      <c r="EM1" s="63"/>
+      <c r="EN1" s="63"/>
+      <c r="EO1" s="63"/>
+      <c r="EP1" s="63"/>
+      <c r="EQ1" s="63"/>
+      <c r="ER1" s="63"/>
+      <c r="ES1" s="63"/>
+      <c r="ET1" s="63"/>
+      <c r="EU1" s="63"/>
+      <c r="EV1" s="63"/>
+      <c r="EW1" s="63"/>
+      <c r="EX1" s="63"/>
+      <c r="EY1" s="63"/>
+      <c r="EZ1" s="63"/>
+      <c r="FA1" s="63"/>
+      <c r="FB1" s="63"/>
+      <c r="FC1" s="63"/>
+      <c r="FD1" s="63"/>
+      <c r="FE1" s="63"/>
+      <c r="FF1" s="63"/>
+      <c r="FG1" s="63"/>
+      <c r="FH1" s="63"/>
+      <c r="FI1" s="63"/>
+      <c r="FJ1" s="63"/>
+      <c r="FK1" s="63"/>
+      <c r="FL1" s="63"/>
+      <c r="FM1" s="63"/>
+      <c r="FN1" s="63"/>
+      <c r="FO1" s="63"/>
+      <c r="FP1" s="63"/>
+      <c r="FQ1" s="63"/>
+      <c r="FR1" s="63"/>
+      <c r="FS1" s="63"/>
+      <c r="FT1" s="63"/>
+      <c r="FU1" s="63"/>
+      <c r="FV1" s="63"/>
+      <c r="FW1" s="63"/>
+      <c r="FX1" s="63"/>
+      <c r="FY1" s="63"/>
+      <c r="FZ1" s="63"/>
+      <c r="GA1" s="63"/>
+      <c r="GB1" s="63"/>
+      <c r="GC1" s="63"/>
+      <c r="GD1" s="63"/>
+      <c r="GE1" s="63"/>
+      <c r="GF1" s="63"/>
+      <c r="GG1" s="63"/>
+      <c r="GH1" s="63"/>
+      <c r="GI1" s="63"/>
+      <c r="GJ1" s="63"/>
+      <c r="GK1" s="63"/>
+      <c r="GL1" s="63"/>
+      <c r="GM1" s="63"/>
+      <c r="GN1" s="63"/>
+      <c r="GO1" s="63"/>
+      <c r="GP1" s="63"/>
+      <c r="GQ1" s="63"/>
+      <c r="GR1" s="63"/>
+      <c r="GS1" s="63"/>
+      <c r="GT1" s="63"/>
+      <c r="GU1" s="63"/>
+      <c r="GV1" s="63"/>
+      <c r="GW1" s="63"/>
+      <c r="GX1" s="63"/>
+      <c r="GY1" s="63"/>
+      <c r="GZ1" s="63"/>
+      <c r="HA1" s="63"/>
+      <c r="HB1" s="63"/>
+      <c r="HC1" s="63"/>
+      <c r="HD1" s="63"/>
+      <c r="HE1" s="63"/>
+      <c r="HF1" s="63"/>
+      <c r="HG1" s="63"/>
+      <c r="HH1" s="63"/>
+      <c r="HI1" s="63"/>
+      <c r="HJ1" s="63"/>
+      <c r="HK1" s="63"/>
+      <c r="HL1" s="63"/>
+      <c r="HM1" s="63"/>
+      <c r="HN1" s="63"/>
+      <c r="HO1" s="63"/>
+      <c r="HP1" s="63"/>
+      <c r="HQ1" s="63"/>
+      <c r="HR1" s="63"/>
+      <c r="HS1" s="63"/>
+      <c r="HT1" s="63"/>
+      <c r="HU1" s="63"/>
+      <c r="HV1" s="63"/>
+      <c r="HW1" s="63"/>
+      <c r="HX1" s="63"/>
+      <c r="HY1" s="63"/>
+      <c r="HZ1" s="63"/>
+      <c r="IA1" s="63"/>
+      <c r="IB1" s="63"/>
+      <c r="IC1" s="63"/>
+      <c r="ID1" s="63"/>
+      <c r="IE1" s="63"/>
+      <c r="IF1" s="63"/>
+      <c r="IG1" s="63"/>
+      <c r="IH1" s="63"/>
+      <c r="II1" s="63"/>
+      <c r="IJ1" s="63"/>
+      <c r="IK1" s="63"/>
+      <c r="IL1" s="63"/>
+      <c r="IM1" s="63"/>
+      <c r="IN1" s="63"/>
+      <c r="IO1" s="63"/>
+      <c r="IP1" s="63"/>
+      <c r="IQ1" s="63"/>
+      <c r="IR1" s="63"/>
+      <c r="IS1" s="63"/>
+      <c r="IT1" s="63"/>
+      <c r="IU1" s="63"/>
+      <c r="IV1" s="63"/>
+      <c r="IW1" s="63"/>
     </row>
     <row r="2" customFormat="false" ht="23.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="64" t="s">
-        <v>149</v>
-      </c>
-      <c r="B2" s="72" t="s">
+      <c r="A2" s="65" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="73" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="64" t="s">
+      <c r="C2" s="65" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="65" t="s">
         <v>151</v>
       </c>
-      <c r="D2" s="64" t="s">
+      <c r="E2" s="65" t="s">
         <v>152</v>
       </c>
-      <c r="E2" s="64" t="s">
-        <v>153</v>
-      </c>
-      <c r="F2" s="64" t="s">
-        <v>153</v>
-      </c>
-      <c r="G2" s="64" t="s">
+      <c r="F2" s="65" t="s">
+        <v>152</v>
+      </c>
+      <c r="G2" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="H2" s="65" t="s">
-        <v>142</v>
-      </c>
-      <c r="I2" s="66"/>
-      <c r="L2" s="63" t="s">
+      <c r="H2" s="66" t="s">
+        <v>141</v>
+      </c>
+      <c r="I2" s="67"/>
+      <c r="L2" s="64" t="s">
         <v>51</v>
       </c>
     </row>
@@ -9004,8 +9216,8 @@
       <c r="D3" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="E3" s="67" t="s">
-        <v>154</v>
+      <c r="E3" s="68" t="s">
+        <v>153</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>74</v>
@@ -9016,55 +9228,55 @@
       <c r="H3" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="I3" s="68"/>
+      <c r="I3" s="69"/>
     </row>
     <row r="4" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="69" t="s">
+      <c r="A4" s="70" t="s">
         <v>87</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="E4" s="68" t="s">
+        <v>177</v>
+      </c>
+      <c r="F4" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="E4" s="67" t="s">
-        <v>178</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="H4" s="69" t="s">
-        <v>139</v>
-      </c>
-      <c r="I4" s="68"/>
+      <c r="H4" s="70" t="s">
+        <v>138</v>
+      </c>
+      <c r="I4" s="69"/>
     </row>
     <row r="5" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="70" t="s">
+      <c r="A5" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="65" t="s">
+      <c r="B5" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="70" t="s">
+      <c r="C5" s="71" t="s">
         <v>24</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="E5" s="70" t="s">
-        <v>156</v>
+      <c r="E5" s="71" t="s">
+        <v>155</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="G5" s="65" t="s">
+      <c r="G5" s="66" t="s">
         <v>71</v>
       </c>
       <c r="H5" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="I5" s="71"/>
+      <c r="I5" s="72"/>
     </row>
     <row r="6" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
@@ -9079,19 +9291,19 @@
       <c r="E6" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="69" t="s">
+      <c r="F6" s="70" t="s">
         <v>120</v>
       </c>
-      <c r="G6" s="69" t="s">
+      <c r="G6" s="70" t="s">
         <v>62</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="I6" s="71"/>
+      <c r="I6" s="72"/>
     </row>
     <row r="7" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="93" t="s">
+      <c r="A7" s="94" t="s">
         <v>27</v>
       </c>
       <c r="B7" s="13" t="s">
@@ -9100,60 +9312,60 @@
       <c r="C7" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="70" t="s">
+      <c r="E7" s="71" t="s">
         <v>23</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>77</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="H7" s="69" t="s">
+        <v>145</v>
+      </c>
+      <c r="H7" s="70" t="s">
         <v>131</v>
       </c>
-      <c r="I7" s="68"/>
+      <c r="I7" s="69"/>
     </row>
     <row r="8" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="70" t="s">
+      <c r="C8" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="70" t="s">
-        <v>167</v>
+      <c r="E8" s="71" t="s">
+        <v>166</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G8" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="H8" s="69" t="s">
+      <c r="H8" s="70" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="75" t="s">
+      <c r="A9" s="76" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="64" t="s">
-        <v>164</v>
+      <c r="B9" s="65" t="s">
+        <v>163</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="70" t="s">
+      <c r="E9" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="74"/>
-      <c r="H9" s="75" t="s">
+      <c r="G9" s="75"/>
+      <c r="H9" s="76" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="73" t="s">
+      <c r="A10" s="74" t="s">
         <v>30</v>
       </c>
       <c r="B10" s="13" t="s">
@@ -9162,28 +9374,28 @@
       <c r="C10" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="75" t="s">
-        <v>172</v>
-      </c>
-      <c r="F10" s="76" t="s">
-        <v>158</v>
-      </c>
-      <c r="G10" s="65"/>
+      <c r="E10" s="76" t="s">
+        <v>171</v>
+      </c>
+      <c r="F10" s="77" t="s">
+        <v>157</v>
+      </c>
+      <c r="G10" s="66"/>
     </row>
     <row r="11" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C11" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="72" t="s">
-        <v>159</v>
-      </c>
-      <c r="E11" s="94" t="s">
+      <c r="D11" s="73" t="s">
+        <v>158</v>
+      </c>
+      <c r="E11" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="69" t="s">
+      <c r="F11" s="70" t="s">
         <v>116</v>
       </c>
-      <c r="H11" s="77"/>
+      <c r="H11" s="78"/>
     </row>
     <row r="12" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C12" s="13" t="s">
@@ -9192,32 +9404,32 @@
       <c r="D12" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="E12" s="67" t="s">
+      <c r="E12" s="68" t="s">
         <v>3</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="77"/>
-      <c r="H12" s="69"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="70"/>
     </row>
     <row r="13" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="65" t="s">
+      <c r="A13" s="66" t="s">
         <v>67</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="70" t="s">
+      <c r="D13" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="E13" s="75" t="s">
+      <c r="E13" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="75" t="s">
+      <c r="F13" s="76" t="s">
         <v>41</v>
       </c>
-      <c r="H13" s="69"/>
+      <c r="H13" s="70"/>
     </row>
     <row r="14" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
@@ -9226,390 +9438,390 @@
       <c r="C14" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="70" t="s">
+      <c r="D14" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="67" t="s">
+      <c r="E14" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="H14" s="78" t="s">
+      <c r="H14" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="I14" s="80" t="s">
         <v>161</v>
       </c>
-      <c r="I14" s="79" t="s">
+      <c r="L14" s="61" t="s">
         <v>162</v>
       </c>
-      <c r="L14" s="60" t="s">
-        <v>163</v>
-      </c>
     </row>
     <row r="15" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C15" s="75" t="s">
+      <c r="C15" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="75" t="s">
-        <v>160</v>
-      </c>
-      <c r="E15" s="75" t="s">
+      <c r="D15" s="76" t="s">
+        <v>159</v>
+      </c>
+      <c r="E15" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="80" t="s">
+      <c r="H15" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="I15" s="81" t="s">
-        <v>147</v>
+      <c r="I15" s="82" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C16" s="67" t="s">
+      <c r="C16" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="75" t="s">
+      <c r="D16" s="76" t="s">
+        <v>164</v>
+      </c>
+      <c r="E16" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="66" t="s">
         <v>165</v>
       </c>
-      <c r="E16" s="67" t="s">
-        <v>36</v>
-      </c>
-      <c r="F16" s="65" t="s">
-        <v>166</v>
-      </c>
-      <c r="H16" s="92" t="s">
+      <c r="H16" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="I16" s="81" t="s">
+      <c r="I16" s="82" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C17" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="70" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17" s="93" t="s">
+        <v>40</v>
+      </c>
+      <c r="I17" s="82" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H18" s="81"/>
+      <c r="I18" s="82" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H19" s="81"/>
+    </row>
+    <row r="20" customFormat="false" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="83"/>
+      <c r="B20" s="83"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="83"/>
+      <c r="J20" s="84"/>
+      <c r="O20" s="83"/>
+      <c r="P20" s="83"/>
+      <c r="Q20" s="83"/>
+      <c r="R20" s="83"/>
+      <c r="S20" s="83"/>
+      <c r="T20" s="83"/>
+      <c r="U20" s="83"/>
+      <c r="V20" s="83"/>
+      <c r="W20" s="83"/>
+      <c r="X20" s="83"/>
+      <c r="Y20" s="83"/>
+      <c r="Z20" s="83"/>
+      <c r="AA20" s="83"/>
+      <c r="AB20" s="83"/>
+      <c r="AC20" s="83"/>
+      <c r="AD20" s="83"/>
+      <c r="AE20" s="83"/>
+      <c r="AF20" s="83"/>
+      <c r="AG20" s="83"/>
+      <c r="AH20" s="83"/>
+      <c r="AI20" s="83"/>
+      <c r="AJ20" s="83"/>
+      <c r="AK20" s="83"/>
+      <c r="AL20" s="83"/>
+      <c r="AM20" s="83"/>
+      <c r="AN20" s="83"/>
+      <c r="AO20" s="83"/>
+      <c r="AP20" s="83"/>
+      <c r="AQ20" s="83"/>
+      <c r="AR20" s="83"/>
+      <c r="AS20" s="83"/>
+      <c r="AT20" s="83"/>
+      <c r="AU20" s="83"/>
+      <c r="AV20" s="83"/>
+      <c r="AW20" s="83"/>
+      <c r="AX20" s="83"/>
+      <c r="AY20" s="83"/>
+      <c r="AZ20" s="83"/>
+      <c r="BA20" s="83"/>
+      <c r="BB20" s="83"/>
+      <c r="BC20" s="83"/>
+      <c r="BD20" s="83"/>
+      <c r="BE20" s="83"/>
+      <c r="BF20" s="83"/>
+      <c r="BG20" s="83"/>
+      <c r="BH20" s="83"/>
+      <c r="BI20" s="83"/>
+      <c r="BJ20" s="83"/>
+      <c r="BK20" s="83"/>
+      <c r="BL20" s="83"/>
+      <c r="BM20" s="83"/>
+      <c r="BN20" s="83"/>
+      <c r="BO20" s="83"/>
+      <c r="BP20" s="83"/>
+      <c r="BQ20" s="83"/>
+      <c r="BR20" s="83"/>
+      <c r="BS20" s="83"/>
+      <c r="BT20" s="83"/>
+      <c r="BU20" s="83"/>
+      <c r="BV20" s="83"/>
+      <c r="BW20" s="83"/>
+      <c r="BX20" s="83"/>
+      <c r="BY20" s="83"/>
+      <c r="BZ20" s="83"/>
+      <c r="CA20" s="83"/>
+      <c r="CB20" s="83"/>
+      <c r="CC20" s="83"/>
+      <c r="CD20" s="83"/>
+      <c r="CE20" s="83"/>
+      <c r="CF20" s="83"/>
+      <c r="CG20" s="83"/>
+      <c r="CH20" s="83"/>
+      <c r="CI20" s="83"/>
+      <c r="CJ20" s="83"/>
+      <c r="CK20" s="83"/>
+      <c r="CL20" s="83"/>
+      <c r="CM20" s="83"/>
+      <c r="CN20" s="83"/>
+      <c r="CO20" s="83"/>
+      <c r="CP20" s="83"/>
+      <c r="CQ20" s="83"/>
+      <c r="CR20" s="83"/>
+      <c r="CS20" s="83"/>
+      <c r="CT20" s="83"/>
+      <c r="CU20" s="83"/>
+      <c r="CV20" s="83"/>
+      <c r="CW20" s="83"/>
+      <c r="CX20" s="83"/>
+      <c r="CY20" s="83"/>
+      <c r="CZ20" s="83"/>
+      <c r="DA20" s="83"/>
+      <c r="DB20" s="83"/>
+      <c r="DC20" s="83"/>
+      <c r="DD20" s="83"/>
+      <c r="DE20" s="83"/>
+      <c r="DF20" s="83"/>
+      <c r="DG20" s="83"/>
+      <c r="DH20" s="83"/>
+      <c r="DI20" s="83"/>
+      <c r="DJ20" s="83"/>
+      <c r="DK20" s="83"/>
+      <c r="DL20" s="83"/>
+      <c r="DM20" s="83"/>
+      <c r="DN20" s="83"/>
+      <c r="DO20" s="83"/>
+      <c r="DP20" s="83"/>
+      <c r="DQ20" s="83"/>
+      <c r="DR20" s="83"/>
+      <c r="DS20" s="83"/>
+      <c r="DT20" s="83"/>
+      <c r="DU20" s="83"/>
+      <c r="DV20" s="83"/>
+      <c r="DW20" s="83"/>
+      <c r="DX20" s="83"/>
+      <c r="DY20" s="83"/>
+      <c r="DZ20" s="83"/>
+      <c r="EA20" s="83"/>
+      <c r="EB20" s="83"/>
+      <c r="EC20" s="83"/>
+      <c r="ED20" s="83"/>
+      <c r="EE20" s="83"/>
+      <c r="EF20" s="83"/>
+      <c r="EG20" s="83"/>
+      <c r="EH20" s="83"/>
+      <c r="EI20" s="83"/>
+      <c r="EJ20" s="83"/>
+      <c r="EK20" s="83"/>
+      <c r="EL20" s="83"/>
+      <c r="EM20" s="83"/>
+      <c r="EN20" s="83"/>
+      <c r="EO20" s="83"/>
+      <c r="EP20" s="83"/>
+      <c r="EQ20" s="83"/>
+      <c r="ER20" s="83"/>
+      <c r="ES20" s="83"/>
+      <c r="ET20" s="83"/>
+      <c r="EU20" s="83"/>
+      <c r="EV20" s="83"/>
+      <c r="EW20" s="83"/>
+      <c r="EX20" s="83"/>
+      <c r="EY20" s="83"/>
+      <c r="EZ20" s="83"/>
+      <c r="FA20" s="83"/>
+      <c r="FB20" s="83"/>
+      <c r="FC20" s="83"/>
+      <c r="FD20" s="83"/>
+      <c r="FE20" s="83"/>
+      <c r="FF20" s="83"/>
+      <c r="FG20" s="83"/>
+      <c r="FH20" s="83"/>
+      <c r="FI20" s="83"/>
+      <c r="FJ20" s="83"/>
+      <c r="FK20" s="83"/>
+      <c r="FL20" s="83"/>
+      <c r="FM20" s="83"/>
+      <c r="FN20" s="83"/>
+      <c r="FO20" s="83"/>
+      <c r="FP20" s="83"/>
+      <c r="FQ20" s="83"/>
+      <c r="FR20" s="83"/>
+      <c r="FS20" s="83"/>
+      <c r="FT20" s="83"/>
+      <c r="FU20" s="83"/>
+      <c r="FV20" s="83"/>
+      <c r="FW20" s="83"/>
+      <c r="FX20" s="83"/>
+      <c r="FY20" s="83"/>
+      <c r="FZ20" s="83"/>
+      <c r="GA20" s="83"/>
+      <c r="GB20" s="83"/>
+      <c r="GC20" s="83"/>
+      <c r="GD20" s="83"/>
+      <c r="GE20" s="83"/>
+      <c r="GF20" s="83"/>
+      <c r="GG20" s="83"/>
+      <c r="GH20" s="83"/>
+      <c r="GI20" s="83"/>
+      <c r="GJ20" s="83"/>
+      <c r="GK20" s="83"/>
+      <c r="GL20" s="83"/>
+      <c r="GM20" s="83"/>
+      <c r="GN20" s="83"/>
+      <c r="GO20" s="83"/>
+      <c r="GP20" s="83"/>
+      <c r="GQ20" s="83"/>
+      <c r="GR20" s="83"/>
+      <c r="GS20" s="83"/>
+      <c r="GT20" s="83"/>
+      <c r="GU20" s="83"/>
+      <c r="GV20" s="83"/>
+      <c r="GW20" s="83"/>
+      <c r="GX20" s="83"/>
+      <c r="GY20" s="83"/>
+      <c r="GZ20" s="83"/>
+      <c r="HA20" s="83"/>
+      <c r="HB20" s="83"/>
+      <c r="HC20" s="83"/>
+      <c r="HD20" s="83"/>
+      <c r="HE20" s="83"/>
+      <c r="HF20" s="83"/>
+      <c r="HG20" s="83"/>
+      <c r="HH20" s="83"/>
+      <c r="HI20" s="83"/>
+      <c r="HJ20" s="83"/>
+      <c r="HK20" s="83"/>
+      <c r="HL20" s="83"/>
+      <c r="HM20" s="83"/>
+      <c r="HN20" s="83"/>
+      <c r="HO20" s="83"/>
+      <c r="HP20" s="83"/>
+      <c r="HQ20" s="83"/>
+      <c r="HR20" s="83"/>
+      <c r="HS20" s="83"/>
+      <c r="HT20" s="83"/>
+      <c r="HU20" s="83"/>
+      <c r="HV20" s="83"/>
+      <c r="HW20" s="83"/>
+      <c r="HX20" s="83"/>
+      <c r="HY20" s="83"/>
+      <c r="HZ20" s="83"/>
+      <c r="IA20" s="83"/>
+      <c r="IB20" s="83"/>
+      <c r="IC20" s="83"/>
+      <c r="ID20" s="83"/>
+      <c r="IE20" s="83"/>
+      <c r="IF20" s="83"/>
+      <c r="IG20" s="83"/>
+      <c r="IH20" s="83"/>
+      <c r="II20" s="83"/>
+      <c r="IJ20" s="83"/>
+      <c r="IK20" s="83"/>
+      <c r="IL20" s="83"/>
+      <c r="IM20" s="83"/>
+      <c r="IN20" s="83"/>
+      <c r="IO20" s="83"/>
+      <c r="IP20" s="83"/>
+      <c r="IQ20" s="83"/>
+      <c r="IR20" s="83"/>
+      <c r="IS20" s="83"/>
+      <c r="IT20" s="83"/>
+      <c r="IU20" s="83"/>
+      <c r="IV20" s="83"/>
+      <c r="IW20" s="83"/>
+    </row>
+    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="83"/>
+      <c r="G21" s="85"/>
+      <c r="H21" s="81"/>
+      <c r="I21" s="82"/>
+      <c r="J21" s="86" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C17" s="67" t="s">
-        <v>26</v>
-      </c>
-      <c r="F17" s="69" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" s="92" t="s">
-        <v>40</v>
-      </c>
-      <c r="I17" s="81" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H18" s="80"/>
-      <c r="I18" s="81" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H19" s="80"/>
-    </row>
-    <row r="20" customFormat="false" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="82"/>
-      <c r="B20" s="82"/>
-      <c r="C20" s="82"/>
-      <c r="D20" s="82"/>
-      <c r="E20" s="82"/>
-      <c r="F20" s="82"/>
-      <c r="G20" s="82"/>
-      <c r="H20" s="80"/>
-      <c r="I20" s="82"/>
-      <c r="J20" s="83"/>
-      <c r="O20" s="82"/>
-      <c r="P20" s="82"/>
-      <c r="Q20" s="82"/>
-      <c r="R20" s="82"/>
-      <c r="S20" s="82"/>
-      <c r="T20" s="82"/>
-      <c r="U20" s="82"/>
-      <c r="V20" s="82"/>
-      <c r="W20" s="82"/>
-      <c r="X20" s="82"/>
-      <c r="Y20" s="82"/>
-      <c r="Z20" s="82"/>
-      <c r="AA20" s="82"/>
-      <c r="AB20" s="82"/>
-      <c r="AC20" s="82"/>
-      <c r="AD20" s="82"/>
-      <c r="AE20" s="82"/>
-      <c r="AF20" s="82"/>
-      <c r="AG20" s="82"/>
-      <c r="AH20" s="82"/>
-      <c r="AI20" s="82"/>
-      <c r="AJ20" s="82"/>
-      <c r="AK20" s="82"/>
-      <c r="AL20" s="82"/>
-      <c r="AM20" s="82"/>
-      <c r="AN20" s="82"/>
-      <c r="AO20" s="82"/>
-      <c r="AP20" s="82"/>
-      <c r="AQ20" s="82"/>
-      <c r="AR20" s="82"/>
-      <c r="AS20" s="82"/>
-      <c r="AT20" s="82"/>
-      <c r="AU20" s="82"/>
-      <c r="AV20" s="82"/>
-      <c r="AW20" s="82"/>
-      <c r="AX20" s="82"/>
-      <c r="AY20" s="82"/>
-      <c r="AZ20" s="82"/>
-      <c r="BA20" s="82"/>
-      <c r="BB20" s="82"/>
-      <c r="BC20" s="82"/>
-      <c r="BD20" s="82"/>
-      <c r="BE20" s="82"/>
-      <c r="BF20" s="82"/>
-      <c r="BG20" s="82"/>
-      <c r="BH20" s="82"/>
-      <c r="BI20" s="82"/>
-      <c r="BJ20" s="82"/>
-      <c r="BK20" s="82"/>
-      <c r="BL20" s="82"/>
-      <c r="BM20" s="82"/>
-      <c r="BN20" s="82"/>
-      <c r="BO20" s="82"/>
-      <c r="BP20" s="82"/>
-      <c r="BQ20" s="82"/>
-      <c r="BR20" s="82"/>
-      <c r="BS20" s="82"/>
-      <c r="BT20" s="82"/>
-      <c r="BU20" s="82"/>
-      <c r="BV20" s="82"/>
-      <c r="BW20" s="82"/>
-      <c r="BX20" s="82"/>
-      <c r="BY20" s="82"/>
-      <c r="BZ20" s="82"/>
-      <c r="CA20" s="82"/>
-      <c r="CB20" s="82"/>
-      <c r="CC20" s="82"/>
-      <c r="CD20" s="82"/>
-      <c r="CE20" s="82"/>
-      <c r="CF20" s="82"/>
-      <c r="CG20" s="82"/>
-      <c r="CH20" s="82"/>
-      <c r="CI20" s="82"/>
-      <c r="CJ20" s="82"/>
-      <c r="CK20" s="82"/>
-      <c r="CL20" s="82"/>
-      <c r="CM20" s="82"/>
-      <c r="CN20" s="82"/>
-      <c r="CO20" s="82"/>
-      <c r="CP20" s="82"/>
-      <c r="CQ20" s="82"/>
-      <c r="CR20" s="82"/>
-      <c r="CS20" s="82"/>
-      <c r="CT20" s="82"/>
-      <c r="CU20" s="82"/>
-      <c r="CV20" s="82"/>
-      <c r="CW20" s="82"/>
-      <c r="CX20" s="82"/>
-      <c r="CY20" s="82"/>
-      <c r="CZ20" s="82"/>
-      <c r="DA20" s="82"/>
-      <c r="DB20" s="82"/>
-      <c r="DC20" s="82"/>
-      <c r="DD20" s="82"/>
-      <c r="DE20" s="82"/>
-      <c r="DF20" s="82"/>
-      <c r="DG20" s="82"/>
-      <c r="DH20" s="82"/>
-      <c r="DI20" s="82"/>
-      <c r="DJ20" s="82"/>
-      <c r="DK20" s="82"/>
-      <c r="DL20" s="82"/>
-      <c r="DM20" s="82"/>
-      <c r="DN20" s="82"/>
-      <c r="DO20" s="82"/>
-      <c r="DP20" s="82"/>
-      <c r="DQ20" s="82"/>
-      <c r="DR20" s="82"/>
-      <c r="DS20" s="82"/>
-      <c r="DT20" s="82"/>
-      <c r="DU20" s="82"/>
-      <c r="DV20" s="82"/>
-      <c r="DW20" s="82"/>
-      <c r="DX20" s="82"/>
-      <c r="DY20" s="82"/>
-      <c r="DZ20" s="82"/>
-      <c r="EA20" s="82"/>
-      <c r="EB20" s="82"/>
-      <c r="EC20" s="82"/>
-      <c r="ED20" s="82"/>
-      <c r="EE20" s="82"/>
-      <c r="EF20" s="82"/>
-      <c r="EG20" s="82"/>
-      <c r="EH20" s="82"/>
-      <c r="EI20" s="82"/>
-      <c r="EJ20" s="82"/>
-      <c r="EK20" s="82"/>
-      <c r="EL20" s="82"/>
-      <c r="EM20" s="82"/>
-      <c r="EN20" s="82"/>
-      <c r="EO20" s="82"/>
-      <c r="EP20" s="82"/>
-      <c r="EQ20" s="82"/>
-      <c r="ER20" s="82"/>
-      <c r="ES20" s="82"/>
-      <c r="ET20" s="82"/>
-      <c r="EU20" s="82"/>
-      <c r="EV20" s="82"/>
-      <c r="EW20" s="82"/>
-      <c r="EX20" s="82"/>
-      <c r="EY20" s="82"/>
-      <c r="EZ20" s="82"/>
-      <c r="FA20" s="82"/>
-      <c r="FB20" s="82"/>
-      <c r="FC20" s="82"/>
-      <c r="FD20" s="82"/>
-      <c r="FE20" s="82"/>
-      <c r="FF20" s="82"/>
-      <c r="FG20" s="82"/>
-      <c r="FH20" s="82"/>
-      <c r="FI20" s="82"/>
-      <c r="FJ20" s="82"/>
-      <c r="FK20" s="82"/>
-      <c r="FL20" s="82"/>
-      <c r="FM20" s="82"/>
-      <c r="FN20" s="82"/>
-      <c r="FO20" s="82"/>
-      <c r="FP20" s="82"/>
-      <c r="FQ20" s="82"/>
-      <c r="FR20" s="82"/>
-      <c r="FS20" s="82"/>
-      <c r="FT20" s="82"/>
-      <c r="FU20" s="82"/>
-      <c r="FV20" s="82"/>
-      <c r="FW20" s="82"/>
-      <c r="FX20" s="82"/>
-      <c r="FY20" s="82"/>
-      <c r="FZ20" s="82"/>
-      <c r="GA20" s="82"/>
-      <c r="GB20" s="82"/>
-      <c r="GC20" s="82"/>
-      <c r="GD20" s="82"/>
-      <c r="GE20" s="82"/>
-      <c r="GF20" s="82"/>
-      <c r="GG20" s="82"/>
-      <c r="GH20" s="82"/>
-      <c r="GI20" s="82"/>
-      <c r="GJ20" s="82"/>
-      <c r="GK20" s="82"/>
-      <c r="GL20" s="82"/>
-      <c r="GM20" s="82"/>
-      <c r="GN20" s="82"/>
-      <c r="GO20" s="82"/>
-      <c r="GP20" s="82"/>
-      <c r="GQ20" s="82"/>
-      <c r="GR20" s="82"/>
-      <c r="GS20" s="82"/>
-      <c r="GT20" s="82"/>
-      <c r="GU20" s="82"/>
-      <c r="GV20" s="82"/>
-      <c r="GW20" s="82"/>
-      <c r="GX20" s="82"/>
-      <c r="GY20" s="82"/>
-      <c r="GZ20" s="82"/>
-      <c r="HA20" s="82"/>
-      <c r="HB20" s="82"/>
-      <c r="HC20" s="82"/>
-      <c r="HD20" s="82"/>
-      <c r="HE20" s="82"/>
-      <c r="HF20" s="82"/>
-      <c r="HG20" s="82"/>
-      <c r="HH20" s="82"/>
-      <c r="HI20" s="82"/>
-      <c r="HJ20" s="82"/>
-      <c r="HK20" s="82"/>
-      <c r="HL20" s="82"/>
-      <c r="HM20" s="82"/>
-      <c r="HN20" s="82"/>
-      <c r="HO20" s="82"/>
-      <c r="HP20" s="82"/>
-      <c r="HQ20" s="82"/>
-      <c r="HR20" s="82"/>
-      <c r="HS20" s="82"/>
-      <c r="HT20" s="82"/>
-      <c r="HU20" s="82"/>
-      <c r="HV20" s="82"/>
-      <c r="HW20" s="82"/>
-      <c r="HX20" s="82"/>
-      <c r="HY20" s="82"/>
-      <c r="HZ20" s="82"/>
-      <c r="IA20" s="82"/>
-      <c r="IB20" s="82"/>
-      <c r="IC20" s="82"/>
-      <c r="ID20" s="82"/>
-      <c r="IE20" s="82"/>
-      <c r="IF20" s="82"/>
-      <c r="IG20" s="82"/>
-      <c r="IH20" s="82"/>
-      <c r="II20" s="82"/>
-      <c r="IJ20" s="82"/>
-      <c r="IK20" s="82"/>
-      <c r="IL20" s="82"/>
-      <c r="IM20" s="82"/>
-      <c r="IN20" s="82"/>
-      <c r="IO20" s="82"/>
-      <c r="IP20" s="82"/>
-      <c r="IQ20" s="82"/>
-      <c r="IR20" s="82"/>
-      <c r="IS20" s="82"/>
-      <c r="IT20" s="82"/>
-      <c r="IU20" s="82"/>
-      <c r="IV20" s="82"/>
-      <c r="IW20" s="82"/>
-    </row>
-    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="82"/>
-      <c r="G21" s="84"/>
-      <c r="H21" s="80"/>
-      <c r="I21" s="81"/>
-      <c r="J21" s="85" t="s">
+    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="87"/>
+      <c r="G22" s="87"/>
+      <c r="H22" s="81"/>
+      <c r="I22" s="82"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="82"/>
+      <c r="R23" s="88"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="82"/>
+      <c r="L24" s="61" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="86"/>
-      <c r="G22" s="86"/>
-      <c r="H22" s="80"/>
-      <c r="I22" s="81"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I23" s="81"/>
-      <c r="R23" s="87"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I24" s="81"/>
-      <c r="L24" s="60" t="s">
-        <v>170</v>
-      </c>
-    </row>
     <row r="25" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I25" s="81"/>
+      <c r="I25" s="82"/>
     </row>
     <row r="26" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="3"/>
-      <c r="I26" s="81"/>
+      <c r="I26" s="82"/>
     </row>
     <row r="28" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D28" s="88"/>
+      <c r="D28" s="89"/>
     </row>
     <row r="29" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="89" t="s">
+      <c r="A29" s="90" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="90" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="89" t="s">
-        <v>180</v>
-      </c>
-    </row>
     <row r="31" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="89" t="s">
+      <c r="A31" s="90" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="81" t="s">
         <v>175</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="80" t="s">
-        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -9636,309 +9848,309 @@
   <dimension ref="A1:IW32"/>
   <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="12.55" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="60" width="12.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="60" width="12.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="60" width="14.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="60" width="12.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="60" width="17.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="60" width="15.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="60" width="13.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="60" width="13.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="60" width="14.55"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="10" min="10" style="60" width="9.1"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="11" style="60" width="9.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="61" width="12.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="61" width="12.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="61" width="14.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="61" width="12.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="61" width="17.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="61" width="15.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="61" width="13.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="61" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="61" width="14.55"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="10" min="10" style="61" width="9.1"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="11" style="61" width="9.1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="26.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="61" t="s">
-        <v>181</v>
-      </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="63" t="s">
+      <c r="A1" s="62" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
-      <c r="T1" s="62"/>
-      <c r="U1" s="62"/>
-      <c r="V1" s="62"/>
-      <c r="W1" s="62"/>
-      <c r="X1" s="62"/>
-      <c r="Y1" s="62"/>
-      <c r="Z1" s="62"/>
-      <c r="AA1" s="62"/>
-      <c r="AB1" s="62"/>
-      <c r="AC1" s="62"/>
-      <c r="AD1" s="62"/>
-      <c r="AE1" s="62"/>
-      <c r="AF1" s="62"/>
-      <c r="AG1" s="62"/>
-      <c r="AH1" s="62"/>
-      <c r="AI1" s="62"/>
-      <c r="AJ1" s="62"/>
-      <c r="AK1" s="62"/>
-      <c r="AL1" s="62"/>
-      <c r="AM1" s="62"/>
-      <c r="AN1" s="62"/>
-      <c r="AO1" s="62"/>
-      <c r="AP1" s="62"/>
-      <c r="AQ1" s="62"/>
-      <c r="AR1" s="62"/>
-      <c r="AS1" s="62"/>
-      <c r="AT1" s="62"/>
-      <c r="AU1" s="62"/>
-      <c r="AV1" s="62"/>
-      <c r="AW1" s="62"/>
-      <c r="AX1" s="62"/>
-      <c r="AY1" s="62"/>
-      <c r="AZ1" s="62"/>
-      <c r="BA1" s="62"/>
-      <c r="BB1" s="62"/>
-      <c r="BC1" s="62"/>
-      <c r="BD1" s="62"/>
-      <c r="BE1" s="62"/>
-      <c r="BF1" s="62"/>
-      <c r="BG1" s="62"/>
-      <c r="BH1" s="62"/>
-      <c r="BI1" s="62"/>
-      <c r="BJ1" s="62"/>
-      <c r="BK1" s="62"/>
-      <c r="BL1" s="62"/>
-      <c r="BM1" s="62"/>
-      <c r="BN1" s="62"/>
-      <c r="BO1" s="62"/>
-      <c r="BP1" s="62"/>
-      <c r="BQ1" s="62"/>
-      <c r="BR1" s="62"/>
-      <c r="BS1" s="62"/>
-      <c r="BT1" s="62"/>
-      <c r="BU1" s="62"/>
-      <c r="BV1" s="62"/>
-      <c r="BW1" s="62"/>
-      <c r="BX1" s="62"/>
-      <c r="BY1" s="62"/>
-      <c r="BZ1" s="62"/>
-      <c r="CA1" s="62"/>
-      <c r="CB1" s="62"/>
-      <c r="CC1" s="62"/>
-      <c r="CD1" s="62"/>
-      <c r="CE1" s="62"/>
-      <c r="CF1" s="62"/>
-      <c r="CG1" s="62"/>
-      <c r="CH1" s="62"/>
-      <c r="CI1" s="62"/>
-      <c r="CJ1" s="62"/>
-      <c r="CK1" s="62"/>
-      <c r="CL1" s="62"/>
-      <c r="CM1" s="62"/>
-      <c r="CN1" s="62"/>
-      <c r="CO1" s="62"/>
-      <c r="CP1" s="62"/>
-      <c r="CQ1" s="62"/>
-      <c r="CR1" s="62"/>
-      <c r="CS1" s="62"/>
-      <c r="CT1" s="62"/>
-      <c r="CU1" s="62"/>
-      <c r="CV1" s="62"/>
-      <c r="CW1" s="62"/>
-      <c r="CX1" s="62"/>
-      <c r="CY1" s="62"/>
-      <c r="CZ1" s="62"/>
-      <c r="DA1" s="62"/>
-      <c r="DB1" s="62"/>
-      <c r="DC1" s="62"/>
-      <c r="DD1" s="62"/>
-      <c r="DE1" s="62"/>
-      <c r="DF1" s="62"/>
-      <c r="DG1" s="62"/>
-      <c r="DH1" s="62"/>
-      <c r="DI1" s="62"/>
-      <c r="DJ1" s="62"/>
-      <c r="DK1" s="62"/>
-      <c r="DL1" s="62"/>
-      <c r="DM1" s="62"/>
-      <c r="DN1" s="62"/>
-      <c r="DO1" s="62"/>
-      <c r="DP1" s="62"/>
-      <c r="DQ1" s="62"/>
-      <c r="DR1" s="62"/>
-      <c r="DS1" s="62"/>
-      <c r="DT1" s="62"/>
-      <c r="DU1" s="62"/>
-      <c r="DV1" s="62"/>
-      <c r="DW1" s="62"/>
-      <c r="DX1" s="62"/>
-      <c r="DY1" s="62"/>
-      <c r="DZ1" s="62"/>
-      <c r="EA1" s="62"/>
-      <c r="EB1" s="62"/>
-      <c r="EC1" s="62"/>
-      <c r="ED1" s="62"/>
-      <c r="EE1" s="62"/>
-      <c r="EF1" s="62"/>
-      <c r="EG1" s="62"/>
-      <c r="EH1" s="62"/>
-      <c r="EI1" s="62"/>
-      <c r="EJ1" s="62"/>
-      <c r="EK1" s="62"/>
-      <c r="EL1" s="62"/>
-      <c r="EM1" s="62"/>
-      <c r="EN1" s="62"/>
-      <c r="EO1" s="62"/>
-      <c r="EP1" s="62"/>
-      <c r="EQ1" s="62"/>
-      <c r="ER1" s="62"/>
-      <c r="ES1" s="62"/>
-      <c r="ET1" s="62"/>
-      <c r="EU1" s="62"/>
-      <c r="EV1" s="62"/>
-      <c r="EW1" s="62"/>
-      <c r="EX1" s="62"/>
-      <c r="EY1" s="62"/>
-      <c r="EZ1" s="62"/>
-      <c r="FA1" s="62"/>
-      <c r="FB1" s="62"/>
-      <c r="FC1" s="62"/>
-      <c r="FD1" s="62"/>
-      <c r="FE1" s="62"/>
-      <c r="FF1" s="62"/>
-      <c r="FG1" s="62"/>
-      <c r="FH1" s="62"/>
-      <c r="FI1" s="62"/>
-      <c r="FJ1" s="62"/>
-      <c r="FK1" s="62"/>
-      <c r="FL1" s="62"/>
-      <c r="FM1" s="62"/>
-      <c r="FN1" s="62"/>
-      <c r="FO1" s="62"/>
-      <c r="FP1" s="62"/>
-      <c r="FQ1" s="62"/>
-      <c r="FR1" s="62"/>
-      <c r="FS1" s="62"/>
-      <c r="FT1" s="62"/>
-      <c r="FU1" s="62"/>
-      <c r="FV1" s="62"/>
-      <c r="FW1" s="62"/>
-      <c r="FX1" s="62"/>
-      <c r="FY1" s="62"/>
-      <c r="FZ1" s="62"/>
-      <c r="GA1" s="62"/>
-      <c r="GB1" s="62"/>
-      <c r="GC1" s="62"/>
-      <c r="GD1" s="62"/>
-      <c r="GE1" s="62"/>
-      <c r="GF1" s="62"/>
-      <c r="GG1" s="62"/>
-      <c r="GH1" s="62"/>
-      <c r="GI1" s="62"/>
-      <c r="GJ1" s="62"/>
-      <c r="GK1" s="62"/>
-      <c r="GL1" s="62"/>
-      <c r="GM1" s="62"/>
-      <c r="GN1" s="62"/>
-      <c r="GO1" s="62"/>
-      <c r="GP1" s="62"/>
-      <c r="GQ1" s="62"/>
-      <c r="GR1" s="62"/>
-      <c r="GS1" s="62"/>
-      <c r="GT1" s="62"/>
-      <c r="GU1" s="62"/>
-      <c r="GV1" s="62"/>
-      <c r="GW1" s="62"/>
-      <c r="GX1" s="62"/>
-      <c r="GY1" s="62"/>
-      <c r="GZ1" s="62"/>
-      <c r="HA1" s="62"/>
-      <c r="HB1" s="62"/>
-      <c r="HC1" s="62"/>
-      <c r="HD1" s="62"/>
-      <c r="HE1" s="62"/>
-      <c r="HF1" s="62"/>
-      <c r="HG1" s="62"/>
-      <c r="HH1" s="62"/>
-      <c r="HI1" s="62"/>
-      <c r="HJ1" s="62"/>
-      <c r="HK1" s="62"/>
-      <c r="HL1" s="62"/>
-      <c r="HM1" s="62"/>
-      <c r="HN1" s="62"/>
-      <c r="HO1" s="62"/>
-      <c r="HP1" s="62"/>
-      <c r="HQ1" s="62"/>
-      <c r="HR1" s="62"/>
-      <c r="HS1" s="62"/>
-      <c r="HT1" s="62"/>
-      <c r="HU1" s="62"/>
-      <c r="HV1" s="62"/>
-      <c r="HW1" s="62"/>
-      <c r="HX1" s="62"/>
-      <c r="HY1" s="62"/>
-      <c r="HZ1" s="62"/>
-      <c r="IA1" s="62"/>
-      <c r="IB1" s="62"/>
-      <c r="IC1" s="62"/>
-      <c r="ID1" s="62"/>
-      <c r="IE1" s="62"/>
-      <c r="IF1" s="62"/>
-      <c r="IG1" s="62"/>
-      <c r="IH1" s="62"/>
-      <c r="II1" s="62"/>
-      <c r="IJ1" s="62"/>
-      <c r="IK1" s="62"/>
-      <c r="IL1" s="62"/>
-      <c r="IM1" s="62"/>
-      <c r="IN1" s="62"/>
-      <c r="IO1" s="62"/>
-      <c r="IP1" s="62"/>
-      <c r="IQ1" s="62"/>
-      <c r="IR1" s="62"/>
-      <c r="IS1" s="62"/>
-      <c r="IT1" s="62"/>
-      <c r="IU1" s="62"/>
-      <c r="IV1" s="62"/>
-      <c r="IW1" s="62"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="63"/>
+      <c r="T1" s="63"/>
+      <c r="U1" s="63"/>
+      <c r="V1" s="63"/>
+      <c r="W1" s="63"/>
+      <c r="X1" s="63"/>
+      <c r="Y1" s="63"/>
+      <c r="Z1" s="63"/>
+      <c r="AA1" s="63"/>
+      <c r="AB1" s="63"/>
+      <c r="AC1" s="63"/>
+      <c r="AD1" s="63"/>
+      <c r="AE1" s="63"/>
+      <c r="AF1" s="63"/>
+      <c r="AG1" s="63"/>
+      <c r="AH1" s="63"/>
+      <c r="AI1" s="63"/>
+      <c r="AJ1" s="63"/>
+      <c r="AK1" s="63"/>
+      <c r="AL1" s="63"/>
+      <c r="AM1" s="63"/>
+      <c r="AN1" s="63"/>
+      <c r="AO1" s="63"/>
+      <c r="AP1" s="63"/>
+      <c r="AQ1" s="63"/>
+      <c r="AR1" s="63"/>
+      <c r="AS1" s="63"/>
+      <c r="AT1" s="63"/>
+      <c r="AU1" s="63"/>
+      <c r="AV1" s="63"/>
+      <c r="AW1" s="63"/>
+      <c r="AX1" s="63"/>
+      <c r="AY1" s="63"/>
+      <c r="AZ1" s="63"/>
+      <c r="BA1" s="63"/>
+      <c r="BB1" s="63"/>
+      <c r="BC1" s="63"/>
+      <c r="BD1" s="63"/>
+      <c r="BE1" s="63"/>
+      <c r="BF1" s="63"/>
+      <c r="BG1" s="63"/>
+      <c r="BH1" s="63"/>
+      <c r="BI1" s="63"/>
+      <c r="BJ1" s="63"/>
+      <c r="BK1" s="63"/>
+      <c r="BL1" s="63"/>
+      <c r="BM1" s="63"/>
+      <c r="BN1" s="63"/>
+      <c r="BO1" s="63"/>
+      <c r="BP1" s="63"/>
+      <c r="BQ1" s="63"/>
+      <c r="BR1" s="63"/>
+      <c r="BS1" s="63"/>
+      <c r="BT1" s="63"/>
+      <c r="BU1" s="63"/>
+      <c r="BV1" s="63"/>
+      <c r="BW1" s="63"/>
+      <c r="BX1" s="63"/>
+      <c r="BY1" s="63"/>
+      <c r="BZ1" s="63"/>
+      <c r="CA1" s="63"/>
+      <c r="CB1" s="63"/>
+      <c r="CC1" s="63"/>
+      <c r="CD1" s="63"/>
+      <c r="CE1" s="63"/>
+      <c r="CF1" s="63"/>
+      <c r="CG1" s="63"/>
+      <c r="CH1" s="63"/>
+      <c r="CI1" s="63"/>
+      <c r="CJ1" s="63"/>
+      <c r="CK1" s="63"/>
+      <c r="CL1" s="63"/>
+      <c r="CM1" s="63"/>
+      <c r="CN1" s="63"/>
+      <c r="CO1" s="63"/>
+      <c r="CP1" s="63"/>
+      <c r="CQ1" s="63"/>
+      <c r="CR1" s="63"/>
+      <c r="CS1" s="63"/>
+      <c r="CT1" s="63"/>
+      <c r="CU1" s="63"/>
+      <c r="CV1" s="63"/>
+      <c r="CW1" s="63"/>
+      <c r="CX1" s="63"/>
+      <c r="CY1" s="63"/>
+      <c r="CZ1" s="63"/>
+      <c r="DA1" s="63"/>
+      <c r="DB1" s="63"/>
+      <c r="DC1" s="63"/>
+      <c r="DD1" s="63"/>
+      <c r="DE1" s="63"/>
+      <c r="DF1" s="63"/>
+      <c r="DG1" s="63"/>
+      <c r="DH1" s="63"/>
+      <c r="DI1" s="63"/>
+      <c r="DJ1" s="63"/>
+      <c r="DK1" s="63"/>
+      <c r="DL1" s="63"/>
+      <c r="DM1" s="63"/>
+      <c r="DN1" s="63"/>
+      <c r="DO1" s="63"/>
+      <c r="DP1" s="63"/>
+      <c r="DQ1" s="63"/>
+      <c r="DR1" s="63"/>
+      <c r="DS1" s="63"/>
+      <c r="DT1" s="63"/>
+      <c r="DU1" s="63"/>
+      <c r="DV1" s="63"/>
+      <c r="DW1" s="63"/>
+      <c r="DX1" s="63"/>
+      <c r="DY1" s="63"/>
+      <c r="DZ1" s="63"/>
+      <c r="EA1" s="63"/>
+      <c r="EB1" s="63"/>
+      <c r="EC1" s="63"/>
+      <c r="ED1" s="63"/>
+      <c r="EE1" s="63"/>
+      <c r="EF1" s="63"/>
+      <c r="EG1" s="63"/>
+      <c r="EH1" s="63"/>
+      <c r="EI1" s="63"/>
+      <c r="EJ1" s="63"/>
+      <c r="EK1" s="63"/>
+      <c r="EL1" s="63"/>
+      <c r="EM1" s="63"/>
+      <c r="EN1" s="63"/>
+      <c r="EO1" s="63"/>
+      <c r="EP1" s="63"/>
+      <c r="EQ1" s="63"/>
+      <c r="ER1" s="63"/>
+      <c r="ES1" s="63"/>
+      <c r="ET1" s="63"/>
+      <c r="EU1" s="63"/>
+      <c r="EV1" s="63"/>
+      <c r="EW1" s="63"/>
+      <c r="EX1" s="63"/>
+      <c r="EY1" s="63"/>
+      <c r="EZ1" s="63"/>
+      <c r="FA1" s="63"/>
+      <c r="FB1" s="63"/>
+      <c r="FC1" s="63"/>
+      <c r="FD1" s="63"/>
+      <c r="FE1" s="63"/>
+      <c r="FF1" s="63"/>
+      <c r="FG1" s="63"/>
+      <c r="FH1" s="63"/>
+      <c r="FI1" s="63"/>
+      <c r="FJ1" s="63"/>
+      <c r="FK1" s="63"/>
+      <c r="FL1" s="63"/>
+      <c r="FM1" s="63"/>
+      <c r="FN1" s="63"/>
+      <c r="FO1" s="63"/>
+      <c r="FP1" s="63"/>
+      <c r="FQ1" s="63"/>
+      <c r="FR1" s="63"/>
+      <c r="FS1" s="63"/>
+      <c r="FT1" s="63"/>
+      <c r="FU1" s="63"/>
+      <c r="FV1" s="63"/>
+      <c r="FW1" s="63"/>
+      <c r="FX1" s="63"/>
+      <c r="FY1" s="63"/>
+      <c r="FZ1" s="63"/>
+      <c r="GA1" s="63"/>
+      <c r="GB1" s="63"/>
+      <c r="GC1" s="63"/>
+      <c r="GD1" s="63"/>
+      <c r="GE1" s="63"/>
+      <c r="GF1" s="63"/>
+      <c r="GG1" s="63"/>
+      <c r="GH1" s="63"/>
+      <c r="GI1" s="63"/>
+      <c r="GJ1" s="63"/>
+      <c r="GK1" s="63"/>
+      <c r="GL1" s="63"/>
+      <c r="GM1" s="63"/>
+      <c r="GN1" s="63"/>
+      <c r="GO1" s="63"/>
+      <c r="GP1" s="63"/>
+      <c r="GQ1" s="63"/>
+      <c r="GR1" s="63"/>
+      <c r="GS1" s="63"/>
+      <c r="GT1" s="63"/>
+      <c r="GU1" s="63"/>
+      <c r="GV1" s="63"/>
+      <c r="GW1" s="63"/>
+      <c r="GX1" s="63"/>
+      <c r="GY1" s="63"/>
+      <c r="GZ1" s="63"/>
+      <c r="HA1" s="63"/>
+      <c r="HB1" s="63"/>
+      <c r="HC1" s="63"/>
+      <c r="HD1" s="63"/>
+      <c r="HE1" s="63"/>
+      <c r="HF1" s="63"/>
+      <c r="HG1" s="63"/>
+      <c r="HH1" s="63"/>
+      <c r="HI1" s="63"/>
+      <c r="HJ1" s="63"/>
+      <c r="HK1" s="63"/>
+      <c r="HL1" s="63"/>
+      <c r="HM1" s="63"/>
+      <c r="HN1" s="63"/>
+      <c r="HO1" s="63"/>
+      <c r="HP1" s="63"/>
+      <c r="HQ1" s="63"/>
+      <c r="HR1" s="63"/>
+      <c r="HS1" s="63"/>
+      <c r="HT1" s="63"/>
+      <c r="HU1" s="63"/>
+      <c r="HV1" s="63"/>
+      <c r="HW1" s="63"/>
+      <c r="HX1" s="63"/>
+      <c r="HY1" s="63"/>
+      <c r="HZ1" s="63"/>
+      <c r="IA1" s="63"/>
+      <c r="IB1" s="63"/>
+      <c r="IC1" s="63"/>
+      <c r="ID1" s="63"/>
+      <c r="IE1" s="63"/>
+      <c r="IF1" s="63"/>
+      <c r="IG1" s="63"/>
+      <c r="IH1" s="63"/>
+      <c r="II1" s="63"/>
+      <c r="IJ1" s="63"/>
+      <c r="IK1" s="63"/>
+      <c r="IL1" s="63"/>
+      <c r="IM1" s="63"/>
+      <c r="IN1" s="63"/>
+      <c r="IO1" s="63"/>
+      <c r="IP1" s="63"/>
+      <c r="IQ1" s="63"/>
+      <c r="IR1" s="63"/>
+      <c r="IS1" s="63"/>
+      <c r="IT1" s="63"/>
+      <c r="IU1" s="63"/>
+      <c r="IV1" s="63"/>
+      <c r="IW1" s="63"/>
     </row>
     <row r="2" customFormat="false" ht="23.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="65" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="65" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="64" t="s">
+      <c r="C2" s="65" t="s">
         <v>150</v>
       </c>
-      <c r="C2" s="64" t="s">
+      <c r="D2" s="65" t="s">
         <v>151</v>
       </c>
-      <c r="D2" s="64" t="s">
+      <c r="E2" s="65" t="s">
         <v>152</v>
       </c>
-      <c r="E2" s="64" t="s">
-        <v>153</v>
-      </c>
-      <c r="F2" s="64" t="s">
-        <v>153</v>
-      </c>
-      <c r="G2" s="64" t="s">
+      <c r="F2" s="65" t="s">
+        <v>152</v>
+      </c>
+      <c r="G2" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="H2" s="65" t="s">
-        <v>142</v>
-      </c>
-      <c r="I2" s="66"/>
-      <c r="L2" s="63" t="s">
+      <c r="H2" s="66" t="s">
+        <v>141</v>
+      </c>
+      <c r="I2" s="67"/>
+      <c r="L2" s="64" t="s">
         <v>51</v>
       </c>
     </row>
@@ -9955,8 +10167,8 @@
       <c r="D3" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="E3" s="67" t="s">
-        <v>154</v>
+      <c r="E3" s="68" t="s">
+        <v>153</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>124</v>
@@ -9965,12 +10177,12 @@
         <v>57</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="I3" s="68"/>
+        <v>181</v>
+      </c>
+      <c r="I3" s="69"/>
     </row>
     <row r="4" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="69" t="s">
+      <c r="A4" s="70" t="s">
         <v>101</v>
       </c>
       <c r="C4" s="13" t="s">
@@ -9979,40 +10191,40 @@
       <c r="D4" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="E4" s="67" t="s">
-        <v>155</v>
-      </c>
-      <c r="F4" s="69" t="s">
-        <v>139</v>
-      </c>
-      <c r="H4" s="69" t="s">
+      <c r="E4" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="F4" s="70" t="s">
+        <v>138</v>
+      </c>
+      <c r="H4" s="70" t="s">
         <v>77</v>
       </c>
-      <c r="I4" s="68"/>
+      <c r="I4" s="69"/>
     </row>
     <row r="5" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="70" t="s">
+      <c r="A5" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="70" t="s">
+      <c r="C5" s="71" t="s">
         <v>24</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="70" t="s">
-        <v>156</v>
+      <c r="E5" s="71" t="s">
+        <v>155</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="G5" s="65" t="s">
+      <c r="G5" s="66" t="s">
         <v>71</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="I5" s="71"/>
+        <v>167</v>
+      </c>
+      <c r="I5" s="72"/>
     </row>
     <row r="6" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
@@ -10021,19 +10233,19 @@
       <c r="C6" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="70" t="s">
-        <v>157</v>
+      <c r="E6" s="71" t="s">
+        <v>156</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="G6" s="69" t="s">
+      <c r="G6" s="70" t="s">
         <v>84</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="I6" s="71"/>
+      <c r="I6" s="72"/>
     </row>
     <row r="7" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
@@ -10049,53 +10261,53 @@
         <v>104</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="H7" s="69" t="s">
-        <v>147</v>
-      </c>
-      <c r="I7" s="68"/>
+        <v>144</v>
+      </c>
+      <c r="H7" s="70" t="s">
+        <v>146</v>
+      </c>
+      <c r="I7" s="69"/>
     </row>
     <row r="8" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="95" t="s">
+      <c r="A8" s="96" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="70" t="s">
+      <c r="C8" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="70" t="s">
+      <c r="E8" s="71" t="s">
         <v>23</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G8" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="H8" s="69" t="s">
+      <c r="H8" s="70" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="75" t="s">
+      <c r="A9" s="76" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="72" t="s">
+      <c r="B9" s="73" t="s">
         <v>63</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="70" t="s">
-        <v>167</v>
-      </c>
-      <c r="G9" s="74"/>
-      <c r="H9" s="75" t="s">
+      <c r="E9" s="71" t="s">
+        <v>166</v>
+      </c>
+      <c r="G9" s="75"/>
+      <c r="H9" s="76" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="73" t="s">
+      <c r="A10" s="74" t="s">
         <v>30</v>
       </c>
       <c r="B10" s="13" t="s">
@@ -10104,28 +10316,28 @@
       <c r="C10" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="70" t="s">
+      <c r="E10" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="76" t="s">
-        <v>158</v>
-      </c>
-      <c r="G10" s="65"/>
+      <c r="F10" s="77" t="s">
+        <v>157</v>
+      </c>
+      <c r="G10" s="66"/>
     </row>
     <row r="11" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C11" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="72" t="s">
-        <v>159</v>
-      </c>
-      <c r="E11" s="75" t="s">
-        <v>172</v>
-      </c>
-      <c r="F11" s="69" t="s">
+      <c r="D11" s="73" t="s">
+        <v>158</v>
+      </c>
+      <c r="E11" s="76" t="s">
+        <v>171</v>
+      </c>
+      <c r="F11" s="70" t="s">
         <v>116</v>
       </c>
-      <c r="H11" s="77"/>
+      <c r="H11" s="78"/>
     </row>
     <row r="12" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C12" s="13" t="s">
@@ -10134,35 +10346,35 @@
       <c r="D12" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="E12" s="96" t="s">
+      <c r="E12" s="97" t="s">
         <v>27</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="77"/>
-      <c r="H12" s="69"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="70"/>
     </row>
     <row r="13" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="65" t="s">
+      <c r="A13" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="B13" s="65" t="s">
+      <c r="B13" s="66" t="s">
         <v>48</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="70" t="s">
+      <c r="D13" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="E13" s="67" t="s">
+      <c r="E13" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="F13" s="75" t="s">
+      <c r="F13" s="76" t="s">
         <v>41</v>
       </c>
-      <c r="H13" s="69"/>
+      <c r="H13" s="70"/>
     </row>
     <row r="14" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
@@ -10174,396 +10386,396 @@
       <c r="C14" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="70" t="s">
+      <c r="D14" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="75" t="s">
+      <c r="E14" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="H14" s="78" t="s">
+      <c r="H14" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="I14" s="80" t="s">
         <v>161</v>
       </c>
-      <c r="I14" s="79" t="s">
+      <c r="L14" s="61" t="s">
         <v>162</v>
       </c>
-      <c r="L14" s="60" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C15" s="76" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="76" t="s">
+        <v>159</v>
+      </c>
+      <c r="E15" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" s="93" t="s">
+        <v>127</v>
+      </c>
+      <c r="I15" s="82" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="65" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C15" s="75" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="75" t="s">
-        <v>160</v>
-      </c>
-      <c r="E15" s="67" t="s">
-        <v>35</v>
-      </c>
-      <c r="H15" s="92" t="s">
-        <v>127</v>
-      </c>
-      <c r="I15" s="81" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="64" t="s">
+      <c r="C16" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="76" t="s">
         <v>164</v>
       </c>
-      <c r="C16" s="67" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="75" t="s">
+      <c r="E16" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="66" t="s">
         <v>165</v>
       </c>
-      <c r="E16" s="75" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" s="65" t="s">
-        <v>166</v>
-      </c>
-      <c r="H16" s="80" t="s">
+      <c r="H16" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="I16" s="81" t="s">
-        <v>144</v>
+      <c r="I16" s="82" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="C17" s="67" t="s">
+      <c r="C17" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="67" t="s">
+      <c r="E17" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="F17" s="69" t="s">
+      <c r="F17" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="80" t="s">
+      <c r="H17" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="I17" s="81" t="s">
+      <c r="I17" s="82" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H18" s="80"/>
+      <c r="H18" s="81"/>
     </row>
     <row r="19" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H19" s="80"/>
+      <c r="H19" s="81"/>
     </row>
     <row r="20" customFormat="false" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="82"/>
-      <c r="B20" s="82"/>
-      <c r="C20" s="82"/>
-      <c r="D20" s="82"/>
-      <c r="E20" s="82"/>
-      <c r="F20" s="82"/>
-      <c r="G20" s="82"/>
-      <c r="H20" s="80"/>
-      <c r="I20" s="82"/>
-      <c r="J20" s="83"/>
-      <c r="O20" s="82"/>
-      <c r="P20" s="82"/>
-      <c r="Q20" s="82"/>
-      <c r="R20" s="82"/>
-      <c r="S20" s="82"/>
-      <c r="T20" s="82"/>
-      <c r="U20" s="82"/>
-      <c r="V20" s="82"/>
-      <c r="W20" s="82"/>
-      <c r="X20" s="82"/>
-      <c r="Y20" s="82"/>
-      <c r="Z20" s="82"/>
-      <c r="AA20" s="82"/>
-      <c r="AB20" s="82"/>
-      <c r="AC20" s="82"/>
-      <c r="AD20" s="82"/>
-      <c r="AE20" s="82"/>
-      <c r="AF20" s="82"/>
-      <c r="AG20" s="82"/>
-      <c r="AH20" s="82"/>
-      <c r="AI20" s="82"/>
-      <c r="AJ20" s="82"/>
-      <c r="AK20" s="82"/>
-      <c r="AL20" s="82"/>
-      <c r="AM20" s="82"/>
-      <c r="AN20" s="82"/>
-      <c r="AO20" s="82"/>
-      <c r="AP20" s="82"/>
-      <c r="AQ20" s="82"/>
-      <c r="AR20" s="82"/>
-      <c r="AS20" s="82"/>
-      <c r="AT20" s="82"/>
-      <c r="AU20" s="82"/>
-      <c r="AV20" s="82"/>
-      <c r="AW20" s="82"/>
-      <c r="AX20" s="82"/>
-      <c r="AY20" s="82"/>
-      <c r="AZ20" s="82"/>
-      <c r="BA20" s="82"/>
-      <c r="BB20" s="82"/>
-      <c r="BC20" s="82"/>
-      <c r="BD20" s="82"/>
-      <c r="BE20" s="82"/>
-      <c r="BF20" s="82"/>
-      <c r="BG20" s="82"/>
-      <c r="BH20" s="82"/>
-      <c r="BI20" s="82"/>
-      <c r="BJ20" s="82"/>
-      <c r="BK20" s="82"/>
-      <c r="BL20" s="82"/>
-      <c r="BM20" s="82"/>
-      <c r="BN20" s="82"/>
-      <c r="BO20" s="82"/>
-      <c r="BP20" s="82"/>
-      <c r="BQ20" s="82"/>
-      <c r="BR20" s="82"/>
-      <c r="BS20" s="82"/>
-      <c r="BT20" s="82"/>
-      <c r="BU20" s="82"/>
-      <c r="BV20" s="82"/>
-      <c r="BW20" s="82"/>
-      <c r="BX20" s="82"/>
-      <c r="BY20" s="82"/>
-      <c r="BZ20" s="82"/>
-      <c r="CA20" s="82"/>
-      <c r="CB20" s="82"/>
-      <c r="CC20" s="82"/>
-      <c r="CD20" s="82"/>
-      <c r="CE20" s="82"/>
-      <c r="CF20" s="82"/>
-      <c r="CG20" s="82"/>
-      <c r="CH20" s="82"/>
-      <c r="CI20" s="82"/>
-      <c r="CJ20" s="82"/>
-      <c r="CK20" s="82"/>
-      <c r="CL20" s="82"/>
-      <c r="CM20" s="82"/>
-      <c r="CN20" s="82"/>
-      <c r="CO20" s="82"/>
-      <c r="CP20" s="82"/>
-      <c r="CQ20" s="82"/>
-      <c r="CR20" s="82"/>
-      <c r="CS20" s="82"/>
-      <c r="CT20" s="82"/>
-      <c r="CU20" s="82"/>
-      <c r="CV20" s="82"/>
-      <c r="CW20" s="82"/>
-      <c r="CX20" s="82"/>
-      <c r="CY20" s="82"/>
-      <c r="CZ20" s="82"/>
-      <c r="DA20" s="82"/>
-      <c r="DB20" s="82"/>
-      <c r="DC20" s="82"/>
-      <c r="DD20" s="82"/>
-      <c r="DE20" s="82"/>
-      <c r="DF20" s="82"/>
-      <c r="DG20" s="82"/>
-      <c r="DH20" s="82"/>
-      <c r="DI20" s="82"/>
-      <c r="DJ20" s="82"/>
-      <c r="DK20" s="82"/>
-      <c r="DL20" s="82"/>
-      <c r="DM20" s="82"/>
-      <c r="DN20" s="82"/>
-      <c r="DO20" s="82"/>
-      <c r="DP20" s="82"/>
-      <c r="DQ20" s="82"/>
-      <c r="DR20" s="82"/>
-      <c r="DS20" s="82"/>
-      <c r="DT20" s="82"/>
-      <c r="DU20" s="82"/>
-      <c r="DV20" s="82"/>
-      <c r="DW20" s="82"/>
-      <c r="DX20" s="82"/>
-      <c r="DY20" s="82"/>
-      <c r="DZ20" s="82"/>
-      <c r="EA20" s="82"/>
-      <c r="EB20" s="82"/>
-      <c r="EC20" s="82"/>
-      <c r="ED20" s="82"/>
-      <c r="EE20" s="82"/>
-      <c r="EF20" s="82"/>
-      <c r="EG20" s="82"/>
-      <c r="EH20" s="82"/>
-      <c r="EI20" s="82"/>
-      <c r="EJ20" s="82"/>
-      <c r="EK20" s="82"/>
-      <c r="EL20" s="82"/>
-      <c r="EM20" s="82"/>
-      <c r="EN20" s="82"/>
-      <c r="EO20" s="82"/>
-      <c r="EP20" s="82"/>
-      <c r="EQ20" s="82"/>
-      <c r="ER20" s="82"/>
-      <c r="ES20" s="82"/>
-      <c r="ET20" s="82"/>
-      <c r="EU20" s="82"/>
-      <c r="EV20" s="82"/>
-      <c r="EW20" s="82"/>
-      <c r="EX20" s="82"/>
-      <c r="EY20" s="82"/>
-      <c r="EZ20" s="82"/>
-      <c r="FA20" s="82"/>
-      <c r="FB20" s="82"/>
-      <c r="FC20" s="82"/>
-      <c r="FD20" s="82"/>
-      <c r="FE20" s="82"/>
-      <c r="FF20" s="82"/>
-      <c r="FG20" s="82"/>
-      <c r="FH20" s="82"/>
-      <c r="FI20" s="82"/>
-      <c r="FJ20" s="82"/>
-      <c r="FK20" s="82"/>
-      <c r="FL20" s="82"/>
-      <c r="FM20" s="82"/>
-      <c r="FN20" s="82"/>
-      <c r="FO20" s="82"/>
-      <c r="FP20" s="82"/>
-      <c r="FQ20" s="82"/>
-      <c r="FR20" s="82"/>
-      <c r="FS20" s="82"/>
-      <c r="FT20" s="82"/>
-      <c r="FU20" s="82"/>
-      <c r="FV20" s="82"/>
-      <c r="FW20" s="82"/>
-      <c r="FX20" s="82"/>
-      <c r="FY20" s="82"/>
-      <c r="FZ20" s="82"/>
-      <c r="GA20" s="82"/>
-      <c r="GB20" s="82"/>
-      <c r="GC20" s="82"/>
-      <c r="GD20" s="82"/>
-      <c r="GE20" s="82"/>
-      <c r="GF20" s="82"/>
-      <c r="GG20" s="82"/>
-      <c r="GH20" s="82"/>
-      <c r="GI20" s="82"/>
-      <c r="GJ20" s="82"/>
-      <c r="GK20" s="82"/>
-      <c r="GL20" s="82"/>
-      <c r="GM20" s="82"/>
-      <c r="GN20" s="82"/>
-      <c r="GO20" s="82"/>
-      <c r="GP20" s="82"/>
-      <c r="GQ20" s="82"/>
-      <c r="GR20" s="82"/>
-      <c r="GS20" s="82"/>
-      <c r="GT20" s="82"/>
-      <c r="GU20" s="82"/>
-      <c r="GV20" s="82"/>
-      <c r="GW20" s="82"/>
-      <c r="GX20" s="82"/>
-      <c r="GY20" s="82"/>
-      <c r="GZ20" s="82"/>
-      <c r="HA20" s="82"/>
-      <c r="HB20" s="82"/>
-      <c r="HC20" s="82"/>
-      <c r="HD20" s="82"/>
-      <c r="HE20" s="82"/>
-      <c r="HF20" s="82"/>
-      <c r="HG20" s="82"/>
-      <c r="HH20" s="82"/>
-      <c r="HI20" s="82"/>
-      <c r="HJ20" s="82"/>
-      <c r="HK20" s="82"/>
-      <c r="HL20" s="82"/>
-      <c r="HM20" s="82"/>
-      <c r="HN20" s="82"/>
-      <c r="HO20" s="82"/>
-      <c r="HP20" s="82"/>
-      <c r="HQ20" s="82"/>
-      <c r="HR20" s="82"/>
-      <c r="HS20" s="82"/>
-      <c r="HT20" s="82"/>
-      <c r="HU20" s="82"/>
-      <c r="HV20" s="82"/>
-      <c r="HW20" s="82"/>
-      <c r="HX20" s="82"/>
-      <c r="HY20" s="82"/>
-      <c r="HZ20" s="82"/>
-      <c r="IA20" s="82"/>
-      <c r="IB20" s="82"/>
-      <c r="IC20" s="82"/>
-      <c r="ID20" s="82"/>
-      <c r="IE20" s="82"/>
-      <c r="IF20" s="82"/>
-      <c r="IG20" s="82"/>
-      <c r="IH20" s="82"/>
-      <c r="II20" s="82"/>
-      <c r="IJ20" s="82"/>
-      <c r="IK20" s="82"/>
-      <c r="IL20" s="82"/>
-      <c r="IM20" s="82"/>
-      <c r="IN20" s="82"/>
-      <c r="IO20" s="82"/>
-      <c r="IP20" s="82"/>
-      <c r="IQ20" s="82"/>
-      <c r="IR20" s="82"/>
-      <c r="IS20" s="82"/>
-      <c r="IT20" s="82"/>
-      <c r="IU20" s="82"/>
-      <c r="IV20" s="82"/>
-      <c r="IW20" s="82"/>
+      <c r="A20" s="83"/>
+      <c r="B20" s="83"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="83"/>
+      <c r="J20" s="84"/>
+      <c r="O20" s="83"/>
+      <c r="P20" s="83"/>
+      <c r="Q20" s="83"/>
+      <c r="R20" s="83"/>
+      <c r="S20" s="83"/>
+      <c r="T20" s="83"/>
+      <c r="U20" s="83"/>
+      <c r="V20" s="83"/>
+      <c r="W20" s="83"/>
+      <c r="X20" s="83"/>
+      <c r="Y20" s="83"/>
+      <c r="Z20" s="83"/>
+      <c r="AA20" s="83"/>
+      <c r="AB20" s="83"/>
+      <c r="AC20" s="83"/>
+      <c r="AD20" s="83"/>
+      <c r="AE20" s="83"/>
+      <c r="AF20" s="83"/>
+      <c r="AG20" s="83"/>
+      <c r="AH20" s="83"/>
+      <c r="AI20" s="83"/>
+      <c r="AJ20" s="83"/>
+      <c r="AK20" s="83"/>
+      <c r="AL20" s="83"/>
+      <c r="AM20" s="83"/>
+      <c r="AN20" s="83"/>
+      <c r="AO20" s="83"/>
+      <c r="AP20" s="83"/>
+      <c r="AQ20" s="83"/>
+      <c r="AR20" s="83"/>
+      <c r="AS20" s="83"/>
+      <c r="AT20" s="83"/>
+      <c r="AU20" s="83"/>
+      <c r="AV20" s="83"/>
+      <c r="AW20" s="83"/>
+      <c r="AX20" s="83"/>
+      <c r="AY20" s="83"/>
+      <c r="AZ20" s="83"/>
+      <c r="BA20" s="83"/>
+      <c r="BB20" s="83"/>
+      <c r="BC20" s="83"/>
+      <c r="BD20" s="83"/>
+      <c r="BE20" s="83"/>
+      <c r="BF20" s="83"/>
+      <c r="BG20" s="83"/>
+      <c r="BH20" s="83"/>
+      <c r="BI20" s="83"/>
+      <c r="BJ20" s="83"/>
+      <c r="BK20" s="83"/>
+      <c r="BL20" s="83"/>
+      <c r="BM20" s="83"/>
+      <c r="BN20" s="83"/>
+      <c r="BO20" s="83"/>
+      <c r="BP20" s="83"/>
+      <c r="BQ20" s="83"/>
+      <c r="BR20" s="83"/>
+      <c r="BS20" s="83"/>
+      <c r="BT20" s="83"/>
+      <c r="BU20" s="83"/>
+      <c r="BV20" s="83"/>
+      <c r="BW20" s="83"/>
+      <c r="BX20" s="83"/>
+      <c r="BY20" s="83"/>
+      <c r="BZ20" s="83"/>
+      <c r="CA20" s="83"/>
+      <c r="CB20" s="83"/>
+      <c r="CC20" s="83"/>
+      <c r="CD20" s="83"/>
+      <c r="CE20" s="83"/>
+      <c r="CF20" s="83"/>
+      <c r="CG20" s="83"/>
+      <c r="CH20" s="83"/>
+      <c r="CI20" s="83"/>
+      <c r="CJ20" s="83"/>
+      <c r="CK20" s="83"/>
+      <c r="CL20" s="83"/>
+      <c r="CM20" s="83"/>
+      <c r="CN20" s="83"/>
+      <c r="CO20" s="83"/>
+      <c r="CP20" s="83"/>
+      <c r="CQ20" s="83"/>
+      <c r="CR20" s="83"/>
+      <c r="CS20" s="83"/>
+      <c r="CT20" s="83"/>
+      <c r="CU20" s="83"/>
+      <c r="CV20" s="83"/>
+      <c r="CW20" s="83"/>
+      <c r="CX20" s="83"/>
+      <c r="CY20" s="83"/>
+      <c r="CZ20" s="83"/>
+      <c r="DA20" s="83"/>
+      <c r="DB20" s="83"/>
+      <c r="DC20" s="83"/>
+      <c r="DD20" s="83"/>
+      <c r="DE20" s="83"/>
+      <c r="DF20" s="83"/>
+      <c r="DG20" s="83"/>
+      <c r="DH20" s="83"/>
+      <c r="DI20" s="83"/>
+      <c r="DJ20" s="83"/>
+      <c r="DK20" s="83"/>
+      <c r="DL20" s="83"/>
+      <c r="DM20" s="83"/>
+      <c r="DN20" s="83"/>
+      <c r="DO20" s="83"/>
+      <c r="DP20" s="83"/>
+      <c r="DQ20" s="83"/>
+      <c r="DR20" s="83"/>
+      <c r="DS20" s="83"/>
+      <c r="DT20" s="83"/>
+      <c r="DU20" s="83"/>
+      <c r="DV20" s="83"/>
+      <c r="DW20" s="83"/>
+      <c r="DX20" s="83"/>
+      <c r="DY20" s="83"/>
+      <c r="DZ20" s="83"/>
+      <c r="EA20" s="83"/>
+      <c r="EB20" s="83"/>
+      <c r="EC20" s="83"/>
+      <c r="ED20" s="83"/>
+      <c r="EE20" s="83"/>
+      <c r="EF20" s="83"/>
+      <c r="EG20" s="83"/>
+      <c r="EH20" s="83"/>
+      <c r="EI20" s="83"/>
+      <c r="EJ20" s="83"/>
+      <c r="EK20" s="83"/>
+      <c r="EL20" s="83"/>
+      <c r="EM20" s="83"/>
+      <c r="EN20" s="83"/>
+      <c r="EO20" s="83"/>
+      <c r="EP20" s="83"/>
+      <c r="EQ20" s="83"/>
+      <c r="ER20" s="83"/>
+      <c r="ES20" s="83"/>
+      <c r="ET20" s="83"/>
+      <c r="EU20" s="83"/>
+      <c r="EV20" s="83"/>
+      <c r="EW20" s="83"/>
+      <c r="EX20" s="83"/>
+      <c r="EY20" s="83"/>
+      <c r="EZ20" s="83"/>
+      <c r="FA20" s="83"/>
+      <c r="FB20" s="83"/>
+      <c r="FC20" s="83"/>
+      <c r="FD20" s="83"/>
+      <c r="FE20" s="83"/>
+      <c r="FF20" s="83"/>
+      <c r="FG20" s="83"/>
+      <c r="FH20" s="83"/>
+      <c r="FI20" s="83"/>
+      <c r="FJ20" s="83"/>
+      <c r="FK20" s="83"/>
+      <c r="FL20" s="83"/>
+      <c r="FM20" s="83"/>
+      <c r="FN20" s="83"/>
+      <c r="FO20" s="83"/>
+      <c r="FP20" s="83"/>
+      <c r="FQ20" s="83"/>
+      <c r="FR20" s="83"/>
+      <c r="FS20" s="83"/>
+      <c r="FT20" s="83"/>
+      <c r="FU20" s="83"/>
+      <c r="FV20" s="83"/>
+      <c r="FW20" s="83"/>
+      <c r="FX20" s="83"/>
+      <c r="FY20" s="83"/>
+      <c r="FZ20" s="83"/>
+      <c r="GA20" s="83"/>
+      <c r="GB20" s="83"/>
+      <c r="GC20" s="83"/>
+      <c r="GD20" s="83"/>
+      <c r="GE20" s="83"/>
+      <c r="GF20" s="83"/>
+      <c r="GG20" s="83"/>
+      <c r="GH20" s="83"/>
+      <c r="GI20" s="83"/>
+      <c r="GJ20" s="83"/>
+      <c r="GK20" s="83"/>
+      <c r="GL20" s="83"/>
+      <c r="GM20" s="83"/>
+      <c r="GN20" s="83"/>
+      <c r="GO20" s="83"/>
+      <c r="GP20" s="83"/>
+      <c r="GQ20" s="83"/>
+      <c r="GR20" s="83"/>
+      <c r="GS20" s="83"/>
+      <c r="GT20" s="83"/>
+      <c r="GU20" s="83"/>
+      <c r="GV20" s="83"/>
+      <c r="GW20" s="83"/>
+      <c r="GX20" s="83"/>
+      <c r="GY20" s="83"/>
+      <c r="GZ20" s="83"/>
+      <c r="HA20" s="83"/>
+      <c r="HB20" s="83"/>
+      <c r="HC20" s="83"/>
+      <c r="HD20" s="83"/>
+      <c r="HE20" s="83"/>
+      <c r="HF20" s="83"/>
+      <c r="HG20" s="83"/>
+      <c r="HH20" s="83"/>
+      <c r="HI20" s="83"/>
+      <c r="HJ20" s="83"/>
+      <c r="HK20" s="83"/>
+      <c r="HL20" s="83"/>
+      <c r="HM20" s="83"/>
+      <c r="HN20" s="83"/>
+      <c r="HO20" s="83"/>
+      <c r="HP20" s="83"/>
+      <c r="HQ20" s="83"/>
+      <c r="HR20" s="83"/>
+      <c r="HS20" s="83"/>
+      <c r="HT20" s="83"/>
+      <c r="HU20" s="83"/>
+      <c r="HV20" s="83"/>
+      <c r="HW20" s="83"/>
+      <c r="HX20" s="83"/>
+      <c r="HY20" s="83"/>
+      <c r="HZ20" s="83"/>
+      <c r="IA20" s="83"/>
+      <c r="IB20" s="83"/>
+      <c r="IC20" s="83"/>
+      <c r="ID20" s="83"/>
+      <c r="IE20" s="83"/>
+      <c r="IF20" s="83"/>
+      <c r="IG20" s="83"/>
+      <c r="IH20" s="83"/>
+      <c r="II20" s="83"/>
+      <c r="IJ20" s="83"/>
+      <c r="IK20" s="83"/>
+      <c r="IL20" s="83"/>
+      <c r="IM20" s="83"/>
+      <c r="IN20" s="83"/>
+      <c r="IO20" s="83"/>
+      <c r="IP20" s="83"/>
+      <c r="IQ20" s="83"/>
+      <c r="IR20" s="83"/>
+      <c r="IS20" s="83"/>
+      <c r="IT20" s="83"/>
+      <c r="IU20" s="83"/>
+      <c r="IV20" s="83"/>
+      <c r="IW20" s="83"/>
     </row>
     <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="82"/>
-      <c r="G21" s="84"/>
-      <c r="H21" s="80"/>
-      <c r="I21" s="81"/>
-      <c r="J21" s="85" t="s">
+      <c r="B21" s="83"/>
+      <c r="G21" s="85"/>
+      <c r="H21" s="81"/>
+      <c r="I21" s="82"/>
+      <c r="J21" s="86" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="87"/>
+      <c r="G22" s="87"/>
+      <c r="H22" s="81"/>
+      <c r="I22" s="82"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="82"/>
+      <c r="R23" s="88"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="82"/>
+      <c r="L24" s="61" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="86"/>
-      <c r="G22" s="86"/>
-      <c r="H22" s="80"/>
-      <c r="I22" s="81"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I23" s="81"/>
-      <c r="R23" s="87"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I24" s="81"/>
-      <c r="L24" s="60" t="s">
-        <v>170</v>
-      </c>
-    </row>
     <row r="25" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I25" s="81"/>
+      <c r="I25" s="82"/>
     </row>
     <row r="26" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="3"/>
-      <c r="I26" s="81"/>
+      <c r="I26" s="82"/>
     </row>
     <row r="28" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D28" s="88"/>
+      <c r="D28" s="89"/>
     </row>
     <row r="29" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="89" t="s">
+      <c r="A29" s="90" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="90" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="89" t="s">
-        <v>180</v>
-      </c>
-    </row>
     <row r="31" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="89" t="s">
+      <c r="A31" s="90" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="81" t="s">
         <v>175</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="80" t="s">
-        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -10590,309 +10802,309 @@
   <dimension ref="A1:IW32"/>
   <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="12.55" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="60" width="12.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="60" width="12.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="60" width="14.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="60" width="12.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="60" width="17.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="60" width="15.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="60" width="13.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="60" width="13.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="60" width="14.55"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="10" min="10" style="60" width="9.1"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="11" style="60" width="9.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="61" width="12.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="61" width="12.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="61" width="14.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="61" width="12.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="61" width="17.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="61" width="15.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="61" width="13.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="61" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="61" width="14.55"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="10" min="10" style="61" width="9.1"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="11" style="61" width="9.1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="26.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="61" t="s">
-        <v>183</v>
-      </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="63" t="s">
+      <c r="A1" s="62" t="s">
+        <v>182</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="64" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="62"/>
-      <c r="N1" s="62"/>
-      <c r="O1" s="62"/>
-      <c r="P1" s="62"/>
-      <c r="Q1" s="62"/>
-      <c r="R1" s="62"/>
-      <c r="S1" s="62"/>
-      <c r="T1" s="62"/>
-      <c r="U1" s="62"/>
-      <c r="V1" s="62"/>
-      <c r="W1" s="62"/>
-      <c r="X1" s="62"/>
-      <c r="Y1" s="62"/>
-      <c r="Z1" s="62"/>
-      <c r="AA1" s="62"/>
-      <c r="AB1" s="62"/>
-      <c r="AC1" s="62"/>
-      <c r="AD1" s="62"/>
-      <c r="AE1" s="62"/>
-      <c r="AF1" s="62"/>
-      <c r="AG1" s="62"/>
-      <c r="AH1" s="62"/>
-      <c r="AI1" s="62"/>
-      <c r="AJ1" s="62"/>
-      <c r="AK1" s="62"/>
-      <c r="AL1" s="62"/>
-      <c r="AM1" s="62"/>
-      <c r="AN1" s="62"/>
-      <c r="AO1" s="62"/>
-      <c r="AP1" s="62"/>
-      <c r="AQ1" s="62"/>
-      <c r="AR1" s="62"/>
-      <c r="AS1" s="62"/>
-      <c r="AT1" s="62"/>
-      <c r="AU1" s="62"/>
-      <c r="AV1" s="62"/>
-      <c r="AW1" s="62"/>
-      <c r="AX1" s="62"/>
-      <c r="AY1" s="62"/>
-      <c r="AZ1" s="62"/>
-      <c r="BA1" s="62"/>
-      <c r="BB1" s="62"/>
-      <c r="BC1" s="62"/>
-      <c r="BD1" s="62"/>
-      <c r="BE1" s="62"/>
-      <c r="BF1" s="62"/>
-      <c r="BG1" s="62"/>
-      <c r="BH1" s="62"/>
-      <c r="BI1" s="62"/>
-      <c r="BJ1" s="62"/>
-      <c r="BK1" s="62"/>
-      <c r="BL1" s="62"/>
-      <c r="BM1" s="62"/>
-      <c r="BN1" s="62"/>
-      <c r="BO1" s="62"/>
-      <c r="BP1" s="62"/>
-      <c r="BQ1" s="62"/>
-      <c r="BR1" s="62"/>
-      <c r="BS1" s="62"/>
-      <c r="BT1" s="62"/>
-      <c r="BU1" s="62"/>
-      <c r="BV1" s="62"/>
-      <c r="BW1" s="62"/>
-      <c r="BX1" s="62"/>
-      <c r="BY1" s="62"/>
-      <c r="BZ1" s="62"/>
-      <c r="CA1" s="62"/>
-      <c r="CB1" s="62"/>
-      <c r="CC1" s="62"/>
-      <c r="CD1" s="62"/>
-      <c r="CE1" s="62"/>
-      <c r="CF1" s="62"/>
-      <c r="CG1" s="62"/>
-      <c r="CH1" s="62"/>
-      <c r="CI1" s="62"/>
-      <c r="CJ1" s="62"/>
-      <c r="CK1" s="62"/>
-      <c r="CL1" s="62"/>
-      <c r="CM1" s="62"/>
-      <c r="CN1" s="62"/>
-      <c r="CO1" s="62"/>
-      <c r="CP1" s="62"/>
-      <c r="CQ1" s="62"/>
-      <c r="CR1" s="62"/>
-      <c r="CS1" s="62"/>
-      <c r="CT1" s="62"/>
-      <c r="CU1" s="62"/>
-      <c r="CV1" s="62"/>
-      <c r="CW1" s="62"/>
-      <c r="CX1" s="62"/>
-      <c r="CY1" s="62"/>
-      <c r="CZ1" s="62"/>
-      <c r="DA1" s="62"/>
-      <c r="DB1" s="62"/>
-      <c r="DC1" s="62"/>
-      <c r="DD1" s="62"/>
-      <c r="DE1" s="62"/>
-      <c r="DF1" s="62"/>
-      <c r="DG1" s="62"/>
-      <c r="DH1" s="62"/>
-      <c r="DI1" s="62"/>
-      <c r="DJ1" s="62"/>
-      <c r="DK1" s="62"/>
-      <c r="DL1" s="62"/>
-      <c r="DM1" s="62"/>
-      <c r="DN1" s="62"/>
-      <c r="DO1" s="62"/>
-      <c r="DP1" s="62"/>
-      <c r="DQ1" s="62"/>
-      <c r="DR1" s="62"/>
-      <c r="DS1" s="62"/>
-      <c r="DT1" s="62"/>
-      <c r="DU1" s="62"/>
-      <c r="DV1" s="62"/>
-      <c r="DW1" s="62"/>
-      <c r="DX1" s="62"/>
-      <c r="DY1" s="62"/>
-      <c r="DZ1" s="62"/>
-      <c r="EA1" s="62"/>
-      <c r="EB1" s="62"/>
-      <c r="EC1" s="62"/>
-      <c r="ED1" s="62"/>
-      <c r="EE1" s="62"/>
-      <c r="EF1" s="62"/>
-      <c r="EG1" s="62"/>
-      <c r="EH1" s="62"/>
-      <c r="EI1" s="62"/>
-      <c r="EJ1" s="62"/>
-      <c r="EK1" s="62"/>
-      <c r="EL1" s="62"/>
-      <c r="EM1" s="62"/>
-      <c r="EN1" s="62"/>
-      <c r="EO1" s="62"/>
-      <c r="EP1" s="62"/>
-      <c r="EQ1" s="62"/>
-      <c r="ER1" s="62"/>
-      <c r="ES1" s="62"/>
-      <c r="ET1" s="62"/>
-      <c r="EU1" s="62"/>
-      <c r="EV1" s="62"/>
-      <c r="EW1" s="62"/>
-      <c r="EX1" s="62"/>
-      <c r="EY1" s="62"/>
-      <c r="EZ1" s="62"/>
-      <c r="FA1" s="62"/>
-      <c r="FB1" s="62"/>
-      <c r="FC1" s="62"/>
-      <c r="FD1" s="62"/>
-      <c r="FE1" s="62"/>
-      <c r="FF1" s="62"/>
-      <c r="FG1" s="62"/>
-      <c r="FH1" s="62"/>
-      <c r="FI1" s="62"/>
-      <c r="FJ1" s="62"/>
-      <c r="FK1" s="62"/>
-      <c r="FL1" s="62"/>
-      <c r="FM1" s="62"/>
-      <c r="FN1" s="62"/>
-      <c r="FO1" s="62"/>
-      <c r="FP1" s="62"/>
-      <c r="FQ1" s="62"/>
-      <c r="FR1" s="62"/>
-      <c r="FS1" s="62"/>
-      <c r="FT1" s="62"/>
-      <c r="FU1" s="62"/>
-      <c r="FV1" s="62"/>
-      <c r="FW1" s="62"/>
-      <c r="FX1" s="62"/>
-      <c r="FY1" s="62"/>
-      <c r="FZ1" s="62"/>
-      <c r="GA1" s="62"/>
-      <c r="GB1" s="62"/>
-      <c r="GC1" s="62"/>
-      <c r="GD1" s="62"/>
-      <c r="GE1" s="62"/>
-      <c r="GF1" s="62"/>
-      <c r="GG1" s="62"/>
-      <c r="GH1" s="62"/>
-      <c r="GI1" s="62"/>
-      <c r="GJ1" s="62"/>
-      <c r="GK1" s="62"/>
-      <c r="GL1" s="62"/>
-      <c r="GM1" s="62"/>
-      <c r="GN1" s="62"/>
-      <c r="GO1" s="62"/>
-      <c r="GP1" s="62"/>
-      <c r="GQ1" s="62"/>
-      <c r="GR1" s="62"/>
-      <c r="GS1" s="62"/>
-      <c r="GT1" s="62"/>
-      <c r="GU1" s="62"/>
-      <c r="GV1" s="62"/>
-      <c r="GW1" s="62"/>
-      <c r="GX1" s="62"/>
-      <c r="GY1" s="62"/>
-      <c r="GZ1" s="62"/>
-      <c r="HA1" s="62"/>
-      <c r="HB1" s="62"/>
-      <c r="HC1" s="62"/>
-      <c r="HD1" s="62"/>
-      <c r="HE1" s="62"/>
-      <c r="HF1" s="62"/>
-      <c r="HG1" s="62"/>
-      <c r="HH1" s="62"/>
-      <c r="HI1" s="62"/>
-      <c r="HJ1" s="62"/>
-      <c r="HK1" s="62"/>
-      <c r="HL1" s="62"/>
-      <c r="HM1" s="62"/>
-      <c r="HN1" s="62"/>
-      <c r="HO1" s="62"/>
-      <c r="HP1" s="62"/>
-      <c r="HQ1" s="62"/>
-      <c r="HR1" s="62"/>
-      <c r="HS1" s="62"/>
-      <c r="HT1" s="62"/>
-      <c r="HU1" s="62"/>
-      <c r="HV1" s="62"/>
-      <c r="HW1" s="62"/>
-      <c r="HX1" s="62"/>
-      <c r="HY1" s="62"/>
-      <c r="HZ1" s="62"/>
-      <c r="IA1" s="62"/>
-      <c r="IB1" s="62"/>
-      <c r="IC1" s="62"/>
-      <c r="ID1" s="62"/>
-      <c r="IE1" s="62"/>
-      <c r="IF1" s="62"/>
-      <c r="IG1" s="62"/>
-      <c r="IH1" s="62"/>
-      <c r="II1" s="62"/>
-      <c r="IJ1" s="62"/>
-      <c r="IK1" s="62"/>
-      <c r="IL1" s="62"/>
-      <c r="IM1" s="62"/>
-      <c r="IN1" s="62"/>
-      <c r="IO1" s="62"/>
-      <c r="IP1" s="62"/>
-      <c r="IQ1" s="62"/>
-      <c r="IR1" s="62"/>
-      <c r="IS1" s="62"/>
-      <c r="IT1" s="62"/>
-      <c r="IU1" s="62"/>
-      <c r="IV1" s="62"/>
-      <c r="IW1" s="62"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="63"/>
+      <c r="T1" s="63"/>
+      <c r="U1" s="63"/>
+      <c r="V1" s="63"/>
+      <c r="W1" s="63"/>
+      <c r="X1" s="63"/>
+      <c r="Y1" s="63"/>
+      <c r="Z1" s="63"/>
+      <c r="AA1" s="63"/>
+      <c r="AB1" s="63"/>
+      <c r="AC1" s="63"/>
+      <c r="AD1" s="63"/>
+      <c r="AE1" s="63"/>
+      <c r="AF1" s="63"/>
+      <c r="AG1" s="63"/>
+      <c r="AH1" s="63"/>
+      <c r="AI1" s="63"/>
+      <c r="AJ1" s="63"/>
+      <c r="AK1" s="63"/>
+      <c r="AL1" s="63"/>
+      <c r="AM1" s="63"/>
+      <c r="AN1" s="63"/>
+      <c r="AO1" s="63"/>
+      <c r="AP1" s="63"/>
+      <c r="AQ1" s="63"/>
+      <c r="AR1" s="63"/>
+      <c r="AS1" s="63"/>
+      <c r="AT1" s="63"/>
+      <c r="AU1" s="63"/>
+      <c r="AV1" s="63"/>
+      <c r="AW1" s="63"/>
+      <c r="AX1" s="63"/>
+      <c r="AY1" s="63"/>
+      <c r="AZ1" s="63"/>
+      <c r="BA1" s="63"/>
+      <c r="BB1" s="63"/>
+      <c r="BC1" s="63"/>
+      <c r="BD1" s="63"/>
+      <c r="BE1" s="63"/>
+      <c r="BF1" s="63"/>
+      <c r="BG1" s="63"/>
+      <c r="BH1" s="63"/>
+      <c r="BI1" s="63"/>
+      <c r="BJ1" s="63"/>
+      <c r="BK1" s="63"/>
+      <c r="BL1" s="63"/>
+      <c r="BM1" s="63"/>
+      <c r="BN1" s="63"/>
+      <c r="BO1" s="63"/>
+      <c r="BP1" s="63"/>
+      <c r="BQ1" s="63"/>
+      <c r="BR1" s="63"/>
+      <c r="BS1" s="63"/>
+      <c r="BT1" s="63"/>
+      <c r="BU1" s="63"/>
+      <c r="BV1" s="63"/>
+      <c r="BW1" s="63"/>
+      <c r="BX1" s="63"/>
+      <c r="BY1" s="63"/>
+      <c r="BZ1" s="63"/>
+      <c r="CA1" s="63"/>
+      <c r="CB1" s="63"/>
+      <c r="CC1" s="63"/>
+      <c r="CD1" s="63"/>
+      <c r="CE1" s="63"/>
+      <c r="CF1" s="63"/>
+      <c r="CG1" s="63"/>
+      <c r="CH1" s="63"/>
+      <c r="CI1" s="63"/>
+      <c r="CJ1" s="63"/>
+      <c r="CK1" s="63"/>
+      <c r="CL1" s="63"/>
+      <c r="CM1" s="63"/>
+      <c r="CN1" s="63"/>
+      <c r="CO1" s="63"/>
+      <c r="CP1" s="63"/>
+      <c r="CQ1" s="63"/>
+      <c r="CR1" s="63"/>
+      <c r="CS1" s="63"/>
+      <c r="CT1" s="63"/>
+      <c r="CU1" s="63"/>
+      <c r="CV1" s="63"/>
+      <c r="CW1" s="63"/>
+      <c r="CX1" s="63"/>
+      <c r="CY1" s="63"/>
+      <c r="CZ1" s="63"/>
+      <c r="DA1" s="63"/>
+      <c r="DB1" s="63"/>
+      <c r="DC1" s="63"/>
+      <c r="DD1" s="63"/>
+      <c r="DE1" s="63"/>
+      <c r="DF1" s="63"/>
+      <c r="DG1" s="63"/>
+      <c r="DH1" s="63"/>
+      <c r="DI1" s="63"/>
+      <c r="DJ1" s="63"/>
+      <c r="DK1" s="63"/>
+      <c r="DL1" s="63"/>
+      <c r="DM1" s="63"/>
+      <c r="DN1" s="63"/>
+      <c r="DO1" s="63"/>
+      <c r="DP1" s="63"/>
+      <c r="DQ1" s="63"/>
+      <c r="DR1" s="63"/>
+      <c r="DS1" s="63"/>
+      <c r="DT1" s="63"/>
+      <c r="DU1" s="63"/>
+      <c r="DV1" s="63"/>
+      <c r="DW1" s="63"/>
+      <c r="DX1" s="63"/>
+      <c r="DY1" s="63"/>
+      <c r="DZ1" s="63"/>
+      <c r="EA1" s="63"/>
+      <c r="EB1" s="63"/>
+      <c r="EC1" s="63"/>
+      <c r="ED1" s="63"/>
+      <c r="EE1" s="63"/>
+      <c r="EF1" s="63"/>
+      <c r="EG1" s="63"/>
+      <c r="EH1" s="63"/>
+      <c r="EI1" s="63"/>
+      <c r="EJ1" s="63"/>
+      <c r="EK1" s="63"/>
+      <c r="EL1" s="63"/>
+      <c r="EM1" s="63"/>
+      <c r="EN1" s="63"/>
+      <c r="EO1" s="63"/>
+      <c r="EP1" s="63"/>
+      <c r="EQ1" s="63"/>
+      <c r="ER1" s="63"/>
+      <c r="ES1" s="63"/>
+      <c r="ET1" s="63"/>
+      <c r="EU1" s="63"/>
+      <c r="EV1" s="63"/>
+      <c r="EW1" s="63"/>
+      <c r="EX1" s="63"/>
+      <c r="EY1" s="63"/>
+      <c r="EZ1" s="63"/>
+      <c r="FA1" s="63"/>
+      <c r="FB1" s="63"/>
+      <c r="FC1" s="63"/>
+      <c r="FD1" s="63"/>
+      <c r="FE1" s="63"/>
+      <c r="FF1" s="63"/>
+      <c r="FG1" s="63"/>
+      <c r="FH1" s="63"/>
+      <c r="FI1" s="63"/>
+      <c r="FJ1" s="63"/>
+      <c r="FK1" s="63"/>
+      <c r="FL1" s="63"/>
+      <c r="FM1" s="63"/>
+      <c r="FN1" s="63"/>
+      <c r="FO1" s="63"/>
+      <c r="FP1" s="63"/>
+      <c r="FQ1" s="63"/>
+      <c r="FR1" s="63"/>
+      <c r="FS1" s="63"/>
+      <c r="FT1" s="63"/>
+      <c r="FU1" s="63"/>
+      <c r="FV1" s="63"/>
+      <c r="FW1" s="63"/>
+      <c r="FX1" s="63"/>
+      <c r="FY1" s="63"/>
+      <c r="FZ1" s="63"/>
+      <c r="GA1" s="63"/>
+      <c r="GB1" s="63"/>
+      <c r="GC1" s="63"/>
+      <c r="GD1" s="63"/>
+      <c r="GE1" s="63"/>
+      <c r="GF1" s="63"/>
+      <c r="GG1" s="63"/>
+      <c r="GH1" s="63"/>
+      <c r="GI1" s="63"/>
+      <c r="GJ1" s="63"/>
+      <c r="GK1" s="63"/>
+      <c r="GL1" s="63"/>
+      <c r="GM1" s="63"/>
+      <c r="GN1" s="63"/>
+      <c r="GO1" s="63"/>
+      <c r="GP1" s="63"/>
+      <c r="GQ1" s="63"/>
+      <c r="GR1" s="63"/>
+      <c r="GS1" s="63"/>
+      <c r="GT1" s="63"/>
+      <c r="GU1" s="63"/>
+      <c r="GV1" s="63"/>
+      <c r="GW1" s="63"/>
+      <c r="GX1" s="63"/>
+      <c r="GY1" s="63"/>
+      <c r="GZ1" s="63"/>
+      <c r="HA1" s="63"/>
+      <c r="HB1" s="63"/>
+      <c r="HC1" s="63"/>
+      <c r="HD1" s="63"/>
+      <c r="HE1" s="63"/>
+      <c r="HF1" s="63"/>
+      <c r="HG1" s="63"/>
+      <c r="HH1" s="63"/>
+      <c r="HI1" s="63"/>
+      <c r="HJ1" s="63"/>
+      <c r="HK1" s="63"/>
+      <c r="HL1" s="63"/>
+      <c r="HM1" s="63"/>
+      <c r="HN1" s="63"/>
+      <c r="HO1" s="63"/>
+      <c r="HP1" s="63"/>
+      <c r="HQ1" s="63"/>
+      <c r="HR1" s="63"/>
+      <c r="HS1" s="63"/>
+      <c r="HT1" s="63"/>
+      <c r="HU1" s="63"/>
+      <c r="HV1" s="63"/>
+      <c r="HW1" s="63"/>
+      <c r="HX1" s="63"/>
+      <c r="HY1" s="63"/>
+      <c r="HZ1" s="63"/>
+      <c r="IA1" s="63"/>
+      <c r="IB1" s="63"/>
+      <c r="IC1" s="63"/>
+      <c r="ID1" s="63"/>
+      <c r="IE1" s="63"/>
+      <c r="IF1" s="63"/>
+      <c r="IG1" s="63"/>
+      <c r="IH1" s="63"/>
+      <c r="II1" s="63"/>
+      <c r="IJ1" s="63"/>
+      <c r="IK1" s="63"/>
+      <c r="IL1" s="63"/>
+      <c r="IM1" s="63"/>
+      <c r="IN1" s="63"/>
+      <c r="IO1" s="63"/>
+      <c r="IP1" s="63"/>
+      <c r="IQ1" s="63"/>
+      <c r="IR1" s="63"/>
+      <c r="IS1" s="63"/>
+      <c r="IT1" s="63"/>
+      <c r="IU1" s="63"/>
+      <c r="IV1" s="63"/>
+      <c r="IW1" s="63"/>
     </row>
     <row r="2" customFormat="false" ht="23.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="64" t="s">
-        <v>149</v>
-      </c>
-      <c r="B2" s="72" t="s">
+      <c r="A2" s="65" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="73" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="64" t="s">
+      <c r="C2" s="65" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="65" t="s">
         <v>151</v>
       </c>
-      <c r="D2" s="64" t="s">
+      <c r="E2" s="65" t="s">
         <v>152</v>
       </c>
-      <c r="E2" s="64" t="s">
-        <v>153</v>
-      </c>
-      <c r="F2" s="64" t="s">
-        <v>153</v>
-      </c>
-      <c r="G2" s="64" t="s">
+      <c r="F2" s="65" t="s">
+        <v>152</v>
+      </c>
+      <c r="G2" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="H2" s="65" t="s">
-        <v>142</v>
-      </c>
-      <c r="I2" s="66"/>
-      <c r="L2" s="63" t="s">
+      <c r="H2" s="66" t="s">
+        <v>141</v>
+      </c>
+      <c r="I2" s="67"/>
+      <c r="L2" s="64" t="s">
         <v>51</v>
       </c>
     </row>
@@ -10909,8 +11121,8 @@
       <c r="D3" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="E3" s="67" t="s">
-        <v>154</v>
+      <c r="E3" s="68" t="s">
+        <v>153</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>124</v>
@@ -10919,13 +11131,16 @@
         <v>57</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="I3" s="68"/>
+        <v>181</v>
+      </c>
+      <c r="I3" s="69"/>
     </row>
     <row r="4" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="69" t="s">
+      <c r="A4" s="70" t="s">
         <v>101</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>10</v>
@@ -10933,64 +11148,64 @@
       <c r="D4" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="E4" s="67" t="s">
-        <v>155</v>
-      </c>
-      <c r="F4" s="69" t="s">
-        <v>139</v>
-      </c>
-      <c r="H4" s="69" t="s">
+      <c r="E4" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="F4" s="70" t="s">
+        <v>138</v>
+      </c>
+      <c r="H4" s="70" t="s">
         <v>77</v>
       </c>
-      <c r="I4" s="68"/>
+      <c r="I4" s="69"/>
     </row>
     <row r="5" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="70" t="s">
+      <c r="A5" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="70" t="s">
+      <c r="C5" s="71" t="s">
         <v>24</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="E5" s="70" t="s">
-        <v>156</v>
+      <c r="E5" s="71" t="s">
+        <v>155</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="G5" s="65" t="s">
+      <c r="G5" s="66" t="s">
         <v>71</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="I5" s="71"/>
+        <v>167</v>
+      </c>
+      <c r="I5" s="72"/>
     </row>
     <row r="6" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="65" t="s">
+      <c r="B6" s="66" t="s">
         <v>48</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="70" t="s">
-        <v>157</v>
+      <c r="E6" s="71" t="s">
+        <v>156</v>
       </c>
       <c r="F6" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="G6" s="69" t="s">
+      <c r="G6" s="70" t="s">
         <v>84</v>
       </c>
       <c r="H6" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="I6" s="71"/>
+      <c r="I6" s="72"/>
     </row>
     <row r="7" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
@@ -11009,77 +11224,77 @@
         <v>104</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="H7" s="69" t="s">
-        <v>147</v>
-      </c>
-      <c r="I7" s="68"/>
+        <v>144</v>
+      </c>
+      <c r="H7" s="70" t="s">
+        <v>146</v>
+      </c>
+      <c r="I7" s="69"/>
     </row>
     <row r="8" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="70" t="s">
+      <c r="C8" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="70" t="s">
+      <c r="E8" s="71" t="s">
         <v>23</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G8" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="H8" s="69" t="s">
+      <c r="H8" s="70" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="75" t="s">
+      <c r="A9" s="76" t="s">
         <v>32</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="70" t="s">
-        <v>167</v>
-      </c>
-      <c r="G9" s="74"/>
-      <c r="H9" s="75" t="s">
+      <c r="E9" s="71" t="s">
+        <v>166</v>
+      </c>
+      <c r="G9" s="75"/>
+      <c r="H9" s="76" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="75" t="s">
+      <c r="A10" s="76" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="70" t="s">
+      <c r="E10" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="76" t="s">
-        <v>158</v>
-      </c>
-      <c r="G10" s="65"/>
+      <c r="F10" s="77" t="s">
+        <v>157</v>
+      </c>
+      <c r="G10" s="66"/>
     </row>
     <row r="11" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C11" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="72" t="s">
-        <v>159</v>
-      </c>
-      <c r="E11" s="75" t="s">
-        <v>172</v>
-      </c>
-      <c r="F11" s="69" t="s">
+      <c r="D11" s="73" t="s">
+        <v>158</v>
+      </c>
+      <c r="E11" s="76" t="s">
+        <v>171</v>
+      </c>
+      <c r="F11" s="70" t="s">
         <v>116</v>
       </c>
-      <c r="H11" s="77"/>
+      <c r="H11" s="78"/>
     </row>
     <row r="12" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C12" s="13" t="s">
@@ -11088,35 +11303,35 @@
       <c r="D12" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="E12" s="75" t="s">
+      <c r="E12" s="76" t="s">
         <v>27</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="77"/>
-      <c r="H12" s="69"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="70"/>
     </row>
     <row r="13" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="65" t="s">
+      <c r="A13" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="B13" s="64" t="s">
-        <v>164</v>
+      <c r="B13" s="65" t="s">
+        <v>163</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="70" t="s">
+      <c r="D13" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="E13" s="67" t="s">
+      <c r="E13" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="F13" s="75" t="s">
+      <c r="F13" s="76" t="s">
         <v>41</v>
       </c>
-      <c r="H13" s="69"/>
+      <c r="H13" s="70"/>
     </row>
     <row r="14" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
@@ -11125,392 +11340,1337 @@
       <c r="B14" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="75" t="s">
+      <c r="C14" s="76" t="s">
+        <v>183</v>
+      </c>
+      <c r="D14" s="76" t="s">
         <v>184</v>
       </c>
-      <c r="E14" s="75" t="s">
+      <c r="E14" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="H14" s="78" t="s">
+      <c r="H14" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="I14" s="80" t="s">
         <v>161</v>
       </c>
-      <c r="I14" s="79" t="s">
+      <c r="L14" s="61" t="s">
         <v>162</v>
       </c>
-      <c r="L14" s="60" t="s">
-        <v>163</v>
-      </c>
     </row>
     <row r="15" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C15" s="75" t="s">
-        <v>185</v>
-      </c>
-      <c r="D15" s="75" t="s">
+      <c r="C15" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="76" t="s">
+        <v>164</v>
+      </c>
+      <c r="E15" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" s="81" t="s">
+        <v>127</v>
+      </c>
+      <c r="I15" s="82" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C16" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="66" t="s">
         <v>165</v>
       </c>
-      <c r="E15" s="67" t="s">
-        <v>35</v>
-      </c>
-      <c r="H15" s="80" t="s">
-        <v>127</v>
-      </c>
-      <c r="I15" s="81" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C16" s="67" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="75" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" s="65" t="s">
-        <v>166</v>
-      </c>
-      <c r="H16" s="80" t="s">
+      <c r="H16" s="81" t="s">
         <v>52</v>
       </c>
-      <c r="I16" s="81" t="s">
-        <v>144</v>
+      <c r="I16" s="82" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C17" s="67" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="67" t="s">
+      <c r="E17" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="F17" s="69" t="s">
+      <c r="F17" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="92" t="s">
+      <c r="H17" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="I17" s="81" t="s">
+      <c r="I17" s="82" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H18" s="92" t="s">
+      <c r="H18" s="93" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="H19" s="80"/>
+      <c r="H19" s="81"/>
     </row>
     <row r="20" customFormat="false" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="82"/>
-      <c r="B20" s="82"/>
-      <c r="C20" s="82"/>
-      <c r="D20" s="82"/>
-      <c r="E20" s="82"/>
-      <c r="F20" s="82"/>
-      <c r="G20" s="82"/>
-      <c r="H20" s="80"/>
-      <c r="I20" s="82"/>
-      <c r="J20" s="83"/>
-      <c r="O20" s="82"/>
-      <c r="P20" s="82"/>
-      <c r="Q20" s="82"/>
-      <c r="R20" s="82"/>
-      <c r="S20" s="82"/>
-      <c r="T20" s="82"/>
-      <c r="U20" s="82"/>
-      <c r="V20" s="82"/>
-      <c r="W20" s="82"/>
-      <c r="X20" s="82"/>
-      <c r="Y20" s="82"/>
-      <c r="Z20" s="82"/>
-      <c r="AA20" s="82"/>
-      <c r="AB20" s="82"/>
-      <c r="AC20" s="82"/>
-      <c r="AD20" s="82"/>
-      <c r="AE20" s="82"/>
-      <c r="AF20" s="82"/>
-      <c r="AG20" s="82"/>
-      <c r="AH20" s="82"/>
-      <c r="AI20" s="82"/>
-      <c r="AJ20" s="82"/>
-      <c r="AK20" s="82"/>
-      <c r="AL20" s="82"/>
-      <c r="AM20" s="82"/>
-      <c r="AN20" s="82"/>
-      <c r="AO20" s="82"/>
-      <c r="AP20" s="82"/>
-      <c r="AQ20" s="82"/>
-      <c r="AR20" s="82"/>
-      <c r="AS20" s="82"/>
-      <c r="AT20" s="82"/>
-      <c r="AU20" s="82"/>
-      <c r="AV20" s="82"/>
-      <c r="AW20" s="82"/>
-      <c r="AX20" s="82"/>
-      <c r="AY20" s="82"/>
-      <c r="AZ20" s="82"/>
-      <c r="BA20" s="82"/>
-      <c r="BB20" s="82"/>
-      <c r="BC20" s="82"/>
-      <c r="BD20" s="82"/>
-      <c r="BE20" s="82"/>
-      <c r="BF20" s="82"/>
-      <c r="BG20" s="82"/>
-      <c r="BH20" s="82"/>
-      <c r="BI20" s="82"/>
-      <c r="BJ20" s="82"/>
-      <c r="BK20" s="82"/>
-      <c r="BL20" s="82"/>
-      <c r="BM20" s="82"/>
-      <c r="BN20" s="82"/>
-      <c r="BO20" s="82"/>
-      <c r="BP20" s="82"/>
-      <c r="BQ20" s="82"/>
-      <c r="BR20" s="82"/>
-      <c r="BS20" s="82"/>
-      <c r="BT20" s="82"/>
-      <c r="BU20" s="82"/>
-      <c r="BV20" s="82"/>
-      <c r="BW20" s="82"/>
-      <c r="BX20" s="82"/>
-      <c r="BY20" s="82"/>
-      <c r="BZ20" s="82"/>
-      <c r="CA20" s="82"/>
-      <c r="CB20" s="82"/>
-      <c r="CC20" s="82"/>
-      <c r="CD20" s="82"/>
-      <c r="CE20" s="82"/>
-      <c r="CF20" s="82"/>
-      <c r="CG20" s="82"/>
-      <c r="CH20" s="82"/>
-      <c r="CI20" s="82"/>
-      <c r="CJ20" s="82"/>
-      <c r="CK20" s="82"/>
-      <c r="CL20" s="82"/>
-      <c r="CM20" s="82"/>
-      <c r="CN20" s="82"/>
-      <c r="CO20" s="82"/>
-      <c r="CP20" s="82"/>
-      <c r="CQ20" s="82"/>
-      <c r="CR20" s="82"/>
-      <c r="CS20" s="82"/>
-      <c r="CT20" s="82"/>
-      <c r="CU20" s="82"/>
-      <c r="CV20" s="82"/>
-      <c r="CW20" s="82"/>
-      <c r="CX20" s="82"/>
-      <c r="CY20" s="82"/>
-      <c r="CZ20" s="82"/>
-      <c r="DA20" s="82"/>
-      <c r="DB20" s="82"/>
-      <c r="DC20" s="82"/>
-      <c r="DD20" s="82"/>
-      <c r="DE20" s="82"/>
-      <c r="DF20" s="82"/>
-      <c r="DG20" s="82"/>
-      <c r="DH20" s="82"/>
-      <c r="DI20" s="82"/>
-      <c r="DJ20" s="82"/>
-      <c r="DK20" s="82"/>
-      <c r="DL20" s="82"/>
-      <c r="DM20" s="82"/>
-      <c r="DN20" s="82"/>
-      <c r="DO20" s="82"/>
-      <c r="DP20" s="82"/>
-      <c r="DQ20" s="82"/>
-      <c r="DR20" s="82"/>
-      <c r="DS20" s="82"/>
-      <c r="DT20" s="82"/>
-      <c r="DU20" s="82"/>
-      <c r="DV20" s="82"/>
-      <c r="DW20" s="82"/>
-      <c r="DX20" s="82"/>
-      <c r="DY20" s="82"/>
-      <c r="DZ20" s="82"/>
-      <c r="EA20" s="82"/>
-      <c r="EB20" s="82"/>
-      <c r="EC20" s="82"/>
-      <c r="ED20" s="82"/>
-      <c r="EE20" s="82"/>
-      <c r="EF20" s="82"/>
-      <c r="EG20" s="82"/>
-      <c r="EH20" s="82"/>
-      <c r="EI20" s="82"/>
-      <c r="EJ20" s="82"/>
-      <c r="EK20" s="82"/>
-      <c r="EL20" s="82"/>
-      <c r="EM20" s="82"/>
-      <c r="EN20" s="82"/>
-      <c r="EO20" s="82"/>
-      <c r="EP20" s="82"/>
-      <c r="EQ20" s="82"/>
-      <c r="ER20" s="82"/>
-      <c r="ES20" s="82"/>
-      <c r="ET20" s="82"/>
-      <c r="EU20" s="82"/>
-      <c r="EV20" s="82"/>
-      <c r="EW20" s="82"/>
-      <c r="EX20" s="82"/>
-      <c r="EY20" s="82"/>
-      <c r="EZ20" s="82"/>
-      <c r="FA20" s="82"/>
-      <c r="FB20" s="82"/>
-      <c r="FC20" s="82"/>
-      <c r="FD20" s="82"/>
-      <c r="FE20" s="82"/>
-      <c r="FF20" s="82"/>
-      <c r="FG20" s="82"/>
-      <c r="FH20" s="82"/>
-      <c r="FI20" s="82"/>
-      <c r="FJ20" s="82"/>
-      <c r="FK20" s="82"/>
-      <c r="FL20" s="82"/>
-      <c r="FM20" s="82"/>
-      <c r="FN20" s="82"/>
-      <c r="FO20" s="82"/>
-      <c r="FP20" s="82"/>
-      <c r="FQ20" s="82"/>
-      <c r="FR20" s="82"/>
-      <c r="FS20" s="82"/>
-      <c r="FT20" s="82"/>
-      <c r="FU20" s="82"/>
-      <c r="FV20" s="82"/>
-      <c r="FW20" s="82"/>
-      <c r="FX20" s="82"/>
-      <c r="FY20" s="82"/>
-      <c r="FZ20" s="82"/>
-      <c r="GA20" s="82"/>
-      <c r="GB20" s="82"/>
-      <c r="GC20" s="82"/>
-      <c r="GD20" s="82"/>
-      <c r="GE20" s="82"/>
-      <c r="GF20" s="82"/>
-      <c r="GG20" s="82"/>
-      <c r="GH20" s="82"/>
-      <c r="GI20" s="82"/>
-      <c r="GJ20" s="82"/>
-      <c r="GK20" s="82"/>
-      <c r="GL20" s="82"/>
-      <c r="GM20" s="82"/>
-      <c r="GN20" s="82"/>
-      <c r="GO20" s="82"/>
-      <c r="GP20" s="82"/>
-      <c r="GQ20" s="82"/>
-      <c r="GR20" s="82"/>
-      <c r="GS20" s="82"/>
-      <c r="GT20" s="82"/>
-      <c r="GU20" s="82"/>
-      <c r="GV20" s="82"/>
-      <c r="GW20" s="82"/>
-      <c r="GX20" s="82"/>
-      <c r="GY20" s="82"/>
-      <c r="GZ20" s="82"/>
-      <c r="HA20" s="82"/>
-      <c r="HB20" s="82"/>
-      <c r="HC20" s="82"/>
-      <c r="HD20" s="82"/>
-      <c r="HE20" s="82"/>
-      <c r="HF20" s="82"/>
-      <c r="HG20" s="82"/>
-      <c r="HH20" s="82"/>
-      <c r="HI20" s="82"/>
-      <c r="HJ20" s="82"/>
-      <c r="HK20" s="82"/>
-      <c r="HL20" s="82"/>
-      <c r="HM20" s="82"/>
-      <c r="HN20" s="82"/>
-      <c r="HO20" s="82"/>
-      <c r="HP20" s="82"/>
-      <c r="HQ20" s="82"/>
-      <c r="HR20" s="82"/>
-      <c r="HS20" s="82"/>
-      <c r="HT20" s="82"/>
-      <c r="HU20" s="82"/>
-      <c r="HV20" s="82"/>
-      <c r="HW20" s="82"/>
-      <c r="HX20" s="82"/>
-      <c r="HY20" s="82"/>
-      <c r="HZ20" s="82"/>
-      <c r="IA20" s="82"/>
-      <c r="IB20" s="82"/>
-      <c r="IC20" s="82"/>
-      <c r="ID20" s="82"/>
-      <c r="IE20" s="82"/>
-      <c r="IF20" s="82"/>
-      <c r="IG20" s="82"/>
-      <c r="IH20" s="82"/>
-      <c r="II20" s="82"/>
-      <c r="IJ20" s="82"/>
-      <c r="IK20" s="82"/>
-      <c r="IL20" s="82"/>
-      <c r="IM20" s="82"/>
-      <c r="IN20" s="82"/>
-      <c r="IO20" s="82"/>
-      <c r="IP20" s="82"/>
-      <c r="IQ20" s="82"/>
-      <c r="IR20" s="82"/>
-      <c r="IS20" s="82"/>
-      <c r="IT20" s="82"/>
-      <c r="IU20" s="82"/>
-      <c r="IV20" s="82"/>
-      <c r="IW20" s="82"/>
+      <c r="A20" s="83"/>
+      <c r="B20" s="83"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="83"/>
+      <c r="J20" s="84"/>
+      <c r="O20" s="83"/>
+      <c r="P20" s="83"/>
+      <c r="Q20" s="83"/>
+      <c r="R20" s="83"/>
+      <c r="S20" s="83"/>
+      <c r="T20" s="83"/>
+      <c r="U20" s="83"/>
+      <c r="V20" s="83"/>
+      <c r="W20" s="83"/>
+      <c r="X20" s="83"/>
+      <c r="Y20" s="83"/>
+      <c r="Z20" s="83"/>
+      <c r="AA20" s="83"/>
+      <c r="AB20" s="83"/>
+      <c r="AC20" s="83"/>
+      <c r="AD20" s="83"/>
+      <c r="AE20" s="83"/>
+      <c r="AF20" s="83"/>
+      <c r="AG20" s="83"/>
+      <c r="AH20" s="83"/>
+      <c r="AI20" s="83"/>
+      <c r="AJ20" s="83"/>
+      <c r="AK20" s="83"/>
+      <c r="AL20" s="83"/>
+      <c r="AM20" s="83"/>
+      <c r="AN20" s="83"/>
+      <c r="AO20" s="83"/>
+      <c r="AP20" s="83"/>
+      <c r="AQ20" s="83"/>
+      <c r="AR20" s="83"/>
+      <c r="AS20" s="83"/>
+      <c r="AT20" s="83"/>
+      <c r="AU20" s="83"/>
+      <c r="AV20" s="83"/>
+      <c r="AW20" s="83"/>
+      <c r="AX20" s="83"/>
+      <c r="AY20" s="83"/>
+      <c r="AZ20" s="83"/>
+      <c r="BA20" s="83"/>
+      <c r="BB20" s="83"/>
+      <c r="BC20" s="83"/>
+      <c r="BD20" s="83"/>
+      <c r="BE20" s="83"/>
+      <c r="BF20" s="83"/>
+      <c r="BG20" s="83"/>
+      <c r="BH20" s="83"/>
+      <c r="BI20" s="83"/>
+      <c r="BJ20" s="83"/>
+      <c r="BK20" s="83"/>
+      <c r="BL20" s="83"/>
+      <c r="BM20" s="83"/>
+      <c r="BN20" s="83"/>
+      <c r="BO20" s="83"/>
+      <c r="BP20" s="83"/>
+      <c r="BQ20" s="83"/>
+      <c r="BR20" s="83"/>
+      <c r="BS20" s="83"/>
+      <c r="BT20" s="83"/>
+      <c r="BU20" s="83"/>
+      <c r="BV20" s="83"/>
+      <c r="BW20" s="83"/>
+      <c r="BX20" s="83"/>
+      <c r="BY20" s="83"/>
+      <c r="BZ20" s="83"/>
+      <c r="CA20" s="83"/>
+      <c r="CB20" s="83"/>
+      <c r="CC20" s="83"/>
+      <c r="CD20" s="83"/>
+      <c r="CE20" s="83"/>
+      <c r="CF20" s="83"/>
+      <c r="CG20" s="83"/>
+      <c r="CH20" s="83"/>
+      <c r="CI20" s="83"/>
+      <c r="CJ20" s="83"/>
+      <c r="CK20" s="83"/>
+      <c r="CL20" s="83"/>
+      <c r="CM20" s="83"/>
+      <c r="CN20" s="83"/>
+      <c r="CO20" s="83"/>
+      <c r="CP20" s="83"/>
+      <c r="CQ20" s="83"/>
+      <c r="CR20" s="83"/>
+      <c r="CS20" s="83"/>
+      <c r="CT20" s="83"/>
+      <c r="CU20" s="83"/>
+      <c r="CV20" s="83"/>
+      <c r="CW20" s="83"/>
+      <c r="CX20" s="83"/>
+      <c r="CY20" s="83"/>
+      <c r="CZ20" s="83"/>
+      <c r="DA20" s="83"/>
+      <c r="DB20" s="83"/>
+      <c r="DC20" s="83"/>
+      <c r="DD20" s="83"/>
+      <c r="DE20" s="83"/>
+      <c r="DF20" s="83"/>
+      <c r="DG20" s="83"/>
+      <c r="DH20" s="83"/>
+      <c r="DI20" s="83"/>
+      <c r="DJ20" s="83"/>
+      <c r="DK20" s="83"/>
+      <c r="DL20" s="83"/>
+      <c r="DM20" s="83"/>
+      <c r="DN20" s="83"/>
+      <c r="DO20" s="83"/>
+      <c r="DP20" s="83"/>
+      <c r="DQ20" s="83"/>
+      <c r="DR20" s="83"/>
+      <c r="DS20" s="83"/>
+      <c r="DT20" s="83"/>
+      <c r="DU20" s="83"/>
+      <c r="DV20" s="83"/>
+      <c r="DW20" s="83"/>
+      <c r="DX20" s="83"/>
+      <c r="DY20" s="83"/>
+      <c r="DZ20" s="83"/>
+      <c r="EA20" s="83"/>
+      <c r="EB20" s="83"/>
+      <c r="EC20" s="83"/>
+      <c r="ED20" s="83"/>
+      <c r="EE20" s="83"/>
+      <c r="EF20" s="83"/>
+      <c r="EG20" s="83"/>
+      <c r="EH20" s="83"/>
+      <c r="EI20" s="83"/>
+      <c r="EJ20" s="83"/>
+      <c r="EK20" s="83"/>
+      <c r="EL20" s="83"/>
+      <c r="EM20" s="83"/>
+      <c r="EN20" s="83"/>
+      <c r="EO20" s="83"/>
+      <c r="EP20" s="83"/>
+      <c r="EQ20" s="83"/>
+      <c r="ER20" s="83"/>
+      <c r="ES20" s="83"/>
+      <c r="ET20" s="83"/>
+      <c r="EU20" s="83"/>
+      <c r="EV20" s="83"/>
+      <c r="EW20" s="83"/>
+      <c r="EX20" s="83"/>
+      <c r="EY20" s="83"/>
+      <c r="EZ20" s="83"/>
+      <c r="FA20" s="83"/>
+      <c r="FB20" s="83"/>
+      <c r="FC20" s="83"/>
+      <c r="FD20" s="83"/>
+      <c r="FE20" s="83"/>
+      <c r="FF20" s="83"/>
+      <c r="FG20" s="83"/>
+      <c r="FH20" s="83"/>
+      <c r="FI20" s="83"/>
+      <c r="FJ20" s="83"/>
+      <c r="FK20" s="83"/>
+      <c r="FL20" s="83"/>
+      <c r="FM20" s="83"/>
+      <c r="FN20" s="83"/>
+      <c r="FO20" s="83"/>
+      <c r="FP20" s="83"/>
+      <c r="FQ20" s="83"/>
+      <c r="FR20" s="83"/>
+      <c r="FS20" s="83"/>
+      <c r="FT20" s="83"/>
+      <c r="FU20" s="83"/>
+      <c r="FV20" s="83"/>
+      <c r="FW20" s="83"/>
+      <c r="FX20" s="83"/>
+      <c r="FY20" s="83"/>
+      <c r="FZ20" s="83"/>
+      <c r="GA20" s="83"/>
+      <c r="GB20" s="83"/>
+      <c r="GC20" s="83"/>
+      <c r="GD20" s="83"/>
+      <c r="GE20" s="83"/>
+      <c r="GF20" s="83"/>
+      <c r="GG20" s="83"/>
+      <c r="GH20" s="83"/>
+      <c r="GI20" s="83"/>
+      <c r="GJ20" s="83"/>
+      <c r="GK20" s="83"/>
+      <c r="GL20" s="83"/>
+      <c r="GM20" s="83"/>
+      <c r="GN20" s="83"/>
+      <c r="GO20" s="83"/>
+      <c r="GP20" s="83"/>
+      <c r="GQ20" s="83"/>
+      <c r="GR20" s="83"/>
+      <c r="GS20" s="83"/>
+      <c r="GT20" s="83"/>
+      <c r="GU20" s="83"/>
+      <c r="GV20" s="83"/>
+      <c r="GW20" s="83"/>
+      <c r="GX20" s="83"/>
+      <c r="GY20" s="83"/>
+      <c r="GZ20" s="83"/>
+      <c r="HA20" s="83"/>
+      <c r="HB20" s="83"/>
+      <c r="HC20" s="83"/>
+      <c r="HD20" s="83"/>
+      <c r="HE20" s="83"/>
+      <c r="HF20" s="83"/>
+      <c r="HG20" s="83"/>
+      <c r="HH20" s="83"/>
+      <c r="HI20" s="83"/>
+      <c r="HJ20" s="83"/>
+      <c r="HK20" s="83"/>
+      <c r="HL20" s="83"/>
+      <c r="HM20" s="83"/>
+      <c r="HN20" s="83"/>
+      <c r="HO20" s="83"/>
+      <c r="HP20" s="83"/>
+      <c r="HQ20" s="83"/>
+      <c r="HR20" s="83"/>
+      <c r="HS20" s="83"/>
+      <c r="HT20" s="83"/>
+      <c r="HU20" s="83"/>
+      <c r="HV20" s="83"/>
+      <c r="HW20" s="83"/>
+      <c r="HX20" s="83"/>
+      <c r="HY20" s="83"/>
+      <c r="HZ20" s="83"/>
+      <c r="IA20" s="83"/>
+      <c r="IB20" s="83"/>
+      <c r="IC20" s="83"/>
+      <c r="ID20" s="83"/>
+      <c r="IE20" s="83"/>
+      <c r="IF20" s="83"/>
+      <c r="IG20" s="83"/>
+      <c r="IH20" s="83"/>
+      <c r="II20" s="83"/>
+      <c r="IJ20" s="83"/>
+      <c r="IK20" s="83"/>
+      <c r="IL20" s="83"/>
+      <c r="IM20" s="83"/>
+      <c r="IN20" s="83"/>
+      <c r="IO20" s="83"/>
+      <c r="IP20" s="83"/>
+      <c r="IQ20" s="83"/>
+      <c r="IR20" s="83"/>
+      <c r="IS20" s="83"/>
+      <c r="IT20" s="83"/>
+      <c r="IU20" s="83"/>
+      <c r="IV20" s="83"/>
+      <c r="IW20" s="83"/>
     </row>
     <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="82"/>
-      <c r="G21" s="84"/>
-      <c r="H21" s="80"/>
-      <c r="I21" s="81"/>
-      <c r="J21" s="85" t="s">
+      <c r="B21" s="83"/>
+      <c r="G21" s="85"/>
+      <c r="H21" s="81"/>
+      <c r="I21" s="82"/>
+      <c r="J21" s="86" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="87"/>
+      <c r="G22" s="87"/>
+      <c r="H22" s="81"/>
+      <c r="I22" s="82"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="82"/>
+      <c r="R23" s="88"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="82"/>
+      <c r="L24" s="61" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="86"/>
-      <c r="G22" s="86"/>
-      <c r="H22" s="80"/>
-      <c r="I22" s="81"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I23" s="81"/>
-      <c r="R23" s="87"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I24" s="81"/>
-      <c r="L24" s="60" t="s">
-        <v>170</v>
-      </c>
-    </row>
     <row r="25" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I25" s="81"/>
+      <c r="I25" s="82"/>
     </row>
     <row r="26" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="3"/>
-      <c r="I26" s="81"/>
+      <c r="I26" s="82"/>
     </row>
     <row r="28" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D28" s="88"/>
+      <c r="D28" s="89"/>
     </row>
     <row r="29" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="89" t="s">
+      <c r="A29" s="90" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="90" t="s">
         <v>179</v>
       </c>
     </row>
+    <row r="31" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="90" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="81" t="s">
+        <v>175</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:IW32"/>
+  <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="12.55" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="61" width="12.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="61" width="12.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="61" width="14.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="61" width="12.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="61" width="17.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="61" width="15.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="61" width="13.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="61" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="61" width="14.55"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="10" min="10" style="61" width="9.1"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="11" style="61" width="9.1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="26.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="62" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="64" t="s">
+        <v>46</v>
+      </c>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="63"/>
+      <c r="T1" s="63"/>
+      <c r="U1" s="63"/>
+      <c r="V1" s="63"/>
+      <c r="W1" s="63"/>
+      <c r="X1" s="63"/>
+      <c r="Y1" s="63"/>
+      <c r="Z1" s="63"/>
+      <c r="AA1" s="63"/>
+      <c r="AB1" s="63"/>
+      <c r="AC1" s="63"/>
+      <c r="AD1" s="63"/>
+      <c r="AE1" s="63"/>
+      <c r="AF1" s="63"/>
+      <c r="AG1" s="63"/>
+      <c r="AH1" s="63"/>
+      <c r="AI1" s="63"/>
+      <c r="AJ1" s="63"/>
+      <c r="AK1" s="63"/>
+      <c r="AL1" s="63"/>
+      <c r="AM1" s="63"/>
+      <c r="AN1" s="63"/>
+      <c r="AO1" s="63"/>
+      <c r="AP1" s="63"/>
+      <c r="AQ1" s="63"/>
+      <c r="AR1" s="63"/>
+      <c r="AS1" s="63"/>
+      <c r="AT1" s="63"/>
+      <c r="AU1" s="63"/>
+      <c r="AV1" s="63"/>
+      <c r="AW1" s="63"/>
+      <c r="AX1" s="63"/>
+      <c r="AY1" s="63"/>
+      <c r="AZ1" s="63"/>
+      <c r="BA1" s="63"/>
+      <c r="BB1" s="63"/>
+      <c r="BC1" s="63"/>
+      <c r="BD1" s="63"/>
+      <c r="BE1" s="63"/>
+      <c r="BF1" s="63"/>
+      <c r="BG1" s="63"/>
+      <c r="BH1" s="63"/>
+      <c r="BI1" s="63"/>
+      <c r="BJ1" s="63"/>
+      <c r="BK1" s="63"/>
+      <c r="BL1" s="63"/>
+      <c r="BM1" s="63"/>
+      <c r="BN1" s="63"/>
+      <c r="BO1" s="63"/>
+      <c r="BP1" s="63"/>
+      <c r="BQ1" s="63"/>
+      <c r="BR1" s="63"/>
+      <c r="BS1" s="63"/>
+      <c r="BT1" s="63"/>
+      <c r="BU1" s="63"/>
+      <c r="BV1" s="63"/>
+      <c r="BW1" s="63"/>
+      <c r="BX1" s="63"/>
+      <c r="BY1" s="63"/>
+      <c r="BZ1" s="63"/>
+      <c r="CA1" s="63"/>
+      <c r="CB1" s="63"/>
+      <c r="CC1" s="63"/>
+      <c r="CD1" s="63"/>
+      <c r="CE1" s="63"/>
+      <c r="CF1" s="63"/>
+      <c r="CG1" s="63"/>
+      <c r="CH1" s="63"/>
+      <c r="CI1" s="63"/>
+      <c r="CJ1" s="63"/>
+      <c r="CK1" s="63"/>
+      <c r="CL1" s="63"/>
+      <c r="CM1" s="63"/>
+      <c r="CN1" s="63"/>
+      <c r="CO1" s="63"/>
+      <c r="CP1" s="63"/>
+      <c r="CQ1" s="63"/>
+      <c r="CR1" s="63"/>
+      <c r="CS1" s="63"/>
+      <c r="CT1" s="63"/>
+      <c r="CU1" s="63"/>
+      <c r="CV1" s="63"/>
+      <c r="CW1" s="63"/>
+      <c r="CX1" s="63"/>
+      <c r="CY1" s="63"/>
+      <c r="CZ1" s="63"/>
+      <c r="DA1" s="63"/>
+      <c r="DB1" s="63"/>
+      <c r="DC1" s="63"/>
+      <c r="DD1" s="63"/>
+      <c r="DE1" s="63"/>
+      <c r="DF1" s="63"/>
+      <c r="DG1" s="63"/>
+      <c r="DH1" s="63"/>
+      <c r="DI1" s="63"/>
+      <c r="DJ1" s="63"/>
+      <c r="DK1" s="63"/>
+      <c r="DL1" s="63"/>
+      <c r="DM1" s="63"/>
+      <c r="DN1" s="63"/>
+      <c r="DO1" s="63"/>
+      <c r="DP1" s="63"/>
+      <c r="DQ1" s="63"/>
+      <c r="DR1" s="63"/>
+      <c r="DS1" s="63"/>
+      <c r="DT1" s="63"/>
+      <c r="DU1" s="63"/>
+      <c r="DV1" s="63"/>
+      <c r="DW1" s="63"/>
+      <c r="DX1" s="63"/>
+      <c r="DY1" s="63"/>
+      <c r="DZ1" s="63"/>
+      <c r="EA1" s="63"/>
+      <c r="EB1" s="63"/>
+      <c r="EC1" s="63"/>
+      <c r="ED1" s="63"/>
+      <c r="EE1" s="63"/>
+      <c r="EF1" s="63"/>
+      <c r="EG1" s="63"/>
+      <c r="EH1" s="63"/>
+      <c r="EI1" s="63"/>
+      <c r="EJ1" s="63"/>
+      <c r="EK1" s="63"/>
+      <c r="EL1" s="63"/>
+      <c r="EM1" s="63"/>
+      <c r="EN1" s="63"/>
+      <c r="EO1" s="63"/>
+      <c r="EP1" s="63"/>
+      <c r="EQ1" s="63"/>
+      <c r="ER1" s="63"/>
+      <c r="ES1" s="63"/>
+      <c r="ET1" s="63"/>
+      <c r="EU1" s="63"/>
+      <c r="EV1" s="63"/>
+      <c r="EW1" s="63"/>
+      <c r="EX1" s="63"/>
+      <c r="EY1" s="63"/>
+      <c r="EZ1" s="63"/>
+      <c r="FA1" s="63"/>
+      <c r="FB1" s="63"/>
+      <c r="FC1" s="63"/>
+      <c r="FD1" s="63"/>
+      <c r="FE1" s="63"/>
+      <c r="FF1" s="63"/>
+      <c r="FG1" s="63"/>
+      <c r="FH1" s="63"/>
+      <c r="FI1" s="63"/>
+      <c r="FJ1" s="63"/>
+      <c r="FK1" s="63"/>
+      <c r="FL1" s="63"/>
+      <c r="FM1" s="63"/>
+      <c r="FN1" s="63"/>
+      <c r="FO1" s="63"/>
+      <c r="FP1" s="63"/>
+      <c r="FQ1" s="63"/>
+      <c r="FR1" s="63"/>
+      <c r="FS1" s="63"/>
+      <c r="FT1" s="63"/>
+      <c r="FU1" s="63"/>
+      <c r="FV1" s="63"/>
+      <c r="FW1" s="63"/>
+      <c r="FX1" s="63"/>
+      <c r="FY1" s="63"/>
+      <c r="FZ1" s="63"/>
+      <c r="GA1" s="63"/>
+      <c r="GB1" s="63"/>
+      <c r="GC1" s="63"/>
+      <c r="GD1" s="63"/>
+      <c r="GE1" s="63"/>
+      <c r="GF1" s="63"/>
+      <c r="GG1" s="63"/>
+      <c r="GH1" s="63"/>
+      <c r="GI1" s="63"/>
+      <c r="GJ1" s="63"/>
+      <c r="GK1" s="63"/>
+      <c r="GL1" s="63"/>
+      <c r="GM1" s="63"/>
+      <c r="GN1" s="63"/>
+      <c r="GO1" s="63"/>
+      <c r="GP1" s="63"/>
+      <c r="GQ1" s="63"/>
+      <c r="GR1" s="63"/>
+      <c r="GS1" s="63"/>
+      <c r="GT1" s="63"/>
+      <c r="GU1" s="63"/>
+      <c r="GV1" s="63"/>
+      <c r="GW1" s="63"/>
+      <c r="GX1" s="63"/>
+      <c r="GY1" s="63"/>
+      <c r="GZ1" s="63"/>
+      <c r="HA1" s="63"/>
+      <c r="HB1" s="63"/>
+      <c r="HC1" s="63"/>
+      <c r="HD1" s="63"/>
+      <c r="HE1" s="63"/>
+      <c r="HF1" s="63"/>
+      <c r="HG1" s="63"/>
+      <c r="HH1" s="63"/>
+      <c r="HI1" s="63"/>
+      <c r="HJ1" s="63"/>
+      <c r="HK1" s="63"/>
+      <c r="HL1" s="63"/>
+      <c r="HM1" s="63"/>
+      <c r="HN1" s="63"/>
+      <c r="HO1" s="63"/>
+      <c r="HP1" s="63"/>
+      <c r="HQ1" s="63"/>
+      <c r="HR1" s="63"/>
+      <c r="HS1" s="63"/>
+      <c r="HT1" s="63"/>
+      <c r="HU1" s="63"/>
+      <c r="HV1" s="63"/>
+      <c r="HW1" s="63"/>
+      <c r="HX1" s="63"/>
+      <c r="HY1" s="63"/>
+      <c r="HZ1" s="63"/>
+      <c r="IA1" s="63"/>
+      <c r="IB1" s="63"/>
+      <c r="IC1" s="63"/>
+      <c r="ID1" s="63"/>
+      <c r="IE1" s="63"/>
+      <c r="IF1" s="63"/>
+      <c r="IG1" s="63"/>
+      <c r="IH1" s="63"/>
+      <c r="II1" s="63"/>
+      <c r="IJ1" s="63"/>
+      <c r="IK1" s="63"/>
+      <c r="IL1" s="63"/>
+      <c r="IM1" s="63"/>
+      <c r="IN1" s="63"/>
+      <c r="IO1" s="63"/>
+      <c r="IP1" s="63"/>
+      <c r="IQ1" s="63"/>
+      <c r="IR1" s="63"/>
+      <c r="IS1" s="63"/>
+      <c r="IT1" s="63"/>
+      <c r="IU1" s="63"/>
+      <c r="IV1" s="63"/>
+      <c r="IW1" s="63"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="65" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="73" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="65" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="65" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" s="65" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2" s="65" t="s">
+        <v>152</v>
+      </c>
+      <c r="G2" s="65" t="s">
+        <v>58</v>
+      </c>
+      <c r="H2" s="66" t="s">
+        <v>141</v>
+      </c>
+      <c r="I2" s="67"/>
+      <c r="L2" s="64" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="I3" s="69"/>
+    </row>
+    <row r="4" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="70" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" s="68" t="s">
+        <v>186</v>
+      </c>
+      <c r="F4" s="70" t="s">
+        <v>138</v>
+      </c>
+      <c r="H4" s="70" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4" s="69"/>
+    </row>
+    <row r="5" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="71" t="s">
+        <v>156</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" s="66" t="s">
+        <v>71</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="I5" s="72"/>
+    </row>
+    <row r="6" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="66" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="G6" s="70" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="I6" s="72"/>
+    </row>
+    <row r="7" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="71" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="H7" s="70" t="s">
+        <v>146</v>
+      </c>
+      <c r="I7" s="69"/>
+    </row>
+    <row r="8" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="71" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="71" t="s">
+        <v>166</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="H8" s="70" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="76" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="71" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="75"/>
+      <c r="H9" s="76" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="76" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="76" t="s">
+        <v>171</v>
+      </c>
+      <c r="F10" s="77" t="s">
+        <v>157</v>
+      </c>
+      <c r="G10" s="66"/>
+    </row>
+    <row r="11" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C11" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="73" t="s">
+        <v>158</v>
+      </c>
+      <c r="E11" s="76" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="70" t="s">
+        <v>116</v>
+      </c>
+      <c r="H11" s="78"/>
+    </row>
+    <row r="12" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C12" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="68" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="78"/>
+      <c r="H12" s="70"/>
+    </row>
+    <row r="13" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="66" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="65" t="s">
+        <v>163</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="76" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="76" t="s">
+        <v>41</v>
+      </c>
+      <c r="H13" s="70"/>
+    </row>
+    <row r="14" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="D14" s="76" t="s">
+        <v>184</v>
+      </c>
+      <c r="E14" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="I14" s="80" t="s">
+        <v>161</v>
+      </c>
+      <c r="L14" s="61" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C15" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="76" t="s">
+        <v>164</v>
+      </c>
+      <c r="E15" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="81" t="s">
+        <v>127</v>
+      </c>
+      <c r="I15" s="82" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C16" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="66" t="s">
+        <v>165</v>
+      </c>
+      <c r="H16" s="81" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16" s="82" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C17" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="70" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" s="81" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" s="82" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H18" s="93" t="s">
+        <v>39</v>
+      </c>
+      <c r="I18" s="93"/>
+    </row>
+    <row r="19" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H19" s="81"/>
+    </row>
+    <row r="20" customFormat="false" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="83"/>
+      <c r="B20" s="83"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="83"/>
+      <c r="J20" s="84"/>
+      <c r="O20" s="83"/>
+      <c r="P20" s="83"/>
+      <c r="Q20" s="83"/>
+      <c r="R20" s="83"/>
+      <c r="S20" s="83"/>
+      <c r="T20" s="83"/>
+      <c r="U20" s="83"/>
+      <c r="V20" s="83"/>
+      <c r="W20" s="83"/>
+      <c r="X20" s="83"/>
+      <c r="Y20" s="83"/>
+      <c r="Z20" s="83"/>
+      <c r="AA20" s="83"/>
+      <c r="AB20" s="83"/>
+      <c r="AC20" s="83"/>
+      <c r="AD20" s="83"/>
+      <c r="AE20" s="83"/>
+      <c r="AF20" s="83"/>
+      <c r="AG20" s="83"/>
+      <c r="AH20" s="83"/>
+      <c r="AI20" s="83"/>
+      <c r="AJ20" s="83"/>
+      <c r="AK20" s="83"/>
+      <c r="AL20" s="83"/>
+      <c r="AM20" s="83"/>
+      <c r="AN20" s="83"/>
+      <c r="AO20" s="83"/>
+      <c r="AP20" s="83"/>
+      <c r="AQ20" s="83"/>
+      <c r="AR20" s="83"/>
+      <c r="AS20" s="83"/>
+      <c r="AT20" s="83"/>
+      <c r="AU20" s="83"/>
+      <c r="AV20" s="83"/>
+      <c r="AW20" s="83"/>
+      <c r="AX20" s="83"/>
+      <c r="AY20" s="83"/>
+      <c r="AZ20" s="83"/>
+      <c r="BA20" s="83"/>
+      <c r="BB20" s="83"/>
+      <c r="BC20" s="83"/>
+      <c r="BD20" s="83"/>
+      <c r="BE20" s="83"/>
+      <c r="BF20" s="83"/>
+      <c r="BG20" s="83"/>
+      <c r="BH20" s="83"/>
+      <c r="BI20" s="83"/>
+      <c r="BJ20" s="83"/>
+      <c r="BK20" s="83"/>
+      <c r="BL20" s="83"/>
+      <c r="BM20" s="83"/>
+      <c r="BN20" s="83"/>
+      <c r="BO20" s="83"/>
+      <c r="BP20" s="83"/>
+      <c r="BQ20" s="83"/>
+      <c r="BR20" s="83"/>
+      <c r="BS20" s="83"/>
+      <c r="BT20" s="83"/>
+      <c r="BU20" s="83"/>
+      <c r="BV20" s="83"/>
+      <c r="BW20" s="83"/>
+      <c r="BX20" s="83"/>
+      <c r="BY20" s="83"/>
+      <c r="BZ20" s="83"/>
+      <c r="CA20" s="83"/>
+      <c r="CB20" s="83"/>
+      <c r="CC20" s="83"/>
+      <c r="CD20" s="83"/>
+      <c r="CE20" s="83"/>
+      <c r="CF20" s="83"/>
+      <c r="CG20" s="83"/>
+      <c r="CH20" s="83"/>
+      <c r="CI20" s="83"/>
+      <c r="CJ20" s="83"/>
+      <c r="CK20" s="83"/>
+      <c r="CL20" s="83"/>
+      <c r="CM20" s="83"/>
+      <c r="CN20" s="83"/>
+      <c r="CO20" s="83"/>
+      <c r="CP20" s="83"/>
+      <c r="CQ20" s="83"/>
+      <c r="CR20" s="83"/>
+      <c r="CS20" s="83"/>
+      <c r="CT20" s="83"/>
+      <c r="CU20" s="83"/>
+      <c r="CV20" s="83"/>
+      <c r="CW20" s="83"/>
+      <c r="CX20" s="83"/>
+      <c r="CY20" s="83"/>
+      <c r="CZ20" s="83"/>
+      <c r="DA20" s="83"/>
+      <c r="DB20" s="83"/>
+      <c r="DC20" s="83"/>
+      <c r="DD20" s="83"/>
+      <c r="DE20" s="83"/>
+      <c r="DF20" s="83"/>
+      <c r="DG20" s="83"/>
+      <c r="DH20" s="83"/>
+      <c r="DI20" s="83"/>
+      <c r="DJ20" s="83"/>
+      <c r="DK20" s="83"/>
+      <c r="DL20" s="83"/>
+      <c r="DM20" s="83"/>
+      <c r="DN20" s="83"/>
+      <c r="DO20" s="83"/>
+      <c r="DP20" s="83"/>
+      <c r="DQ20" s="83"/>
+      <c r="DR20" s="83"/>
+      <c r="DS20" s="83"/>
+      <c r="DT20" s="83"/>
+      <c r="DU20" s="83"/>
+      <c r="DV20" s="83"/>
+      <c r="DW20" s="83"/>
+      <c r="DX20" s="83"/>
+      <c r="DY20" s="83"/>
+      <c r="DZ20" s="83"/>
+      <c r="EA20" s="83"/>
+      <c r="EB20" s="83"/>
+      <c r="EC20" s="83"/>
+      <c r="ED20" s="83"/>
+      <c r="EE20" s="83"/>
+      <c r="EF20" s="83"/>
+      <c r="EG20" s="83"/>
+      <c r="EH20" s="83"/>
+      <c r="EI20" s="83"/>
+      <c r="EJ20" s="83"/>
+      <c r="EK20" s="83"/>
+      <c r="EL20" s="83"/>
+      <c r="EM20" s="83"/>
+      <c r="EN20" s="83"/>
+      <c r="EO20" s="83"/>
+      <c r="EP20" s="83"/>
+      <c r="EQ20" s="83"/>
+      <c r="ER20" s="83"/>
+      <c r="ES20" s="83"/>
+      <c r="ET20" s="83"/>
+      <c r="EU20" s="83"/>
+      <c r="EV20" s="83"/>
+      <c r="EW20" s="83"/>
+      <c r="EX20" s="83"/>
+      <c r="EY20" s="83"/>
+      <c r="EZ20" s="83"/>
+      <c r="FA20" s="83"/>
+      <c r="FB20" s="83"/>
+      <c r="FC20" s="83"/>
+      <c r="FD20" s="83"/>
+      <c r="FE20" s="83"/>
+      <c r="FF20" s="83"/>
+      <c r="FG20" s="83"/>
+      <c r="FH20" s="83"/>
+      <c r="FI20" s="83"/>
+      <c r="FJ20" s="83"/>
+      <c r="FK20" s="83"/>
+      <c r="FL20" s="83"/>
+      <c r="FM20" s="83"/>
+      <c r="FN20" s="83"/>
+      <c r="FO20" s="83"/>
+      <c r="FP20" s="83"/>
+      <c r="FQ20" s="83"/>
+      <c r="FR20" s="83"/>
+      <c r="FS20" s="83"/>
+      <c r="FT20" s="83"/>
+      <c r="FU20" s="83"/>
+      <c r="FV20" s="83"/>
+      <c r="FW20" s="83"/>
+      <c r="FX20" s="83"/>
+      <c r="FY20" s="83"/>
+      <c r="FZ20" s="83"/>
+      <c r="GA20" s="83"/>
+      <c r="GB20" s="83"/>
+      <c r="GC20" s="83"/>
+      <c r="GD20" s="83"/>
+      <c r="GE20" s="83"/>
+      <c r="GF20" s="83"/>
+      <c r="GG20" s="83"/>
+      <c r="GH20" s="83"/>
+      <c r="GI20" s="83"/>
+      <c r="GJ20" s="83"/>
+      <c r="GK20" s="83"/>
+      <c r="GL20" s="83"/>
+      <c r="GM20" s="83"/>
+      <c r="GN20" s="83"/>
+      <c r="GO20" s="83"/>
+      <c r="GP20" s="83"/>
+      <c r="GQ20" s="83"/>
+      <c r="GR20" s="83"/>
+      <c r="GS20" s="83"/>
+      <c r="GT20" s="83"/>
+      <c r="GU20" s="83"/>
+      <c r="GV20" s="83"/>
+      <c r="GW20" s="83"/>
+      <c r="GX20" s="83"/>
+      <c r="GY20" s="83"/>
+      <c r="GZ20" s="83"/>
+      <c r="HA20" s="83"/>
+      <c r="HB20" s="83"/>
+      <c r="HC20" s="83"/>
+      <c r="HD20" s="83"/>
+      <c r="HE20" s="83"/>
+      <c r="HF20" s="83"/>
+      <c r="HG20" s="83"/>
+      <c r="HH20" s="83"/>
+      <c r="HI20" s="83"/>
+      <c r="HJ20" s="83"/>
+      <c r="HK20" s="83"/>
+      <c r="HL20" s="83"/>
+      <c r="HM20" s="83"/>
+      <c r="HN20" s="83"/>
+      <c r="HO20" s="83"/>
+      <c r="HP20" s="83"/>
+      <c r="HQ20" s="83"/>
+      <c r="HR20" s="83"/>
+      <c r="HS20" s="83"/>
+      <c r="HT20" s="83"/>
+      <c r="HU20" s="83"/>
+      <c r="HV20" s="83"/>
+      <c r="HW20" s="83"/>
+      <c r="HX20" s="83"/>
+      <c r="HY20" s="83"/>
+      <c r="HZ20" s="83"/>
+      <c r="IA20" s="83"/>
+      <c r="IB20" s="83"/>
+      <c r="IC20" s="83"/>
+      <c r="ID20" s="83"/>
+      <c r="IE20" s="83"/>
+      <c r="IF20" s="83"/>
+      <c r="IG20" s="83"/>
+      <c r="IH20" s="83"/>
+      <c r="II20" s="83"/>
+      <c r="IJ20" s="83"/>
+      <c r="IK20" s="83"/>
+      <c r="IL20" s="83"/>
+      <c r="IM20" s="83"/>
+      <c r="IN20" s="83"/>
+      <c r="IO20" s="83"/>
+      <c r="IP20" s="83"/>
+      <c r="IQ20" s="83"/>
+      <c r="IR20" s="83"/>
+      <c r="IS20" s="83"/>
+      <c r="IT20" s="83"/>
+      <c r="IU20" s="83"/>
+      <c r="IV20" s="83"/>
+      <c r="IW20" s="83"/>
+    </row>
+    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="83"/>
+      <c r="G21" s="85"/>
+      <c r="H21" s="81"/>
+      <c r="I21" s="82"/>
+      <c r="J21" s="86" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="87"/>
+      <c r="G22" s="87"/>
+      <c r="H22" s="81"/>
+      <c r="I22" s="82"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="82"/>
+      <c r="R23" s="88"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="82"/>
+      <c r="L24" s="61" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I25" s="82"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="3"/>
+      <c r="I26" s="82"/>
+    </row>
+    <row r="28" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D28" s="89"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="90" t="s">
+        <v>178</v>
+      </c>
+    </row>
     <row r="30" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="89" t="s">
-        <v>180</v>
+      <c r="A30" s="90" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="89" t="s">
+      <c r="A31" s="90" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="81" t="s">
         <v>175</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="80" t="s">
-        <v>176</v>
       </c>
     </row>
   </sheetData>

--- a/raw/BUS.xlsx
+++ b/raw/BUS.xlsx
@@ -1470,7 +1470,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="188">
   <si>
     <t xml:space="preserve">35.1-2673</t>
   </si>
@@ -12029,8 +12029,8 @@
       <c r="A2" s="65" t="s">
         <v>148</v>
       </c>
-      <c r="B2" s="73" t="s">
-        <v>63</v>
+      <c r="B2" s="65" t="s">
+        <v>149</v>
       </c>
       <c r="C2" s="65" t="s">
         <v>150</v>
@@ -12060,7 +12060,7 @@
         <v>91</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>14</v>
@@ -12086,9 +12086,6 @@
       <c r="A4" s="70" t="s">
         <v>101</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>34</v>
-      </c>
       <c r="C4" s="13" t="s">
         <v>10</v>
       </c>
@@ -12202,6 +12199,9 @@
       <c r="A9" s="76" t="s">
         <v>32</v>
       </c>
+      <c r="B9" s="73" t="s">
+        <v>63</v>
+      </c>
       <c r="C9" s="13" t="s">
         <v>25</v>
       </c>
@@ -12216,6 +12216,9 @@
     <row r="10" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="76" t="s">
         <v>30</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>80</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>29</v>

--- a/raw/BUS.xlsx
+++ b/raw/BUS.xlsx
@@ -16,6 +16,7 @@
     <sheet name="28" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="29" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="30" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="31" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -1469,8 +1470,204 @@
 </comments>
 </file>
 
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">20
+ kbm-13
+tms -  8
+dtt - 6/1</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>25</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>30</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A29" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">35--8/9</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>27</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>32</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A30" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">35-   15/6
+</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>28</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>33</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A31" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">35.1- 1/1
+</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>29</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>34</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A32" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve"> 35.2-  2/2
+</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>30</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>35</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="191">
   <si>
     <t xml:space="preserve">35.1-2673</t>
   </si>
@@ -2034,6 +2231,15 @@
   </si>
   <si>
     <t xml:space="preserve">35-2714 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> сводка выхода  31  октября 2026 года </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-228 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">kbm 18/6</t>
   </si>
 </sst>
 </file>
@@ -5695,6 +5901,51 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>23400</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>48240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>321840</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>31680</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="AutoShape 3" descr="C:\Users\A_Tumayeva\Desktop\9hq.webp"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="883800" y="5872320"/>
+          <a:ext cx="298440" cy="2254320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
   <a:themeElements>
@@ -12690,4 +12941,955 @@
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:IW32"/>
+  <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="12.55" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="61" width="12.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="61" width="12.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="61" width="14.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="61" width="12.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="61" width="17.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="61" width="15.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="61" width="13.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="61" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="61" width="14.55"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="10" min="10" style="61" width="9.1"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="11" style="61" width="9.1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="26.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="62" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="64" t="s">
+        <v>46</v>
+      </c>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="63"/>
+      <c r="T1" s="63"/>
+      <c r="U1" s="63"/>
+      <c r="V1" s="63"/>
+      <c r="W1" s="63"/>
+      <c r="X1" s="63"/>
+      <c r="Y1" s="63"/>
+      <c r="Z1" s="63"/>
+      <c r="AA1" s="63"/>
+      <c r="AB1" s="63"/>
+      <c r="AC1" s="63"/>
+      <c r="AD1" s="63"/>
+      <c r="AE1" s="63"/>
+      <c r="AF1" s="63"/>
+      <c r="AG1" s="63"/>
+      <c r="AH1" s="63"/>
+      <c r="AI1" s="63"/>
+      <c r="AJ1" s="63"/>
+      <c r="AK1" s="63"/>
+      <c r="AL1" s="63"/>
+      <c r="AM1" s="63"/>
+      <c r="AN1" s="63"/>
+      <c r="AO1" s="63"/>
+      <c r="AP1" s="63"/>
+      <c r="AQ1" s="63"/>
+      <c r="AR1" s="63"/>
+      <c r="AS1" s="63"/>
+      <c r="AT1" s="63"/>
+      <c r="AU1" s="63"/>
+      <c r="AV1" s="63"/>
+      <c r="AW1" s="63"/>
+      <c r="AX1" s="63"/>
+      <c r="AY1" s="63"/>
+      <c r="AZ1" s="63"/>
+      <c r="BA1" s="63"/>
+      <c r="BB1" s="63"/>
+      <c r="BC1" s="63"/>
+      <c r="BD1" s="63"/>
+      <c r="BE1" s="63"/>
+      <c r="BF1" s="63"/>
+      <c r="BG1" s="63"/>
+      <c r="BH1" s="63"/>
+      <c r="BI1" s="63"/>
+      <c r="BJ1" s="63"/>
+      <c r="BK1" s="63"/>
+      <c r="BL1" s="63"/>
+      <c r="BM1" s="63"/>
+      <c r="BN1" s="63"/>
+      <c r="BO1" s="63"/>
+      <c r="BP1" s="63"/>
+      <c r="BQ1" s="63"/>
+      <c r="BR1" s="63"/>
+      <c r="BS1" s="63"/>
+      <c r="BT1" s="63"/>
+      <c r="BU1" s="63"/>
+      <c r="BV1" s="63"/>
+      <c r="BW1" s="63"/>
+      <c r="BX1" s="63"/>
+      <c r="BY1" s="63"/>
+      <c r="BZ1" s="63"/>
+      <c r="CA1" s="63"/>
+      <c r="CB1" s="63"/>
+      <c r="CC1" s="63"/>
+      <c r="CD1" s="63"/>
+      <c r="CE1" s="63"/>
+      <c r="CF1" s="63"/>
+      <c r="CG1" s="63"/>
+      <c r="CH1" s="63"/>
+      <c r="CI1" s="63"/>
+      <c r="CJ1" s="63"/>
+      <c r="CK1" s="63"/>
+      <c r="CL1" s="63"/>
+      <c r="CM1" s="63"/>
+      <c r="CN1" s="63"/>
+      <c r="CO1" s="63"/>
+      <c r="CP1" s="63"/>
+      <c r="CQ1" s="63"/>
+      <c r="CR1" s="63"/>
+      <c r="CS1" s="63"/>
+      <c r="CT1" s="63"/>
+      <c r="CU1" s="63"/>
+      <c r="CV1" s="63"/>
+      <c r="CW1" s="63"/>
+      <c r="CX1" s="63"/>
+      <c r="CY1" s="63"/>
+      <c r="CZ1" s="63"/>
+      <c r="DA1" s="63"/>
+      <c r="DB1" s="63"/>
+      <c r="DC1" s="63"/>
+      <c r="DD1" s="63"/>
+      <c r="DE1" s="63"/>
+      <c r="DF1" s="63"/>
+      <c r="DG1" s="63"/>
+      <c r="DH1" s="63"/>
+      <c r="DI1" s="63"/>
+      <c r="DJ1" s="63"/>
+      <c r="DK1" s="63"/>
+      <c r="DL1" s="63"/>
+      <c r="DM1" s="63"/>
+      <c r="DN1" s="63"/>
+      <c r="DO1" s="63"/>
+      <c r="DP1" s="63"/>
+      <c r="DQ1" s="63"/>
+      <c r="DR1" s="63"/>
+      <c r="DS1" s="63"/>
+      <c r="DT1" s="63"/>
+      <c r="DU1" s="63"/>
+      <c r="DV1" s="63"/>
+      <c r="DW1" s="63"/>
+      <c r="DX1" s="63"/>
+      <c r="DY1" s="63"/>
+      <c r="DZ1" s="63"/>
+      <c r="EA1" s="63"/>
+      <c r="EB1" s="63"/>
+      <c r="EC1" s="63"/>
+      <c r="ED1" s="63"/>
+      <c r="EE1" s="63"/>
+      <c r="EF1" s="63"/>
+      <c r="EG1" s="63"/>
+      <c r="EH1" s="63"/>
+      <c r="EI1" s="63"/>
+      <c r="EJ1" s="63"/>
+      <c r="EK1" s="63"/>
+      <c r="EL1" s="63"/>
+      <c r="EM1" s="63"/>
+      <c r="EN1" s="63"/>
+      <c r="EO1" s="63"/>
+      <c r="EP1" s="63"/>
+      <c r="EQ1" s="63"/>
+      <c r="ER1" s="63"/>
+      <c r="ES1" s="63"/>
+      <c r="ET1" s="63"/>
+      <c r="EU1" s="63"/>
+      <c r="EV1" s="63"/>
+      <c r="EW1" s="63"/>
+      <c r="EX1" s="63"/>
+      <c r="EY1" s="63"/>
+      <c r="EZ1" s="63"/>
+      <c r="FA1" s="63"/>
+      <c r="FB1" s="63"/>
+      <c r="FC1" s="63"/>
+      <c r="FD1" s="63"/>
+      <c r="FE1" s="63"/>
+      <c r="FF1" s="63"/>
+      <c r="FG1" s="63"/>
+      <c r="FH1" s="63"/>
+      <c r="FI1" s="63"/>
+      <c r="FJ1" s="63"/>
+      <c r="FK1" s="63"/>
+      <c r="FL1" s="63"/>
+      <c r="FM1" s="63"/>
+      <c r="FN1" s="63"/>
+      <c r="FO1" s="63"/>
+      <c r="FP1" s="63"/>
+      <c r="FQ1" s="63"/>
+      <c r="FR1" s="63"/>
+      <c r="FS1" s="63"/>
+      <c r="FT1" s="63"/>
+      <c r="FU1" s="63"/>
+      <c r="FV1" s="63"/>
+      <c r="FW1" s="63"/>
+      <c r="FX1" s="63"/>
+      <c r="FY1" s="63"/>
+      <c r="FZ1" s="63"/>
+      <c r="GA1" s="63"/>
+      <c r="GB1" s="63"/>
+      <c r="GC1" s="63"/>
+      <c r="GD1" s="63"/>
+      <c r="GE1" s="63"/>
+      <c r="GF1" s="63"/>
+      <c r="GG1" s="63"/>
+      <c r="GH1" s="63"/>
+      <c r="GI1" s="63"/>
+      <c r="GJ1" s="63"/>
+      <c r="GK1" s="63"/>
+      <c r="GL1" s="63"/>
+      <c r="GM1" s="63"/>
+      <c r="GN1" s="63"/>
+      <c r="GO1" s="63"/>
+      <c r="GP1" s="63"/>
+      <c r="GQ1" s="63"/>
+      <c r="GR1" s="63"/>
+      <c r="GS1" s="63"/>
+      <c r="GT1" s="63"/>
+      <c r="GU1" s="63"/>
+      <c r="GV1" s="63"/>
+      <c r="GW1" s="63"/>
+      <c r="GX1" s="63"/>
+      <c r="GY1" s="63"/>
+      <c r="GZ1" s="63"/>
+      <c r="HA1" s="63"/>
+      <c r="HB1" s="63"/>
+      <c r="HC1" s="63"/>
+      <c r="HD1" s="63"/>
+      <c r="HE1" s="63"/>
+      <c r="HF1" s="63"/>
+      <c r="HG1" s="63"/>
+      <c r="HH1" s="63"/>
+      <c r="HI1" s="63"/>
+      <c r="HJ1" s="63"/>
+      <c r="HK1" s="63"/>
+      <c r="HL1" s="63"/>
+      <c r="HM1" s="63"/>
+      <c r="HN1" s="63"/>
+      <c r="HO1" s="63"/>
+      <c r="HP1" s="63"/>
+      <c r="HQ1" s="63"/>
+      <c r="HR1" s="63"/>
+      <c r="HS1" s="63"/>
+      <c r="HT1" s="63"/>
+      <c r="HU1" s="63"/>
+      <c r="HV1" s="63"/>
+      <c r="HW1" s="63"/>
+      <c r="HX1" s="63"/>
+      <c r="HY1" s="63"/>
+      <c r="HZ1" s="63"/>
+      <c r="IA1" s="63"/>
+      <c r="IB1" s="63"/>
+      <c r="IC1" s="63"/>
+      <c r="ID1" s="63"/>
+      <c r="IE1" s="63"/>
+      <c r="IF1" s="63"/>
+      <c r="IG1" s="63"/>
+      <c r="IH1" s="63"/>
+      <c r="II1" s="63"/>
+      <c r="IJ1" s="63"/>
+      <c r="IK1" s="63"/>
+      <c r="IL1" s="63"/>
+      <c r="IM1" s="63"/>
+      <c r="IN1" s="63"/>
+      <c r="IO1" s="63"/>
+      <c r="IP1" s="63"/>
+      <c r="IQ1" s="63"/>
+      <c r="IR1" s="63"/>
+      <c r="IS1" s="63"/>
+      <c r="IT1" s="63"/>
+      <c r="IU1" s="63"/>
+      <c r="IV1" s="63"/>
+      <c r="IW1" s="63"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="65" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="65" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="65" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="65" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" s="65" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2" s="65" t="s">
+        <v>152</v>
+      </c>
+      <c r="G2" s="65" t="s">
+        <v>58</v>
+      </c>
+      <c r="H2" s="66" t="s">
+        <v>141</v>
+      </c>
+      <c r="I2" s="67"/>
+      <c r="L2" s="64" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="I3" s="69"/>
+    </row>
+    <row r="4" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="70" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="F4" s="70" t="s">
+        <v>138</v>
+      </c>
+      <c r="H4" s="70" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4" s="69"/>
+    </row>
+    <row r="5" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="71" t="s">
+        <v>155</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" s="66" t="s">
+        <v>71</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="I5" s="72"/>
+    </row>
+    <row r="6" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="66" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="71" t="s">
+        <v>156</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="G6" s="70" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="I6" s="72"/>
+    </row>
+    <row r="7" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="71" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="H7" s="70" t="s">
+        <v>146</v>
+      </c>
+      <c r="I7" s="69"/>
+    </row>
+    <row r="8" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="71" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="H8" s="70" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="76" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="71" t="s">
+        <v>166</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="76" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="76" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="73" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="71" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="77" t="s">
+        <v>157</v>
+      </c>
+      <c r="G10" s="66"/>
+    </row>
+    <row r="11" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="D11" s="73" t="s">
+        <v>158</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="70" t="s">
+        <v>116</v>
+      </c>
+      <c r="H11" s="78"/>
+    </row>
+    <row r="12" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C12" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="76" t="s">
+        <v>171</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="78"/>
+      <c r="H12" s="70"/>
+    </row>
+    <row r="13" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="66" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="76" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="76" t="s">
+        <v>41</v>
+      </c>
+      <c r="H13" s="70"/>
+    </row>
+    <row r="14" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="65" t="s">
+        <v>163</v>
+      </c>
+      <c r="C14" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="71" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="68" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="I14" s="80" t="s">
+        <v>161</v>
+      </c>
+      <c r="L14" s="61" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="D15" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="E15" s="76" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="81" t="s">
+        <v>127</v>
+      </c>
+      <c r="I15" s="82" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D16" s="76" t="s">
+        <v>164</v>
+      </c>
+      <c r="E16" s="68" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="66" t="s">
+        <v>165</v>
+      </c>
+      <c r="H16" s="81" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16" s="82" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E17" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="70" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" s="93" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E18" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="H18" s="81"/>
+      <c r="I18" s="82"/>
+    </row>
+    <row r="19" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="H19" s="81"/>
+    </row>
+    <row r="20" customFormat="false" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="83"/>
+      <c r="B20" s="83"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="83"/>
+      <c r="J20" s="84"/>
+      <c r="O20" s="83"/>
+      <c r="P20" s="83"/>
+      <c r="Q20" s="83"/>
+      <c r="R20" s="83"/>
+      <c r="S20" s="83"/>
+      <c r="T20" s="83"/>
+      <c r="U20" s="83"/>
+      <c r="V20" s="83"/>
+      <c r="W20" s="83"/>
+      <c r="X20" s="83"/>
+      <c r="Y20" s="83"/>
+      <c r="Z20" s="83"/>
+      <c r="AA20" s="83"/>
+      <c r="AB20" s="83"/>
+      <c r="AC20" s="83"/>
+      <c r="AD20" s="83"/>
+      <c r="AE20" s="83"/>
+      <c r="AF20" s="83"/>
+      <c r="AG20" s="83"/>
+      <c r="AH20" s="83"/>
+      <c r="AI20" s="83"/>
+      <c r="AJ20" s="83"/>
+      <c r="AK20" s="83"/>
+      <c r="AL20" s="83"/>
+      <c r="AM20" s="83"/>
+      <c r="AN20" s="83"/>
+      <c r="AO20" s="83"/>
+      <c r="AP20" s="83"/>
+      <c r="AQ20" s="83"/>
+      <c r="AR20" s="83"/>
+      <c r="AS20" s="83"/>
+      <c r="AT20" s="83"/>
+      <c r="AU20" s="83"/>
+      <c r="AV20" s="83"/>
+      <c r="AW20" s="83"/>
+      <c r="AX20" s="83"/>
+      <c r="AY20" s="83"/>
+      <c r="AZ20" s="83"/>
+      <c r="BA20" s="83"/>
+      <c r="BB20" s="83"/>
+      <c r="BC20" s="83"/>
+      <c r="BD20" s="83"/>
+      <c r="BE20" s="83"/>
+      <c r="BF20" s="83"/>
+      <c r="BG20" s="83"/>
+      <c r="BH20" s="83"/>
+      <c r="BI20" s="83"/>
+      <c r="BJ20" s="83"/>
+      <c r="BK20" s="83"/>
+      <c r="BL20" s="83"/>
+      <c r="BM20" s="83"/>
+      <c r="BN20" s="83"/>
+      <c r="BO20" s="83"/>
+      <c r="BP20" s="83"/>
+      <c r="BQ20" s="83"/>
+      <c r="BR20" s="83"/>
+      <c r="BS20" s="83"/>
+      <c r="BT20" s="83"/>
+      <c r="BU20" s="83"/>
+      <c r="BV20" s="83"/>
+      <c r="BW20" s="83"/>
+      <c r="BX20" s="83"/>
+      <c r="BY20" s="83"/>
+      <c r="BZ20" s="83"/>
+      <c r="CA20" s="83"/>
+      <c r="CB20" s="83"/>
+      <c r="CC20" s="83"/>
+      <c r="CD20" s="83"/>
+      <c r="CE20" s="83"/>
+      <c r="CF20" s="83"/>
+      <c r="CG20" s="83"/>
+      <c r="CH20" s="83"/>
+      <c r="CI20" s="83"/>
+      <c r="CJ20" s="83"/>
+      <c r="CK20" s="83"/>
+      <c r="CL20" s="83"/>
+      <c r="CM20" s="83"/>
+      <c r="CN20" s="83"/>
+      <c r="CO20" s="83"/>
+      <c r="CP20" s="83"/>
+      <c r="CQ20" s="83"/>
+      <c r="CR20" s="83"/>
+      <c r="CS20" s="83"/>
+      <c r="CT20" s="83"/>
+      <c r="CU20" s="83"/>
+      <c r="CV20" s="83"/>
+      <c r="CW20" s="83"/>
+      <c r="CX20" s="83"/>
+      <c r="CY20" s="83"/>
+      <c r="CZ20" s="83"/>
+      <c r="DA20" s="83"/>
+      <c r="DB20" s="83"/>
+      <c r="DC20" s="83"/>
+      <c r="DD20" s="83"/>
+      <c r="DE20" s="83"/>
+      <c r="DF20" s="83"/>
+      <c r="DG20" s="83"/>
+      <c r="DH20" s="83"/>
+      <c r="DI20" s="83"/>
+      <c r="DJ20" s="83"/>
+      <c r="DK20" s="83"/>
+      <c r="DL20" s="83"/>
+      <c r="DM20" s="83"/>
+      <c r="DN20" s="83"/>
+      <c r="DO20" s="83"/>
+      <c r="DP20" s="83"/>
+      <c r="DQ20" s="83"/>
+      <c r="DR20" s="83"/>
+      <c r="DS20" s="83"/>
+      <c r="DT20" s="83"/>
+      <c r="DU20" s="83"/>
+      <c r="DV20" s="83"/>
+      <c r="DW20" s="83"/>
+      <c r="DX20" s="83"/>
+      <c r="DY20" s="83"/>
+      <c r="DZ20" s="83"/>
+      <c r="EA20" s="83"/>
+      <c r="EB20" s="83"/>
+      <c r="EC20" s="83"/>
+      <c r="ED20" s="83"/>
+      <c r="EE20" s="83"/>
+      <c r="EF20" s="83"/>
+      <c r="EG20" s="83"/>
+      <c r="EH20" s="83"/>
+      <c r="EI20" s="83"/>
+      <c r="EJ20" s="83"/>
+      <c r="EK20" s="83"/>
+      <c r="EL20" s="83"/>
+      <c r="EM20" s="83"/>
+      <c r="EN20" s="83"/>
+      <c r="EO20" s="83"/>
+      <c r="EP20" s="83"/>
+      <c r="EQ20" s="83"/>
+      <c r="ER20" s="83"/>
+      <c r="ES20" s="83"/>
+      <c r="ET20" s="83"/>
+      <c r="EU20" s="83"/>
+      <c r="EV20" s="83"/>
+      <c r="EW20" s="83"/>
+      <c r="EX20" s="83"/>
+      <c r="EY20" s="83"/>
+      <c r="EZ20" s="83"/>
+      <c r="FA20" s="83"/>
+      <c r="FB20" s="83"/>
+      <c r="FC20" s="83"/>
+      <c r="FD20" s="83"/>
+      <c r="FE20" s="83"/>
+      <c r="FF20" s="83"/>
+      <c r="FG20" s="83"/>
+      <c r="FH20" s="83"/>
+      <c r="FI20" s="83"/>
+      <c r="FJ20" s="83"/>
+      <c r="FK20" s="83"/>
+      <c r="FL20" s="83"/>
+      <c r="FM20" s="83"/>
+      <c r="FN20" s="83"/>
+      <c r="FO20" s="83"/>
+      <c r="FP20" s="83"/>
+      <c r="FQ20" s="83"/>
+      <c r="FR20" s="83"/>
+      <c r="FS20" s="83"/>
+      <c r="FT20" s="83"/>
+      <c r="FU20" s="83"/>
+      <c r="FV20" s="83"/>
+      <c r="FW20" s="83"/>
+      <c r="FX20" s="83"/>
+      <c r="FY20" s="83"/>
+      <c r="FZ20" s="83"/>
+      <c r="GA20" s="83"/>
+      <c r="GB20" s="83"/>
+      <c r="GC20" s="83"/>
+      <c r="GD20" s="83"/>
+      <c r="GE20" s="83"/>
+      <c r="GF20" s="83"/>
+      <c r="GG20" s="83"/>
+      <c r="GH20" s="83"/>
+      <c r="GI20" s="83"/>
+      <c r="GJ20" s="83"/>
+      <c r="GK20" s="83"/>
+      <c r="GL20" s="83"/>
+      <c r="GM20" s="83"/>
+      <c r="GN20" s="83"/>
+      <c r="GO20" s="83"/>
+      <c r="GP20" s="83"/>
+      <c r="GQ20" s="83"/>
+      <c r="GR20" s="83"/>
+      <c r="GS20" s="83"/>
+      <c r="GT20" s="83"/>
+      <c r="GU20" s="83"/>
+      <c r="GV20" s="83"/>
+      <c r="GW20" s="83"/>
+      <c r="GX20" s="83"/>
+      <c r="GY20" s="83"/>
+      <c r="GZ20" s="83"/>
+      <c r="HA20" s="83"/>
+      <c r="HB20" s="83"/>
+      <c r="HC20" s="83"/>
+      <c r="HD20" s="83"/>
+      <c r="HE20" s="83"/>
+      <c r="HF20" s="83"/>
+      <c r="HG20" s="83"/>
+      <c r="HH20" s="83"/>
+      <c r="HI20" s="83"/>
+      <c r="HJ20" s="83"/>
+      <c r="HK20" s="83"/>
+      <c r="HL20" s="83"/>
+      <c r="HM20" s="83"/>
+      <c r="HN20" s="83"/>
+      <c r="HO20" s="83"/>
+      <c r="HP20" s="83"/>
+      <c r="HQ20" s="83"/>
+      <c r="HR20" s="83"/>
+      <c r="HS20" s="83"/>
+      <c r="HT20" s="83"/>
+      <c r="HU20" s="83"/>
+      <c r="HV20" s="83"/>
+      <c r="HW20" s="83"/>
+      <c r="HX20" s="83"/>
+      <c r="HY20" s="83"/>
+      <c r="HZ20" s="83"/>
+      <c r="IA20" s="83"/>
+      <c r="IB20" s="83"/>
+      <c r="IC20" s="83"/>
+      <c r="ID20" s="83"/>
+      <c r="IE20" s="83"/>
+      <c r="IF20" s="83"/>
+      <c r="IG20" s="83"/>
+      <c r="IH20" s="83"/>
+      <c r="II20" s="83"/>
+      <c r="IJ20" s="83"/>
+      <c r="IK20" s="83"/>
+      <c r="IL20" s="83"/>
+      <c r="IM20" s="83"/>
+      <c r="IN20" s="83"/>
+      <c r="IO20" s="83"/>
+      <c r="IP20" s="83"/>
+      <c r="IQ20" s="83"/>
+      <c r="IR20" s="83"/>
+      <c r="IS20" s="83"/>
+      <c r="IT20" s="83"/>
+      <c r="IU20" s="83"/>
+      <c r="IV20" s="83"/>
+      <c r="IW20" s="83"/>
+    </row>
+    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="83"/>
+      <c r="G21" s="85"/>
+      <c r="H21" s="81"/>
+      <c r="I21" s="82"/>
+      <c r="J21" s="86" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="87"/>
+      <c r="G22" s="87"/>
+      <c r="H22" s="81"/>
+      <c r="I22" s="82"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="82"/>
+      <c r="R23" s="88"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="82"/>
+      <c r="L24" s="61" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I25" s="82"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="3"/>
+      <c r="I26" s="82"/>
+    </row>
+    <row r="28" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D28" s="89"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="90" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="90" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="90" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="81" t="s">
+        <v>175</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
 </file>
--- a/raw/BUS.xlsx
+++ b/raw/BUS.xlsx
@@ -17,6 +17,7 @@
     <sheet name="29" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="30" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="31" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="пересменка" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -113,8 +114,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">Тумаева Алуа Матаевна:
 </t>
@@ -135,6 +136,202 @@
                 <xdr:colOff>41</xdr:colOff>
                 <xdr:row>38</xdr:row>
                 <xdr:rowOff>17</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">20
+ kbm-13
+tms -  8
+dtt - 6/1</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>25</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>30</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A29" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">35--8/9</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>27</xdr:row>
+                <xdr:rowOff>13</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>32</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A30" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">35-   15/6
+</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>28</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>33</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A31" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">35.1- 1/1
+</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>29</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>34</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A32" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b val="true"/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve"> 35.2-  2/2
+</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>12</xdr:colOff>
+                <xdr:row>30</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>54</xdr:colOff>
+                <xdr:row>35</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1007,8 +1204,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">после обеда
 цдн-3
@@ -1241,8 +1438,8 @@
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
-            <family val="0"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">с вод
 </t>
@@ -1667,7 +1864,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="192">
   <si>
     <t xml:space="preserve">35.1-2673</t>
   </si>
@@ -2240,6 +2437,9 @@
   </si>
   <si>
     <t xml:space="preserve">kbm 18/6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-219 d/n</t>
   </si>
 </sst>
 </file>
@@ -2256,7 +2456,7 @@
     <numFmt numFmtId="170" formatCode="[$-409]m/d/yyyy"/>
     <numFmt numFmtId="171" formatCode="[$-409]d\-mmm"/>
   </numFmts>
-  <fonts count="55">
+  <fonts count="53">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2388,15 +2588,8 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2617,14 +2810,6 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b val="true"/>
       <sz val="11"/>
       <color rgb="FFFF00FF"/>
       <name val="Arial"/>
@@ -4108,27 +4293,27 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4136,63 +4321,63 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="27" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="29" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="3" borderId="1" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="3" borderId="1" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="31" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="30" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="4" borderId="1" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="4" borderId="1" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="29" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="28" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4204,23 +4389,23 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="32" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="31" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="33" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="32" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4228,7 +4413,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="3" borderId="3" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="3" borderId="3" xfId="25" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4240,11 +4425,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4252,15 +4441,11 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4268,27 +4453,27 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="0" borderId="1" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="1" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="1" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="1" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="1" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="1" xfId="26" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4296,7 +4481,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="43" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4308,11 +4493,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="43" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="42" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4320,7 +4505,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="44" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="43" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4328,7 +4513,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="1" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="1" xfId="28" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4336,47 +4537,31 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="47" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="46" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="46" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="47" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="46" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="47" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="46" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="49" fillId="0" borderId="1" xfId="1207" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="48" fillId="0" borderId="1" xfId="1207" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4384,31 +4569,31 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="49" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="49" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="50" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="51" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="51" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="51" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="52" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="52" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="53" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="53" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="54" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="54" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="52" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5946,6 +6131,51 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>23400</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>48240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>321840</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>71640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="AutoShape 3" descr="C:\Users\A_Tumayeva\Desktop\9hq.webp"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="883800" y="5872320"/>
+          <a:ext cx="298440" cy="2294280"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
   <a:themeElements>
@@ -6449,6 +6679,955 @@
     <oddFooter/>
   </headerFooter>
   <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:IW32"/>
+  <sheetFormatPr defaultColWidth="9.1015625" defaultRowHeight="12.55" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="61" width="12.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="61" width="12.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="61" width="14.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="61" width="12.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="61" width="17.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="61" width="15.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="61" width="13.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="61" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="61" width="14.55"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="10" min="10" style="61" width="9.1"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="257" min="11" style="61" width="9.1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="26.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="62" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="64" t="s">
+        <v>46</v>
+      </c>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="63"/>
+      <c r="T1" s="63"/>
+      <c r="U1" s="63"/>
+      <c r="V1" s="63"/>
+      <c r="W1" s="63"/>
+      <c r="X1" s="63"/>
+      <c r="Y1" s="63"/>
+      <c r="Z1" s="63"/>
+      <c r="AA1" s="63"/>
+      <c r="AB1" s="63"/>
+      <c r="AC1" s="63"/>
+      <c r="AD1" s="63"/>
+      <c r="AE1" s="63"/>
+      <c r="AF1" s="63"/>
+      <c r="AG1" s="63"/>
+      <c r="AH1" s="63"/>
+      <c r="AI1" s="63"/>
+      <c r="AJ1" s="63"/>
+      <c r="AK1" s="63"/>
+      <c r="AL1" s="63"/>
+      <c r="AM1" s="63"/>
+      <c r="AN1" s="63"/>
+      <c r="AO1" s="63"/>
+      <c r="AP1" s="63"/>
+      <c r="AQ1" s="63"/>
+      <c r="AR1" s="63"/>
+      <c r="AS1" s="63"/>
+      <c r="AT1" s="63"/>
+      <c r="AU1" s="63"/>
+      <c r="AV1" s="63"/>
+      <c r="AW1" s="63"/>
+      <c r="AX1" s="63"/>
+      <c r="AY1" s="63"/>
+      <c r="AZ1" s="63"/>
+      <c r="BA1" s="63"/>
+      <c r="BB1" s="63"/>
+      <c r="BC1" s="63"/>
+      <c r="BD1" s="63"/>
+      <c r="BE1" s="63"/>
+      <c r="BF1" s="63"/>
+      <c r="BG1" s="63"/>
+      <c r="BH1" s="63"/>
+      <c r="BI1" s="63"/>
+      <c r="BJ1" s="63"/>
+      <c r="BK1" s="63"/>
+      <c r="BL1" s="63"/>
+      <c r="BM1" s="63"/>
+      <c r="BN1" s="63"/>
+      <c r="BO1" s="63"/>
+      <c r="BP1" s="63"/>
+      <c r="BQ1" s="63"/>
+      <c r="BR1" s="63"/>
+      <c r="BS1" s="63"/>
+      <c r="BT1" s="63"/>
+      <c r="BU1" s="63"/>
+      <c r="BV1" s="63"/>
+      <c r="BW1" s="63"/>
+      <c r="BX1" s="63"/>
+      <c r="BY1" s="63"/>
+      <c r="BZ1" s="63"/>
+      <c r="CA1" s="63"/>
+      <c r="CB1" s="63"/>
+      <c r="CC1" s="63"/>
+      <c r="CD1" s="63"/>
+      <c r="CE1" s="63"/>
+      <c r="CF1" s="63"/>
+      <c r="CG1" s="63"/>
+      <c r="CH1" s="63"/>
+      <c r="CI1" s="63"/>
+      <c r="CJ1" s="63"/>
+      <c r="CK1" s="63"/>
+      <c r="CL1" s="63"/>
+      <c r="CM1" s="63"/>
+      <c r="CN1" s="63"/>
+      <c r="CO1" s="63"/>
+      <c r="CP1" s="63"/>
+      <c r="CQ1" s="63"/>
+      <c r="CR1" s="63"/>
+      <c r="CS1" s="63"/>
+      <c r="CT1" s="63"/>
+      <c r="CU1" s="63"/>
+      <c r="CV1" s="63"/>
+      <c r="CW1" s="63"/>
+      <c r="CX1" s="63"/>
+      <c r="CY1" s="63"/>
+      <c r="CZ1" s="63"/>
+      <c r="DA1" s="63"/>
+      <c r="DB1" s="63"/>
+      <c r="DC1" s="63"/>
+      <c r="DD1" s="63"/>
+      <c r="DE1" s="63"/>
+      <c r="DF1" s="63"/>
+      <c r="DG1" s="63"/>
+      <c r="DH1" s="63"/>
+      <c r="DI1" s="63"/>
+      <c r="DJ1" s="63"/>
+      <c r="DK1" s="63"/>
+      <c r="DL1" s="63"/>
+      <c r="DM1" s="63"/>
+      <c r="DN1" s="63"/>
+      <c r="DO1" s="63"/>
+      <c r="DP1" s="63"/>
+      <c r="DQ1" s="63"/>
+      <c r="DR1" s="63"/>
+      <c r="DS1" s="63"/>
+      <c r="DT1" s="63"/>
+      <c r="DU1" s="63"/>
+      <c r="DV1" s="63"/>
+      <c r="DW1" s="63"/>
+      <c r="DX1" s="63"/>
+      <c r="DY1" s="63"/>
+      <c r="DZ1" s="63"/>
+      <c r="EA1" s="63"/>
+      <c r="EB1" s="63"/>
+      <c r="EC1" s="63"/>
+      <c r="ED1" s="63"/>
+      <c r="EE1" s="63"/>
+      <c r="EF1" s="63"/>
+      <c r="EG1" s="63"/>
+      <c r="EH1" s="63"/>
+      <c r="EI1" s="63"/>
+      <c r="EJ1" s="63"/>
+      <c r="EK1" s="63"/>
+      <c r="EL1" s="63"/>
+      <c r="EM1" s="63"/>
+      <c r="EN1" s="63"/>
+      <c r="EO1" s="63"/>
+      <c r="EP1" s="63"/>
+      <c r="EQ1" s="63"/>
+      <c r="ER1" s="63"/>
+      <c r="ES1" s="63"/>
+      <c r="ET1" s="63"/>
+      <c r="EU1" s="63"/>
+      <c r="EV1" s="63"/>
+      <c r="EW1" s="63"/>
+      <c r="EX1" s="63"/>
+      <c r="EY1" s="63"/>
+      <c r="EZ1" s="63"/>
+      <c r="FA1" s="63"/>
+      <c r="FB1" s="63"/>
+      <c r="FC1" s="63"/>
+      <c r="FD1" s="63"/>
+      <c r="FE1" s="63"/>
+      <c r="FF1" s="63"/>
+      <c r="FG1" s="63"/>
+      <c r="FH1" s="63"/>
+      <c r="FI1" s="63"/>
+      <c r="FJ1" s="63"/>
+      <c r="FK1" s="63"/>
+      <c r="FL1" s="63"/>
+      <c r="FM1" s="63"/>
+      <c r="FN1" s="63"/>
+      <c r="FO1" s="63"/>
+      <c r="FP1" s="63"/>
+      <c r="FQ1" s="63"/>
+      <c r="FR1" s="63"/>
+      <c r="FS1" s="63"/>
+      <c r="FT1" s="63"/>
+      <c r="FU1" s="63"/>
+      <c r="FV1" s="63"/>
+      <c r="FW1" s="63"/>
+      <c r="FX1" s="63"/>
+      <c r="FY1" s="63"/>
+      <c r="FZ1" s="63"/>
+      <c r="GA1" s="63"/>
+      <c r="GB1" s="63"/>
+      <c r="GC1" s="63"/>
+      <c r="GD1" s="63"/>
+      <c r="GE1" s="63"/>
+      <c r="GF1" s="63"/>
+      <c r="GG1" s="63"/>
+      <c r="GH1" s="63"/>
+      <c r="GI1" s="63"/>
+      <c r="GJ1" s="63"/>
+      <c r="GK1" s="63"/>
+      <c r="GL1" s="63"/>
+      <c r="GM1" s="63"/>
+      <c r="GN1" s="63"/>
+      <c r="GO1" s="63"/>
+      <c r="GP1" s="63"/>
+      <c r="GQ1" s="63"/>
+      <c r="GR1" s="63"/>
+      <c r="GS1" s="63"/>
+      <c r="GT1" s="63"/>
+      <c r="GU1" s="63"/>
+      <c r="GV1" s="63"/>
+      <c r="GW1" s="63"/>
+      <c r="GX1" s="63"/>
+      <c r="GY1" s="63"/>
+      <c r="GZ1" s="63"/>
+      <c r="HA1" s="63"/>
+      <c r="HB1" s="63"/>
+      <c r="HC1" s="63"/>
+      <c r="HD1" s="63"/>
+      <c r="HE1" s="63"/>
+      <c r="HF1" s="63"/>
+      <c r="HG1" s="63"/>
+      <c r="HH1" s="63"/>
+      <c r="HI1" s="63"/>
+      <c r="HJ1" s="63"/>
+      <c r="HK1" s="63"/>
+      <c r="HL1" s="63"/>
+      <c r="HM1" s="63"/>
+      <c r="HN1" s="63"/>
+      <c r="HO1" s="63"/>
+      <c r="HP1" s="63"/>
+      <c r="HQ1" s="63"/>
+      <c r="HR1" s="63"/>
+      <c r="HS1" s="63"/>
+      <c r="HT1" s="63"/>
+      <c r="HU1" s="63"/>
+      <c r="HV1" s="63"/>
+      <c r="HW1" s="63"/>
+      <c r="HX1" s="63"/>
+      <c r="HY1" s="63"/>
+      <c r="HZ1" s="63"/>
+      <c r="IA1" s="63"/>
+      <c r="IB1" s="63"/>
+      <c r="IC1" s="63"/>
+      <c r="ID1" s="63"/>
+      <c r="IE1" s="63"/>
+      <c r="IF1" s="63"/>
+      <c r="IG1" s="63"/>
+      <c r="IH1" s="63"/>
+      <c r="II1" s="63"/>
+      <c r="IJ1" s="63"/>
+      <c r="IK1" s="63"/>
+      <c r="IL1" s="63"/>
+      <c r="IM1" s="63"/>
+      <c r="IN1" s="63"/>
+      <c r="IO1" s="63"/>
+      <c r="IP1" s="63"/>
+      <c r="IQ1" s="63"/>
+      <c r="IR1" s="63"/>
+      <c r="IS1" s="63"/>
+      <c r="IT1" s="63"/>
+      <c r="IU1" s="63"/>
+      <c r="IV1" s="63"/>
+      <c r="IW1" s="63"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="65" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="65" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="65" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="65" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" s="65" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2" s="65" t="s">
+        <v>152</v>
+      </c>
+      <c r="G2" s="65" t="s">
+        <v>58</v>
+      </c>
+      <c r="H2" s="66" t="s">
+        <v>141</v>
+      </c>
+      <c r="I2" s="67"/>
+      <c r="L2" s="64" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" s="71" t="s">
+        <v>154</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="I3" s="69"/>
+    </row>
+    <row r="4" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="70" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" s="71" t="s">
+        <v>153</v>
+      </c>
+      <c r="F4" s="70" t="s">
+        <v>138</v>
+      </c>
+      <c r="H4" s="70" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4" s="69"/>
+    </row>
+    <row r="5" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="71" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="68" t="s">
+        <v>155</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" s="66" t="s">
+        <v>71</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="I5" s="72"/>
+    </row>
+    <row r="6" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="66" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="71" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="68" t="s">
+        <v>156</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="G6" s="70" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="I6" s="72"/>
+    </row>
+    <row r="7" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="71" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="H7" s="70" t="s">
+        <v>146</v>
+      </c>
+      <c r="I7" s="69"/>
+    </row>
+    <row r="8" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="H8" s="70" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="71" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="76" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="76" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="73" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="71" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="77" t="s">
+        <v>157</v>
+      </c>
+      <c r="G10" s="66"/>
+    </row>
+    <row r="11" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="73" t="s">
+        <v>158</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="F11" s="70" t="s">
+        <v>116</v>
+      </c>
+      <c r="H11" s="78"/>
+    </row>
+    <row r="12" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C12" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="78"/>
+      <c r="H12" s="70"/>
+    </row>
+    <row r="13" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="66" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="68" t="s">
+        <v>191</v>
+      </c>
+      <c r="D13" s="71" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="76" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13" s="70"/>
+    </row>
+    <row r="14" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="65" t="s">
+        <v>163</v>
+      </c>
+      <c r="C14" s="68" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="71" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="76" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="I14" s="80" t="s">
+        <v>161</v>
+      </c>
+      <c r="L14" s="61" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="76" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="68" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="81" t="s">
+        <v>127</v>
+      </c>
+      <c r="I15" s="82" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D16" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="E16" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="66" t="s">
+        <v>165</v>
+      </c>
+      <c r="H16" s="81" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E17" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="70" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" s="81" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E18" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" s="81" t="s">
+        <v>140</v>
+      </c>
+      <c r="I18" s="82"/>
+    </row>
+    <row r="19" customFormat="false" ht="18.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E19" s="68" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" s="81"/>
+    </row>
+    <row r="20" customFormat="false" ht="16.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="83"/>
+      <c r="B20" s="83"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="83"/>
+      <c r="J20" s="84"/>
+      <c r="T20" s="83"/>
+      <c r="U20" s="83"/>
+      <c r="V20" s="83"/>
+      <c r="W20" s="83"/>
+      <c r="X20" s="83"/>
+      <c r="Y20" s="83"/>
+      <c r="Z20" s="83"/>
+      <c r="AA20" s="83"/>
+      <c r="AB20" s="83"/>
+      <c r="AC20" s="83"/>
+      <c r="AD20" s="83"/>
+      <c r="AE20" s="83"/>
+      <c r="AF20" s="83"/>
+      <c r="AG20" s="83"/>
+      <c r="AH20" s="83"/>
+      <c r="AI20" s="83"/>
+      <c r="AJ20" s="83"/>
+      <c r="AK20" s="83"/>
+      <c r="AL20" s="83"/>
+      <c r="AM20" s="83"/>
+      <c r="AN20" s="83"/>
+      <c r="AO20" s="83"/>
+      <c r="AP20" s="83"/>
+      <c r="AQ20" s="83"/>
+      <c r="AR20" s="83"/>
+      <c r="AS20" s="83"/>
+      <c r="AT20" s="83"/>
+      <c r="AU20" s="83"/>
+      <c r="AV20" s="83"/>
+      <c r="AW20" s="83"/>
+      <c r="AX20" s="83"/>
+      <c r="AY20" s="83"/>
+      <c r="AZ20" s="83"/>
+      <c r="BA20" s="83"/>
+      <c r="BB20" s="83"/>
+      <c r="BC20" s="83"/>
+      <c r="BD20" s="83"/>
+      <c r="BE20" s="83"/>
+      <c r="BF20" s="83"/>
+      <c r="BG20" s="83"/>
+      <c r="BH20" s="83"/>
+      <c r="BI20" s="83"/>
+      <c r="BJ20" s="83"/>
+      <c r="BK20" s="83"/>
+      <c r="BL20" s="83"/>
+      <c r="BM20" s="83"/>
+      <c r="BN20" s="83"/>
+      <c r="BO20" s="83"/>
+      <c r="BP20" s="83"/>
+      <c r="BQ20" s="83"/>
+      <c r="BR20" s="83"/>
+      <c r="BS20" s="83"/>
+      <c r="BT20" s="83"/>
+      <c r="BU20" s="83"/>
+      <c r="BV20" s="83"/>
+      <c r="BW20" s="83"/>
+      <c r="BX20" s="83"/>
+      <c r="BY20" s="83"/>
+      <c r="BZ20" s="83"/>
+      <c r="CA20" s="83"/>
+      <c r="CB20" s="83"/>
+      <c r="CC20" s="83"/>
+      <c r="CD20" s="83"/>
+      <c r="CE20" s="83"/>
+      <c r="CF20" s="83"/>
+      <c r="CG20" s="83"/>
+      <c r="CH20" s="83"/>
+      <c r="CI20" s="83"/>
+      <c r="CJ20" s="83"/>
+      <c r="CK20" s="83"/>
+      <c r="CL20" s="83"/>
+      <c r="CM20" s="83"/>
+      <c r="CN20" s="83"/>
+      <c r="CO20" s="83"/>
+      <c r="CP20" s="83"/>
+      <c r="CQ20" s="83"/>
+      <c r="CR20" s="83"/>
+      <c r="CS20" s="83"/>
+      <c r="CT20" s="83"/>
+      <c r="CU20" s="83"/>
+      <c r="CV20" s="83"/>
+      <c r="CW20" s="83"/>
+      <c r="CX20" s="83"/>
+      <c r="CY20" s="83"/>
+      <c r="CZ20" s="83"/>
+      <c r="DA20" s="83"/>
+      <c r="DB20" s="83"/>
+      <c r="DC20" s="83"/>
+      <c r="DD20" s="83"/>
+      <c r="DE20" s="83"/>
+      <c r="DF20" s="83"/>
+      <c r="DG20" s="83"/>
+      <c r="DH20" s="83"/>
+      <c r="DI20" s="83"/>
+      <c r="DJ20" s="83"/>
+      <c r="DK20" s="83"/>
+      <c r="DL20" s="83"/>
+      <c r="DM20" s="83"/>
+      <c r="DN20" s="83"/>
+      <c r="DO20" s="83"/>
+      <c r="DP20" s="83"/>
+      <c r="DQ20" s="83"/>
+      <c r="DR20" s="83"/>
+      <c r="DS20" s="83"/>
+      <c r="DT20" s="83"/>
+      <c r="DU20" s="83"/>
+      <c r="DV20" s="83"/>
+      <c r="DW20" s="83"/>
+      <c r="DX20" s="83"/>
+      <c r="DY20" s="83"/>
+      <c r="DZ20" s="83"/>
+      <c r="EA20" s="83"/>
+      <c r="EB20" s="83"/>
+      <c r="EC20" s="83"/>
+      <c r="ED20" s="83"/>
+      <c r="EE20" s="83"/>
+      <c r="EF20" s="83"/>
+      <c r="EG20" s="83"/>
+      <c r="EH20" s="83"/>
+      <c r="EI20" s="83"/>
+      <c r="EJ20" s="83"/>
+      <c r="EK20" s="83"/>
+      <c r="EL20" s="83"/>
+      <c r="EM20" s="83"/>
+      <c r="EN20" s="83"/>
+      <c r="EO20" s="83"/>
+      <c r="EP20" s="83"/>
+      <c r="EQ20" s="83"/>
+      <c r="ER20" s="83"/>
+      <c r="ES20" s="83"/>
+      <c r="ET20" s="83"/>
+      <c r="EU20" s="83"/>
+      <c r="EV20" s="83"/>
+      <c r="EW20" s="83"/>
+      <c r="EX20" s="83"/>
+      <c r="EY20" s="83"/>
+      <c r="EZ20" s="83"/>
+      <c r="FA20" s="83"/>
+      <c r="FB20" s="83"/>
+      <c r="FC20" s="83"/>
+      <c r="FD20" s="83"/>
+      <c r="FE20" s="83"/>
+      <c r="FF20" s="83"/>
+      <c r="FG20" s="83"/>
+      <c r="FH20" s="83"/>
+      <c r="FI20" s="83"/>
+      <c r="FJ20" s="83"/>
+      <c r="FK20" s="83"/>
+      <c r="FL20" s="83"/>
+      <c r="FM20" s="83"/>
+      <c r="FN20" s="83"/>
+      <c r="FO20" s="83"/>
+      <c r="FP20" s="83"/>
+      <c r="FQ20" s="83"/>
+      <c r="FR20" s="83"/>
+      <c r="FS20" s="83"/>
+      <c r="FT20" s="83"/>
+      <c r="FU20" s="83"/>
+      <c r="FV20" s="83"/>
+      <c r="FW20" s="83"/>
+      <c r="FX20" s="83"/>
+      <c r="FY20" s="83"/>
+      <c r="FZ20" s="83"/>
+      <c r="GA20" s="83"/>
+      <c r="GB20" s="83"/>
+      <c r="GC20" s="83"/>
+      <c r="GD20" s="83"/>
+      <c r="GE20" s="83"/>
+      <c r="GF20" s="83"/>
+      <c r="GG20" s="83"/>
+      <c r="GH20" s="83"/>
+      <c r="GI20" s="83"/>
+      <c r="GJ20" s="83"/>
+      <c r="GK20" s="83"/>
+      <c r="GL20" s="83"/>
+      <c r="GM20" s="83"/>
+      <c r="GN20" s="83"/>
+      <c r="GO20" s="83"/>
+      <c r="GP20" s="83"/>
+      <c r="GQ20" s="83"/>
+      <c r="GR20" s="83"/>
+      <c r="GS20" s="83"/>
+      <c r="GT20" s="83"/>
+      <c r="GU20" s="83"/>
+      <c r="GV20" s="83"/>
+      <c r="GW20" s="83"/>
+      <c r="GX20" s="83"/>
+      <c r="GY20" s="83"/>
+      <c r="GZ20" s="83"/>
+      <c r="HA20" s="83"/>
+      <c r="HB20" s="83"/>
+      <c r="HC20" s="83"/>
+      <c r="HD20" s="83"/>
+      <c r="HE20" s="83"/>
+      <c r="HF20" s="83"/>
+      <c r="HG20" s="83"/>
+      <c r="HH20" s="83"/>
+      <c r="HI20" s="83"/>
+      <c r="HJ20" s="83"/>
+      <c r="HK20" s="83"/>
+      <c r="HL20" s="83"/>
+      <c r="HM20" s="83"/>
+      <c r="HN20" s="83"/>
+      <c r="HO20" s="83"/>
+      <c r="HP20" s="83"/>
+      <c r="HQ20" s="83"/>
+      <c r="HR20" s="83"/>
+      <c r="HS20" s="83"/>
+      <c r="HT20" s="83"/>
+      <c r="HU20" s="83"/>
+      <c r="HV20" s="83"/>
+      <c r="HW20" s="83"/>
+      <c r="HX20" s="83"/>
+      <c r="HY20" s="83"/>
+      <c r="HZ20" s="83"/>
+      <c r="IA20" s="83"/>
+      <c r="IB20" s="83"/>
+      <c r="IC20" s="83"/>
+      <c r="ID20" s="83"/>
+      <c r="IE20" s="83"/>
+      <c r="IF20" s="83"/>
+      <c r="IG20" s="83"/>
+      <c r="IH20" s="83"/>
+      <c r="II20" s="83"/>
+      <c r="IJ20" s="83"/>
+      <c r="IK20" s="83"/>
+      <c r="IL20" s="83"/>
+      <c r="IM20" s="83"/>
+      <c r="IN20" s="83"/>
+      <c r="IO20" s="83"/>
+      <c r="IP20" s="83"/>
+      <c r="IQ20" s="83"/>
+      <c r="IR20" s="83"/>
+      <c r="IS20" s="83"/>
+      <c r="IT20" s="83"/>
+      <c r="IU20" s="83"/>
+      <c r="IV20" s="83"/>
+      <c r="IW20" s="83"/>
+    </row>
+    <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="83"/>
+      <c r="G21" s="85"/>
+      <c r="H21" s="81"/>
+      <c r="I21" s="82"/>
+      <c r="J21" s="86" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="87"/>
+      <c r="G22" s="87"/>
+      <c r="H22" s="81"/>
+      <c r="I22" s="82"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="82"/>
+      <c r="R23" s="88"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="82"/>
+      <c r="L24" s="61" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I25" s="82"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="3"/>
+      <c r="I26" s="82"/>
+    </row>
+    <row r="28" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D28" s="89"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="90" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="90" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="90" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="81" t="s">
+        <v>175</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
